--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070"/>
+    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="States" sheetId="1" r:id="rId1"/>
@@ -662,10 +662,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -676,11 +676,108 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -689,6 +786,21 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -702,119 +814,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -829,7 +829,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -841,7 +925,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -853,19 +955,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -877,133 +997,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1020,6 +1020,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1041,19 +1056,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1088,26 +1092,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1116,7 +1105,18 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1128,145 +1128,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="8270"/>
   </bookViews>
   <sheets>
     <sheet name="States" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="215">
   <si>
     <t>Id</t>
   </si>
@@ -27,7 +27,13 @@
     <t>_</t>
   </si>
   <si>
+    <t>IconBack</t>
+  </si>
+  <si>
     <t>IconIndex</t>
+  </si>
+  <si>
+    <t>IconPath</t>
   </si>
   <si>
     <t>RemovalTiming</t>
@@ -662,10 +668,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -685,16 +691,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -706,22 +713,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -735,25 +727,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -773,11 +749,41 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -797,8 +803,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -812,9 +819,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -835,13 +841,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -853,73 +895,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -937,7 +913,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -949,31 +997,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -985,31 +1015,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1023,16 +1029,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -1049,30 +1055,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1095,8 +1077,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1106,6 +1103,15 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1128,145 +1134,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1593,25 +1599,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S76"/>
+  <dimension ref="A1:U76"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="21.8181818181818" customWidth="1"/>
-    <col min="4" max="4" width="15.5454545454545" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="5.54545454545455" customWidth="1"/>
-    <col min="8" max="8" width="12.8181818181818" customWidth="1"/>
-    <col min="9" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="10" customWidth="1"/>
-    <col min="11" max="11" width="8.63636363636364" customWidth="1"/>
-    <col min="12" max="12" width="8.54545454545454" customWidth="1"/>
-    <col min="13" max="16" width="11.2727272727273" customWidth="1"/>
-    <col min="17" max="17" width="16.7272727272727" customWidth="1"/>
-    <col min="18" max="18" width="5.72727272727273" customWidth="1"/>
+    <col min="4" max="4" width="9.09090909090909" customWidth="1"/>
+    <col min="5" max="5" width="13.7272727272727" customWidth="1"/>
+    <col min="6" max="6" width="15.5454545454545" customWidth="1"/>
+    <col min="7" max="7" width="7" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="5.54545454545455" customWidth="1"/>
+    <col min="10" max="10" width="12.8181818181818" customWidth="1"/>
+    <col min="11" max="11" width="8" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="13" width="8.63636363636364" customWidth="1"/>
+    <col min="14" max="14" width="8.54545454545454" customWidth="1"/>
+    <col min="15" max="18" width="11.2727272727273" customWidth="1"/>
+    <col min="19" max="19" width="16.7272727272727" customWidth="1"/>
+    <col min="20" max="20" width="5.72727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:20">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1628,13 +1636,13 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
         <v>2</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" t="s">
-        <v>6</v>
       </c>
       <c r="I1" t="s">
         <v>7</v>
@@ -1666,8 +1674,14 @@
       <c r="R1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:19">
+      <c r="S1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1678,33 +1692,33 @@
         <f>INDEX(TextData!B:B,MATCH(B2,TextData!A:A))</f>
         <v>戦闘不能</v>
       </c>
-      <c r="D2" t="s">
-        <v>17</v>
+      <c r="D2">
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" t="str">
-        <f>INDEX(Define!B:B,MATCH(E2,Define!A:A))</f>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="str">
+        <f>INDEX(Define!B:B,MATCH(G2,Define!A:A))</f>
         <v>なし</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
-        <v>1</v>
+      <c r="J2" t="s">
+        <v>20</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -1724,12 +1738,18 @@
       <c r="R2">
         <v>0</v>
       </c>
-      <c r="S2" t="str">
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2" t="str">
         <f>TextData!C2</f>
         <v>""</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:21">
       <c r="A3">
         <v>10</v>
       </c>
@@ -1740,33 +1760,33 @@
         <f>INDEX(TextData!B:B,MATCH(B3,TextData!A:A))</f>
         <v>待機</v>
       </c>
-      <c r="D3" t="s">
-        <v>19</v>
+      <c r="D3">
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" t="str">
-        <f>INDEX(Define!B:B,MATCH(E3,Define!A:A))</f>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3" t="str">
+        <f>INDEX(Define!B:B,MATCH(G3,Define!A:A))</f>
         <v>なし</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3" t="s">
-        <v>18</v>
-      </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
-        <v>1</v>
+      <c r="J3" t="s">
+        <v>20</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -1784,14 +1804,20 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="S3" t="str">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
+      </c>
+      <c r="U3" t="str">
         <f>TextData!B3</f>
         <v>待機</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:21">
       <c r="A4">
         <v>201</v>
       </c>
@@ -1803,32 +1829,32 @@
         <v>炎適正</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" t="str">
-        <f>INDEX(Define!B:B,MATCH(E4,Define!A:A))</f>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="str">
+        <f>INDEX(Define!B:B,MATCH(G4,Define!A:A))</f>
         <v>なし</v>
       </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
       <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -1848,12 +1874,18 @@
       <c r="R4">
         <v>0</v>
       </c>
-      <c r="S4" t="str">
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4" t="str">
         <f>TextData!B4</f>
         <v>炎適正</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:21">
       <c r="A5">
         <v>202</v>
       </c>
@@ -1865,32 +1897,32 @@
         <v>雷適性</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" t="str">
-        <f>INDEX(Define!B:B,MATCH(E5,Define!A:A))</f>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="str">
+        <f>INDEX(Define!B:B,MATCH(G5,Define!A:A))</f>
         <v>なし</v>
       </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
       <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>20</v>
       </c>
       <c r="K5">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -1910,12 +1942,18 @@
       <c r="R5">
         <v>0</v>
       </c>
-      <c r="S5" t="str">
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5" t="str">
         <f>TextData!B5</f>
         <v>雷適性</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:21">
       <c r="A6">
         <v>203</v>
       </c>
@@ -1927,32 +1965,32 @@
         <v>氷適性</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" t="str">
-        <f>INDEX(Define!B:B,MATCH(E6,Define!A:A))</f>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6" t="str">
+        <f>INDEX(Define!B:B,MATCH(G6,Define!A:A))</f>
         <v>なし</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6" t="s">
-        <v>18</v>
-      </c>
       <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>20</v>
       </c>
       <c r="K6">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -1972,12 +2010,18 @@
       <c r="R6">
         <v>0</v>
       </c>
-      <c r="S6" t="str">
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6" t="str">
         <f>TextData!B6</f>
         <v>氷適性</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:21">
       <c r="A7">
         <v>204</v>
       </c>
@@ -1989,32 +2033,32 @@
         <v>光適性</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" t="str">
-        <f>INDEX(Define!B:B,MATCH(E7,Define!A:A))</f>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="str">
+        <f>INDEX(Define!B:B,MATCH(G7,Define!A:A))</f>
         <v>なし</v>
       </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7" t="s">
-        <v>18</v>
-      </c>
       <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>20</v>
       </c>
       <c r="K7">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -2034,12 +2078,18 @@
       <c r="R7">
         <v>0</v>
       </c>
-      <c r="S7" t="str">
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7" t="str">
         <f>TextData!B7</f>
         <v>光適性</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:21">
       <c r="A8">
         <v>205</v>
       </c>
@@ -2051,32 +2101,32 @@
         <v>闇適性</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" t="str">
-        <f>INDEX(Define!B:B,MATCH(E8,Define!A:A))</f>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8" t="str">
+        <f>INDEX(Define!B:B,MATCH(G8,Define!A:A))</f>
         <v>なし</v>
       </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>18</v>
-      </c>
       <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>20</v>
       </c>
       <c r="K8">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -2096,12 +2146,18 @@
       <c r="R8">
         <v>0</v>
       </c>
-      <c r="S8" t="str">
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8" t="str">
         <f>TextData!B8</f>
         <v>闇適性</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:21">
       <c r="A9">
         <v>1010</v>
       </c>
@@ -2112,33 +2168,33 @@
         <f>INDEX(TextData!B:B,MATCH(B9,TextData!A:A))</f>
         <v>覚醒</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="str">
+        <f>INDEX(Define!B:B,MATCH(G9,Define!A:A))</f>
+        <v>なし</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
         <v>20</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" t="str">
-        <f>INDEX(Define!B:B,MATCH(E9,Define!A:A))</f>
-        <v>なし</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
       <c r="K9">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -2156,14 +2212,20 @@
         <v>0</v>
       </c>
       <c r="R9">
-        <v>1</v>
-      </c>
-      <c r="S9" t="str">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9" t="str">
         <f>TextData!B9</f>
         <v>覚醒</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:21">
       <c r="A10">
         <v>1011</v>
       </c>
@@ -2174,58 +2236,64 @@
         <f>INDEX(TextData!B:B,MATCH(B10,TextData!A:A))</f>
         <v>全ステータスアップ</v>
       </c>
-      <c r="D10" t="s">
-        <v>21</v>
+      <c r="D10">
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
-      <c r="F10" t="str">
-        <f>INDEX(Define!B:B,MATCH(E10,Define!A:A))</f>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10" t="str">
+        <f>INDEX(Define!B:B,MATCH(G10,Define!A:A))</f>
         <v>なし</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>18</v>
-      </c>
       <c r="I10">
         <v>0</v>
       </c>
-      <c r="J10">
-        <v>1</v>
+      <c r="J10" t="s">
+        <v>20</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10">
         <v>0</v>
       </c>
       <c r="N10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10">
         <v>0</v>
       </c>
       <c r="R10">
-        <v>1</v>
-      </c>
-      <c r="S10" t="str">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>1</v>
+      </c>
+      <c r="U10" t="str">
         <f>TextData!B10</f>
         <v>全ステータスアップ</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:21">
       <c r="A11">
         <v>1020</v>
       </c>
@@ -2236,27 +2304,27 @@
         <f>INDEX(TextData!B:B,MATCH(B11,TextData!A:A))</f>
         <v>最大Hpアップ</v>
       </c>
-      <c r="D11" t="s">
-        <v>22</v>
+      <c r="D11">
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11" t="str">
-        <f>INDEX(Define!B:B,MATCH(E11,Define!A:A))</f>
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="str">
+        <f>INDEX(Define!B:B,MATCH(G11,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11" t="s">
-        <v>18</v>
-      </c>
       <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J11" t="s">
+        <v>20</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -2274,20 +2342,26 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11">
         <v>0</v>
       </c>
       <c r="R11">
-        <v>1</v>
-      </c>
-      <c r="S11" t="str">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
+      </c>
+      <c r="U11" t="str">
         <f>TextData!B11</f>
         <v>最大Hpアップ</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:21">
       <c r="A12">
         <v>1030</v>
       </c>
@@ -2298,27 +2372,27 @@
         <f>INDEX(TextData!B:B,MATCH(B12,TextData!A:A))</f>
         <v>最大Mpアップ</v>
       </c>
-      <c r="D12" t="s">
-        <v>23</v>
+      <c r="D12">
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12" t="str">
-        <f>INDEX(Define!B:B,MATCH(E12,Define!A:A))</f>
+        <v>12</v>
+      </c>
+      <c r="F12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="str">
+        <f>INDEX(Define!B:B,MATCH(G12,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12" t="s">
-        <v>18</v>
-      </c>
       <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
+        <v>20</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -2336,20 +2410,26 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12">
         <v>0</v>
       </c>
       <c r="R12">
-        <v>1</v>
-      </c>
-      <c r="S12" t="str">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>1</v>
+      </c>
+      <c r="U12" t="str">
         <f>TextData!B12</f>
         <v>最大Mpアップ</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:21">
       <c r="A13">
         <v>1040</v>
       </c>
@@ -2360,27 +2440,27 @@
         <f>INDEX(TextData!B:B,MATCH(B13,TextData!A:A))</f>
         <v>攻撃アップ</v>
       </c>
-      <c r="D13" t="s">
-        <v>24</v>
+      <c r="D13">
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13" t="str">
-        <f>INDEX(Define!B:B,MATCH(E13,Define!A:A))</f>
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="str">
+        <f>INDEX(Define!B:B,MATCH(G13,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13" t="s">
-        <v>18</v>
-      </c>
       <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J13" t="s">
+        <v>20</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -2398,20 +2478,26 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13">
         <v>0</v>
       </c>
       <c r="R13">
-        <v>1</v>
-      </c>
-      <c r="S13" t="str">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>1</v>
+      </c>
+      <c r="U13" t="str">
         <f>TextData!B13</f>
         <v>攻撃アップ</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:21">
       <c r="A14">
         <v>1041</v>
       </c>
@@ -2422,33 +2508,33 @@
         <f>INDEX(TextData!B:B,MATCH(B14,TextData!A:A))</f>
         <v>攻撃ダウン</v>
       </c>
-      <c r="D14" t="s">
-        <v>24</v>
+      <c r="D14">
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14" t="str">
-        <f>INDEX(Define!B:B,MATCH(E14,Define!A:A))</f>
+        <v>27</v>
+      </c>
+      <c r="F14" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="str">
+        <f>INDEX(Define!B:B,MATCH(G14,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14" t="s">
-        <v>18</v>
-      </c>
       <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J14" t="s">
+        <v>20</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -2457,23 +2543,29 @@
         <v>0</v>
       </c>
       <c r="O14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14">
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14">
-        <v>1</v>
-      </c>
-      <c r="S14" t="str">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>1</v>
+      </c>
+      <c r="U14" t="str">
         <f>TextData!B14</f>
         <v>攻撃ダウン</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:21">
       <c r="A15">
         <v>1043</v>
       </c>
@@ -2484,33 +2576,33 @@
         <f>INDEX(TextData!B:B,MATCH(B15,TextData!A:A))</f>
         <v>攻撃ダウン</v>
       </c>
-      <c r="D15" t="s">
-        <v>24</v>
+      <c r="D15">
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15" t="str">
-        <f>INDEX(Define!B:B,MATCH(E15,Define!A:A))</f>
+        <v>29</v>
+      </c>
+      <c r="F15" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="str">
+        <f>INDEX(Define!B:B,MATCH(G15,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15" t="s">
-        <v>18</v>
-      </c>
       <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J15" t="s">
+        <v>20</v>
       </c>
       <c r="K15">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -2519,23 +2611,29 @@
         <v>0</v>
       </c>
       <c r="O15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15">
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15">
-        <v>1</v>
-      </c>
-      <c r="S15" t="str">
+        <v>0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>1</v>
+      </c>
+      <c r="U15" t="str">
         <f>TextData!B15</f>
         <v>攻撃%ダウン</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:21">
       <c r="A16">
         <v>1044</v>
       </c>
@@ -2546,37 +2644,37 @@
         <f>INDEX(TextData!B:B,MATCH(B16,TextData!A:A))</f>
         <v>攻撃アップ</v>
       </c>
-      <c r="D16" t="s">
-        <v>24</v>
+      <c r="D16">
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16" t="str">
-        <f>INDEX(Define!B:B,MATCH(E16,Define!A:A))</f>
+        <v>29</v>
+      </c>
+      <c r="F16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="str">
+        <f>INDEX(Define!B:B,MATCH(G16,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16" t="s">
-        <v>18</v>
-      </c>
       <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J16" t="s">
+        <v>20</v>
       </c>
       <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
         <v>5</v>
       </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
       <c r="N16">
         <v>1</v>
       </c>
@@ -2584,20 +2682,26 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16">
         <v>0</v>
       </c>
       <c r="R16">
-        <v>1</v>
-      </c>
-      <c r="S16" t="str">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>1</v>
+      </c>
+      <c r="U16" t="str">
         <f>TextData!B16</f>
         <v>攻撃アップ</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:21">
       <c r="A17">
         <v>1050</v>
       </c>
@@ -2608,27 +2712,27 @@
         <f>INDEX(TextData!B:B,MATCH(B17,TextData!A:A))</f>
         <v>防御アップ</v>
       </c>
-      <c r="D17" t="s">
-        <v>25</v>
+      <c r="D17">
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17" t="str">
-        <f>INDEX(Define!B:B,MATCH(E17,Define!A:A))</f>
+        <v>14</v>
+      </c>
+      <c r="F17" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17" t="str">
+        <f>INDEX(Define!B:B,MATCH(G17,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17" t="s">
-        <v>18</v>
-      </c>
       <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J17" t="s">
+        <v>20</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -2646,20 +2750,26 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17">
         <v>0</v>
       </c>
       <c r="R17">
-        <v>1</v>
-      </c>
-      <c r="S17" t="str">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>1</v>
+      </c>
+      <c r="U17" t="str">
         <f>TextData!B17</f>
         <v>防御アップ</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:21">
       <c r="A18">
         <v>1051</v>
       </c>
@@ -2670,33 +2780,33 @@
         <f>INDEX(TextData!B:B,MATCH(B18,TextData!A:A))</f>
         <v>防御ダウン</v>
       </c>
-      <c r="D18" t="s">
-        <v>25</v>
+      <c r="D18">
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="F18" t="str">
-        <f>INDEX(Define!B:B,MATCH(E18,Define!A:A))</f>
+        <v>30</v>
+      </c>
+      <c r="F18" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="str">
+        <f>INDEX(Define!B:B,MATCH(G18,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18" t="s">
-        <v>18</v>
-      </c>
       <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J18" t="s">
+        <v>20</v>
       </c>
       <c r="K18">
         <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -2705,23 +2815,29 @@
         <v>0</v>
       </c>
       <c r="O18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18">
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18">
-        <v>1</v>
-      </c>
-      <c r="S18" t="str">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>1</v>
+      </c>
+      <c r="U18" t="str">
         <f>TextData!B18</f>
         <v>防御ダウン</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:21">
       <c r="A19">
         <v>1052</v>
       </c>
@@ -2732,33 +2848,33 @@
         <f>INDEX(TextData!B:B,MATCH(B19,TextData!A:A))</f>
         <v>防御ブレイク</v>
       </c>
-      <c r="D19" t="s">
-        <v>26</v>
+      <c r="D19">
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19" t="str">
-        <f>INDEX(Define!B:B,MATCH(E19,Define!A:A))</f>
+        <v>38</v>
+      </c>
+      <c r="F19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="str">
+        <f>INDEX(Define!B:B,MATCH(G19,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19" t="s">
-        <v>18</v>
-      </c>
       <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J19" t="s">
+        <v>20</v>
       </c>
       <c r="K19">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19">
         <v>0</v>
@@ -2767,23 +2883,29 @@
         <v>0</v>
       </c>
       <c r="O19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P19">
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19">
-        <v>1</v>
-      </c>
-      <c r="S19" t="str">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>1</v>
+      </c>
+      <c r="U19" t="str">
         <f>TextData!B19</f>
         <v>防御ブレイク</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:21">
       <c r="A20">
         <v>1060</v>
       </c>
@@ -2794,27 +2916,27 @@
         <f>INDEX(TextData!B:B,MATCH(B20,TextData!A:A))</f>
         <v>速度アップ</v>
       </c>
-      <c r="D20" t="s">
-        <v>19</v>
+      <c r="D20">
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="F20" t="str">
-        <f>INDEX(Define!B:B,MATCH(E20,Define!A:A))</f>
+        <v>17</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="str">
+        <f>INDEX(Define!B:B,MATCH(G20,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-      <c r="H20" t="s">
-        <v>18</v>
-      </c>
       <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J20" t="s">
+        <v>20</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -2832,20 +2954,26 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20">
         <v>0</v>
       </c>
       <c r="R20">
-        <v>1</v>
-      </c>
-      <c r="S20" t="str">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>1</v>
+      </c>
+      <c r="U20" t="str">
         <f>TextData!B20</f>
         <v>速度アップ</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:21">
       <c r="A21">
         <v>1070</v>
       </c>
@@ -2856,27 +2984,27 @@
         <f>INDEX(TextData!B:B,MATCH(B21,TextData!A:A))</f>
         <v>会心率アップ</v>
       </c>
-      <c r="D21" t="s">
-        <v>27</v>
+      <c r="D21">
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="F21" t="str">
-        <f>INDEX(Define!B:B,MATCH(E21,Define!A:A))</f>
+        <v>0</v>
+      </c>
+      <c r="F21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" t="str">
+        <f>INDEX(Define!B:B,MATCH(G21,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-      <c r="H21" t="s">
-        <v>18</v>
-      </c>
       <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J21" t="s">
+        <v>20</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -2894,20 +3022,26 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21">
         <v>0</v>
       </c>
       <c r="R21">
-        <v>1</v>
-      </c>
-      <c r="S21" t="str">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>1</v>
+      </c>
+      <c r="U21" t="str">
         <f>TextData!B21</f>
         <v>会心率アップ</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:21">
       <c r="A22">
         <v>1074</v>
       </c>
@@ -2918,27 +3052,27 @@
         <f>INDEX(TextData!B:B,MATCH(B22,TextData!A:A))</f>
         <v>会心ダメージアップ</v>
       </c>
-      <c r="D22" t="s">
-        <v>27</v>
+      <c r="D22">
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22" t="str">
-        <f>INDEX(Define!B:B,MATCH(E22,Define!A:A))</f>
+        <v>0</v>
+      </c>
+      <c r="F22" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" t="str">
+        <f>INDEX(Define!B:B,MATCH(G22,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-      <c r="H22" t="s">
-        <v>18</v>
-      </c>
       <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J22" t="s">
+        <v>20</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -2956,20 +3090,26 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22">
         <v>0</v>
       </c>
       <c r="R22">
-        <v>1</v>
-      </c>
-      <c r="S22" t="str">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
+      </c>
+      <c r="U22" t="str">
         <f>TextData!B22</f>
         <v>会心ダメージアップ</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:21">
       <c r="A23">
         <v>1080</v>
       </c>
@@ -2980,27 +3120,27 @@
         <f>INDEX(TextData!B:B,MATCH(B23,TextData!A:A))</f>
         <v>命中アップ</v>
       </c>
-      <c r="D23" t="s">
-        <v>28</v>
+      <c r="D23">
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23" t="str">
-        <f>INDEX(Define!B:B,MATCH(E23,Define!A:A))</f>
+        <v>0</v>
+      </c>
+      <c r="F23" t="s">
+        <v>30</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="str">
+        <f>INDEX(Define!B:B,MATCH(G23,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-      <c r="H23" t="s">
-        <v>18</v>
-      </c>
       <c r="I23">
-        <v>0</v>
-      </c>
-      <c r="J23">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J23" t="s">
+        <v>20</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -3018,20 +3158,26 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23">
         <v>0</v>
       </c>
       <c r="R23">
-        <v>1</v>
-      </c>
-      <c r="S23" t="str">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>1</v>
+      </c>
+      <c r="U23" t="str">
         <f>TextData!B23</f>
         <v>命中アップ</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:21">
       <c r="A24">
         <v>1081</v>
       </c>
@@ -3042,37 +3188,37 @@
         <f>INDEX(TextData!B:B,MATCH(B24,TextData!A:A))</f>
         <v>命中アップ</v>
       </c>
-      <c r="D24" t="s">
-        <v>28</v>
+      <c r="D24">
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>1</v>
-      </c>
-      <c r="F24" t="str">
-        <f>INDEX(Define!B:B,MATCH(E24,Define!A:A))</f>
+        <v>0</v>
+      </c>
+      <c r="F24" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="str">
+        <f>INDEX(Define!B:B,MATCH(G24,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24" t="s">
-        <v>18</v>
-      </c>
       <c r="I24">
-        <v>0</v>
-      </c>
-      <c r="J24">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J24" t="s">
+        <v>20</v>
       </c>
       <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>1</v>
+      </c>
+      <c r="M24">
         <v>5</v>
       </c>
-      <c r="L24">
-        <v>1</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
       <c r="N24">
         <v>1</v>
       </c>
@@ -3080,20 +3226,26 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24">
         <v>0</v>
       </c>
       <c r="R24">
-        <v>1</v>
-      </c>
-      <c r="S24" t="str">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
+      </c>
+      <c r="U24" t="str">
         <f>TextData!B26</f>
         <v>回避アップ</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:21">
       <c r="A25">
         <v>1082</v>
       </c>
@@ -3104,33 +3256,33 @@
         <f>INDEX(TextData!B:B,MATCH(B25,TextData!A:A))</f>
         <v>命中ダウン</v>
       </c>
-      <c r="D25" t="s">
-        <v>28</v>
+      <c r="D25">
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>1</v>
-      </c>
-      <c r="F25" t="str">
-        <f>INDEX(Define!B:B,MATCH(E25,Define!A:A))</f>
+        <v>0</v>
+      </c>
+      <c r="F25" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25" t="str">
+        <f>INDEX(Define!B:B,MATCH(G25,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G25">
-        <v>1</v>
-      </c>
-      <c r="H25" t="s">
-        <v>18</v>
-      </c>
       <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J25" t="s">
+        <v>20</v>
       </c>
       <c r="K25">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -3139,23 +3291,29 @@
         <v>0</v>
       </c>
       <c r="O25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25">
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25">
-        <v>1</v>
-      </c>
-      <c r="S25" t="str">
+        <v>0</v>
+      </c>
+      <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <v>1</v>
+      </c>
+      <c r="U25" t="str">
         <f>TextData!B27</f>
         <v>回避ダウン</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:21">
       <c r="A26">
         <v>1090</v>
       </c>
@@ -3166,27 +3324,27 @@
         <f>INDEX(TextData!B:B,MATCH(B26,TextData!A:A))</f>
         <v>回避アップ</v>
       </c>
-      <c r="D26" t="s">
-        <v>29</v>
+      <c r="D26">
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>1</v>
-      </c>
-      <c r="F26" t="str">
-        <f>INDEX(Define!B:B,MATCH(E26,Define!A:A))</f>
+        <v>0</v>
+      </c>
+      <c r="F26" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26" t="str">
+        <f>INDEX(Define!B:B,MATCH(G26,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26" t="s">
-        <v>18</v>
-      </c>
       <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J26" t="s">
+        <v>20</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -3204,20 +3362,26 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26">
         <v>0</v>
       </c>
       <c r="R26">
-        <v>1</v>
-      </c>
-      <c r="S26" t="str">
+        <v>0</v>
+      </c>
+      <c r="S26">
+        <v>0</v>
+      </c>
+      <c r="T26">
+        <v>1</v>
+      </c>
+      <c r="U26" t="str">
         <f>TextData!B26</f>
         <v>回避アップ</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:21">
       <c r="A27">
         <v>1091</v>
       </c>
@@ -3228,27 +3392,27 @@
         <f>INDEX(TextData!B:B,MATCH(B27,TextData!A:A))</f>
         <v>回避ダウン</v>
       </c>
-      <c r="D27" t="s">
-        <v>29</v>
+      <c r="D27">
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="F27" t="str">
-        <f>INDEX(Define!B:B,MATCH(E27,Define!A:A))</f>
+        <v>0</v>
+      </c>
+      <c r="F27" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27" t="str">
+        <f>INDEX(Define!B:B,MATCH(G27,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27" t="s">
-        <v>18</v>
-      </c>
       <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J27" t="s">
+        <v>20</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -3260,26 +3424,32 @@
         <v>0</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P27">
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27">
-        <v>1</v>
-      </c>
-      <c r="S27" t="str">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>1</v>
+      </c>
+      <c r="U27" t="str">
         <f>TextData!B27</f>
         <v>回避ダウン</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:21">
       <c r="A28">
         <v>1092</v>
       </c>
@@ -3290,37 +3460,37 @@
         <f>INDEX(TextData!B:B,MATCH(B28,TextData!A:A))</f>
         <v>回避アップ</v>
       </c>
-      <c r="D28" t="s">
-        <v>29</v>
+      <c r="D28">
+        <v>0</v>
       </c>
       <c r="E28">
-        <v>1</v>
-      </c>
-      <c r="F28" t="str">
-        <f>INDEX(Define!B:B,MATCH(E28,Define!A:A))</f>
+        <v>0</v>
+      </c>
+      <c r="F28" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28" t="str">
+        <f>INDEX(Define!B:B,MATCH(G28,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-      <c r="H28" t="s">
-        <v>18</v>
-      </c>
       <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J28" t="s">
+        <v>20</v>
       </c>
       <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="M28">
         <v>5</v>
       </c>
-      <c r="L28">
-        <v>1</v>
-      </c>
-      <c r="M28">
-        <v>0</v>
-      </c>
       <c r="N28">
         <v>1</v>
       </c>
@@ -3328,20 +3498,26 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28">
         <v>0</v>
       </c>
       <c r="R28">
-        <v>1</v>
-      </c>
-      <c r="S28" t="str">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <v>1</v>
+      </c>
+      <c r="U28" t="str">
         <f>TextData!B28</f>
         <v>回避アップ</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:21">
       <c r="A29">
         <v>1100</v>
       </c>
@@ -3352,27 +3528,27 @@
         <f>INDEX(TextData!B:B,MATCH(B29,TextData!A:A))</f>
         <v>ダメージカット</v>
       </c>
-      <c r="D29" t="s">
-        <v>30</v>
+      <c r="D29">
+        <v>0</v>
       </c>
       <c r="E29">
+        <v>96</v>
+      </c>
+      <c r="F29" t="s">
+        <v>32</v>
+      </c>
+      <c r="G29">
         <v>4</v>
       </c>
-      <c r="F29" t="str">
-        <f>INDEX(Define!B:B,MATCH(E29,Define!A:A))</f>
+      <c r="H29" t="str">
+        <f>INDEX(Define!B:B,MATCH(G29,Define!A:A))</f>
         <v>効果発揮回数</v>
       </c>
-      <c r="G29">
-        <v>1</v>
-      </c>
-      <c r="H29" t="s">
-        <v>18</v>
-      </c>
       <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J29" t="s">
+        <v>20</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -3390,20 +3566,26 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29">
         <v>0</v>
       </c>
       <c r="R29">
-        <v>1</v>
-      </c>
-      <c r="S29" t="str">
+        <v>0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <v>1</v>
+      </c>
+      <c r="U29" t="str">
         <f>TextData!B29</f>
         <v>ダメージカット</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:21">
       <c r="A30">
         <v>1101</v>
       </c>
@@ -3414,27 +3596,27 @@
         <f>INDEX(TextData!B:B,MATCH(B30,TextData!A:A))</f>
         <v>ダメージカット</v>
       </c>
-      <c r="D30" t="s">
-        <v>30</v>
+      <c r="D30">
+        <v>0</v>
       </c>
       <c r="E30">
+        <v>96</v>
+      </c>
+      <c r="F30" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30">
         <v>4</v>
       </c>
-      <c r="F30" t="str">
-        <f>INDEX(Define!B:B,MATCH(E30,Define!A:A))</f>
+      <c r="H30" t="str">
+        <f>INDEX(Define!B:B,MATCH(G30,Define!A:A))</f>
         <v>効果発揮回数</v>
       </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-      <c r="H30" t="s">
-        <v>18</v>
-      </c>
       <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J30" t="s">
+        <v>20</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -3452,20 +3634,26 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30">
         <v>0</v>
       </c>
       <c r="R30">
-        <v>1</v>
-      </c>
-      <c r="S30" t="str">
+        <v>0</v>
+      </c>
+      <c r="S30">
+        <v>0</v>
+      </c>
+      <c r="T30">
+        <v>1</v>
+      </c>
+      <c r="U30" t="str">
         <f>TextData!B30</f>
         <v>ダメージカット</v>
       </c>
     </row>
-    <row r="31" ht="12" customHeight="1" spans="1:19">
+    <row r="31" ht="12" customHeight="1" spans="1:21">
       <c r="A31">
         <v>2010</v>
       </c>
@@ -3476,36 +3664,36 @@
         <f>INDEX(TextData!B:B,MATCH(B31,TextData!A:A))</f>
         <v>毒</v>
       </c>
-      <c r="D31" t="s">
-        <v>31</v>
+      <c r="D31">
+        <v>26</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
-      <c r="F31" t="str">
-        <f>INDEX(Define!B:B,MATCH(E31,Define!A:A))</f>
+      <c r="F31" t="s">
+        <v>33</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31" t="str">
+        <f>INDEX(Define!B:B,MATCH(G31,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-      <c r="H31" t="s">
-        <v>32</v>
-      </c>
       <c r="I31">
         <v>1</v>
       </c>
-      <c r="J31">
-        <v>1</v>
+      <c r="J31" t="s">
+        <v>34</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -3514,20 +3702,26 @@
         <v>1</v>
       </c>
       <c r="P31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31">
         <v>1</v>
       </c>
-      <c r="S31" t="str">
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>1</v>
+      </c>
+      <c r="U31" t="str">
         <f>TextData!B31</f>
         <v>毒</v>
       </c>
     </row>
-    <row r="32" ht="12" customHeight="1" spans="1:19">
+    <row r="32" ht="12" customHeight="1" spans="1:21">
       <c r="A32">
         <v>2011</v>
       </c>
@@ -3535,38 +3729,38 @@
         <v>2010</v>
       </c>
       <c r="C32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32">
+        <v>26</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+      <c r="F32" t="s">
         <v>33</v>
       </c>
-      <c r="D32" t="s">
-        <v>31</v>
-      </c>
-      <c r="E32">
-        <v>1</v>
-      </c>
-      <c r="F32" t="str">
-        <f>INDEX(Define!B:B,MATCH(E32,Define!A:A))</f>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32" t="str">
+        <f>INDEX(Define!B:B,MATCH(G32,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-      <c r="H32" t="s">
-        <v>32</v>
-      </c>
       <c r="I32">
         <v>1</v>
       </c>
-      <c r="J32">
-        <v>1</v>
+      <c r="J32" t="s">
+        <v>34</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -3575,20 +3769,26 @@
         <v>1</v>
       </c>
       <c r="P32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32">
         <v>1</v>
       </c>
-      <c r="S32" t="str">
+      <c r="S32">
+        <v>0</v>
+      </c>
+      <c r="T32">
+        <v>1</v>
+      </c>
+      <c r="U32" t="str">
         <f>TextData!B31</f>
         <v>毒</v>
       </c>
     </row>
-    <row r="33" ht="12" customHeight="1" spans="1:19">
+    <row r="33" ht="12" customHeight="1" spans="1:21">
       <c r="A33">
         <v>2020</v>
       </c>
@@ -3599,36 +3799,36 @@
         <f>INDEX(TextData!B:B,MATCH(B33,TextData!A:A))</f>
         <v>暗闇</v>
       </c>
-      <c r="D33" t="s">
-        <v>28</v>
+      <c r="D33">
+        <v>33</v>
       </c>
       <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="F33" t="s">
+        <v>30</v>
+      </c>
+      <c r="G33">
         <v>4</v>
       </c>
-      <c r="F33" t="str">
-        <f>INDEX(Define!B:B,MATCH(E33,Define!A:A))</f>
+      <c r="H33" t="str">
+        <f>INDEX(Define!B:B,MATCH(G33,Define!A:A))</f>
         <v>効果発揮回数</v>
       </c>
-      <c r="G33">
-        <v>1</v>
-      </c>
-      <c r="H33" t="s">
-        <v>34</v>
-      </c>
       <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="J33" t="s">
+        <v>36</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+      <c r="L33">
         <v>0.1</v>
       </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
       <c r="M33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -3637,20 +3837,26 @@
         <v>1</v>
       </c>
       <c r="P33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33">
         <v>1</v>
       </c>
-      <c r="S33" t="str">
+      <c r="S33">
+        <v>0</v>
+      </c>
+      <c r="T33">
+        <v>1</v>
+      </c>
+      <c r="U33" t="str">
         <f>TextData!B32</f>
         <v>暗闇</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:21">
       <c r="A34">
         <v>2030</v>
       </c>
@@ -3661,33 +3867,33 @@
         <f>INDEX(TextData!B:B,MATCH(B34,TextData!A:A))</f>
         <v>カウンタ</v>
       </c>
-      <c r="D34" t="s">
-        <v>35</v>
+      <c r="D34">
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>1</v>
-      </c>
-      <c r="F34" t="str">
-        <f>INDEX(Define!B:B,MATCH(E34,Define!A:A))</f>
+        <v>66</v>
+      </c>
+      <c r="F34" t="s">
+        <v>37</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34" t="str">
+        <f>INDEX(Define!B:B,MATCH(G34,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34" t="s">
-        <v>36</v>
-      </c>
       <c r="I34">
         <v>0</v>
       </c>
-      <c r="J34">
-        <v>1</v>
+      <c r="J34" t="s">
+        <v>38</v>
       </c>
       <c r="K34">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -3705,14 +3911,20 @@
         <v>0</v>
       </c>
       <c r="R34">
-        <v>1</v>
-      </c>
-      <c r="S34" t="str">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <v>1</v>
+      </c>
+      <c r="U34" t="str">
         <f>TextData!B33</f>
         <v>カウンタ</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:21">
       <c r="A35">
         <v>2031</v>
       </c>
@@ -3723,33 +3935,33 @@
         <f>INDEX(TextData!B:B,MATCH(B35,TextData!A:A))</f>
         <v>CAダメージ</v>
       </c>
-      <c r="D35" t="s">
-        <v>35</v>
+      <c r="D35">
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>1</v>
-      </c>
-      <c r="F35" t="str">
-        <f>INDEX(Define!B:B,MATCH(E35,Define!A:A))</f>
+        <v>66</v>
+      </c>
+      <c r="F35" t="s">
+        <v>37</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35" t="str">
+        <f>INDEX(Define!B:B,MATCH(G35,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-      <c r="H35" t="s">
-        <v>18</v>
-      </c>
       <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J35" t="s">
+        <v>20</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -3767,14 +3979,20 @@
         <v>0</v>
       </c>
       <c r="R35">
-        <v>1</v>
-      </c>
-      <c r="S35" t="str">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>1</v>
+      </c>
+      <c r="U35" t="str">
         <f>TextData!B34</f>
         <v>CAダメージ</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:21">
       <c r="A36">
         <v>2032</v>
       </c>
@@ -3785,33 +4003,33 @@
         <f>INDEX(TextData!B:B,MATCH(B36,TextData!A:A))</f>
         <v>CAシェル</v>
       </c>
-      <c r="D36" t="s">
-        <v>37</v>
+      <c r="D36">
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36" t="str">
-        <f>INDEX(Define!B:B,MATCH(E36,Define!A:A))</f>
+        <v>66</v>
+      </c>
+      <c r="F36" t="s">
+        <v>39</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36" t="str">
+        <f>INDEX(Define!B:B,MATCH(G36,Define!A:A))</f>
         <v>なし</v>
       </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-      <c r="H36" t="s">
-        <v>18</v>
-      </c>
       <c r="I36">
-        <v>0</v>
-      </c>
-      <c r="J36">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J36" t="s">
+        <v>20</v>
       </c>
       <c r="K36">
         <v>0</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -3829,14 +4047,20 @@
         <v>0</v>
       </c>
       <c r="R36">
-        <v>1</v>
-      </c>
-      <c r="S36" t="str">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>1</v>
+      </c>
+      <c r="U36" t="str">
         <f>TextData!B35</f>
         <v>CAシェル</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:21">
       <c r="A37">
         <v>2040</v>
       </c>
@@ -3847,33 +4071,33 @@
         <f>INDEX(TextData!B:B,MATCH(B37,TextData!A:A))</f>
         <v>リジェネ</v>
       </c>
-      <c r="D37" t="s">
-        <v>37</v>
+      <c r="D37">
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>1</v>
-      </c>
-      <c r="F37" t="str">
-        <f>INDEX(Define!B:B,MATCH(E37,Define!A:A))</f>
+        <v>46</v>
+      </c>
+      <c r="F37" t="s">
+        <v>39</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="H37" t="str">
+        <f>INDEX(Define!B:B,MATCH(G37,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G37">
-        <v>1</v>
-      </c>
-      <c r="H37" t="s">
-        <v>18</v>
-      </c>
       <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J37" t="s">
+        <v>20</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -3891,14 +4115,20 @@
         <v>0</v>
       </c>
       <c r="R37">
-        <v>1</v>
-      </c>
-      <c r="S37" t="str">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>1</v>
+      </c>
+      <c r="U37" t="str">
         <f>TextData!B36</f>
         <v>リジェネ</v>
       </c>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:21">
       <c r="A38">
         <v>2050</v>
       </c>
@@ -3909,33 +4139,33 @@
         <f>INDEX(TextData!B:B,MATCH(B38,TextData!A:A))</f>
         <v>攻撃無効</v>
       </c>
-      <c r="D38" t="s">
-        <v>38</v>
+      <c r="D38">
+        <v>0</v>
       </c>
       <c r="E38">
+        <v>226</v>
+      </c>
+      <c r="F38" t="s">
+        <v>40</v>
+      </c>
+      <c r="G38">
         <v>4</v>
       </c>
-      <c r="F38" t="str">
-        <f>INDEX(Define!B:B,MATCH(E38,Define!A:A))</f>
+      <c r="H38" t="str">
+        <f>INDEX(Define!B:B,MATCH(G38,Define!A:A))</f>
         <v>効果発揮回数</v>
       </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38" t="s">
-        <v>39</v>
-      </c>
       <c r="I38">
         <v>0</v>
       </c>
-      <c r="J38">
-        <v>1</v>
+      <c r="J38" t="s">
+        <v>41</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38">
         <v>0</v>
@@ -3953,14 +4183,20 @@
         <v>0</v>
       </c>
       <c r="R38">
-        <v>1</v>
-      </c>
-      <c r="S38" t="str">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>1</v>
+      </c>
+      <c r="U38" t="str">
         <f>TextData!B37</f>
         <v>攻撃無効</v>
       </c>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:21">
       <c r="A39">
         <v>2060</v>
       </c>
@@ -3971,33 +4207,33 @@
         <f>INDEX(TextData!B:B,MATCH(B39,TextData!A:A))</f>
         <v>ドレイン</v>
       </c>
-      <c r="D39" t="s">
-        <v>40</v>
+      <c r="D39">
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>1</v>
-      </c>
-      <c r="F39" t="str">
-        <f>INDEX(Define!B:B,MATCH(E39,Define!A:A))</f>
+        <v>167</v>
+      </c>
+      <c r="F39" t="s">
+        <v>42</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39" t="str">
+        <f>INDEX(Define!B:B,MATCH(G39,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-      <c r="H39" t="s">
-        <v>18</v>
-      </c>
       <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J39" t="s">
+        <v>20</v>
       </c>
       <c r="K39">
         <v>0</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39">
         <v>0</v>
@@ -4015,14 +4251,20 @@
         <v>0</v>
       </c>
       <c r="R39">
-        <v>1</v>
-      </c>
-      <c r="S39" t="str">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>1</v>
+      </c>
+      <c r="U39" t="str">
         <f>TextData!B38</f>
         <v>ドレイン</v>
       </c>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:21">
       <c r="A40">
         <v>2070</v>
       </c>
@@ -4033,33 +4275,33 @@
         <f>INDEX(TextData!B:B,MATCH(B40,TextData!A:A))</f>
         <v>状態異常CA</v>
       </c>
-      <c r="D40" t="s">
-        <v>41</v>
+      <c r="D40">
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>1</v>
-      </c>
-      <c r="F40" t="str">
-        <f>INDEX(Define!B:B,MATCH(E40,Define!A:A))</f>
+        <v>226</v>
+      </c>
+      <c r="F40" t="s">
+        <v>43</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40" t="str">
+        <f>INDEX(Define!B:B,MATCH(G40,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
-      <c r="H40" t="s">
-        <v>18</v>
-      </c>
       <c r="I40">
         <v>0</v>
       </c>
-      <c r="J40">
-        <v>1</v>
+      <c r="J40" t="s">
+        <v>20</v>
       </c>
       <c r="K40">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -4077,14 +4319,20 @@
         <v>0</v>
       </c>
       <c r="R40">
-        <v>1</v>
-      </c>
-      <c r="S40" t="str">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>1</v>
+      </c>
+      <c r="U40" t="str">
         <f>TextData!B39</f>
         <v>状態異常CA</v>
       </c>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:21">
       <c r="A41">
         <v>2080</v>
       </c>
@@ -4095,33 +4343,33 @@
         <f>INDEX(TextData!B:B,MATCH(B41,TextData!A:A))</f>
         <v>反撃</v>
       </c>
-      <c r="D41" t="s">
-        <v>35</v>
+      <c r="D41">
+        <v>0</v>
       </c>
       <c r="E41">
         <v>4</v>
       </c>
-      <c r="F41" t="str">
-        <f>INDEX(Define!B:B,MATCH(E41,Define!A:A))</f>
+      <c r="F41" t="s">
+        <v>37</v>
+      </c>
+      <c r="G41">
+        <v>4</v>
+      </c>
+      <c r="H41" t="str">
+        <f>INDEX(Define!B:B,MATCH(G41,Define!A:A))</f>
         <v>効果発揮回数</v>
       </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
-      <c r="H41" t="s">
-        <v>18</v>
-      </c>
       <c r="I41">
         <v>0</v>
       </c>
-      <c r="J41">
-        <v>1</v>
+      <c r="J41" t="s">
+        <v>20</v>
       </c>
       <c r="K41">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -4139,14 +4387,20 @@
         <v>0</v>
       </c>
       <c r="R41">
-        <v>1</v>
-      </c>
-      <c r="S41" t="str">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>1</v>
+      </c>
+      <c r="U41" t="str">
         <f>TextData!B40</f>
         <v>反撃</v>
       </c>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:21">
       <c r="A42">
         <v>2090</v>
       </c>
@@ -4157,36 +4411,36 @@
         <f>INDEX(TextData!B:B,MATCH(B42,TextData!A:A))</f>
         <v>パッシブ封じ</v>
       </c>
-      <c r="D42" t="s">
-        <v>42</v>
+      <c r="D42">
+        <v>0</v>
       </c>
       <c r="E42">
+        <v>10</v>
+      </c>
+      <c r="F42" t="s">
+        <v>44</v>
+      </c>
+      <c r="G42">
         <v>4</v>
       </c>
-      <c r="F42" t="str">
-        <f>INDEX(Define!B:B,MATCH(E42,Define!A:A))</f>
+      <c r="H42" t="str">
+        <f>INDEX(Define!B:B,MATCH(G42,Define!A:A))</f>
         <v>効果発揮回数</v>
       </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42" t="s">
-        <v>18</v>
-      </c>
       <c r="I42">
         <v>0</v>
       </c>
-      <c r="J42">
-        <v>1</v>
+      <c r="J42" t="s">
+        <v>20</v>
       </c>
       <c r="K42">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42">
         <v>0</v>
@@ -4195,20 +4449,26 @@
         <v>1</v>
       </c>
       <c r="P42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42">
         <v>1</v>
       </c>
-      <c r="S42" t="str">
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>1</v>
+      </c>
+      <c r="U42" t="str">
         <f>TextData!B41</f>
         <v>パッシブ封じ</v>
       </c>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:21">
       <c r="A43">
         <v>2120</v>
       </c>
@@ -4219,34 +4479,34 @@
         <f>INDEX(TextData!B:B,MATCH(B43,TextData!A:A))</f>
         <v>デバフ強化</v>
       </c>
-      <c r="D43" t="s">
-        <v>43</v>
+      <c r="D43">
+        <v>0</v>
       </c>
       <c r="E43">
+        <v>9</v>
+      </c>
+      <c r="F43" t="s">
+        <v>45</v>
+      </c>
+      <c r="G43">
         <v>4</v>
       </c>
-      <c r="F43" t="str">
-        <f>INDEX(Define!B:B,MATCH(E43,Define!A:A))</f>
+      <c r="H43" t="str">
+        <f>INDEX(Define!B:B,MATCH(G43,Define!A:A))</f>
         <v>効果発揮回数</v>
       </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-      <c r="H43" t="s">
-        <v>44</v>
-      </c>
       <c r="I43">
-        <v>0</v>
-      </c>
-      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="J43" t="s">
+        <v>46</v>
+      </c>
+      <c r="K43">
+        <v>0</v>
+      </c>
+      <c r="L43">
         <v>0.2</v>
       </c>
-      <c r="K43">
-        <v>0</v>
-      </c>
-      <c r="L43">
-        <v>0</v>
-      </c>
       <c r="M43">
         <v>0</v>
       </c>
@@ -4257,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="P43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -4265,12 +4525,18 @@
       <c r="R43">
         <v>1</v>
       </c>
-      <c r="S43" t="str">
+      <c r="S43">
+        <v>0</v>
+      </c>
+      <c r="T43">
+        <v>1</v>
+      </c>
+      <c r="U43" t="str">
         <f>TextData!B42</f>
         <v>デバフ強化</v>
       </c>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:21">
       <c r="A44">
         <v>2130</v>
       </c>
@@ -4281,33 +4547,33 @@
         <f>INDEX(TextData!B:B,MATCH(B44,TextData!A:A))</f>
         <v>挑発</v>
       </c>
-      <c r="D44" t="s">
-        <v>45</v>
+      <c r="D44">
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>1</v>
-      </c>
-      <c r="F44" t="str">
-        <f>INDEX(Define!B:B,MATCH(E44,Define!A:A))</f>
+        <v>4</v>
+      </c>
+      <c r="F44" t="s">
+        <v>47</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+      <c r="H44" t="str">
+        <f>INDEX(Define!B:B,MATCH(G44,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G44">
-        <v>0</v>
-      </c>
-      <c r="H44" t="s">
-        <v>18</v>
-      </c>
       <c r="I44">
         <v>0</v>
       </c>
-      <c r="J44">
-        <v>1</v>
+      <c r="J44" t="s">
+        <v>20</v>
       </c>
       <c r="K44">
         <v>0</v>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44">
         <v>0</v>
@@ -4319,7 +4585,7 @@
         <v>0</v>
       </c>
       <c r="P44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q44">
         <v>0</v>
@@ -4327,12 +4593,18 @@
       <c r="R44">
         <v>1</v>
       </c>
-      <c r="S44" t="str">
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>1</v>
+      </c>
+      <c r="U44" t="str">
         <f>TextData!B43</f>
         <v>挑発</v>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:21">
       <c r="A45">
         <v>2140</v>
       </c>
@@ -4343,36 +4615,36 @@
         <f>INDEX(TextData!B:B,MATCH(B45,TextData!A:A))</f>
         <v>凍結</v>
       </c>
-      <c r="D45" t="s">
-        <v>46</v>
+      <c r="D45">
+        <v>18</v>
       </c>
       <c r="E45">
+        <v>44</v>
+      </c>
+      <c r="F45" t="s">
+        <v>48</v>
+      </c>
+      <c r="G45">
         <v>4</v>
       </c>
-      <c r="F45" t="str">
-        <f>INDEX(Define!B:B,MATCH(E45,Define!A:A))</f>
+      <c r="H45" t="str">
+        <f>INDEX(Define!B:B,MATCH(G45,Define!A:A))</f>
         <v>効果発揮回数</v>
       </c>
-      <c r="G45">
-        <v>1</v>
-      </c>
-      <c r="H45" t="s">
-        <v>47</v>
-      </c>
       <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J45" t="s">
+        <v>49</v>
       </c>
       <c r="K45">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45">
         <v>0</v>
@@ -4381,20 +4653,26 @@
         <v>1</v>
       </c>
       <c r="P45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45">
         <v>1</v>
       </c>
-      <c r="S45" t="str">
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>1</v>
+      </c>
+      <c r="U45" t="str">
         <f>TextData!B44</f>
         <v>凍結</v>
       </c>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:21">
       <c r="A46">
         <v>2150</v>
       </c>
@@ -4405,36 +4683,36 @@
         <f>INDEX(TextData!B:B,MATCH(B46,TextData!A:A))</f>
         <v>スタン</v>
       </c>
-      <c r="D46" t="s">
-        <v>48</v>
+      <c r="D46">
+        <v>0</v>
       </c>
       <c r="E46">
+        <v>5</v>
+      </c>
+      <c r="F46" t="s">
+        <v>50</v>
+      </c>
+      <c r="G46">
         <v>2</v>
       </c>
-      <c r="F46" t="str">
-        <f>INDEX(Define!B:B,MATCH(E46,Define!A:A))</f>
+      <c r="H46" t="str">
+        <f>INDEX(Define!B:B,MATCH(G46,Define!A:A))</f>
         <v>APカウント</v>
       </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
-      <c r="H46" t="s">
-        <v>49</v>
-      </c>
       <c r="I46">
         <v>0</v>
       </c>
-      <c r="J46">
-        <v>1</v>
+      <c r="J46" t="s">
+        <v>51</v>
       </c>
       <c r="K46">
         <v>0</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46">
         <v>0</v>
@@ -4443,20 +4721,26 @@
         <v>1</v>
       </c>
       <c r="P46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46">
         <v>1</v>
       </c>
-      <c r="S46" t="str">
+      <c r="S46">
+        <v>0</v>
+      </c>
+      <c r="T46">
+        <v>1</v>
+      </c>
+      <c r="U46" t="str">
         <f>TextData!B45</f>
         <v>スタン</v>
       </c>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:21">
       <c r="A47">
         <v>2180</v>
       </c>
@@ -4467,33 +4751,33 @@
         <f>INDEX(TextData!B:B,MATCH(B47,TextData!A:A))</f>
         <v>状態異常回避</v>
       </c>
-      <c r="D47" t="s">
-        <v>50</v>
+      <c r="D47">
+        <v>0</v>
       </c>
       <c r="E47">
+        <v>99</v>
+      </c>
+      <c r="F47" t="s">
+        <v>52</v>
+      </c>
+      <c r="G47">
         <v>4</v>
       </c>
-      <c r="F47" t="str">
-        <f>INDEX(Define!B:B,MATCH(E47,Define!A:A))</f>
+      <c r="H47" t="str">
+        <f>INDEX(Define!B:B,MATCH(G47,Define!A:A))</f>
         <v>効果発揮回数</v>
       </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47" t="s">
-        <v>18</v>
-      </c>
       <c r="I47">
         <v>0</v>
       </c>
-      <c r="J47">
-        <v>1</v>
+      <c r="J47" t="s">
+        <v>20</v>
       </c>
       <c r="K47">
         <v>0</v>
       </c>
       <c r="L47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47">
         <v>0</v>
@@ -4511,14 +4795,20 @@
         <v>0</v>
       </c>
       <c r="R47">
-        <v>1</v>
-      </c>
-      <c r="S47" t="str">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>1</v>
+      </c>
+      <c r="U47" t="str">
         <f>TextData!B46</f>
         <v>状態異常回避</v>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:21">
       <c r="A48">
         <v>2190</v>
       </c>
@@ -4529,33 +4819,33 @@
         <f>INDEX(TextData!B:B,MATCH(B48,TextData!A:A))</f>
         <v>対象範囲延長</v>
       </c>
-      <c r="D48" t="s">
-        <v>51</v>
+      <c r="D48">
+        <v>0</v>
       </c>
       <c r="E48">
-        <v>1</v>
-      </c>
-      <c r="F48" t="str">
-        <f>INDEX(Define!B:B,MATCH(E48,Define!A:A))</f>
+        <v>73</v>
+      </c>
+      <c r="F48" t="s">
+        <v>53</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48" t="str">
+        <f>INDEX(Define!B:B,MATCH(G48,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48" t="s">
-        <v>18</v>
-      </c>
       <c r="I48">
         <v>0</v>
       </c>
-      <c r="J48">
-        <v>1</v>
+      <c r="J48" t="s">
+        <v>20</v>
       </c>
       <c r="K48">
         <v>0</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48">
         <v>0</v>
@@ -4575,12 +4865,18 @@
       <c r="R48">
         <v>0</v>
       </c>
-      <c r="S48" t="str">
+      <c r="S48">
+        <v>0</v>
+      </c>
+      <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48" t="str">
         <f>TextData!B47</f>
         <v>対象範囲延長</v>
       </c>
     </row>
-    <row r="49" spans="1:19">
+    <row r="49" spans="1:21">
       <c r="A49">
         <v>2210</v>
       </c>
@@ -4591,33 +4887,33 @@
         <f>INDEX(TextData!B:B,MATCH(B49,TextData!A:A))</f>
         <v>アフターヒール</v>
       </c>
-      <c r="D49" t="s">
-        <v>37</v>
+      <c r="D49">
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>1</v>
-      </c>
-      <c r="F49" t="str">
-        <f>INDEX(Define!B:B,MATCH(E49,Define!A:A))</f>
+        <v>63</v>
+      </c>
+      <c r="F49" t="s">
+        <v>39</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+      <c r="H49" t="str">
+        <f>INDEX(Define!B:B,MATCH(G49,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G49">
-        <v>1</v>
-      </c>
-      <c r="H49" t="s">
-        <v>18</v>
-      </c>
       <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J49" t="s">
+        <v>20</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49">
         <v>0</v>
@@ -4635,14 +4931,20 @@
         <v>0</v>
       </c>
       <c r="R49">
-        <v>1</v>
-      </c>
-      <c r="S49" t="str">
+        <v>0</v>
+      </c>
+      <c r="S49">
+        <v>0</v>
+      </c>
+      <c r="T49">
+        <v>1</v>
+      </c>
+      <c r="U49" t="str">
         <f>TextData!B48</f>
         <v>アフターヒール</v>
       </c>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:21">
       <c r="A50">
         <v>2220</v>
       </c>
@@ -4653,33 +4955,33 @@
         <f>INDEX(TextData!B:B,MATCH(B50,TextData!A:A))</f>
         <v>即死付与</v>
       </c>
-      <c r="D50" t="s">
-        <v>17</v>
+      <c r="D50">
+        <v>0</v>
       </c>
       <c r="E50">
         <v>1</v>
       </c>
-      <c r="F50" t="str">
-        <f>INDEX(Define!B:B,MATCH(E50,Define!A:A))</f>
+      <c r="F50" t="s">
+        <v>19</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50" t="str">
+        <f>INDEX(Define!B:B,MATCH(G50,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G50">
-        <v>0</v>
-      </c>
-      <c r="H50" t="s">
-        <v>18</v>
-      </c>
       <c r="I50">
         <v>0</v>
       </c>
-      <c r="J50">
-        <v>1</v>
+      <c r="J50" t="s">
+        <v>20</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50">
         <v>0</v>
@@ -4691,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="P50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -4699,12 +5001,18 @@
       <c r="R50">
         <v>1</v>
       </c>
-      <c r="S50" t="str">
+      <c r="S50">
+        <v>0</v>
+      </c>
+      <c r="T50">
+        <v>1</v>
+      </c>
+      <c r="U50" t="str">
         <f>TextData!B49</f>
         <v>即死付与</v>
       </c>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:21">
       <c r="A51">
         <v>2230</v>
       </c>
@@ -4715,33 +5023,33 @@
         <f>INDEX(TextData!B:B,MATCH(B51,TextData!A:A))</f>
         <v>同時回復</v>
       </c>
-      <c r="D51" t="s">
-        <v>37</v>
+      <c r="D51">
+        <v>0</v>
       </c>
       <c r="E51">
-        <v>0</v>
-      </c>
-      <c r="F51" t="str">
-        <f>INDEX(Define!B:B,MATCH(E51,Define!A:A))</f>
+        <v>46</v>
+      </c>
+      <c r="F51" t="s">
+        <v>39</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51" t="str">
+        <f>INDEX(Define!B:B,MATCH(G51,Define!A:A))</f>
         <v>なし</v>
       </c>
-      <c r="G51">
-        <v>1</v>
-      </c>
-      <c r="H51" t="s">
-        <v>18</v>
-      </c>
       <c r="I51">
-        <v>0</v>
-      </c>
-      <c r="J51">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J51" t="s">
+        <v>20</v>
       </c>
       <c r="K51">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51">
         <v>0</v>
@@ -4759,14 +5067,20 @@
         <v>0</v>
       </c>
       <c r="R51">
-        <v>1</v>
-      </c>
-      <c r="S51" t="str">
+        <v>0</v>
+      </c>
+      <c r="S51">
+        <v>0</v>
+      </c>
+      <c r="T51">
+        <v>1</v>
+      </c>
+      <c r="U51" t="str">
         <f>TextData!B50</f>
         <v>同時回復</v>
       </c>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" spans="1:21">
       <c r="A52">
         <v>2240</v>
       </c>
@@ -4777,33 +5091,33 @@
         <f>INDEX(TextData!B:B,MATCH(B52,TextData!A:A))</f>
         <v>必中</v>
       </c>
-      <c r="D52" t="s">
-        <v>28</v>
+      <c r="D52">
+        <v>0</v>
       </c>
       <c r="E52">
+        <v>62</v>
+      </c>
+      <c r="F52" t="s">
+        <v>30</v>
+      </c>
+      <c r="G52">
         <v>4</v>
       </c>
-      <c r="F52" t="str">
-        <f>INDEX(Define!B:B,MATCH(E52,Define!A:A))</f>
+      <c r="H52" t="str">
+        <f>INDEX(Define!B:B,MATCH(G52,Define!A:A))</f>
         <v>効果発揮回数</v>
       </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52" t="s">
-        <v>18</v>
-      </c>
       <c r="I52">
         <v>0</v>
       </c>
-      <c r="J52">
-        <v>1</v>
+      <c r="J52" t="s">
+        <v>20</v>
       </c>
       <c r="K52">
         <v>0</v>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52">
         <v>0</v>
@@ -4821,14 +5135,20 @@
         <v>0</v>
       </c>
       <c r="R52">
-        <v>1</v>
-      </c>
-      <c r="S52" t="str">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <v>1</v>
+      </c>
+      <c r="U52" t="str">
         <f>TextData!B51</f>
         <v>必中</v>
       </c>
     </row>
-    <row r="53" spans="1:19">
+    <row r="53" spans="1:21">
       <c r="A53">
         <v>2250</v>
       </c>
@@ -4839,33 +5159,33 @@
         <f>INDEX(TextData!B:B,MATCH(B53,TextData!A:A))</f>
         <v>アシストヒール</v>
       </c>
-      <c r="D53" t="s">
-        <v>52</v>
+      <c r="D53">
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="F53" t="str">
-        <f>INDEX(Define!B:B,MATCH(E53,Define!A:A))</f>
+        <v>46</v>
+      </c>
+      <c r="F53" t="s">
+        <v>54</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53" t="str">
+        <f>INDEX(Define!B:B,MATCH(G53,Define!A:A))</f>
         <v>なし</v>
       </c>
-      <c r="G53">
-        <v>0</v>
-      </c>
-      <c r="H53" t="s">
-        <v>18</v>
-      </c>
       <c r="I53">
         <v>0</v>
       </c>
-      <c r="J53">
-        <v>1</v>
+      <c r="J53" t="s">
+        <v>20</v>
       </c>
       <c r="K53">
         <v>0</v>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53">
         <v>0</v>
@@ -4883,14 +5203,20 @@
         <v>0</v>
       </c>
       <c r="R53">
-        <v>1</v>
-      </c>
-      <c r="S53" t="str">
+        <v>0</v>
+      </c>
+      <c r="S53">
+        <v>0</v>
+      </c>
+      <c r="T53">
+        <v>1</v>
+      </c>
+      <c r="U53" t="str">
         <f>TextData!B52</f>
         <v>アシストヒール</v>
       </c>
     </row>
-    <row r="54" spans="1:19">
+    <row r="54" spans="1:21">
       <c r="A54">
         <v>2270</v>
       </c>
@@ -4901,33 +5227,33 @@
         <f>INDEX(TextData!B:B,MATCH(B54,TextData!A:A))</f>
         <v>アンデッド</v>
       </c>
-      <c r="D54" t="s">
-        <v>53</v>
+      <c r="D54">
+        <v>0</v>
       </c>
       <c r="E54">
-        <v>0</v>
-      </c>
-      <c r="F54" t="str">
-        <f>INDEX(Define!B:B,MATCH(E54,Define!A:A))</f>
+        <v>9</v>
+      </c>
+      <c r="F54" t="s">
+        <v>55</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54" t="str">
+        <f>INDEX(Define!B:B,MATCH(G54,Define!A:A))</f>
         <v>なし</v>
       </c>
-      <c r="G54">
-        <v>0</v>
-      </c>
-      <c r="H54" t="s">
-        <v>18</v>
-      </c>
       <c r="I54">
         <v>0</v>
       </c>
-      <c r="J54">
-        <v>1</v>
+      <c r="J54" t="s">
+        <v>20</v>
       </c>
       <c r="K54">
         <v>0</v>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54">
         <v>0</v>
@@ -4945,14 +5271,20 @@
         <v>0</v>
       </c>
       <c r="R54">
-        <v>1</v>
-      </c>
-      <c r="S54" t="str">
+        <v>0</v>
+      </c>
+      <c r="S54">
+        <v>0</v>
+      </c>
+      <c r="T54">
+        <v>1</v>
+      </c>
+      <c r="U54" t="str">
         <f>TextData!B53</f>
         <v>アンデッド</v>
       </c>
     </row>
-    <row r="55" spans="1:19">
+    <row r="55" spans="1:21">
       <c r="A55">
         <v>2280</v>
       </c>
@@ -4963,33 +5295,33 @@
         <f>INDEX(TextData!B:B,MATCH(B55,TextData!A:A))</f>
         <v>アクセル</v>
       </c>
-      <c r="D55" t="s">
-        <v>19</v>
+      <c r="D55">
+        <v>0</v>
       </c>
       <c r="E55">
-        <v>0</v>
-      </c>
-      <c r="F55" t="str">
-        <f>INDEX(Define!B:B,MATCH(E55,Define!A:A))</f>
+        <v>25</v>
+      </c>
+      <c r="F55" t="s">
+        <v>21</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55" t="str">
+        <f>INDEX(Define!B:B,MATCH(G55,Define!A:A))</f>
         <v>なし</v>
       </c>
-      <c r="G55">
-        <v>0</v>
-      </c>
-      <c r="H55" t="s">
-        <v>18</v>
-      </c>
       <c r="I55">
         <v>0</v>
       </c>
-      <c r="J55">
-        <v>1</v>
+      <c r="J55" t="s">
+        <v>20</v>
       </c>
       <c r="K55">
         <v>0</v>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55">
         <v>0</v>
@@ -5007,14 +5339,20 @@
         <v>0</v>
       </c>
       <c r="R55">
-        <v>1</v>
-      </c>
-      <c r="S55" t="str">
+        <v>0</v>
+      </c>
+      <c r="S55">
+        <v>0</v>
+      </c>
+      <c r="T55">
+        <v>1</v>
+      </c>
+      <c r="U55" t="str">
         <f>TextData!B54</f>
         <v>アクセル</v>
       </c>
     </row>
-    <row r="56" spans="1:19">
+    <row r="56" spans="1:21">
       <c r="A56">
         <v>2290</v>
       </c>
@@ -5025,58 +5363,64 @@
         <f>INDEX(TextData!B:B,MATCH(B56,TextData!A:A))</f>
         <v>ダメージ威力アップ</v>
       </c>
-      <c r="D56" t="s">
-        <v>54</v>
+      <c r="D56">
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>1</v>
-      </c>
-      <c r="F56" t="str">
-        <f>INDEX(Define!B:B,MATCH(E56,Define!A:A))</f>
+        <v>21</v>
+      </c>
+      <c r="F56" t="s">
+        <v>56</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+      <c r="H56" t="str">
+        <f>INDEX(Define!B:B,MATCH(G56,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G56">
-        <v>1</v>
-      </c>
-      <c r="H56" t="s">
-        <v>18</v>
-      </c>
       <c r="I56">
-        <v>0</v>
-      </c>
-      <c r="J56">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J56" t="s">
+        <v>20</v>
       </c>
       <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>1</v>
+      </c>
+      <c r="M56">
         <v>10</v>
       </c>
-      <c r="L56">
-        <v>0</v>
-      </c>
-      <c r="M56">
-        <v>0</v>
-      </c>
       <c r="N56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q56">
         <v>0</v>
       </c>
       <c r="R56">
-        <v>1</v>
-      </c>
-      <c r="S56" t="str">
+        <v>0</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>1</v>
+      </c>
+      <c r="U56" t="str">
         <f>TextData!B55</f>
         <v>ダメージ威力アップ</v>
       </c>
     </row>
-    <row r="57" spans="1:19">
+    <row r="57" spans="1:21">
       <c r="A57">
         <v>2320</v>
       </c>
@@ -5088,32 +5432,32 @@
         <v>バフ解除</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E57">
         <v>0</v>
       </c>
-      <c r="F57" t="str">
-        <f>INDEX(Define!B:B,MATCH(E57,Define!A:A))</f>
+      <c r="F57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57" t="str">
+        <f>INDEX(Define!B:B,MATCH(G57,Define!A:A))</f>
         <v>なし</v>
       </c>
-      <c r="G57">
-        <v>1</v>
-      </c>
-      <c r="H57" t="s">
-        <v>18</v>
-      </c>
       <c r="I57">
-        <v>0</v>
-      </c>
-      <c r="J57">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J57" t="s">
+        <v>20</v>
       </c>
       <c r="K57">
         <v>0</v>
       </c>
       <c r="L57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57">
         <v>0</v>
@@ -5131,14 +5475,20 @@
         <v>0</v>
       </c>
       <c r="R57">
-        <v>1</v>
-      </c>
-      <c r="S57" t="str">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>1</v>
+      </c>
+      <c r="U57" t="str">
         <f>TextData!B56</f>
         <v>バフ解除</v>
       </c>
     </row>
-    <row r="58" spans="1:19">
+    <row r="58" spans="1:21">
       <c r="A58">
         <v>2330</v>
       </c>
@@ -5149,27 +5499,27 @@
         <f>INDEX(TextData!B:B,MATCH(B58,TextData!A:A))</f>
         <v>貫通</v>
       </c>
-      <c r="D58" t="s">
-        <v>55</v>
+      <c r="D58">
+        <v>0</v>
       </c>
       <c r="E58">
-        <v>1</v>
-      </c>
-      <c r="F58" t="str">
-        <f>INDEX(Define!B:B,MATCH(E58,Define!A:A))</f>
+        <v>56</v>
+      </c>
+      <c r="F58" t="s">
+        <v>57</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+      <c r="H58" t="str">
+        <f>INDEX(Define!B:B,MATCH(G58,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G58">
-        <v>1</v>
-      </c>
-      <c r="H58" t="s">
-        <v>18</v>
-      </c>
       <c r="I58">
-        <v>0</v>
-      </c>
-      <c r="J58">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J58" t="s">
+        <v>20</v>
       </c>
       <c r="K58">
         <v>0</v>
@@ -5181,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58">
         <v>0</v>
@@ -5193,14 +5543,20 @@
         <v>0</v>
       </c>
       <c r="R58">
-        <v>1</v>
-      </c>
-      <c r="S58" t="str">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>1</v>
+      </c>
+      <c r="U58" t="str">
         <f>TextData!B57</f>
         <v>貫通</v>
       </c>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:21">
       <c r="A59">
         <v>2340</v>
       </c>
@@ -5211,27 +5567,27 @@
         <f>INDEX(TextData!B:B,MATCH(B59,TextData!A:A))</f>
         <v>対象列化</v>
       </c>
-      <c r="D59" t="s">
-        <v>56</v>
+      <c r="D59">
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>1</v>
-      </c>
-      <c r="F59" t="str">
-        <f>INDEX(Define!B:B,MATCH(E59,Define!A:A))</f>
+        <v>66</v>
+      </c>
+      <c r="F59" t="s">
+        <v>58</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59" t="str">
+        <f>INDEX(Define!B:B,MATCH(G59,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G59">
-        <v>1</v>
-      </c>
-      <c r="H59" t="s">
-        <v>18</v>
-      </c>
       <c r="I59">
-        <v>0</v>
-      </c>
-      <c r="J59">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J59" t="s">
+        <v>20</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -5243,7 +5599,7 @@
         <v>0</v>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -5255,14 +5611,20 @@
         <v>0</v>
       </c>
       <c r="R59">
-        <v>1</v>
-      </c>
-      <c r="S59" t="str">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>1</v>
+      </c>
+      <c r="U59" t="str">
         <f>TextData!B58</f>
         <v>対象列化</v>
       </c>
     </row>
-    <row r="60" spans="1:19">
+    <row r="60" spans="1:21">
       <c r="A60">
         <v>2341</v>
       </c>
@@ -5273,27 +5635,27 @@
         <f>INDEX(TextData!B:B,MATCH(B60,TextData!A:A))</f>
         <v>対象全体化</v>
       </c>
-      <c r="D60" t="s">
-        <v>57</v>
+      <c r="D60">
+        <v>0</v>
       </c>
       <c r="E60">
-        <v>1</v>
-      </c>
-      <c r="F60" t="str">
-        <f>INDEX(Define!B:B,MATCH(E60,Define!A:A))</f>
+        <v>66</v>
+      </c>
+      <c r="F60" t="s">
+        <v>59</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60" t="str">
+        <f>INDEX(Define!B:B,MATCH(G60,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G60">
-        <v>1</v>
-      </c>
-      <c r="H60" t="s">
-        <v>18</v>
-      </c>
       <c r="I60">
-        <v>0</v>
-      </c>
-      <c r="J60">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J60" t="s">
+        <v>20</v>
       </c>
       <c r="K60">
         <v>0</v>
@@ -5305,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -5317,14 +5679,20 @@
         <v>0</v>
       </c>
       <c r="R60">
-        <v>1</v>
-      </c>
-      <c r="S60" t="str">
+        <v>0</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <v>1</v>
+      </c>
+      <c r="U60" t="str">
         <f>TextData!B59</f>
         <v>対象全体化</v>
       </c>
     </row>
-    <row r="61" spans="1:19">
+    <row r="61" spans="1:21">
       <c r="A61">
         <v>2350</v>
       </c>
@@ -5335,27 +5703,27 @@
         <f>INDEX(TextData!B:B,MATCH(B61,TextData!A:A))</f>
         <v>聖棺</v>
       </c>
-      <c r="D61" t="s">
-        <v>58</v>
+      <c r="D61">
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>1</v>
-      </c>
-      <c r="F61" t="str">
-        <f>INDEX(Define!B:B,MATCH(E61,Define!A:A))</f>
+        <v>0</v>
+      </c>
+      <c r="F61" t="s">
+        <v>60</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61" t="str">
+        <f>INDEX(Define!B:B,MATCH(G61,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G61">
-        <v>1</v>
-      </c>
-      <c r="H61" t="s">
-        <v>18</v>
-      </c>
       <c r="I61">
-        <v>0</v>
-      </c>
-      <c r="J61">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J61" t="s">
+        <v>20</v>
       </c>
       <c r="K61">
         <v>0</v>
@@ -5367,7 +5735,7 @@
         <v>0</v>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -5379,14 +5747,20 @@
         <v>0</v>
       </c>
       <c r="R61">
-        <v>1</v>
-      </c>
-      <c r="S61" t="str">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="T61">
+        <v>1</v>
+      </c>
+      <c r="U61" t="str">
         <f>TextData!B60</f>
         <v>聖棺</v>
       </c>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" spans="1:21">
       <c r="A62">
         <v>2360</v>
       </c>
@@ -5397,27 +5771,27 @@
         <f>INDEX(TextData!B:B,MATCH(B62,TextData!A:A))</f>
         <v>追加ダメージ</v>
       </c>
-      <c r="D62" t="s">
-        <v>59</v>
+      <c r="D62">
+        <v>0</v>
       </c>
       <c r="E62">
-        <v>1</v>
-      </c>
-      <c r="F62" t="str">
-        <f>INDEX(Define!B:B,MATCH(E62,Define!A:A))</f>
+        <v>13</v>
+      </c>
+      <c r="F62" t="s">
+        <v>61</v>
+      </c>
+      <c r="G62">
+        <v>1</v>
+      </c>
+      <c r="H62" t="str">
+        <f>INDEX(Define!B:B,MATCH(G62,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G62">
-        <v>1</v>
-      </c>
-      <c r="H62" t="s">
-        <v>18</v>
-      </c>
       <c r="I62">
-        <v>0</v>
-      </c>
-      <c r="J62">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J62" t="s">
+        <v>20</v>
       </c>
       <c r="K62">
         <v>0</v>
@@ -5429,7 +5803,7 @@
         <v>0</v>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -5441,14 +5815,20 @@
         <v>0</v>
       </c>
       <c r="R62">
-        <v>1</v>
-      </c>
-      <c r="S62" t="str">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>0</v>
+      </c>
+      <c r="T62">
+        <v>1</v>
+      </c>
+      <c r="U62" t="str">
         <f>TextData!B61</f>
         <v>追加ダメージ</v>
       </c>
     </row>
-    <row r="63" spans="1:19">
+    <row r="63" spans="1:21">
       <c r="A63">
         <v>2370</v>
       </c>
@@ -5459,27 +5839,27 @@
         <f>INDEX(TextData!B:B,MATCH(B63,TextData!A:A))</f>
         <v>追加効果</v>
       </c>
-      <c r="D63" t="s">
-        <v>59</v>
+      <c r="D63">
+        <v>0</v>
       </c>
       <c r="E63">
-        <v>1</v>
-      </c>
-      <c r="F63" t="str">
-        <f>INDEX(Define!B:B,MATCH(E63,Define!A:A))</f>
+        <v>56</v>
+      </c>
+      <c r="F63" t="s">
+        <v>61</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63" t="str">
+        <f>INDEX(Define!B:B,MATCH(G63,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G63">
-        <v>1</v>
-      </c>
-      <c r="H63" t="s">
-        <v>18</v>
-      </c>
       <c r="I63">
-        <v>0</v>
-      </c>
-      <c r="J63">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J63" t="s">
+        <v>20</v>
       </c>
       <c r="K63">
         <v>0</v>
@@ -5491,7 +5871,7 @@
         <v>0</v>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -5503,14 +5883,20 @@
         <v>0</v>
       </c>
       <c r="R63">
-        <v>1</v>
-      </c>
-      <c r="S63" t="str">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63">
+        <v>1</v>
+      </c>
+      <c r="U63" t="str">
         <f>TextData!B62</f>
         <v>追加効果</v>
       </c>
     </row>
-    <row r="64" spans="1:19">
+    <row r="64" spans="1:21">
       <c r="A64">
         <v>2380</v>
       </c>
@@ -5521,27 +5907,27 @@
         <f>INDEX(TextData!B:B,MATCH(B64,TextData!A:A))</f>
         <v>透明</v>
       </c>
-      <c r="D64" t="s">
-        <v>60</v>
+      <c r="D64">
+        <v>0</v>
       </c>
       <c r="E64">
-        <v>1</v>
-      </c>
-      <c r="F64" t="str">
-        <f>INDEX(Define!B:B,MATCH(E64,Define!A:A))</f>
+        <v>0</v>
+      </c>
+      <c r="F64" t="s">
+        <v>62</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+      <c r="H64" t="str">
+        <f>INDEX(Define!B:B,MATCH(G64,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G64">
-        <v>1</v>
-      </c>
-      <c r="H64" t="s">
-        <v>18</v>
-      </c>
       <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J64" t="s">
+        <v>20</v>
       </c>
       <c r="K64">
         <v>0</v>
@@ -5553,7 +5939,7 @@
         <v>0</v>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -5565,14 +5951,20 @@
         <v>0</v>
       </c>
       <c r="R64">
-        <v>1</v>
-      </c>
-      <c r="S64" t="str">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>1</v>
+      </c>
+      <c r="U64" t="str">
         <f>TextData!B63</f>
         <v>透明</v>
       </c>
     </row>
-    <row r="65" spans="1:19">
+    <row r="65" spans="1:21">
       <c r="A65">
         <v>2390</v>
       </c>
@@ -5583,36 +5975,36 @@
         <f>INDEX(TextData!B:B,MATCH(B65,TextData!A:A))</f>
         <v>沈黙</v>
       </c>
-      <c r="D65" t="s">
-        <v>61</v>
+      <c r="D65">
+        <v>36</v>
       </c>
       <c r="E65">
-        <v>1</v>
-      </c>
-      <c r="F65" t="str">
-        <f>INDEX(Define!B:B,MATCH(E65,Define!A:A))</f>
+        <v>3</v>
+      </c>
+      <c r="F65" t="s">
+        <v>63</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+      <c r="H65" t="str">
+        <f>INDEX(Define!B:B,MATCH(G65,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G65">
-        <v>1</v>
-      </c>
-      <c r="H65" t="s">
-        <v>18</v>
-      </c>
       <c r="I65">
-        <v>0</v>
-      </c>
-      <c r="J65">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J65" t="s">
+        <v>20</v>
       </c>
       <c r="K65">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N65">
         <v>0</v>
@@ -5621,20 +6013,26 @@
         <v>1</v>
       </c>
       <c r="P65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65">
         <v>1</v>
       </c>
-      <c r="S65" t="str">
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>1</v>
+      </c>
+      <c r="U65" t="str">
         <f>TextData!B64</f>
         <v>沈黙</v>
       </c>
     </row>
-    <row r="66" spans="1:19">
+    <row r="66" spans="1:21">
       <c r="A66">
         <v>2400</v>
       </c>
@@ -5645,36 +6043,36 @@
         <f>INDEX(TextData!B:B,MATCH(B66,TextData!A:A))</f>
         <v>不治</v>
       </c>
-      <c r="D66" t="s">
-        <v>62</v>
+      <c r="D66">
+        <v>0</v>
       </c>
       <c r="E66">
-        <v>1</v>
-      </c>
-      <c r="F66" t="str">
-        <f>INDEX(Define!B:B,MATCH(E66,Define!A:A))</f>
+        <v>0</v>
+      </c>
+      <c r="F66" t="s">
+        <v>64</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66" t="str">
+        <f>INDEX(Define!B:B,MATCH(G66,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G66">
-        <v>1</v>
-      </c>
-      <c r="H66" t="s">
-        <v>18</v>
-      </c>
       <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J66" t="s">
+        <v>20</v>
       </c>
       <c r="K66">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N66">
         <v>0</v>
@@ -5683,20 +6081,26 @@
         <v>1</v>
       </c>
       <c r="P66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66">
         <v>1</v>
       </c>
-      <c r="S66" t="str">
+      <c r="S66">
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <v>1</v>
+      </c>
+      <c r="U66" t="str">
         <f>TextData!B65</f>
         <v>不治</v>
       </c>
     </row>
-    <row r="67" spans="1:19">
+    <row r="67" spans="1:21">
       <c r="A67">
         <v>2410</v>
       </c>
@@ -5707,27 +6111,27 @@
         <f>INDEX(TextData!B:B,MATCH(B67,TextData!A:A))</f>
         <v>シールド</v>
       </c>
-      <c r="D67" t="s">
-        <v>63</v>
+      <c r="D67">
+        <v>0</v>
       </c>
       <c r="E67">
-        <v>1</v>
-      </c>
-      <c r="F67" t="str">
-        <f>INDEX(Define!B:B,MATCH(E67,Define!A:A))</f>
+        <v>0</v>
+      </c>
+      <c r="F67" t="s">
+        <v>65</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67" t="str">
+        <f>INDEX(Define!B:B,MATCH(G67,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G67">
-        <v>1</v>
-      </c>
-      <c r="H67" t="s">
-        <v>18</v>
-      </c>
       <c r="I67">
-        <v>0</v>
-      </c>
-      <c r="J67">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J67" t="s">
+        <v>20</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -5753,12 +6157,18 @@
       <c r="R67">
         <v>1</v>
       </c>
-      <c r="S67" t="str">
+      <c r="S67">
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <v>1</v>
+      </c>
+      <c r="U67" t="str">
         <f>TextData!B66</f>
         <v>シールド</v>
       </c>
     </row>
-    <row r="68" spans="1:19">
+    <row r="68" spans="1:21">
       <c r="A68">
         <v>2420</v>
       </c>
@@ -5769,27 +6179,27 @@
         <f>INDEX(TextData!B:B,MATCH(B68,TextData!A:A))</f>
         <v>フォロー</v>
       </c>
-      <c r="D68" t="s">
-        <v>64</v>
+      <c r="D68">
+        <v>0</v>
       </c>
       <c r="E68">
-        <v>1</v>
-      </c>
-      <c r="F68" t="str">
-        <f>INDEX(Define!B:B,MATCH(E68,Define!A:A))</f>
+        <v>0</v>
+      </c>
+      <c r="F68" t="s">
+        <v>66</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+      <c r="H68" t="str">
+        <f>INDEX(Define!B:B,MATCH(G68,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G68">
-        <v>1</v>
-      </c>
-      <c r="H68" t="s">
-        <v>18</v>
-      </c>
       <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J68" t="s">
+        <v>20</v>
       </c>
       <c r="K68">
         <v>0</v>
@@ -5815,12 +6225,18 @@
       <c r="R68">
         <v>1</v>
       </c>
-      <c r="S68" t="str">
+      <c r="S68">
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <v>1</v>
+      </c>
+      <c r="U68" t="str">
         <f>TextData!B67</f>
         <v>フォロー</v>
       </c>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:21">
       <c r="A69">
         <v>2430</v>
       </c>
@@ -5831,27 +6247,27 @@
         <f>INDEX(TextData!B:B,MATCH(B69,TextData!A:A))</f>
         <v>かばう</v>
       </c>
-      <c r="D69" t="s">
-        <v>65</v>
+      <c r="D69">
+        <v>0</v>
       </c>
       <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69" t="s">
+        <v>67</v>
+      </c>
+      <c r="G69">
         <v>4</v>
       </c>
-      <c r="F69" t="str">
-        <f>INDEX(Define!B:B,MATCH(E69,Define!A:A))</f>
+      <c r="H69" t="str">
+        <f>INDEX(Define!B:B,MATCH(G69,Define!A:A))</f>
         <v>効果発揮回数</v>
       </c>
-      <c r="G69">
-        <v>1</v>
-      </c>
-      <c r="H69" t="s">
-        <v>18</v>
-      </c>
       <c r="I69">
-        <v>0</v>
-      </c>
-      <c r="J69">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J69" t="s">
+        <v>20</v>
       </c>
       <c r="K69">
         <v>0</v>
@@ -5872,17 +6288,23 @@
         <v>1</v>
       </c>
       <c r="Q69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69">
         <v>1</v>
       </c>
-      <c r="S69" t="str">
+      <c r="S69">
+        <v>1</v>
+      </c>
+      <c r="T69">
+        <v>1</v>
+      </c>
+      <c r="U69" t="str">
         <f>TextData!B68</f>
         <v>かばう</v>
       </c>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:21">
       <c r="A70">
         <v>2440</v>
       </c>
@@ -5893,27 +6315,27 @@
         <f>INDEX(TextData!B:B,MATCH(B70,TextData!A:A))</f>
         <v>Ap消費半減</v>
       </c>
-      <c r="D70" t="s">
-        <v>19</v>
+      <c r="D70">
+        <v>0</v>
       </c>
       <c r="E70">
-        <v>1</v>
-      </c>
-      <c r="F70" t="str">
-        <f>INDEX(Define!B:B,MATCH(E70,Define!A:A))</f>
+        <v>0</v>
+      </c>
+      <c r="F70" t="s">
+        <v>21</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="H70" t="str">
+        <f>INDEX(Define!B:B,MATCH(G70,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G70">
-        <v>1</v>
-      </c>
-      <c r="H70" t="s">
-        <v>18</v>
-      </c>
       <c r="I70">
-        <v>0</v>
-      </c>
-      <c r="J70">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J70" t="s">
+        <v>20</v>
       </c>
       <c r="K70">
         <v>0</v>
@@ -5939,12 +6361,18 @@
       <c r="R70">
         <v>1</v>
       </c>
-      <c r="S70" t="str">
+      <c r="S70">
+        <v>0</v>
+      </c>
+      <c r="T70">
+        <v>1</v>
+      </c>
+      <c r="U70" t="str">
         <f>TextData!B69</f>
         <v>Ap消費半減</v>
       </c>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:21">
       <c r="A71">
         <v>2450</v>
       </c>
@@ -5955,27 +6383,27 @@
         <f>INDEX(TextData!B:B,MATCH(B71,TextData!A:A))</f>
         <v>不死</v>
       </c>
-      <c r="D71" t="s">
-        <v>53</v>
+      <c r="D71">
+        <v>0</v>
       </c>
       <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71" t="s">
+        <v>55</v>
+      </c>
+      <c r="G71">
         <v>4</v>
       </c>
-      <c r="F71" t="str">
-        <f>INDEX(Define!B:B,MATCH(E71,Define!A:A))</f>
+      <c r="H71" t="str">
+        <f>INDEX(Define!B:B,MATCH(G71,Define!A:A))</f>
         <v>効果発揮回数</v>
       </c>
-      <c r="G71">
-        <v>1</v>
-      </c>
-      <c r="H71" t="s">
-        <v>18</v>
-      </c>
       <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="J71">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J71" t="s">
+        <v>20</v>
       </c>
       <c r="K71">
         <v>0</v>
@@ -6001,12 +6429,18 @@
       <c r="R71">
         <v>1</v>
       </c>
-      <c r="S71" t="str">
+      <c r="S71">
+        <v>0</v>
+      </c>
+      <c r="T71">
+        <v>1</v>
+      </c>
+      <c r="U71" t="str">
         <f>TextData!B70</f>
         <v>不死</v>
       </c>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:21">
       <c r="A72">
         <v>2460</v>
       </c>
@@ -6017,27 +6451,27 @@
         <f>INDEX(TextData!B:B,MATCH(B72,TextData!A:A))</f>
         <v>Hp回復効果アップ</v>
       </c>
-      <c r="D72" t="s">
-        <v>66</v>
+      <c r="D72">
+        <v>0</v>
       </c>
       <c r="E72">
-        <v>1</v>
-      </c>
-      <c r="F72" t="str">
-        <f>INDEX(Define!B:B,MATCH(E72,Define!A:A))</f>
+        <v>0</v>
+      </c>
+      <c r="F72" t="s">
+        <v>68</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+      <c r="H72" t="str">
+        <f>INDEX(Define!B:B,MATCH(G72,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G72">
-        <v>1</v>
-      </c>
-      <c r="H72" t="s">
-        <v>18</v>
-      </c>
       <c r="I72">
-        <v>0</v>
-      </c>
-      <c r="J72">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J72" t="s">
+        <v>20</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -6063,12 +6497,18 @@
       <c r="R72">
         <v>1</v>
       </c>
-      <c r="S72" t="str">
+      <c r="S72">
+        <v>0</v>
+      </c>
+      <c r="T72">
+        <v>1</v>
+      </c>
+      <c r="U72" t="str">
         <f>TextData!B71</f>
         <v>Hp回復効果アップ</v>
       </c>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:21">
       <c r="A73">
         <v>2470</v>
       </c>
@@ -6079,27 +6519,27 @@
         <f>INDEX(TextData!B:B,MATCH(B73,TextData!A:A))</f>
         <v>呪詛</v>
       </c>
-      <c r="D73" t="s">
-        <v>67</v>
+      <c r="D73">
+        <v>0</v>
       </c>
       <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73" t="s">
+        <v>69</v>
+      </c>
+      <c r="G73">
         <v>4</v>
       </c>
-      <c r="F73" t="str">
-        <f>INDEX(Define!B:B,MATCH(E73,Define!A:A))</f>
+      <c r="H73" t="str">
+        <f>INDEX(Define!B:B,MATCH(G73,Define!A:A))</f>
         <v>効果発揮回数</v>
       </c>
-      <c r="G73">
-        <v>1</v>
-      </c>
-      <c r="H73" t="s">
-        <v>18</v>
-      </c>
       <c r="I73">
-        <v>0</v>
-      </c>
-      <c r="J73">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J73" t="s">
+        <v>20</v>
       </c>
       <c r="K73">
         <v>0</v>
@@ -6125,12 +6565,18 @@
       <c r="R73">
         <v>1</v>
       </c>
-      <c r="S73" t="str">
+      <c r="S73">
+        <v>0</v>
+      </c>
+      <c r="T73">
+        <v>1</v>
+      </c>
+      <c r="U73" t="str">
         <f>TextData!B72</f>
         <v>呪詛</v>
       </c>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:21">
       <c r="A74">
         <v>3010</v>
       </c>
@@ -6141,33 +6587,33 @@
         <f>INDEX(TextData!B:B,MATCH(B74,TextData!A:A))</f>
         <v>チャージ</v>
       </c>
-      <c r="D74" t="s">
-        <v>59</v>
+      <c r="D74">
+        <v>0</v>
       </c>
       <c r="E74">
-        <v>1</v>
-      </c>
-      <c r="F74" t="str">
-        <f>INDEX(Define!B:B,MATCH(E74,Define!A:A))</f>
+        <v>0</v>
+      </c>
+      <c r="F74" t="s">
+        <v>61</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+      <c r="H74" t="str">
+        <f>INDEX(Define!B:B,MATCH(G74,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G74">
-        <v>1</v>
-      </c>
-      <c r="H74" t="s">
-        <v>18</v>
-      </c>
       <c r="I74">
-        <v>0</v>
-      </c>
-      <c r="J74">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J74" t="s">
+        <v>20</v>
       </c>
       <c r="K74">
         <v>0</v>
       </c>
       <c r="L74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M74">
         <v>0</v>
@@ -6185,14 +6631,20 @@
         <v>0</v>
       </c>
       <c r="R74">
-        <v>1</v>
-      </c>
-      <c r="S74" t="str">
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <v>0</v>
+      </c>
+      <c r="T74">
+        <v>1</v>
+      </c>
+      <c r="U74" t="str">
         <f>TextData!B73</f>
         <v>チャージ</v>
       </c>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:21">
       <c r="A75">
         <v>3020</v>
       </c>
@@ -6203,33 +6655,33 @@
         <f>INDEX(TextData!B:B,MATCH(B75,TextData!A:A))</f>
         <v>リンケージ</v>
       </c>
-      <c r="D75" t="s">
-        <v>59</v>
+      <c r="D75">
+        <v>0</v>
       </c>
       <c r="E75">
-        <v>1</v>
-      </c>
-      <c r="F75" t="str">
-        <f>INDEX(Define!B:B,MATCH(E75,Define!A:A))</f>
+        <v>0</v>
+      </c>
+      <c r="F75" t="s">
+        <v>61</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75" t="str">
+        <f>INDEX(Define!B:B,MATCH(G75,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G75">
-        <v>1</v>
-      </c>
-      <c r="H75" t="s">
-        <v>18</v>
-      </c>
       <c r="I75">
-        <v>0</v>
-      </c>
-      <c r="J75">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J75" t="s">
+        <v>20</v>
       </c>
       <c r="K75">
         <v>0</v>
       </c>
       <c r="L75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M75">
         <v>0</v>
@@ -6247,14 +6699,20 @@
         <v>0</v>
       </c>
       <c r="R75">
-        <v>1</v>
-      </c>
-      <c r="S75" t="str">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <v>1</v>
+      </c>
+      <c r="U75" t="str">
         <f>TextData!B74</f>
         <v>リンケージ</v>
       </c>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" spans="1:21">
       <c r="A76">
         <v>9999</v>
       </c>
@@ -6265,33 +6723,33 @@
         <f>INDEX(TextData!B:B,MATCH(B76,TextData!A:A))</f>
         <v>テスト用</v>
       </c>
-      <c r="D76" t="s">
-        <v>59</v>
+      <c r="D76">
+        <v>0</v>
       </c>
       <c r="E76">
-        <v>1</v>
-      </c>
-      <c r="F76" t="str">
-        <f>INDEX(Define!B:B,MATCH(E76,Define!A:A))</f>
+        <v>0</v>
+      </c>
+      <c r="F76" t="s">
+        <v>61</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76" t="str">
+        <f>INDEX(Define!B:B,MATCH(G76,Define!A:A))</f>
         <v>ターン数</v>
       </c>
-      <c r="G76">
-        <v>1</v>
-      </c>
-      <c r="H76" t="s">
-        <v>18</v>
-      </c>
       <c r="I76">
-        <v>0</v>
-      </c>
-      <c r="J76">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="J76" t="s">
+        <v>20</v>
       </c>
       <c r="K76">
         <v>0</v>
       </c>
       <c r="L76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76">
         <v>0</v>
@@ -6309,9 +6767,15 @@
         <v>0</v>
       </c>
       <c r="R76">
-        <v>1</v>
-      </c>
-      <c r="S76" t="str">
+        <v>0</v>
+      </c>
+      <c r="S76">
+        <v>0</v>
+      </c>
+      <c r="T76">
+        <v>1</v>
+      </c>
+      <c r="U76" t="str">
         <f>TextData!B75</f>
         <v>テスト用</v>
       </c>
@@ -6337,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -6348,10 +6812,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -6359,10 +6823,10 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6370,10 +6834,10 @@
         <v>201</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6381,10 +6845,10 @@
         <v>202</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6392,10 +6856,10 @@
         <v>203</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -6403,10 +6867,10 @@
         <v>204</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -6414,10 +6878,10 @@
         <v>205</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -6425,10 +6889,10 @@
         <v>1010</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -6436,10 +6900,10 @@
         <v>1011</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6447,10 +6911,10 @@
         <v>1020</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -6458,10 +6922,10 @@
         <v>1030</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -6469,10 +6933,10 @@
         <v>1040</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -6480,10 +6944,10 @@
         <v>1041</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -6491,10 +6955,10 @@
         <v>1043</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -6502,10 +6966,10 @@
         <v>1044</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6513,10 +6977,10 @@
         <v>1050</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -6524,10 +6988,10 @@
         <v>1051</v>
       </c>
       <c r="B18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -6535,10 +6999,10 @@
         <v>1052</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -6546,10 +7010,10 @@
         <v>1060</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -6557,10 +7021,10 @@
         <v>1070</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -6568,10 +7032,10 @@
         <v>1074</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -6579,10 +7043,10 @@
         <v>1080</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -6590,10 +7054,10 @@
         <v>1081</v>
       </c>
       <c r="B24" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -6601,10 +7065,10 @@
         <v>1082</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -6612,10 +7076,10 @@
         <v>1090</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -6623,10 +7087,10 @@
         <v>1091</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -6634,10 +7098,10 @@
         <v>1092</v>
       </c>
       <c r="B28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -6645,10 +7109,10 @@
         <v>1100</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C29" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -6656,10 +7120,10 @@
         <v>1101</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -6667,10 +7131,10 @@
         <v>2010</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -6678,10 +7142,10 @@
         <v>2020</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -6689,10 +7153,10 @@
         <v>2030</v>
       </c>
       <c r="B33" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -6700,10 +7164,10 @@
         <v>2031</v>
       </c>
       <c r="B34" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -6711,10 +7175,10 @@
         <v>2032</v>
       </c>
       <c r="B35" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -6722,10 +7186,10 @@
         <v>2040</v>
       </c>
       <c r="B36" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C36" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -6733,10 +7197,10 @@
         <v>2050</v>
       </c>
       <c r="B37" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C37" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -6744,10 +7208,10 @@
         <v>2060</v>
       </c>
       <c r="B38" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -6755,10 +7219,10 @@
         <v>2070</v>
       </c>
       <c r="B39" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C39" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -6766,10 +7230,10 @@
         <v>2080</v>
       </c>
       <c r="B40" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C40" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -6777,10 +7241,10 @@
         <v>2090</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C41" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -6788,10 +7252,10 @@
         <v>2120</v>
       </c>
       <c r="B42" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C42" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -6799,10 +7263,10 @@
         <v>2130</v>
       </c>
       <c r="B43" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C43" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -6810,10 +7274,10 @@
         <v>2140</v>
       </c>
       <c r="B44" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C44" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -6821,10 +7285,10 @@
         <v>2150</v>
       </c>
       <c r="B45" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C45" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -6832,10 +7296,10 @@
         <v>2180</v>
       </c>
       <c r="B46" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C46" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -6843,10 +7307,10 @@
         <v>2190</v>
       </c>
       <c r="B47" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C47" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -6854,10 +7318,10 @@
         <v>2210</v>
       </c>
       <c r="B48" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C48" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -6865,10 +7329,10 @@
         <v>2220</v>
       </c>
       <c r="B49" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C49" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -6876,10 +7340,10 @@
         <v>2230</v>
       </c>
       <c r="B50" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C50" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -6887,10 +7351,10 @@
         <v>2240</v>
       </c>
       <c r="B51" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C51" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -6898,10 +7362,10 @@
         <v>2250</v>
       </c>
       <c r="B52" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C52" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -6909,10 +7373,10 @@
         <v>2270</v>
       </c>
       <c r="B53" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C53" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -6920,10 +7384,10 @@
         <v>2280</v>
       </c>
       <c r="B54" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C54" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -6931,10 +7395,10 @@
         <v>2290</v>
       </c>
       <c r="B55" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C55" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -6942,10 +7406,10 @@
         <v>2320</v>
       </c>
       <c r="B56" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C56" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -6953,10 +7417,10 @@
         <v>2330</v>
       </c>
       <c r="B57" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C57" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -6964,10 +7428,10 @@
         <v>2340</v>
       </c>
       <c r="B58" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C58" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -6975,10 +7439,10 @@
         <v>2341</v>
       </c>
       <c r="B59" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C59" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -6986,10 +7450,10 @@
         <v>2350</v>
       </c>
       <c r="B60" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C60" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -6997,10 +7461,10 @@
         <v>2360</v>
       </c>
       <c r="B61" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C61" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -7008,10 +7472,10 @@
         <v>2370</v>
       </c>
       <c r="B62" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C62" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -7019,10 +7483,10 @@
         <v>2380</v>
       </c>
       <c r="B63" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C63" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -7030,10 +7494,10 @@
         <v>2390</v>
       </c>
       <c r="B64" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C64" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -7041,10 +7505,10 @@
         <v>2400</v>
       </c>
       <c r="B65" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C65" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -7052,10 +7516,10 @@
         <v>2410</v>
       </c>
       <c r="B66" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C66" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -7063,10 +7527,10 @@
         <v>2420</v>
       </c>
       <c r="B67" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C67" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -7074,10 +7538,10 @@
         <v>2430</v>
       </c>
       <c r="B68" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C68" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -7085,10 +7549,10 @@
         <v>2440</v>
       </c>
       <c r="B69" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C69" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -7096,10 +7560,10 @@
         <v>2450</v>
       </c>
       <c r="B70" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C70" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -7107,10 +7571,10 @@
         <v>2460</v>
       </c>
       <c r="B71" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C71" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -7118,10 +7582,10 @@
         <v>2470</v>
       </c>
       <c r="B72" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C72" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -7129,10 +7593,10 @@
         <v>3010</v>
       </c>
       <c r="B73" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C73" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="74" spans="1:3">
@@ -7140,10 +7604,10 @@
         <v>3020</v>
       </c>
       <c r="B74" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C74" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="75" spans="1:3">
@@ -7151,10 +7615,10 @@
         <v>9999</v>
       </c>
       <c r="B75" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C75" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -7171,7 +7635,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -7179,7 +7643,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7187,7 +7651,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7195,7 +7659,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7203,7 +7667,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -7211,7 +7675,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -7219,7 +7683,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -670,8 +670,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -683,7 +683,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -692,88 +692,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -795,17 +713,52 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -819,10 +772,57 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -835,7 +835,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -847,7 +847,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -859,7 +871,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -871,31 +925,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -907,85 +943,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -997,7 +967,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1015,7 +985,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1045,45 +1045,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -1107,11 +1068,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1126,6 +1108,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1134,145 +1134,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -6155,7 +6155,7 @@
         <v>0</v>
       </c>
       <c r="R67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -6223,7 +6223,7 @@
         <v>0</v>
       </c>
       <c r="R68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -6291,7 +6291,7 @@
         <v>0</v>
       </c>
       <c r="R69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S69">
         <v>1</v>
@@ -6495,7 +6495,7 @@
         <v>0</v>
       </c>
       <c r="R72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72">
         <v>0</v>

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="218">
   <si>
     <t>Id</t>
   </si>
@@ -342,6 +342,12 @@
     <t>会心率\d%アップ</t>
   </si>
   <si>
+    <t>会心率ダウン</t>
+  </si>
+  <si>
+    <t>会心率\d%ダウン</t>
+  </si>
+  <si>
     <t>会心ダメージアップ</t>
   </si>
   <si>
@@ -382,6 +388,9 @@
   </si>
   <si>
     <t>行動後ダメージ</t>
+  </si>
+  <si>
+    <t>火傷</t>
   </si>
   <si>
     <t>暗闇</t>
@@ -669,8 +678,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
@@ -683,9 +692,32 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -698,8 +730,83 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -714,105 +821,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -835,13 +844,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -853,7 +886,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -865,13 +934,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -883,7 +1000,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -895,127 +1018,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1026,6 +1035,26 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1040,6 +1069,30 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1059,15 +1112,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -1083,46 +1127,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1134,7 +1143,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1143,7 +1152,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1152,127 +1161,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1599,7 +1608,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U76"/>
+  <dimension ref="A1:U78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="21.8181818181818" customWidth="1"/>
@@ -3043,14 +3052,14 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="B22">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="C22" t="str">
         <f>INDEX(TextData!B:B,MATCH(B22,TextData!A:A))</f>
-        <v>会心ダメージアップ</v>
+        <v>会心率ダウン</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -3084,16 +3093,16 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -3106,19 +3115,19 @@
       </c>
       <c r="U22" t="str">
         <f>TextData!B22</f>
-        <v>会心ダメージアップ</v>
+        <v>会心率ダウン</v>
       </c>
     </row>
     <row r="23" spans="1:21">
       <c r="A23">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="B23">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="C23" t="str">
         <f>INDEX(TextData!B:B,MATCH(B23,TextData!A:A))</f>
-        <v>命中アップ</v>
+        <v>会心ダメージアップ</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -3127,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -3174,15 +3183,15 @@
       </c>
       <c r="U23" t="str">
         <f>TextData!B23</f>
-        <v>命中アップ</v>
+        <v>会心ダメージアップ</v>
       </c>
     </row>
     <row r="24" spans="1:21">
       <c r="A24">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B24">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C24" t="str">
         <f>INDEX(TextData!B:B,MATCH(B24,TextData!A:A))</f>
@@ -3217,7 +3226,7 @@
         <v>1</v>
       </c>
       <c r="M24">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N24">
         <v>1</v>
@@ -3241,20 +3250,20 @@
         <v>1</v>
       </c>
       <c r="U24" t="str">
-        <f>TextData!B26</f>
-        <v>回避アップ</v>
+        <f>TextData!B24</f>
+        <v>命中アップ</v>
       </c>
     </row>
     <row r="25" spans="1:21">
       <c r="A25">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B25">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C25" t="str">
         <f>INDEX(TextData!B:B,MATCH(B25,TextData!A:A))</f>
-        <v>命中ダウン</v>
+        <v>命中アップ</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -3285,19 +3294,19 @@
         <v>1</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -3310,19 +3319,19 @@
       </c>
       <c r="U25" t="str">
         <f>TextData!B27</f>
-        <v>回避ダウン</v>
+        <v>回避アップ</v>
       </c>
     </row>
     <row r="26" spans="1:21">
       <c r="A26">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="B26">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="C26" t="str">
         <f>INDEX(TextData!B:B,MATCH(B26,TextData!A:A))</f>
-        <v>回避アップ</v>
+        <v>命中ダウン</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -3331,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -3356,16 +3365,16 @@
         <v>0</v>
       </c>
       <c r="N26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -3377,20 +3386,20 @@
         <v>1</v>
       </c>
       <c r="U26" t="str">
-        <f>TextData!B26</f>
-        <v>回避アップ</v>
+        <f>TextData!B28</f>
+        <v>回避ダウン</v>
       </c>
     </row>
     <row r="27" spans="1:21">
       <c r="A27">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B27">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C27" t="str">
         <f>INDEX(TextData!B:B,MATCH(B27,TextData!A:A))</f>
-        <v>回避ダウン</v>
+        <v>回避アップ</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -3430,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -3446,19 +3455,19 @@
       </c>
       <c r="U27" t="str">
         <f>TextData!B27</f>
-        <v>回避ダウン</v>
+        <v>回避アップ</v>
       </c>
     </row>
     <row r="28" spans="1:21">
       <c r="A28">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B28">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C28" t="str">
         <f>INDEX(TextData!B:B,MATCH(B28,TextData!A:A))</f>
-        <v>回避アップ</v>
+        <v>回避ダウン</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -3489,7 +3498,7 @@
         <v>1</v>
       </c>
       <c r="M28">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N28">
         <v>1</v>
@@ -3498,10 +3507,10 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -3514,35 +3523,35 @@
       </c>
       <c r="U28" t="str">
         <f>TextData!B28</f>
-        <v>回避アップ</v>
+        <v>回避ダウン</v>
       </c>
     </row>
     <row r="29" spans="1:21">
       <c r="A29">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="B29">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="C29" t="str">
         <f>INDEX(TextData!B:B,MATCH(B29,TextData!A:A))</f>
-        <v>ダメージカット</v>
+        <v>回避アップ</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G29">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H29" t="str">
         <f>INDEX(Define!B:B,MATCH(G29,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I29">
         <v>1</v>
@@ -3557,7 +3566,7 @@
         <v>1</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>1</v>
@@ -3582,15 +3591,15 @@
       </c>
       <c r="U29" t="str">
         <f>TextData!B29</f>
-        <v>ダメージカット</v>
+        <v>回避アップ</v>
       </c>
     </row>
     <row r="30" spans="1:21">
       <c r="A30">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B30">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C30" t="str">
         <f>INDEX(TextData!B:B,MATCH(B30,TextData!A:A))</f>
@@ -3653,41 +3662,41 @@
         <v>ダメージカット</v>
       </c>
     </row>
-    <row r="31" ht="12" customHeight="1" spans="1:21">
+    <row r="31" spans="1:21">
       <c r="A31">
-        <v>2010</v>
+        <v>1101</v>
       </c>
       <c r="B31">
-        <v>2010</v>
+        <v>1101</v>
       </c>
       <c r="C31" t="str">
         <f>INDEX(TextData!B:B,MATCH(B31,TextData!A:A))</f>
-        <v>毒</v>
+        <v>ダメージカット</v>
       </c>
       <c r="D31">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="F31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H31" t="str">
         <f>INDEX(Define!B:B,MATCH(G31,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I31">
         <v>1</v>
       </c>
       <c r="J31" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="K31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31">
         <v>1</v>
@@ -3696,19 +3705,19 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <v>0</v>
@@ -3718,18 +3727,19 @@
       </c>
       <c r="U31" t="str">
         <f>TextData!B31</f>
-        <v>毒</v>
+        <v>ダメージカット</v>
       </c>
     </row>
     <row r="32" ht="12" customHeight="1" spans="1:21">
       <c r="A32">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B32">
         <v>2010</v>
       </c>
-      <c r="C32" t="s">
-        <v>35</v>
+      <c r="C32" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B32,TextData!A:A))</f>
+        <v>毒</v>
       </c>
       <c r="D32">
         <v>26</v>
@@ -3784,48 +3794,47 @@
         <v>1</v>
       </c>
       <c r="U32" t="str">
-        <f>TextData!B31</f>
+        <f>TextData!B32</f>
         <v>毒</v>
       </c>
     </row>
     <row r="33" ht="12" customHeight="1" spans="1:21">
       <c r="A33">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="B33">
-        <v>2020</v>
-      </c>
-      <c r="C33" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B33,TextData!A:A))</f>
-        <v>暗闇</v>
+        <v>2010</v>
+      </c>
+      <c r="C33" t="s">
+        <v>35</v>
       </c>
       <c r="D33">
+        <v>26</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+      <c r="F33" t="s">
         <v>33</v>
       </c>
-      <c r="E33">
-        <v>2</v>
-      </c>
-      <c r="F33" t="s">
-        <v>30</v>
-      </c>
       <c r="G33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H33" t="str">
         <f>INDEX(Define!B:B,MATCH(G33,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I33">
         <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="M33">
         <v>0</v>
@@ -3853,28 +3862,27 @@
       </c>
       <c r="U33" t="str">
         <f>TextData!B32</f>
-        <v>暗闇</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21">
+        <v>毒</v>
+      </c>
+    </row>
+    <row r="34" ht="12" customHeight="1" spans="1:21">
       <c r="A34">
-        <v>2030</v>
+        <v>2012</v>
       </c>
       <c r="B34">
-        <v>2030</v>
-      </c>
-      <c r="C34" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B34,TextData!A:A))</f>
-        <v>カウンタ</v>
+        <v>2012</v>
+      </c>
+      <c r="C34" t="s">
+        <v>35</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E34">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -3884,13 +3892,13 @@
         <v>ターン数</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34">
         <v>1</v>
@@ -3902,16 +3910,16 @@
         <v>0</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34">
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -3921,47 +3929,47 @@
       </c>
       <c r="U34" t="str">
         <f>TextData!B33</f>
-        <v>カウンタ</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21">
+        <v>火傷</v>
+      </c>
+    </row>
+    <row r="35" ht="12" customHeight="1" spans="1:21">
       <c r="A35">
-        <v>2031</v>
+        <v>2020</v>
       </c>
       <c r="B35">
-        <v>2031</v>
+        <v>2020</v>
       </c>
       <c r="C35" t="str">
         <f>INDEX(TextData!B:B,MATCH(B35,TextData!A:A))</f>
-        <v>CAダメージ</v>
+        <v>暗闇</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E35">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H35" t="str">
         <f>INDEX(Define!B:B,MATCH(G35,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I35">
         <v>1</v>
       </c>
       <c r="J35" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="K35">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -3970,16 +3978,16 @@
         <v>0</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P35">
         <v>0</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -3989,19 +3997,19 @@
       </c>
       <c r="U35" t="str">
         <f>TextData!B34</f>
-        <v>CAダメージ</v>
+        <v>暗闇</v>
       </c>
     </row>
     <row r="36" spans="1:21">
       <c r="A36">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="B36">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="C36" t="str">
         <f>INDEX(TextData!B:B,MATCH(B36,TextData!A:A))</f>
-        <v>CAシェル</v>
+        <v>カウンタ</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -4010,20 +4018,20 @@
         <v>66</v>
       </c>
       <c r="F36" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H36" t="str">
         <f>INDEX(Define!B:B,MATCH(G36,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -4057,28 +4065,28 @@
       </c>
       <c r="U36" t="str">
         <f>TextData!B35</f>
-        <v>CAシェル</v>
+        <v>カウンタ</v>
       </c>
     </row>
     <row r="37" spans="1:21">
       <c r="A37">
-        <v>2040</v>
+        <v>2031</v>
       </c>
       <c r="B37">
-        <v>2040</v>
+        <v>2031</v>
       </c>
       <c r="C37" t="str">
         <f>INDEX(TextData!B:B,MATCH(B37,TextData!A:A))</f>
-        <v>リジェネ</v>
+        <v>CAダメージ</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="F37" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -4125,41 +4133,41 @@
       </c>
       <c r="U37" t="str">
         <f>TextData!B36</f>
-        <v>リジェネ</v>
+        <v>CAダメージ</v>
       </c>
     </row>
     <row r="38" spans="1:21">
       <c r="A38">
-        <v>2050</v>
+        <v>2032</v>
       </c>
       <c r="B38">
-        <v>2050</v>
+        <v>2032</v>
       </c>
       <c r="C38" t="str">
         <f>INDEX(TextData!B:B,MATCH(B38,TextData!A:A))</f>
-        <v>攻撃無効</v>
+        <v>CAシェル</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>226</v>
+        <v>66</v>
       </c>
       <c r="F38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G38">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H38" t="str">
         <f>INDEX(Define!B:B,MATCH(G38,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>なし</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -4193,28 +4201,28 @@
       </c>
       <c r="U38" t="str">
         <f>TextData!B37</f>
-        <v>攻撃無効</v>
+        <v>CAシェル</v>
       </c>
     </row>
     <row r="39" spans="1:21">
       <c r="A39">
-        <v>2060</v>
+        <v>2040</v>
       </c>
       <c r="B39">
-        <v>2060</v>
+        <v>2040</v>
       </c>
       <c r="C39" t="str">
         <f>INDEX(TextData!B:B,MATCH(B39,TextData!A:A))</f>
-        <v>ドレイン</v>
+        <v>リジェネ</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>167</v>
+        <v>46</v>
       </c>
       <c r="F39" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -4261,19 +4269,19 @@
       </c>
       <c r="U39" t="str">
         <f>TextData!B38</f>
-        <v>ドレイン</v>
+        <v>リジェネ</v>
       </c>
     </row>
     <row r="40" spans="1:21">
       <c r="A40">
-        <v>2070</v>
+        <v>2050</v>
       </c>
       <c r="B40">
-        <v>2070</v>
+        <v>2050</v>
       </c>
       <c r="C40" t="str">
         <f>INDEX(TextData!B:B,MATCH(B40,TextData!A:A))</f>
-        <v>状態異常CA</v>
+        <v>攻撃無効</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -4282,20 +4290,20 @@
         <v>226</v>
       </c>
       <c r="F40" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H40" t="str">
         <f>INDEX(Define!B:B,MATCH(G40,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I40">
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -4329,38 +4337,38 @@
       </c>
       <c r="U40" t="str">
         <f>TextData!B39</f>
-        <v>状態異常CA</v>
+        <v>攻撃無効</v>
       </c>
     </row>
     <row r="41" spans="1:21">
       <c r="A41">
-        <v>2080</v>
+        <v>2060</v>
       </c>
       <c r="B41">
-        <v>2080</v>
+        <v>2060</v>
       </c>
       <c r="C41" t="str">
         <f>INDEX(TextData!B:B,MATCH(B41,TextData!A:A))</f>
-        <v>反撃</v>
+        <v>ドレイン</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="F41" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H41" t="str">
         <f>INDEX(Define!B:B,MATCH(G41,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="s">
         <v>20</v>
@@ -4397,35 +4405,35 @@
       </c>
       <c r="U41" t="str">
         <f>TextData!B40</f>
-        <v>反撃</v>
+        <v>ドレイン</v>
       </c>
     </row>
     <row r="42" spans="1:21">
       <c r="A42">
-        <v>2090</v>
+        <v>2070</v>
       </c>
       <c r="B42">
-        <v>2090</v>
+        <v>2070</v>
       </c>
       <c r="C42" t="str">
         <f>INDEX(TextData!B:B,MATCH(B42,TextData!A:A))</f>
-        <v>パッシブ封じ</v>
+        <v>状態異常CA</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>10</v>
+        <v>226</v>
       </c>
       <c r="F42" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H42" t="str">
         <f>INDEX(Define!B:B,MATCH(G42,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -4446,16 +4454,16 @@
         <v>0</v>
       </c>
       <c r="O42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P42">
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -4465,28 +4473,28 @@
       </c>
       <c r="U42" t="str">
         <f>TextData!B41</f>
-        <v>パッシブ封じ</v>
+        <v>状態異常CA</v>
       </c>
     </row>
     <row r="43" spans="1:21">
       <c r="A43">
-        <v>2120</v>
+        <v>2080</v>
       </c>
       <c r="B43">
-        <v>2120</v>
+        <v>2080</v>
       </c>
       <c r="C43" t="str">
         <f>INDEX(TextData!B:B,MATCH(B43,TextData!A:A))</f>
-        <v>デバフ強化</v>
+        <v>反撃</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F43" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G43">
         <v>4</v>
@@ -4496,16 +4504,16 @@
         <v>効果発揮回数</v>
       </c>
       <c r="I43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="K43">
         <v>0</v>
       </c>
       <c r="L43">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -4523,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="R43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -4533,35 +4541,35 @@
       </c>
       <c r="U43" t="str">
         <f>TextData!B42</f>
-        <v>デバフ強化</v>
+        <v>反撃</v>
       </c>
     </row>
     <row r="44" spans="1:21">
       <c r="A44">
-        <v>2130</v>
+        <v>2090</v>
       </c>
       <c r="B44">
-        <v>2130</v>
+        <v>2090</v>
       </c>
       <c r="C44" t="str">
         <f>INDEX(TextData!B:B,MATCH(B44,TextData!A:A))</f>
-        <v>挑発</v>
+        <v>パッシブ封じ</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
+        <v>10</v>
+      </c>
+      <c r="F44" t="s">
+        <v>44</v>
+      </c>
+      <c r="G44">
         <v>4</v>
-      </c>
-      <c r="F44" t="s">
-        <v>47</v>
-      </c>
-      <c r="G44">
-        <v>1</v>
       </c>
       <c r="H44" t="str">
         <f>INDEX(Define!B:B,MATCH(G44,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -4582,13 +4590,13 @@
         <v>0</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44">
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44">
         <v>1</v>
@@ -4601,28 +4609,28 @@
       </c>
       <c r="U44" t="str">
         <f>TextData!B43</f>
-        <v>挑発</v>
+        <v>パッシブ封じ</v>
       </c>
     </row>
     <row r="45" spans="1:21">
       <c r="A45">
-        <v>2140</v>
+        <v>2120</v>
       </c>
       <c r="B45">
-        <v>2140</v>
+        <v>2120</v>
       </c>
       <c r="C45" t="str">
         <f>INDEX(TextData!B:B,MATCH(B45,TextData!A:A))</f>
-        <v>凍結</v>
+        <v>デバフ強化</v>
       </c>
       <c r="D45">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="F45" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G45">
         <v>4</v>
@@ -4635,13 +4643,13 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K45">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="M45">
         <v>0</v>
@@ -4650,13 +4658,13 @@
         <v>0</v>
       </c>
       <c r="O45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P45">
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45">
         <v>1</v>
@@ -4669,41 +4677,41 @@
       </c>
       <c r="U45" t="str">
         <f>TextData!B44</f>
-        <v>凍結</v>
+        <v>デバフ強化</v>
       </c>
     </row>
     <row r="46" spans="1:21">
       <c r="A46">
-        <v>2150</v>
+        <v>2130</v>
       </c>
       <c r="B46">
-        <v>2150</v>
+        <v>2130</v>
       </c>
       <c r="C46" t="str">
         <f>INDEX(TextData!B:B,MATCH(B46,TextData!A:A))</f>
-        <v>スタン</v>
+        <v>挑発</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F46" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" t="str">
         <f>INDEX(Define!B:B,MATCH(G46,Define!A:A))</f>
-        <v>APカウント</v>
+        <v>ターン数</v>
       </c>
       <c r="I46">
         <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="K46">
         <v>0</v>
@@ -4718,13 +4726,13 @@
         <v>0</v>
       </c>
       <c r="O46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P46">
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46">
         <v>1</v>
@@ -4737,28 +4745,28 @@
       </c>
       <c r="U46" t="str">
         <f>TextData!B45</f>
-        <v>スタン</v>
+        <v>挑発</v>
       </c>
     </row>
     <row r="47" spans="1:21">
       <c r="A47">
-        <v>2180</v>
+        <v>2140</v>
       </c>
       <c r="B47">
-        <v>2180</v>
+        <v>2140</v>
       </c>
       <c r="C47" t="str">
         <f>INDEX(TextData!B:B,MATCH(B47,TextData!A:A))</f>
-        <v>状態異常回避</v>
+        <v>凍結</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E47">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="F47" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G47">
         <v>4</v>
@@ -4768,10 +4776,10 @@
         <v>効果発揮回数</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -4786,16 +4794,16 @@
         <v>0</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P47">
         <v>0</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -4805,41 +4813,41 @@
       </c>
       <c r="U47" t="str">
         <f>TextData!B46</f>
-        <v>状態異常回避</v>
+        <v>凍結</v>
       </c>
     </row>
     <row r="48" spans="1:21">
       <c r="A48">
-        <v>2190</v>
+        <v>2150</v>
       </c>
       <c r="B48">
-        <v>2190</v>
+        <v>2150</v>
       </c>
       <c r="C48" t="str">
         <f>INDEX(TextData!B:B,MATCH(B48,TextData!A:A))</f>
-        <v>対象範囲延長</v>
+        <v>スタン</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="F48" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H48" t="str">
         <f>INDEX(Define!B:B,MATCH(G48,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>APカウント</v>
       </c>
       <c r="I48">
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -4854,57 +4862,57 @@
         <v>0</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P48">
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S48">
         <v>0</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" t="str">
         <f>TextData!B47</f>
-        <v>対象範囲延長</v>
+        <v>スタン</v>
       </c>
     </row>
     <row r="49" spans="1:21">
       <c r="A49">
-        <v>2210</v>
+        <v>2180</v>
       </c>
       <c r="B49">
-        <v>2210</v>
+        <v>2180</v>
       </c>
       <c r="C49" t="str">
         <f>INDEX(TextData!B:B,MATCH(B49,TextData!A:A))</f>
-        <v>アフターヒール</v>
+        <v>状態異常回避</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="F49" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H49" t="str">
         <f>INDEX(Define!B:B,MATCH(G49,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="s">
         <v>20</v>
@@ -4941,28 +4949,28 @@
       </c>
       <c r="U49" t="str">
         <f>TextData!B48</f>
-        <v>アフターヒール</v>
+        <v>状態異常回避</v>
       </c>
     </row>
     <row r="50" spans="1:21">
       <c r="A50">
-        <v>2220</v>
+        <v>2190</v>
       </c>
       <c r="B50">
-        <v>2220</v>
+        <v>2190</v>
       </c>
       <c r="C50" t="str">
         <f>INDEX(TextData!B:B,MATCH(B50,TextData!A:A))</f>
-        <v>即死付与</v>
+        <v>対象範囲延長</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>73</v>
       </c>
       <c r="F50" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -4999,45 +5007,45 @@
         <v>0</v>
       </c>
       <c r="R50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50">
         <v>0</v>
       </c>
       <c r="T50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U50" t="str">
         <f>TextData!B49</f>
-        <v>即死付与</v>
+        <v>対象範囲延長</v>
       </c>
     </row>
     <row r="51" spans="1:21">
       <c r="A51">
-        <v>2230</v>
+        <v>2210</v>
       </c>
       <c r="B51">
-        <v>2230</v>
+        <v>2210</v>
       </c>
       <c r="C51" t="str">
         <f>INDEX(TextData!B:B,MATCH(B51,TextData!A:A))</f>
-        <v>同時回復</v>
+        <v>アフターヒール</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="F51" t="s">
         <v>39</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" t="str">
         <f>INDEX(Define!B:B,MATCH(G51,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I51">
         <v>1</v>
@@ -5077,35 +5085,35 @@
       </c>
       <c r="U51" t="str">
         <f>TextData!B50</f>
-        <v>同時回復</v>
+        <v>アフターヒール</v>
       </c>
     </row>
     <row r="52" spans="1:21">
       <c r="A52">
-        <v>2240</v>
+        <v>2220</v>
       </c>
       <c r="B52">
-        <v>2240</v>
+        <v>2220</v>
       </c>
       <c r="C52" t="str">
         <f>INDEX(TextData!B:B,MATCH(B52,TextData!A:A))</f>
-        <v>必中</v>
+        <v>即死付与</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H52" t="str">
         <f>INDEX(Define!B:B,MATCH(G52,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -5135,7 +5143,7 @@
         <v>0</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -5145,19 +5153,19 @@
       </c>
       <c r="U52" t="str">
         <f>TextData!B51</f>
-        <v>必中</v>
+        <v>即死付与</v>
       </c>
     </row>
     <row r="53" spans="1:21">
       <c r="A53">
-        <v>2250</v>
+        <v>2230</v>
       </c>
       <c r="B53">
-        <v>2250</v>
+        <v>2230</v>
       </c>
       <c r="C53" t="str">
         <f>INDEX(TextData!B:B,MATCH(B53,TextData!A:A))</f>
-        <v>アシストヒール</v>
+        <v>同時回復</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -5166,7 +5174,7 @@
         <v>46</v>
       </c>
       <c r="F53" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5176,7 +5184,7 @@
         <v>なし</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="s">
         <v>20</v>
@@ -5213,35 +5221,35 @@
       </c>
       <c r="U53" t="str">
         <f>TextData!B52</f>
-        <v>アシストヒール</v>
+        <v>同時回復</v>
       </c>
     </row>
     <row r="54" spans="1:21">
       <c r="A54">
-        <v>2270</v>
+        <v>2240</v>
       </c>
       <c r="B54">
-        <v>2270</v>
+        <v>2240</v>
       </c>
       <c r="C54" t="str">
         <f>INDEX(TextData!B:B,MATCH(B54,TextData!A:A))</f>
-        <v>アンデッド</v>
+        <v>必中</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="F54" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H54" t="str">
         <f>INDEX(Define!B:B,MATCH(G54,Define!A:A))</f>
-        <v>なし</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -5281,28 +5289,28 @@
       </c>
       <c r="U54" t="str">
         <f>TextData!B53</f>
-        <v>アンデッド</v>
+        <v>必中</v>
       </c>
     </row>
     <row r="55" spans="1:21">
       <c r="A55">
-        <v>2280</v>
+        <v>2250</v>
       </c>
       <c r="B55">
-        <v>2280</v>
+        <v>2250</v>
       </c>
       <c r="C55" t="str">
         <f>INDEX(TextData!B:B,MATCH(B55,TextData!A:A))</f>
-        <v>アクセル</v>
+        <v>アシストヒール</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="F55" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5349,38 +5357,38 @@
       </c>
       <c r="U55" t="str">
         <f>TextData!B54</f>
-        <v>アクセル</v>
+        <v>アシストヒール</v>
       </c>
     </row>
     <row r="56" spans="1:21">
       <c r="A56">
-        <v>2290</v>
+        <v>2270</v>
       </c>
       <c r="B56">
-        <v>2290</v>
+        <v>2270</v>
       </c>
       <c r="C56" t="str">
         <f>INDEX(TextData!B:B,MATCH(B56,TextData!A:A))</f>
-        <v>ダメージ威力アップ</v>
+        <v>アンデッド</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F56" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="str">
         <f>INDEX(Define!B:B,MATCH(G56,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="s">
         <v>20</v>
@@ -5392,7 +5400,7 @@
         <v>1</v>
       </c>
       <c r="M56">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N56">
         <v>0</v>
@@ -5401,7 +5409,7 @@
         <v>0</v>
       </c>
       <c r="P56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -5417,28 +5425,28 @@
       </c>
       <c r="U56" t="str">
         <f>TextData!B55</f>
-        <v>ダメージ威力アップ</v>
+        <v>アンデッド</v>
       </c>
     </row>
     <row r="57" spans="1:21">
       <c r="A57">
-        <v>2320</v>
+        <v>2280</v>
       </c>
       <c r="B57">
-        <v>2320</v>
+        <v>2280</v>
       </c>
       <c r="C57" t="str">
         <f>INDEX(TextData!B:B,MATCH(B57,TextData!A:A))</f>
-        <v>バフ解除</v>
+        <v>アクセル</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>0</v>
-      </c>
-      <c r="F57">
-        <v>1</v>
+        <v>25</v>
+      </c>
+      <c r="F57" t="s">
+        <v>21</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5448,7 +5456,7 @@
         <v>なし</v>
       </c>
       <c r="I57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="s">
         <v>20</v>
@@ -5485,28 +5493,28 @@
       </c>
       <c r="U57" t="str">
         <f>TextData!B56</f>
-        <v>バフ解除</v>
+        <v>アクセル</v>
       </c>
     </row>
     <row r="58" spans="1:21">
       <c r="A58">
-        <v>2330</v>
+        <v>2290</v>
       </c>
       <c r="B58">
-        <v>2330</v>
+        <v>2290</v>
       </c>
       <c r="C58" t="str">
         <f>INDEX(TextData!B:B,MATCH(B58,TextData!A:A))</f>
-        <v>貫通</v>
+        <v>ダメージ威力アップ</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
+        <v>21</v>
+      </c>
+      <c r="F58" t="s">
         <v>56</v>
-      </c>
-      <c r="F58" t="s">
-        <v>57</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -5528,16 +5536,16 @@
         <v>1</v>
       </c>
       <c r="M58">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -5553,35 +5561,35 @@
       </c>
       <c r="U58" t="str">
         <f>TextData!B57</f>
-        <v>貫通</v>
+        <v>ダメージ威力アップ</v>
       </c>
     </row>
     <row r="59" spans="1:21">
       <c r="A59">
-        <v>2340</v>
+        <v>2320</v>
       </c>
       <c r="B59">
-        <v>2340</v>
+        <v>2320</v>
       </c>
       <c r="C59" t="str">
         <f>INDEX(TextData!B:B,MATCH(B59,TextData!A:A))</f>
-        <v>対象列化</v>
+        <v>バフ解除</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>66</v>
-      </c>
-      <c r="F59" t="s">
-        <v>58</v>
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>1</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="str">
         <f>INDEX(Define!B:B,MATCH(G59,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I59">
         <v>1</v>
@@ -5599,7 +5607,7 @@
         <v>0</v>
       </c>
       <c r="N59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -5621,28 +5629,28 @@
       </c>
       <c r="U59" t="str">
         <f>TextData!B58</f>
-        <v>対象列化</v>
+        <v>バフ解除</v>
       </c>
     </row>
     <row r="60" spans="1:21">
       <c r="A60">
-        <v>2341</v>
+        <v>2330</v>
       </c>
       <c r="B60">
-        <v>2341</v>
+        <v>2330</v>
       </c>
       <c r="C60" t="str">
         <f>INDEX(TextData!B:B,MATCH(B60,TextData!A:A))</f>
-        <v>対象全体化</v>
+        <v>貫通</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F60" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -5689,28 +5697,28 @@
       </c>
       <c r="U60" t="str">
         <f>TextData!B59</f>
-        <v>対象全体化</v>
+        <v>貫通</v>
       </c>
     </row>
     <row r="61" spans="1:21">
       <c r="A61">
-        <v>2350</v>
+        <v>2340</v>
       </c>
       <c r="B61">
-        <v>2350</v>
+        <v>2340</v>
       </c>
       <c r="C61" t="str">
         <f>INDEX(TextData!B:B,MATCH(B61,TextData!A:A))</f>
-        <v>聖棺</v>
+        <v>対象列化</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F61" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -5757,28 +5765,28 @@
       </c>
       <c r="U61" t="str">
         <f>TextData!B60</f>
-        <v>聖棺</v>
+        <v>対象列化</v>
       </c>
     </row>
     <row r="62" spans="1:21">
       <c r="A62">
-        <v>2360</v>
+        <v>2341</v>
       </c>
       <c r="B62">
-        <v>2360</v>
+        <v>2341</v>
       </c>
       <c r="C62" t="str">
         <f>INDEX(TextData!B:B,MATCH(B62,TextData!A:A))</f>
-        <v>追加ダメージ</v>
+        <v>対象全体化</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="F62" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -5825,28 +5833,28 @@
       </c>
       <c r="U62" t="str">
         <f>TextData!B61</f>
-        <v>追加ダメージ</v>
+        <v>対象全体化</v>
       </c>
     </row>
     <row r="63" spans="1:21">
       <c r="A63">
-        <v>2370</v>
+        <v>2350</v>
       </c>
       <c r="B63">
-        <v>2370</v>
+        <v>2350</v>
       </c>
       <c r="C63" t="str">
         <f>INDEX(TextData!B:B,MATCH(B63,TextData!A:A))</f>
-        <v>追加効果</v>
+        <v>聖棺</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="F63" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -5893,28 +5901,28 @@
       </c>
       <c r="U63" t="str">
         <f>TextData!B62</f>
-        <v>追加効果</v>
+        <v>聖棺</v>
       </c>
     </row>
     <row r="64" spans="1:21">
       <c r="A64">
-        <v>2380</v>
+        <v>2360</v>
       </c>
       <c r="B64">
-        <v>2380</v>
+        <v>2360</v>
       </c>
       <c r="C64" t="str">
         <f>INDEX(TextData!B:B,MATCH(B64,TextData!A:A))</f>
-        <v>透明</v>
+        <v>追加ダメージ</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F64" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -5961,28 +5969,28 @@
       </c>
       <c r="U64" t="str">
         <f>TextData!B63</f>
-        <v>透明</v>
+        <v>追加ダメージ</v>
       </c>
     </row>
     <row r="65" spans="1:21">
       <c r="A65">
-        <v>2390</v>
+        <v>2370</v>
       </c>
       <c r="B65">
-        <v>2390</v>
+        <v>2370</v>
       </c>
       <c r="C65" t="str">
         <f>INDEX(TextData!B:B,MATCH(B65,TextData!A:A))</f>
-        <v>沈黙</v>
+        <v>追加効果</v>
       </c>
       <c r="D65">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E65">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="F65" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -6007,19 +6015,19 @@
         <v>0</v>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P65">
         <v>0</v>
       </c>
       <c r="Q65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S65">
         <v>0</v>
@@ -6029,19 +6037,19 @@
       </c>
       <c r="U65" t="str">
         <f>TextData!B64</f>
-        <v>沈黙</v>
+        <v>追加効果</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66">
-        <v>2400</v>
+        <v>2380</v>
       </c>
       <c r="B66">
-        <v>2400</v>
+        <v>2380</v>
       </c>
       <c r="C66" t="str">
         <f>INDEX(TextData!B:B,MATCH(B66,TextData!A:A))</f>
-        <v>不治</v>
+        <v>透明</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -6050,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="F66" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -6075,19 +6083,19 @@
         <v>0</v>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P66">
         <v>0</v>
       </c>
       <c r="Q66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S66">
         <v>0</v>
@@ -6097,28 +6105,28 @@
       </c>
       <c r="U66" t="str">
         <f>TextData!B65</f>
-        <v>不治</v>
+        <v>透明</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67">
-        <v>2410</v>
+        <v>2390</v>
       </c>
       <c r="B67">
-        <v>2410</v>
+        <v>2390</v>
       </c>
       <c r="C67" t="str">
         <f>INDEX(TextData!B:B,MATCH(B67,TextData!A:A))</f>
-        <v>シールド</v>
+        <v>沈黙</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F67" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -6143,19 +6151,19 @@
         <v>0</v>
       </c>
       <c r="N67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -6165,19 +6173,19 @@
       </c>
       <c r="U67" t="str">
         <f>TextData!B66</f>
-        <v>シールド</v>
+        <v>沈黙</v>
       </c>
     </row>
     <row r="68" spans="1:21">
       <c r="A68">
-        <v>2420</v>
+        <v>2400</v>
       </c>
       <c r="B68">
-        <v>2420</v>
+        <v>2400</v>
       </c>
       <c r="C68" t="str">
         <f>INDEX(TextData!B:B,MATCH(B68,TextData!A:A))</f>
-        <v>フォロー</v>
+        <v>不治</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -6186,7 +6194,7 @@
         <v>0</v>
       </c>
       <c r="F68" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -6211,19 +6219,19 @@
         <v>0</v>
       </c>
       <c r="N68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -6233,19 +6241,19 @@
       </c>
       <c r="U68" t="str">
         <f>TextData!B67</f>
-        <v>フォロー</v>
+        <v>不治</v>
       </c>
     </row>
     <row r="69" spans="1:21">
       <c r="A69">
-        <v>2430</v>
+        <v>2410</v>
       </c>
       <c r="B69">
-        <v>2430</v>
+        <v>2410</v>
       </c>
       <c r="C69" t="str">
         <f>INDEX(TextData!B:B,MATCH(B69,TextData!A:A))</f>
-        <v>かばう</v>
+        <v>シールド</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -6254,14 +6262,14 @@
         <v>0</v>
       </c>
       <c r="F69" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G69">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H69" t="str">
         <f>INDEX(Define!B:B,MATCH(G69,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I69">
         <v>1</v>
@@ -6294,26 +6302,26 @@
         <v>0</v>
       </c>
       <c r="S69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T69">
         <v>1</v>
       </c>
       <c r="U69" t="str">
         <f>TextData!B68</f>
-        <v>かばう</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="70" spans="1:21">
       <c r="A70">
-        <v>2440</v>
+        <v>2420</v>
       </c>
       <c r="B70">
-        <v>2440</v>
+        <v>2420</v>
       </c>
       <c r="C70" t="str">
         <f>INDEX(TextData!B:B,MATCH(B70,TextData!A:A))</f>
-        <v>Ap消費半減</v>
+        <v>フォロー</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -6322,7 +6330,7 @@
         <v>0</v>
       </c>
       <c r="F70" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -6359,7 +6367,7 @@
         <v>0</v>
       </c>
       <c r="R70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -6369,19 +6377,19 @@
       </c>
       <c r="U70" t="str">
         <f>TextData!B69</f>
-        <v>Ap消費半減</v>
+        <v>フォロー</v>
       </c>
     </row>
     <row r="71" spans="1:21">
       <c r="A71">
-        <v>2450</v>
+        <v>2430</v>
       </c>
       <c r="B71">
-        <v>2450</v>
+        <v>2430</v>
       </c>
       <c r="C71" t="str">
         <f>INDEX(TextData!B:B,MATCH(B71,TextData!A:A))</f>
-        <v>不死</v>
+        <v>かばう</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -6390,7 +6398,7 @@
         <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="G71">
         <v>4</v>
@@ -6427,29 +6435,29 @@
         <v>0</v>
       </c>
       <c r="R71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T71">
         <v>1</v>
       </c>
       <c r="U71" t="str">
         <f>TextData!B70</f>
-        <v>不死</v>
+        <v>かばう</v>
       </c>
     </row>
     <row r="72" spans="1:21">
       <c r="A72">
-        <v>2460</v>
+        <v>2440</v>
       </c>
       <c r="B72">
-        <v>2460</v>
+        <v>2440</v>
       </c>
       <c r="C72" t="str">
         <f>INDEX(TextData!B:B,MATCH(B72,TextData!A:A))</f>
-        <v>Hp回復効果アップ</v>
+        <v>Ap消費半減</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -6458,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="F72" t="s">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -6495,7 +6503,7 @@
         <v>0</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -6505,19 +6513,19 @@
       </c>
       <c r="U72" t="str">
         <f>TextData!B71</f>
-        <v>Hp回復効果アップ</v>
+        <v>Ap消費半減</v>
       </c>
     </row>
     <row r="73" spans="1:21">
       <c r="A73">
-        <v>2470</v>
+        <v>2450</v>
       </c>
       <c r="B73">
-        <v>2470</v>
+        <v>2450</v>
       </c>
       <c r="C73" t="str">
         <f>INDEX(TextData!B:B,MATCH(B73,TextData!A:A))</f>
-        <v>呪詛</v>
+        <v>不死</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -6526,7 +6534,7 @@
         <v>0</v>
       </c>
       <c r="F73" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="G73">
         <v>4</v>
@@ -6573,19 +6581,19 @@
       </c>
       <c r="U73" t="str">
         <f>TextData!B72</f>
-        <v>呪詛</v>
+        <v>不死</v>
       </c>
     </row>
     <row r="74" spans="1:21">
       <c r="A74">
-        <v>3010</v>
+        <v>2460</v>
       </c>
       <c r="B74">
-        <v>3010</v>
+        <v>2460</v>
       </c>
       <c r="C74" t="str">
         <f>INDEX(TextData!B:B,MATCH(B74,TextData!A:A))</f>
-        <v>チャージ</v>
+        <v>Hp回復効果アップ</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -6594,7 +6602,7 @@
         <v>0</v>
       </c>
       <c r="F74" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -6619,13 +6627,13 @@
         <v>0</v>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O74">
         <v>0</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -6641,19 +6649,19 @@
       </c>
       <c r="U74" t="str">
         <f>TextData!B73</f>
-        <v>チャージ</v>
+        <v>Hp回復効果アップ</v>
       </c>
     </row>
     <row r="75" spans="1:21">
       <c r="A75">
-        <v>3020</v>
+        <v>2470</v>
       </c>
       <c r="B75">
-        <v>3020</v>
+        <v>2470</v>
       </c>
       <c r="C75" t="str">
         <f>INDEX(TextData!B:B,MATCH(B75,TextData!A:A))</f>
-        <v>リンケージ</v>
+        <v>呪詛</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -6662,14 +6670,14 @@
         <v>0</v>
       </c>
       <c r="F75" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H75" t="str">
         <f>INDEX(Define!B:B,MATCH(G75,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I75">
         <v>1</v>
@@ -6687,19 +6695,19 @@
         <v>0</v>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O75">
         <v>0</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q75">
         <v>0</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -6709,19 +6717,19 @@
       </c>
       <c r="U75" t="str">
         <f>TextData!B74</f>
-        <v>リンケージ</v>
+        <v>呪詛</v>
       </c>
     </row>
     <row r="76" spans="1:21">
       <c r="A76">
-        <v>9999</v>
+        <v>3010</v>
       </c>
       <c r="B76">
-        <v>9999</v>
+        <v>3010</v>
       </c>
       <c r="C76" t="str">
         <f>INDEX(TextData!B:B,MATCH(B76,TextData!A:A))</f>
-        <v>テスト用</v>
+        <v>チャージ</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -6777,6 +6785,142 @@
       </c>
       <c r="U76" t="str">
         <f>TextData!B75</f>
+        <v>チャージ</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21">
+      <c r="A77">
+        <v>3020</v>
+      </c>
+      <c r="B77">
+        <v>3020</v>
+      </c>
+      <c r="C77" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B77,TextData!A:A))</f>
+        <v>リンケージ</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77" t="s">
+        <v>61</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77" t="str">
+        <f>INDEX(Define!B:B,MATCH(G77,Define!A:A))</f>
+        <v>ターン数</v>
+      </c>
+      <c r="I77">
+        <v>1</v>
+      </c>
+      <c r="J77" t="s">
+        <v>20</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>1</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+      <c r="Q77">
+        <v>0</v>
+      </c>
+      <c r="R77">
+        <v>0</v>
+      </c>
+      <c r="S77">
+        <v>0</v>
+      </c>
+      <c r="T77">
+        <v>1</v>
+      </c>
+      <c r="U77" t="str">
+        <f>TextData!B76</f>
+        <v>リンケージ</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21">
+      <c r="A78">
+        <v>9999</v>
+      </c>
+      <c r="B78">
+        <v>9999</v>
+      </c>
+      <c r="C78" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B78,TextData!A:A))</f>
+        <v>テスト用</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78" t="s">
+        <v>61</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="H78" t="str">
+        <f>INDEX(Define!B:B,MATCH(G78,Define!A:A))</f>
+        <v>ターン数</v>
+      </c>
+      <c r="I78">
+        <v>1</v>
+      </c>
+      <c r="J78" t="s">
+        <v>20</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>1</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <v>0</v>
+      </c>
+      <c r="R78">
+        <v>0</v>
+      </c>
+      <c r="S78">
+        <v>0</v>
+      </c>
+      <c r="T78">
+        <v>1</v>
+      </c>
+      <c r="U78" t="str">
+        <f>TextData!B77</f>
         <v>テスト用</v>
       </c>
     </row>
@@ -6790,7 +6934,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C75"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="14.6363636363636" customWidth="1"/>
@@ -7029,7 +7173,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="B22" t="s">
         <v>108</v>
@@ -7040,7 +7184,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="B23" t="s">
         <v>110</v>
@@ -7051,18 +7195,18 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B25" t="s">
         <v>112</v>
@@ -7073,7 +7217,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="B26" t="s">
         <v>114</v>
@@ -7084,7 +7228,7 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B27" t="s">
         <v>116</v>
@@ -7095,54 +7239,54 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B28" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="B29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>2010</v>
+        <v>1101</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B32" t="s">
-        <v>122</v>
+        <v>35</v>
       </c>
       <c r="C32" t="s">
         <v>123</v>
@@ -7150,474 +7294,496 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>2030</v>
+        <v>2012</v>
       </c>
       <c r="B33" t="s">
         <v>124</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>2031</v>
+        <v>2020</v>
       </c>
       <c r="B34" t="s">
+        <v>125</v>
+      </c>
+      <c r="C34" t="s">
         <v>126</v>
-      </c>
-      <c r="C34" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="B35" t="s">
+        <v>127</v>
+      </c>
+      <c r="C35" t="s">
         <v>128</v>
-      </c>
-      <c r="C35" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>2040</v>
+        <v>2031</v>
       </c>
       <c r="B36" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" t="s">
         <v>130</v>
-      </c>
-      <c r="C36" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2050</v>
+        <v>2032</v>
       </c>
       <c r="B37" t="s">
+        <v>131</v>
+      </c>
+      <c r="C37" t="s">
         <v>132</v>
-      </c>
-      <c r="C37" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2060</v>
+        <v>2040</v>
       </c>
       <c r="B38" t="s">
+        <v>133</v>
+      </c>
+      <c r="C38" t="s">
         <v>134</v>
-      </c>
-      <c r="C38" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2070</v>
+        <v>2050</v>
       </c>
       <c r="B39" t="s">
+        <v>135</v>
+      </c>
+      <c r="C39" t="s">
         <v>136</v>
-      </c>
-      <c r="C39" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2080</v>
+        <v>2060</v>
       </c>
       <c r="B40" t="s">
+        <v>137</v>
+      </c>
+      <c r="C40" t="s">
         <v>138</v>
-      </c>
-      <c r="C40" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2090</v>
+        <v>2070</v>
       </c>
       <c r="B41" t="s">
+        <v>139</v>
+      </c>
+      <c r="C41" t="s">
         <v>140</v>
-      </c>
-      <c r="C41" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2120</v>
+        <v>2080</v>
       </c>
       <c r="B42" t="s">
+        <v>141</v>
+      </c>
+      <c r="C42" t="s">
         <v>142</v>
-      </c>
-      <c r="C42" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2130</v>
+        <v>2090</v>
       </c>
       <c r="B43" t="s">
+        <v>143</v>
+      </c>
+      <c r="C43" t="s">
         <v>144</v>
-      </c>
-      <c r="C43" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2140</v>
+        <v>2120</v>
       </c>
       <c r="B44" t="s">
+        <v>145</v>
+      </c>
+      <c r="C44" t="s">
         <v>146</v>
-      </c>
-      <c r="C44" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2150</v>
+        <v>2130</v>
       </c>
       <c r="B45" t="s">
+        <v>147</v>
+      </c>
+      <c r="C45" t="s">
         <v>148</v>
-      </c>
-      <c r="C45" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2180</v>
+        <v>2140</v>
       </c>
       <c r="B46" t="s">
+        <v>149</v>
+      </c>
+      <c r="C46" t="s">
         <v>150</v>
-      </c>
-      <c r="C46" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2190</v>
+        <v>2150</v>
       </c>
       <c r="B47" t="s">
+        <v>151</v>
+      </c>
+      <c r="C47" t="s">
         <v>152</v>
-      </c>
-      <c r="C47" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2210</v>
+        <v>2180</v>
       </c>
       <c r="B48" t="s">
+        <v>153</v>
+      </c>
+      <c r="C48" t="s">
         <v>154</v>
-      </c>
-      <c r="C48" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2220</v>
+        <v>2190</v>
       </c>
       <c r="B49" t="s">
+        <v>155</v>
+      </c>
+      <c r="C49" t="s">
         <v>156</v>
-      </c>
-      <c r="C49" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2230</v>
+        <v>2210</v>
       </c>
       <c r="B50" t="s">
+        <v>157</v>
+      </c>
+      <c r="C50" t="s">
         <v>158</v>
-      </c>
-      <c r="C50" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2240</v>
+        <v>2220</v>
       </c>
       <c r="B51" t="s">
+        <v>159</v>
+      </c>
+      <c r="C51" t="s">
         <v>160</v>
-      </c>
-      <c r="C51" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2250</v>
+        <v>2230</v>
       </c>
       <c r="B52" t="s">
+        <v>161</v>
+      </c>
+      <c r="C52" t="s">
         <v>162</v>
-      </c>
-      <c r="C52" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2270</v>
+        <v>2240</v>
       </c>
       <c r="B53" t="s">
+        <v>163</v>
+      </c>
+      <c r="C53" t="s">
         <v>164</v>
-      </c>
-      <c r="C53" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2280</v>
+        <v>2250</v>
       </c>
       <c r="B54" t="s">
+        <v>165</v>
+      </c>
+      <c r="C54" t="s">
         <v>166</v>
-      </c>
-      <c r="C54" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2290</v>
+        <v>2270</v>
       </c>
       <c r="B55" t="s">
+        <v>167</v>
+      </c>
+      <c r="C55" t="s">
         <v>168</v>
-      </c>
-      <c r="C55" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>2320</v>
+        <v>2280</v>
       </c>
       <c r="B56" t="s">
+        <v>169</v>
+      </c>
+      <c r="C56" t="s">
         <v>170</v>
-      </c>
-      <c r="C56" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>2330</v>
+        <v>2290</v>
       </c>
       <c r="B57" t="s">
+        <v>171</v>
+      </c>
+      <c r="C57" t="s">
         <v>172</v>
-      </c>
-      <c r="C57" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>2340</v>
+        <v>2320</v>
       </c>
       <c r="B58" t="s">
+        <v>173</v>
+      </c>
+      <c r="C58" t="s">
         <v>174</v>
-      </c>
-      <c r="C58" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>2341</v>
+        <v>2330</v>
       </c>
       <c r="B59" t="s">
+        <v>175</v>
+      </c>
+      <c r="C59" t="s">
         <v>176</v>
-      </c>
-      <c r="C59" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2350</v>
+        <v>2340</v>
       </c>
       <c r="B60" t="s">
+        <v>177</v>
+      </c>
+      <c r="C60" t="s">
         <v>178</v>
-      </c>
-      <c r="C60" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>2360</v>
+        <v>2341</v>
       </c>
       <c r="B61" t="s">
+        <v>179</v>
+      </c>
+      <c r="C61" t="s">
         <v>180</v>
-      </c>
-      <c r="C61" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>2370</v>
+        <v>2350</v>
       </c>
       <c r="B62" t="s">
+        <v>181</v>
+      </c>
+      <c r="C62" t="s">
         <v>182</v>
-      </c>
-      <c r="C62" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>2380</v>
+        <v>2360</v>
       </c>
       <c r="B63" t="s">
+        <v>183</v>
+      </c>
+      <c r="C63" t="s">
         <v>184</v>
-      </c>
-      <c r="C63" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>2390</v>
+        <v>2370</v>
       </c>
       <c r="B64" t="s">
+        <v>185</v>
+      </c>
+      <c r="C64" t="s">
         <v>186</v>
-      </c>
-      <c r="C64" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>2400</v>
+        <v>2380</v>
       </c>
       <c r="B65" t="s">
+        <v>187</v>
+      </c>
+      <c r="C65" t="s">
         <v>188</v>
-      </c>
-      <c r="C65" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>2410</v>
+        <v>2390</v>
       </c>
       <c r="B66" t="s">
+        <v>189</v>
+      </c>
+      <c r="C66" t="s">
         <v>190</v>
-      </c>
-      <c r="C66" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>2420</v>
+        <v>2400</v>
       </c>
       <c r="B67" t="s">
+        <v>191</v>
+      </c>
+      <c r="C67" t="s">
         <v>192</v>
-      </c>
-      <c r="C67" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>2430</v>
+        <v>2410</v>
       </c>
       <c r="B68" t="s">
+        <v>193</v>
+      </c>
+      <c r="C68" t="s">
         <v>194</v>
-      </c>
-      <c r="C68" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>2440</v>
+        <v>2420</v>
       </c>
       <c r="B69" t="s">
+        <v>195</v>
+      </c>
+      <c r="C69" t="s">
         <v>196</v>
-      </c>
-      <c r="C69" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>2450</v>
+        <v>2430</v>
       </c>
       <c r="B70" t="s">
+        <v>197</v>
+      </c>
+      <c r="C70" t="s">
         <v>198</v>
-      </c>
-      <c r="C70" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2460</v>
+        <v>2440</v>
       </c>
       <c r="B71" t="s">
+        <v>199</v>
+      </c>
+      <c r="C71" t="s">
         <v>200</v>
-      </c>
-      <c r="C71" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>2470</v>
+        <v>2450</v>
       </c>
       <c r="B72" t="s">
+        <v>201</v>
+      </c>
+      <c r="C72" t="s">
         <v>202</v>
-      </c>
-      <c r="C72" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>3010</v>
+        <v>2460</v>
       </c>
       <c r="B73" t="s">
+        <v>203</v>
+      </c>
+      <c r="C73" t="s">
         <v>204</v>
-      </c>
-      <c r="C73" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>3020</v>
+        <v>2470</v>
       </c>
       <c r="B74" t="s">
+        <v>205</v>
+      </c>
+      <c r="C74" t="s">
         <v>206</v>
-      </c>
-      <c r="C74" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
+        <v>3010</v>
+      </c>
+      <c r="B75" t="s">
+        <v>207</v>
+      </c>
+      <c r="C75" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76">
+        <v>3020</v>
+      </c>
+      <c r="B76" t="s">
+        <v>209</v>
+      </c>
+      <c r="C76" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77">
         <v>9999</v>
       </c>
-      <c r="B75" t="s">
-        <v>208</v>
-      </c>
-      <c r="C75" t="s">
+      <c r="B77" t="s">
+        <v>211</v>
+      </c>
+      <c r="C77" t="s">
         <v>20</v>
       </c>
     </row>
@@ -7643,7 +7809,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7651,7 +7817,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7659,7 +7825,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7667,7 +7833,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -7675,7 +7841,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -7683,7 +7849,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -126,6 +126,9 @@
     <t>毒</t>
   </si>
   <si>
+    <t>火傷</t>
+  </si>
+  <si>
     <t>Blind</t>
   </si>
   <si>
@@ -388,9 +391,6 @@
   </si>
   <si>
     <t>行動後ダメージ</t>
-  </si>
-  <si>
-    <t>火傷</t>
   </si>
   <si>
     <t>暗闇</t>
@@ -677,10 +677,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -691,8 +691,92 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -706,15 +790,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -723,90 +799,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -820,18 +813,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -844,13 +844,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -862,73 +934,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -946,49 +958,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1040,6 +1040,17 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
@@ -1047,13 +1058,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1073,30 +1112,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1112,26 +1127,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1143,145 +1143,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3873,13 +3873,13 @@
         <v>2012</v>
       </c>
       <c r="C34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D34">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="F34" t="s">
         <v>33</v>
@@ -3963,7 +3963,7 @@
         <v>1</v>
       </c>
       <c r="J35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -4018,7 +4018,7 @@
         <v>66</v>
       </c>
       <c r="F36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G36">
         <v>1</v>
@@ -4031,7 +4031,7 @@
         <v>0</v>
       </c>
       <c r="J36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K36">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>66</v>
       </c>
       <c r="F37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -4154,7 +4154,7 @@
         <v>66</v>
       </c>
       <c r="F38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4222,7 +4222,7 @@
         <v>46</v>
       </c>
       <c r="F39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -4290,7 +4290,7 @@
         <v>226</v>
       </c>
       <c r="F40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G40">
         <v>4</v>
@@ -4303,7 +4303,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -4358,7 +4358,7 @@
         <v>167</v>
       </c>
       <c r="F41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -4426,7 +4426,7 @@
         <v>226</v>
       </c>
       <c r="F42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -4494,7 +4494,7 @@
         <v>4</v>
       </c>
       <c r="F43" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G43">
         <v>4</v>
@@ -4562,7 +4562,7 @@
         <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G44">
         <v>4</v>
@@ -4630,7 +4630,7 @@
         <v>9</v>
       </c>
       <c r="F45" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G45">
         <v>4</v>
@@ -4643,7 +4643,7 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -4698,7 +4698,7 @@
         <v>4</v>
       </c>
       <c r="F46" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -4766,7 +4766,7 @@
         <v>44</v>
       </c>
       <c r="F47" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G47">
         <v>4</v>
@@ -4779,7 +4779,7 @@
         <v>1</v>
       </c>
       <c r="J47" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -4834,7 +4834,7 @@
         <v>5</v>
       </c>
       <c r="F48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G48">
         <v>2</v>
@@ -4847,7 +4847,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -4902,7 +4902,7 @@
         <v>99</v>
       </c>
       <c r="F49" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G49">
         <v>4</v>
@@ -4970,7 +4970,7 @@
         <v>73</v>
       </c>
       <c r="F50" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -5038,7 +5038,7 @@
         <v>63</v>
       </c>
       <c r="F51" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -5174,7 +5174,7 @@
         <v>46</v>
       </c>
       <c r="F53" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5310,7 +5310,7 @@
         <v>46</v>
       </c>
       <c r="F55" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5378,7 +5378,7 @@
         <v>9</v>
       </c>
       <c r="F56" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5514,7 +5514,7 @@
         <v>21</v>
       </c>
       <c r="F58" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -5650,7 +5650,7 @@
         <v>56</v>
       </c>
       <c r="F60" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -5718,7 +5718,7 @@
         <v>66</v>
       </c>
       <c r="F61" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -5786,7 +5786,7 @@
         <v>66</v>
       </c>
       <c r="F62" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -5854,7 +5854,7 @@
         <v>0</v>
       </c>
       <c r="F63" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -5922,7 +5922,7 @@
         <v>13</v>
       </c>
       <c r="F64" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -5990,7 +5990,7 @@
         <v>56</v>
       </c>
       <c r="F65" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="F66" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -6126,7 +6126,7 @@
         <v>3</v>
       </c>
       <c r="F67" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -6194,7 +6194,7 @@
         <v>0</v>
       </c>
       <c r="F68" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -6262,7 +6262,7 @@
         <v>0</v>
       </c>
       <c r="F69" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -6330,7 +6330,7 @@
         <v>0</v>
       </c>
       <c r="F70" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -6398,7 +6398,7 @@
         <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G71">
         <v>4</v>
@@ -6534,7 +6534,7 @@
         <v>0</v>
       </c>
       <c r="F73" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G73">
         <v>4</v>
@@ -6602,7 +6602,7 @@
         <v>0</v>
       </c>
       <c r="F74" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -6670,7 +6670,7 @@
         <v>0</v>
       </c>
       <c r="F75" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G75">
         <v>4</v>
@@ -6738,7 +6738,7 @@
         <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -6806,7 +6806,7 @@
         <v>0</v>
       </c>
       <c r="F77" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -6874,7 +6874,7 @@
         <v>0</v>
       </c>
       <c r="F78" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -6945,10 +6945,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -6956,7 +6956,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
@@ -6967,7 +6967,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
@@ -6978,10 +6978,10 @@
         <v>201</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6989,10 +6989,10 @@
         <v>202</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7000,10 +7000,10 @@
         <v>203</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7011,10 +7011,10 @@
         <v>204</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7022,10 +7022,10 @@
         <v>205</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7033,10 +7033,10 @@
         <v>1010</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7044,10 +7044,10 @@
         <v>1011</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7055,10 +7055,10 @@
         <v>1020</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -7066,10 +7066,10 @@
         <v>1030</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -7077,10 +7077,10 @@
         <v>1040</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -7088,10 +7088,10 @@
         <v>1041</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -7099,10 +7099,10 @@
         <v>1043</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7110,10 +7110,10 @@
         <v>1044</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7121,10 +7121,10 @@
         <v>1050</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -7132,10 +7132,10 @@
         <v>1051</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -7143,10 +7143,10 @@
         <v>1052</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -7154,10 +7154,10 @@
         <v>1060</v>
       </c>
       <c r="B20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -7165,10 +7165,10 @@
         <v>1070</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -7176,10 +7176,10 @@
         <v>1071</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -7187,10 +7187,10 @@
         <v>1074</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -7198,10 +7198,10 @@
         <v>1080</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -7209,10 +7209,10 @@
         <v>1081</v>
       </c>
       <c r="B25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C25" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -7220,10 +7220,10 @@
         <v>1082</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -7231,10 +7231,10 @@
         <v>1090</v>
       </c>
       <c r="B27" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -7242,10 +7242,10 @@
         <v>1091</v>
       </c>
       <c r="B28" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -7253,10 +7253,10 @@
         <v>1092</v>
       </c>
       <c r="B29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -7264,10 +7264,10 @@
         <v>1100</v>
       </c>
       <c r="B30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C30" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -7275,10 +7275,10 @@
         <v>1101</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -7289,7 +7289,7 @@
         <v>35</v>
       </c>
       <c r="C32" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -7297,10 +7297,10 @@
         <v>2012</v>
       </c>
       <c r="B33" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" t="s">
         <v>124</v>
-      </c>
-      <c r="C33" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:3">

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8270"/>
+    <workbookView windowWidth="19200" windowHeight="8410"/>
   </bookViews>
   <sheets>
     <sheet name="States" sheetId="1" r:id="rId1"/>
@@ -677,10 +677,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -688,43 +688,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -743,6 +706,42 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -751,32 +750,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -789,11 +773,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -814,6 +797,14 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -821,15 +812,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -841,18 +841,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -868,13 +856,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -886,19 +928,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -916,49 +958,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -970,13 +976,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -994,25 +994,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1024,7 +1018,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1035,26 +1035,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1069,15 +1049,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1097,17 +1068,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1131,7 +1096,42 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1143,142 +1143,142 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="States" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="219">
   <si>
     <t>Id</t>
   </si>
@@ -670,6 +670,9 @@
   </si>
   <si>
     <t>次に行動するまでの間</t>
+  </si>
+  <si>
+    <t>ターンの終了</t>
   </si>
 </sst>
 </file>
@@ -677,8 +680,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -691,9 +694,62 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -714,37 +770,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -758,23 +791,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -788,19 +807,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -813,23 +824,15 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -844,7 +847,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -856,25 +877,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -886,13 +901,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -904,79 +967,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -994,13 +985,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1012,19 +1015,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1038,17 +1041,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1068,11 +1065,52 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1096,42 +1134,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1143,145 +1146,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1298,12 +1301,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -6401,11 +6404,11 @@
         <v>68</v>
       </c>
       <c r="G71">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H71" t="str">
         <f>INDEX(Define!B:B,MATCH(G71,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターンの終了</v>
       </c>
       <c r="I71">
         <v>1</v>
@@ -7796,8 +7799,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="6" outlineLevelCol="1"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelRow="7" outlineLevelCol="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
@@ -7850,6 +7853,14 @@
       </c>
       <c r="B7" t="s">
         <v>217</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="2"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="States" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="218">
   <si>
     <t>Id</t>
   </si>
@@ -102,9 +102,6 @@
     <t>Shield</t>
   </si>
   <si>
-    <t>CrackedShield</t>
-  </si>
-  <si>
     <t>Bullseye</t>
   </si>
   <si>
@@ -327,10 +324,10 @@
     <t>DEF\dダウン</t>
   </si>
   <si>
-    <t>防御ブレイク</t>
-  </si>
-  <si>
-    <t>DEFを半減させる</t>
+    <t>DEF\d%アップ</t>
+  </si>
+  <si>
+    <t>DEF\d%ダウン</t>
   </si>
   <si>
     <t>速度アップ</t>
@@ -680,9 +677,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
@@ -691,13 +688,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -711,22 +701,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -762,6 +736,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -776,40 +766,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -824,15 +783,53 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -844,12 +841,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -877,13 +868,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -901,7 +892,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -913,13 +904,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -931,13 +1006,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -949,85 +1018,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1115,6 +1112,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1129,15 +1135,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1146,145 +1143,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1611,7 +1608,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U78"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="21.8181818181818" customWidth="1"/>
@@ -2858,16 +2855,16 @@
       </c>
       <c r="C19" t="str">
         <f>INDEX(TextData!B:B,MATCH(B19,TextData!A:A))</f>
-        <v>防御ブレイク</v>
+        <v>防御アップ</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -2892,16 +2889,16 @@
         <v>0</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -2914,28 +2911,28 @@
       </c>
       <c r="U19" t="str">
         <f>TextData!B19</f>
-        <v>防御ブレイク</v>
+        <v>防御アップ</v>
       </c>
     </row>
     <row r="20" spans="1:21">
       <c r="A20">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="B20">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="C20" t="str">
         <f>INDEX(TextData!B:B,MATCH(B20,TextData!A:A))</f>
-        <v>速度アップ</v>
+        <v>防御ダウン</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F20" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -2960,16 +2957,16 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -2982,28 +2979,28 @@
       </c>
       <c r="U20" t="str">
         <f>TextData!B20</f>
-        <v>速度アップ</v>
+        <v>防御ダウン</v>
       </c>
     </row>
     <row r="21" spans="1:21">
       <c r="A21">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="B21">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="C21" t="str">
         <f>INDEX(TextData!B:B,MATCH(B21,TextData!A:A))</f>
-        <v>会心率アップ</v>
+        <v>速度アップ</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F21" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -3050,19 +3047,19 @@
       </c>
       <c r="U21" t="str">
         <f>TextData!B21</f>
-        <v>会心率アップ</v>
+        <v>速度アップ</v>
       </c>
     </row>
     <row r="22" spans="1:21">
       <c r="A22">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B22">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C22" t="str">
         <f>INDEX(TextData!B:B,MATCH(B22,TextData!A:A))</f>
-        <v>会心率ダウン</v>
+        <v>会心率アップ</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -3071,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -3096,16 +3093,16 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -3118,19 +3115,19 @@
       </c>
       <c r="U22" t="str">
         <f>TextData!B22</f>
-        <v>会心率ダウン</v>
+        <v>会心率アップ</v>
       </c>
     </row>
     <row r="23" spans="1:21">
       <c r="A23">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="B23">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="C23" t="str">
         <f>INDEX(TextData!B:B,MATCH(B23,TextData!A:A))</f>
-        <v>会心ダメージアップ</v>
+        <v>会心率ダウン</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -3139,7 +3136,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -3164,16 +3161,16 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -3186,19 +3183,19 @@
       </c>
       <c r="U23" t="str">
         <f>TextData!B23</f>
-        <v>会心ダメージアップ</v>
+        <v>会心率ダウン</v>
       </c>
     </row>
     <row r="24" spans="1:21">
       <c r="A24">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="B24">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="C24" t="str">
         <f>INDEX(TextData!B:B,MATCH(B24,TextData!A:A))</f>
-        <v>命中アップ</v>
+        <v>会心ダメージアップ</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -3207,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -3254,15 +3251,15 @@
       </c>
       <c r="U24" t="str">
         <f>TextData!B24</f>
-        <v>命中アップ</v>
+        <v>会心ダメージアップ</v>
       </c>
     </row>
     <row r="25" spans="1:21">
       <c r="A25">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B25">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C25" t="str">
         <f>INDEX(TextData!B:B,MATCH(B25,TextData!A:A))</f>
@@ -3275,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -3297,7 +3294,7 @@
         <v>1</v>
       </c>
       <c r="M25">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N25">
         <v>1</v>
@@ -3321,20 +3318,20 @@
         <v>1</v>
       </c>
       <c r="U25" t="str">
-        <f>TextData!B27</f>
-        <v>回避アップ</v>
+        <f>TextData!B25</f>
+        <v>命中アップ</v>
       </c>
     </row>
     <row r="26" spans="1:21">
       <c r="A26">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B26">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C26" t="str">
         <f>INDEX(TextData!B:B,MATCH(B26,TextData!A:A))</f>
-        <v>命中ダウン</v>
+        <v>命中アップ</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -3343,7 +3340,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -3365,19 +3362,19 @@
         <v>1</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -3390,19 +3387,19 @@
       </c>
       <c r="U26" t="str">
         <f>TextData!B28</f>
-        <v>回避ダウン</v>
+        <v>回避アップ</v>
       </c>
     </row>
     <row r="27" spans="1:21">
       <c r="A27">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="B27">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="C27" t="str">
         <f>INDEX(TextData!B:B,MATCH(B27,TextData!A:A))</f>
-        <v>回避アップ</v>
+        <v>命中ダウン</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -3411,7 +3408,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -3436,16 +3433,16 @@
         <v>0</v>
       </c>
       <c r="N27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -3457,20 +3454,20 @@
         <v>1</v>
       </c>
       <c r="U27" t="str">
-        <f>TextData!B27</f>
-        <v>回避アップ</v>
+        <f>TextData!B29</f>
+        <v>回避ダウン</v>
       </c>
     </row>
     <row r="28" spans="1:21">
       <c r="A28">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B28">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C28" t="str">
         <f>INDEX(TextData!B:B,MATCH(B28,TextData!A:A))</f>
-        <v>回避ダウン</v>
+        <v>回避アップ</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -3479,7 +3476,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -3510,10 +3507,10 @@
         <v>0</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -3526,19 +3523,19 @@
       </c>
       <c r="U28" t="str">
         <f>TextData!B28</f>
-        <v>回避ダウン</v>
+        <v>回避アップ</v>
       </c>
     </row>
     <row r="29" spans="1:21">
       <c r="A29">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B29">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C29" t="str">
         <f>INDEX(TextData!B:B,MATCH(B29,TextData!A:A))</f>
-        <v>回避アップ</v>
+        <v>回避ダウン</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -3547,7 +3544,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G29">
         <v>1</v>
@@ -3569,7 +3566,7 @@
         <v>1</v>
       </c>
       <c r="M29">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N29">
         <v>1</v>
@@ -3578,10 +3575,10 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -3594,35 +3591,35 @@
       </c>
       <c r="U29" t="str">
         <f>TextData!B29</f>
-        <v>回避アップ</v>
+        <v>回避ダウン</v>
       </c>
     </row>
     <row r="30" spans="1:21">
       <c r="A30">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="B30">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="C30" t="str">
         <f>INDEX(TextData!B:B,MATCH(B30,TextData!A:A))</f>
-        <v>ダメージカット</v>
+        <v>回避アップ</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="F30" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H30" t="str">
         <f>INDEX(Define!B:B,MATCH(G30,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I30">
         <v>1</v>
@@ -3637,7 +3634,7 @@
         <v>1</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N30">
         <v>1</v>
@@ -3662,15 +3659,15 @@
       </c>
       <c r="U30" t="str">
         <f>TextData!B30</f>
-        <v>ダメージカット</v>
+        <v>回避アップ</v>
       </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B31">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C31" t="str">
         <f>INDEX(TextData!B:B,MATCH(B31,TextData!A:A))</f>
@@ -3683,7 +3680,7 @@
         <v>96</v>
       </c>
       <c r="F31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G31">
         <v>4</v>
@@ -3733,41 +3730,41 @@
         <v>ダメージカット</v>
       </c>
     </row>
-    <row r="32" ht="12" customHeight="1" spans="1:21">
+    <row r="32" spans="1:21">
       <c r="A32">
-        <v>2010</v>
+        <v>1101</v>
       </c>
       <c r="B32">
-        <v>2010</v>
+        <v>1101</v>
       </c>
       <c r="C32" t="str">
         <f>INDEX(TextData!B:B,MATCH(B32,TextData!A:A))</f>
-        <v>毒</v>
+        <v>ダメージカット</v>
       </c>
       <c r="D32">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="F32" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H32" t="str">
         <f>INDEX(Define!B:B,MATCH(G32,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I32">
         <v>1</v>
       </c>
       <c r="J32" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="K32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32">
         <v>1</v>
@@ -3776,19 +3773,19 @@
         <v>0</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <v>0</v>
@@ -3798,18 +3795,19 @@
       </c>
       <c r="U32" t="str">
         <f>TextData!B32</f>
-        <v>毒</v>
+        <v>ダメージカット</v>
       </c>
     </row>
     <row r="33" ht="12" customHeight="1" spans="1:21">
       <c r="A33">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B33">
         <v>2010</v>
       </c>
-      <c r="C33" t="s">
-        <v>35</v>
+      <c r="C33" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B33,TextData!A:A))</f>
+        <v>毒</v>
       </c>
       <c r="D33">
         <v>26</v>
@@ -3818,7 +3816,7 @@
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -3831,7 +3829,7 @@
         <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -3864,28 +3862,28 @@
         <v>1</v>
       </c>
       <c r="U33" t="str">
-        <f>TextData!B32</f>
+        <f>TextData!B33</f>
         <v>毒</v>
       </c>
     </row>
     <row r="34" ht="12" customHeight="1" spans="1:21">
       <c r="A34">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B34">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C34" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E34">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G34">
         <v>1</v>
@@ -3898,7 +3896,7 @@
         <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K34">
         <v>1</v>
@@ -3932,47 +3930,46 @@
       </c>
       <c r="U34" t="str">
         <f>TextData!B33</f>
-        <v>火傷</v>
+        <v>毒</v>
       </c>
     </row>
     <row r="35" ht="12" customHeight="1" spans="1:21">
       <c r="A35">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="B35">
-        <v>2020</v>
-      </c>
-      <c r="C35" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B35,TextData!A:A))</f>
-        <v>暗闇</v>
+        <v>2012</v>
+      </c>
+      <c r="C35" t="s">
+        <v>35</v>
       </c>
       <c r="D35">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="F35" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H35" t="str">
         <f>INDEX(Define!B:B,MATCH(G35,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I35">
         <v>1</v>
       </c>
       <c r="J35" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -4000,47 +3997,47 @@
       </c>
       <c r="U35" t="str">
         <f>TextData!B34</f>
-        <v>暗闇</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21">
+        <v>火傷</v>
+      </c>
+    </row>
+    <row r="36" ht="12" customHeight="1" spans="1:21">
       <c r="A36">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B36">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="C36" t="str">
         <f>INDEX(TextData!B:B,MATCH(B36,TextData!A:A))</f>
-        <v>カウンタ</v>
+        <v>暗闇</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E36">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="F36" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H36" t="str">
         <f>INDEX(Define!B:B,MATCH(G36,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K36">
         <v>0</v>
       </c>
       <c r="L36">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -4049,16 +4046,16 @@
         <v>0</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36">
         <v>0</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -4068,19 +4065,19 @@
       </c>
       <c r="U36" t="str">
         <f>TextData!B35</f>
-        <v>カウンタ</v>
+        <v>暗闇</v>
       </c>
     </row>
     <row r="37" spans="1:21">
       <c r="A37">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B37">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C37" t="str">
         <f>INDEX(TextData!B:B,MATCH(B37,TextData!A:A))</f>
-        <v>CAダメージ</v>
+        <v>カウンタ</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -4089,7 +4086,7 @@
         <v>66</v>
       </c>
       <c r="F37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G37">
         <v>1</v>
@@ -4099,10 +4096,10 @@
         <v>ターン数</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J37" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -4136,19 +4133,19 @@
       </c>
       <c r="U37" t="str">
         <f>TextData!B36</f>
-        <v>CAダメージ</v>
+        <v>カウンタ</v>
       </c>
     </row>
     <row r="38" spans="1:21">
       <c r="A38">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B38">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="C38" t="str">
         <f>INDEX(TextData!B:B,MATCH(B38,TextData!A:A))</f>
-        <v>CAシェル</v>
+        <v>CAダメージ</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -4157,14 +4154,14 @@
         <v>66</v>
       </c>
       <c r="F38" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="str">
         <f>INDEX(Define!B:B,MATCH(G38,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I38">
         <v>1</v>
@@ -4204,35 +4201,35 @@
       </c>
       <c r="U38" t="str">
         <f>TextData!B37</f>
-        <v>CAシェル</v>
+        <v>CAダメージ</v>
       </c>
     </row>
     <row r="39" spans="1:21">
       <c r="A39">
-        <v>2040</v>
+        <v>2032</v>
       </c>
       <c r="B39">
-        <v>2040</v>
+        <v>2032</v>
       </c>
       <c r="C39" t="str">
         <f>INDEX(TextData!B:B,MATCH(B39,TextData!A:A))</f>
-        <v>リジェネ</v>
+        <v>CAシェル</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="F39" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="str">
         <f>INDEX(Define!B:B,MATCH(G39,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I39">
         <v>1</v>
@@ -4272,41 +4269,41 @@
       </c>
       <c r="U39" t="str">
         <f>TextData!B38</f>
-        <v>リジェネ</v>
+        <v>CAシェル</v>
       </c>
     </row>
     <row r="40" spans="1:21">
       <c r="A40">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="B40">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C40" t="str">
         <f>INDEX(TextData!B:B,MATCH(B40,TextData!A:A))</f>
-        <v>攻撃無効</v>
+        <v>リジェネ</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>226</v>
+        <v>46</v>
       </c>
       <c r="F40" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H40" t="str">
         <f>INDEX(Define!B:B,MATCH(G40,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -4340,41 +4337,41 @@
       </c>
       <c r="U40" t="str">
         <f>TextData!B39</f>
-        <v>攻撃無効</v>
+        <v>リジェネ</v>
       </c>
     </row>
     <row r="41" spans="1:21">
       <c r="A41">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="B41">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="C41" t="str">
         <f>INDEX(TextData!B:B,MATCH(B41,TextData!A:A))</f>
-        <v>ドレイン</v>
+        <v>攻撃無効</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>167</v>
+        <v>226</v>
       </c>
       <c r="F41" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H41" t="str">
         <f>INDEX(Define!B:B,MATCH(G41,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -4408,28 +4405,28 @@
       </c>
       <c r="U41" t="str">
         <f>TextData!B40</f>
-        <v>ドレイン</v>
+        <v>攻撃無効</v>
       </c>
     </row>
     <row r="42" spans="1:21">
       <c r="A42">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="B42">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="C42" t="str">
         <f>INDEX(TextData!B:B,MATCH(B42,TextData!A:A))</f>
-        <v>状態異常CA</v>
+        <v>ドレイン</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>226</v>
+        <v>167</v>
       </c>
       <c r="F42" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -4439,7 +4436,7 @@
         <v>ターン数</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="s">
         <v>20</v>
@@ -4476,35 +4473,35 @@
       </c>
       <c r="U42" t="str">
         <f>TextData!B41</f>
-        <v>状態異常CA</v>
+        <v>ドレイン</v>
       </c>
     </row>
     <row r="43" spans="1:21">
       <c r="A43">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="B43">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="C43" t="str">
         <f>INDEX(TextData!B:B,MATCH(B43,TextData!A:A))</f>
-        <v>反撃</v>
+        <v>状態異常CA</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>4</v>
+        <v>226</v>
       </c>
       <c r="F43" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H43" t="str">
         <f>INDEX(Define!B:B,MATCH(G43,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -4544,28 +4541,28 @@
       </c>
       <c r="U43" t="str">
         <f>TextData!B42</f>
-        <v>反撃</v>
+        <v>状態異常CA</v>
       </c>
     </row>
     <row r="44" spans="1:21">
       <c r="A44">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="B44">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="C44" t="str">
         <f>INDEX(TextData!B:B,MATCH(B44,TextData!A:A))</f>
-        <v>パッシブ封じ</v>
+        <v>反撃</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F44" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G44">
         <v>4</v>
@@ -4593,16 +4590,16 @@
         <v>0</v>
       </c>
       <c r="O44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P44">
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -4612,28 +4609,28 @@
       </c>
       <c r="U44" t="str">
         <f>TextData!B43</f>
-        <v>パッシブ封じ</v>
+        <v>反撃</v>
       </c>
     </row>
     <row r="45" spans="1:21">
       <c r="A45">
-        <v>2120</v>
+        <v>2090</v>
       </c>
       <c r="B45">
-        <v>2120</v>
+        <v>2090</v>
       </c>
       <c r="C45" t="str">
         <f>INDEX(TextData!B:B,MATCH(B45,TextData!A:A))</f>
-        <v>デバフ強化</v>
+        <v>パッシブ封じ</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G45">
         <v>4</v>
@@ -4643,16 +4640,16 @@
         <v>効果発揮回数</v>
       </c>
       <c r="I45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="K45">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M45">
         <v>0</v>
@@ -4661,13 +4658,13 @@
         <v>0</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P45">
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45">
         <v>1</v>
@@ -4680,47 +4677,47 @@
       </c>
       <c r="U45" t="str">
         <f>TextData!B44</f>
-        <v>デバフ強化</v>
+        <v>パッシブ封じ</v>
       </c>
     </row>
     <row r="46" spans="1:21">
       <c r="A46">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="B46">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="C46" t="str">
         <f>INDEX(TextData!B:B,MATCH(B46,TextData!A:A))</f>
-        <v>挑発</v>
+        <v>デバフ強化</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
+        <v>9</v>
+      </c>
+      <c r="F46" t="s">
+        <v>45</v>
+      </c>
+      <c r="G46">
         <v>4</v>
-      </c>
-      <c r="F46" t="s">
-        <v>48</v>
-      </c>
-      <c r="G46">
-        <v>1</v>
       </c>
       <c r="H46" t="str">
         <f>INDEX(Define!B:B,MATCH(G46,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="K46">
         <v>0</v>
       </c>
       <c r="L46">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="M46">
         <v>0</v>
@@ -4748,41 +4745,41 @@
       </c>
       <c r="U46" t="str">
         <f>TextData!B45</f>
-        <v>挑発</v>
+        <v>デバフ強化</v>
       </c>
     </row>
     <row r="47" spans="1:21">
       <c r="A47">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="B47">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="C47" t="str">
         <f>INDEX(TextData!B:B,MATCH(B47,TextData!A:A))</f>
-        <v>凍結</v>
+        <v>挑発</v>
       </c>
       <c r="D47">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="F47" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H47" t="str">
         <f>INDEX(Define!B:B,MATCH(G47,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K47">
         <v>0</v>
@@ -4797,13 +4794,13 @@
         <v>0</v>
       </c>
       <c r="O47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P47">
         <v>0</v>
       </c>
       <c r="Q47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47">
         <v>1</v>
@@ -4816,41 +4813,41 @@
       </c>
       <c r="U47" t="str">
         <f>TextData!B46</f>
-        <v>凍結</v>
+        <v>挑発</v>
       </c>
     </row>
     <row r="48" spans="1:21">
       <c r="A48">
-        <v>2150</v>
+        <v>2140</v>
       </c>
       <c r="B48">
-        <v>2150</v>
+        <v>2140</v>
       </c>
       <c r="C48" t="str">
         <f>INDEX(TextData!B:B,MATCH(B48,TextData!A:A))</f>
-        <v>スタン</v>
+        <v>凍結</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E48">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="F48" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G48">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H48" t="str">
         <f>INDEX(Define!B:B,MATCH(G48,Define!A:A))</f>
-        <v>APカウント</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -4884,41 +4881,41 @@
       </c>
       <c r="U48" t="str">
         <f>TextData!B47</f>
-        <v>スタン</v>
+        <v>凍結</v>
       </c>
     </row>
     <row r="49" spans="1:21">
       <c r="A49">
-        <v>2180</v>
+        <v>2150</v>
       </c>
       <c r="B49">
-        <v>2180</v>
+        <v>2150</v>
       </c>
       <c r="C49" t="str">
         <f>INDEX(TextData!B:B,MATCH(B49,TextData!A:A))</f>
-        <v>状態異常回避</v>
+        <v>スタン</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="F49" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G49">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H49" t="str">
         <f>INDEX(Define!B:B,MATCH(G49,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>APカウント</v>
       </c>
       <c r="I49">
         <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -4933,16 +4930,16 @@
         <v>0</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P49">
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -4952,35 +4949,35 @@
       </c>
       <c r="U49" t="str">
         <f>TextData!B48</f>
-        <v>状態異常回避</v>
+        <v>スタン</v>
       </c>
     </row>
     <row r="50" spans="1:21">
       <c r="A50">
-        <v>2190</v>
+        <v>2180</v>
       </c>
       <c r="B50">
-        <v>2190</v>
+        <v>2180</v>
       </c>
       <c r="C50" t="str">
         <f>INDEX(TextData!B:B,MATCH(B50,TextData!A:A))</f>
-        <v>対象範囲延長</v>
+        <v>状態異常回避</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="F50" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H50" t="str">
         <f>INDEX(Define!B:B,MATCH(G50,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -5016,32 +5013,32 @@
         <v>0</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U50" t="str">
         <f>TextData!B49</f>
-        <v>対象範囲延長</v>
+        <v>状態異常回避</v>
       </c>
     </row>
     <row r="51" spans="1:21">
       <c r="A51">
-        <v>2210</v>
+        <v>2190</v>
       </c>
       <c r="B51">
-        <v>2210</v>
+        <v>2190</v>
       </c>
       <c r="C51" t="str">
         <f>INDEX(TextData!B:B,MATCH(B51,TextData!A:A))</f>
-        <v>アフターヒール</v>
+        <v>対象範囲延長</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F51" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -5051,7 +5048,7 @@
         <v>ターン数</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="s">
         <v>20</v>
@@ -5084,32 +5081,32 @@
         <v>0</v>
       </c>
       <c r="T51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U51" t="str">
         <f>TextData!B50</f>
-        <v>アフターヒール</v>
+        <v>対象範囲延長</v>
       </c>
     </row>
     <row r="52" spans="1:21">
       <c r="A52">
-        <v>2220</v>
+        <v>2210</v>
       </c>
       <c r="B52">
-        <v>2220</v>
+        <v>2210</v>
       </c>
       <c r="C52" t="str">
         <f>INDEX(TextData!B:B,MATCH(B52,TextData!A:A))</f>
-        <v>即死付与</v>
+        <v>アフターヒール</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="F52" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -5119,7 +5116,7 @@
         <v>ターン数</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" t="s">
         <v>20</v>
@@ -5146,7 +5143,7 @@
         <v>0</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -5156,38 +5153,38 @@
       </c>
       <c r="U52" t="str">
         <f>TextData!B51</f>
-        <v>即死付与</v>
+        <v>アフターヒール</v>
       </c>
     </row>
     <row r="53" spans="1:21">
       <c r="A53">
-        <v>2230</v>
+        <v>2220</v>
       </c>
       <c r="B53">
-        <v>2230</v>
+        <v>2220</v>
       </c>
       <c r="C53" t="str">
         <f>INDEX(TextData!B:B,MATCH(B53,TextData!A:A))</f>
-        <v>同時回復</v>
+        <v>即死付与</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="G53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" t="str">
         <f>INDEX(Define!B:B,MATCH(G53,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="s">
         <v>20</v>
@@ -5214,7 +5211,7 @@
         <v>0</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -5224,38 +5221,38 @@
       </c>
       <c r="U53" t="str">
         <f>TextData!B52</f>
-        <v>同時回復</v>
+        <v>即死付与</v>
       </c>
     </row>
     <row r="54" spans="1:21">
       <c r="A54">
-        <v>2240</v>
+        <v>2230</v>
       </c>
       <c r="B54">
-        <v>2240</v>
+        <v>2230</v>
       </c>
       <c r="C54" t="str">
         <f>INDEX(TextData!B:B,MATCH(B54,TextData!A:A))</f>
-        <v>必中</v>
+        <v>同時回復</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F54" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G54">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H54" t="str">
         <f>INDEX(Define!B:B,MATCH(G54,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>なし</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="s">
         <v>20</v>
@@ -5292,35 +5289,35 @@
       </c>
       <c r="U54" t="str">
         <f>TextData!B53</f>
-        <v>必中</v>
+        <v>同時回復</v>
       </c>
     </row>
     <row r="55" spans="1:21">
       <c r="A55">
-        <v>2250</v>
+        <v>2240</v>
       </c>
       <c r="B55">
-        <v>2250</v>
+        <v>2240</v>
       </c>
       <c r="C55" t="str">
         <f>INDEX(TextData!B:B,MATCH(B55,TextData!A:A))</f>
-        <v>アシストヒール</v>
+        <v>必中</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="F55" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H55" t="str">
         <f>INDEX(Define!B:B,MATCH(G55,Define!A:A))</f>
-        <v>なし</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -5360,28 +5357,28 @@
       </c>
       <c r="U55" t="str">
         <f>TextData!B54</f>
-        <v>アシストヒール</v>
+        <v>必中</v>
       </c>
     </row>
     <row r="56" spans="1:21">
       <c r="A56">
-        <v>2270</v>
+        <v>2250</v>
       </c>
       <c r="B56">
-        <v>2270</v>
+        <v>2250</v>
       </c>
       <c r="C56" t="str">
         <f>INDEX(TextData!B:B,MATCH(B56,TextData!A:A))</f>
-        <v>アンデッド</v>
+        <v>アシストヒール</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="F56" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5428,28 +5425,28 @@
       </c>
       <c r="U56" t="str">
         <f>TextData!B55</f>
-        <v>アンデッド</v>
+        <v>アシストヒール</v>
       </c>
     </row>
     <row r="57" spans="1:21">
       <c r="A57">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="B57">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="C57" t="str">
         <f>INDEX(TextData!B:B,MATCH(B57,TextData!A:A))</f>
-        <v>アクセル</v>
+        <v>アンデッド</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F57" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5496,38 +5493,38 @@
       </c>
       <c r="U57" t="str">
         <f>TextData!B56</f>
-        <v>アクセル</v>
+        <v>アンデッド</v>
       </c>
     </row>
     <row r="58" spans="1:21">
       <c r="A58">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="B58">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="C58" t="str">
         <f>INDEX(TextData!B:B,MATCH(B58,TextData!A:A))</f>
-        <v>ダメージ威力アップ</v>
+        <v>アクセル</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
+        <v>25</v>
+      </c>
+      <c r="F58" t="s">
         <v>21</v>
       </c>
-      <c r="F58" t="s">
-        <v>57</v>
-      </c>
       <c r="G58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" t="str">
         <f>INDEX(Define!B:B,MATCH(G58,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="s">
         <v>20</v>
@@ -5539,7 +5536,7 @@
         <v>1</v>
       </c>
       <c r="M58">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N58">
         <v>0</v>
@@ -5548,7 +5545,7 @@
         <v>0</v>
       </c>
       <c r="P58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -5564,35 +5561,35 @@
       </c>
       <c r="U58" t="str">
         <f>TextData!B57</f>
-        <v>ダメージ威力アップ</v>
+        <v>アクセル</v>
       </c>
     </row>
     <row r="59" spans="1:21">
       <c r="A59">
-        <v>2320</v>
+        <v>2290</v>
       </c>
       <c r="B59">
-        <v>2320</v>
+        <v>2290</v>
       </c>
       <c r="C59" t="str">
         <f>INDEX(TextData!B:B,MATCH(B59,TextData!A:A))</f>
-        <v>バフ解除</v>
+        <v>ダメージ威力アップ</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="F59">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="F59" t="s">
+        <v>56</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="str">
         <f>INDEX(Define!B:B,MATCH(G59,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I59">
         <v>1</v>
@@ -5607,7 +5604,7 @@
         <v>1</v>
       </c>
       <c r="M59">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N59">
         <v>0</v>
@@ -5616,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -5632,35 +5629,35 @@
       </c>
       <c r="U59" t="str">
         <f>TextData!B58</f>
-        <v>バフ解除</v>
+        <v>ダメージ威力アップ</v>
       </c>
     </row>
     <row r="60" spans="1:21">
       <c r="A60">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="B60">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="C60" t="str">
         <f>INDEX(TextData!B:B,MATCH(B60,TextData!A:A))</f>
-        <v>貫通</v>
+        <v>バフ解除</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>56</v>
-      </c>
-      <c r="F60" t="s">
-        <v>58</v>
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" t="str">
         <f>INDEX(Define!B:B,MATCH(G60,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I60">
         <v>1</v>
@@ -5678,7 +5675,7 @@
         <v>0</v>
       </c>
       <c r="N60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -5700,28 +5697,28 @@
       </c>
       <c r="U60" t="str">
         <f>TextData!B59</f>
-        <v>貫通</v>
+        <v>バフ解除</v>
       </c>
     </row>
     <row r="61" spans="1:21">
       <c r="A61">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="B61">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="C61" t="str">
         <f>INDEX(TextData!B:B,MATCH(B61,TextData!A:A))</f>
-        <v>対象列化</v>
+        <v>貫通</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F61" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -5768,19 +5765,19 @@
       </c>
       <c r="U61" t="str">
         <f>TextData!B60</f>
-        <v>対象列化</v>
+        <v>貫通</v>
       </c>
     </row>
     <row r="62" spans="1:21">
       <c r="A62">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="B62">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="C62" t="str">
         <f>INDEX(TextData!B:B,MATCH(B62,TextData!A:A))</f>
-        <v>対象全体化</v>
+        <v>対象列化</v>
       </c>
       <c r="D62">
         <v>0</v>
@@ -5789,7 +5786,7 @@
         <v>66</v>
       </c>
       <c r="F62" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -5836,28 +5833,28 @@
       </c>
       <c r="U62" t="str">
         <f>TextData!B61</f>
-        <v>対象全体化</v>
+        <v>対象列化</v>
       </c>
     </row>
     <row r="63" spans="1:21">
       <c r="A63">
-        <v>2350</v>
+        <v>2341</v>
       </c>
       <c r="B63">
-        <v>2350</v>
+        <v>2341</v>
       </c>
       <c r="C63" t="str">
         <f>INDEX(TextData!B:B,MATCH(B63,TextData!A:A))</f>
-        <v>聖棺</v>
+        <v>対象全体化</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F63" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -5904,28 +5901,28 @@
       </c>
       <c r="U63" t="str">
         <f>TextData!B62</f>
-        <v>聖棺</v>
+        <v>対象全体化</v>
       </c>
     </row>
     <row r="64" spans="1:21">
       <c r="A64">
-        <v>2360</v>
+        <v>2350</v>
       </c>
       <c r="B64">
-        <v>2360</v>
+        <v>2350</v>
       </c>
       <c r="C64" t="str">
         <f>INDEX(TextData!B:B,MATCH(B64,TextData!A:A))</f>
-        <v>追加ダメージ</v>
+        <v>聖棺</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F64" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -5972,28 +5969,28 @@
       </c>
       <c r="U64" t="str">
         <f>TextData!B63</f>
-        <v>追加ダメージ</v>
+        <v>聖棺</v>
       </c>
     </row>
     <row r="65" spans="1:21">
       <c r="A65">
-        <v>2370</v>
+        <v>2360</v>
       </c>
       <c r="B65">
-        <v>2370</v>
+        <v>2360</v>
       </c>
       <c r="C65" t="str">
         <f>INDEX(TextData!B:B,MATCH(B65,TextData!A:A))</f>
-        <v>追加効果</v>
+        <v>追加ダメージ</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F65" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -6040,28 +6037,28 @@
       </c>
       <c r="U65" t="str">
         <f>TextData!B64</f>
-        <v>追加効果</v>
+        <v>追加ダメージ</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66">
-        <v>2380</v>
+        <v>2370</v>
       </c>
       <c r="B66">
-        <v>2380</v>
+        <v>2370</v>
       </c>
       <c r="C66" t="str">
         <f>INDEX(TextData!B:B,MATCH(B66,TextData!A:A))</f>
-        <v>透明</v>
+        <v>追加効果</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F66" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -6108,28 +6105,28 @@
       </c>
       <c r="U66" t="str">
         <f>TextData!B65</f>
-        <v>透明</v>
+        <v>追加効果</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67">
-        <v>2390</v>
+        <v>2380</v>
       </c>
       <c r="B67">
-        <v>2390</v>
+        <v>2380</v>
       </c>
       <c r="C67" t="str">
         <f>INDEX(TextData!B:B,MATCH(B67,TextData!A:A))</f>
-        <v>沈黙</v>
+        <v>透明</v>
       </c>
       <c r="D67">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F67" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -6154,19 +6151,19 @@
         <v>0</v>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P67">
         <v>0</v>
       </c>
       <c r="Q67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S67">
         <v>0</v>
@@ -6176,28 +6173,28 @@
       </c>
       <c r="U67" t="str">
         <f>TextData!B66</f>
-        <v>沈黙</v>
+        <v>透明</v>
       </c>
     </row>
     <row r="68" spans="1:21">
       <c r="A68">
-        <v>2400</v>
+        <v>2390</v>
       </c>
       <c r="B68">
-        <v>2400</v>
+        <v>2390</v>
       </c>
       <c r="C68" t="str">
         <f>INDEX(TextData!B:B,MATCH(B68,TextData!A:A))</f>
-        <v>不治</v>
+        <v>沈黙</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F68" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -6244,19 +6241,19 @@
       </c>
       <c r="U68" t="str">
         <f>TextData!B67</f>
-        <v>不治</v>
+        <v>沈黙</v>
       </c>
     </row>
     <row r="69" spans="1:21">
       <c r="A69">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="B69">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="C69" t="str">
         <f>INDEX(TextData!B:B,MATCH(B69,TextData!A:A))</f>
-        <v>シールド</v>
+        <v>不治</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -6265,7 +6262,7 @@
         <v>0</v>
       </c>
       <c r="F69" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -6290,19 +6287,19 @@
         <v>0</v>
       </c>
       <c r="N69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -6312,19 +6309,19 @@
       </c>
       <c r="U69" t="str">
         <f>TextData!B68</f>
-        <v>シールド</v>
+        <v>不治</v>
       </c>
     </row>
     <row r="70" spans="1:21">
       <c r="A70">
-        <v>2420</v>
+        <v>2410</v>
       </c>
       <c r="B70">
-        <v>2420</v>
+        <v>2410</v>
       </c>
       <c r="C70" t="str">
         <f>INDEX(TextData!B:B,MATCH(B70,TextData!A:A))</f>
-        <v>フォロー</v>
+        <v>シールド</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -6333,7 +6330,7 @@
         <v>0</v>
       </c>
       <c r="F70" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -6380,19 +6377,19 @@
       </c>
       <c r="U70" t="str">
         <f>TextData!B69</f>
-        <v>フォロー</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="71" spans="1:21">
       <c r="A71">
-        <v>2430</v>
+        <v>2420</v>
       </c>
       <c r="B71">
-        <v>2430</v>
+        <v>2420</v>
       </c>
       <c r="C71" t="str">
         <f>INDEX(TextData!B:B,MATCH(B71,TextData!A:A))</f>
-        <v>かばう</v>
+        <v>フォロー</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -6401,14 +6398,14 @@
         <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G71">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H71" t="str">
         <f>INDEX(Define!B:B,MATCH(G71,Define!A:A))</f>
-        <v>ターンの終了</v>
+        <v>ターン数</v>
       </c>
       <c r="I71">
         <v>1</v>
@@ -6441,26 +6438,26 @@
         <v>0</v>
       </c>
       <c r="S71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T71">
         <v>1</v>
       </c>
       <c r="U71" t="str">
         <f>TextData!B70</f>
-        <v>かばう</v>
+        <v>フォロー</v>
       </c>
     </row>
     <row r="72" spans="1:21">
       <c r="A72">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="B72">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="C72" t="str">
         <f>INDEX(TextData!B:B,MATCH(B72,TextData!A:A))</f>
-        <v>Ap消費半減</v>
+        <v>かばう</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -6469,14 +6466,14 @@
         <v>0</v>
       </c>
       <c r="F72" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="G72">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H72" t="str">
         <f>INDEX(Define!B:B,MATCH(G72,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>ターンの終了</v>
       </c>
       <c r="I72">
         <v>1</v>
@@ -6506,29 +6503,29 @@
         <v>0</v>
       </c>
       <c r="R72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72">
         <v>1</v>
       </c>
       <c r="U72" t="str">
         <f>TextData!B71</f>
-        <v>Ap消費半減</v>
+        <v>かばう</v>
       </c>
     </row>
     <row r="73" spans="1:21">
       <c r="A73">
-        <v>2450</v>
+        <v>2440</v>
       </c>
       <c r="B73">
-        <v>2450</v>
+        <v>2440</v>
       </c>
       <c r="C73" t="str">
         <f>INDEX(TextData!B:B,MATCH(B73,TextData!A:A))</f>
-        <v>不死</v>
+        <v>Ap消費半減</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -6537,14 +6534,14 @@
         <v>0</v>
       </c>
       <c r="F73" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="G73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H73" t="str">
         <f>INDEX(Define!B:B,MATCH(G73,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I73">
         <v>1</v>
@@ -6584,19 +6581,19 @@
       </c>
       <c r="U73" t="str">
         <f>TextData!B72</f>
-        <v>不死</v>
+        <v>Ap消費半減</v>
       </c>
     </row>
     <row r="74" spans="1:21">
       <c r="A74">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="B74">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="C74" t="str">
         <f>INDEX(TextData!B:B,MATCH(B74,TextData!A:A))</f>
-        <v>Hp回復効果アップ</v>
+        <v>不死</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -6605,14 +6602,14 @@
         <v>0</v>
       </c>
       <c r="F74" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H74" t="str">
         <f>INDEX(Define!B:B,MATCH(G74,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I74">
         <v>1</v>
@@ -6642,7 +6639,7 @@
         <v>0</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S74">
         <v>0</v>
@@ -6652,19 +6649,19 @@
       </c>
       <c r="U74" t="str">
         <f>TextData!B73</f>
-        <v>Hp回復効果アップ</v>
+        <v>不死</v>
       </c>
     </row>
     <row r="75" spans="1:21">
       <c r="A75">
-        <v>2470</v>
+        <v>2460</v>
       </c>
       <c r="B75">
-        <v>2470</v>
+        <v>2460</v>
       </c>
       <c r="C75" t="str">
         <f>INDEX(TextData!B:B,MATCH(B75,TextData!A:A))</f>
-        <v>呪詛</v>
+        <v>Hp回復効果アップ</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -6673,14 +6670,14 @@
         <v>0</v>
       </c>
       <c r="F75" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H75" t="str">
         <f>INDEX(Define!B:B,MATCH(G75,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I75">
         <v>1</v>
@@ -6710,7 +6707,7 @@
         <v>0</v>
       </c>
       <c r="R75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -6720,19 +6717,19 @@
       </c>
       <c r="U75" t="str">
         <f>TextData!B74</f>
-        <v>呪詛</v>
+        <v>Hp回復効果アップ</v>
       </c>
     </row>
     <row r="76" spans="1:21">
       <c r="A76">
-        <v>3010</v>
+        <v>2470</v>
       </c>
       <c r="B76">
-        <v>3010</v>
+        <v>2470</v>
       </c>
       <c r="C76" t="str">
         <f>INDEX(TextData!B:B,MATCH(B76,TextData!A:A))</f>
-        <v>チャージ</v>
+        <v>呪詛</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -6741,14 +6738,14 @@
         <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H76" t="str">
         <f>INDEX(Define!B:B,MATCH(G76,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I76">
         <v>1</v>
@@ -6766,19 +6763,19 @@
         <v>0</v>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O76">
         <v>0</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q76">
         <v>0</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -6788,19 +6785,19 @@
       </c>
       <c r="U76" t="str">
         <f>TextData!B75</f>
-        <v>チャージ</v>
+        <v>呪詛</v>
       </c>
     </row>
     <row r="77" spans="1:21">
       <c r="A77">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B77">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="C77" t="str">
         <f>INDEX(TextData!B:B,MATCH(B77,TextData!A:A))</f>
-        <v>リンケージ</v>
+        <v>チャージ</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -6809,7 +6806,7 @@
         <v>0</v>
       </c>
       <c r="F77" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G77">
         <v>1</v>
@@ -6856,19 +6853,19 @@
       </c>
       <c r="U77" t="str">
         <f>TextData!B76</f>
-        <v>リンケージ</v>
+        <v>チャージ</v>
       </c>
     </row>
     <row r="78" spans="1:21">
       <c r="A78">
-        <v>9999</v>
+        <v>3020</v>
       </c>
       <c r="B78">
-        <v>9999</v>
+        <v>3020</v>
       </c>
       <c r="C78" t="str">
         <f>INDEX(TextData!B:B,MATCH(B78,TextData!A:A))</f>
-        <v>テスト用</v>
+        <v>リンケージ</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -6877,7 +6874,7 @@
         <v>0</v>
       </c>
       <c r="F78" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -6924,6 +6921,74 @@
       </c>
       <c r="U78" t="str">
         <f>TextData!B77</f>
+        <v>リンケージ</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21">
+      <c r="A79">
+        <v>9999</v>
+      </c>
+      <c r="B79">
+        <v>9999</v>
+      </c>
+      <c r="C79" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B79,TextData!A:A))</f>
+        <v>テスト用</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79" t="s">
+        <v>61</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
+      <c r="H79" t="str">
+        <f>INDEX(Define!B:B,MATCH(G79,Define!A:A))</f>
+        <v>ターン数</v>
+      </c>
+      <c r="I79">
+        <v>1</v>
+      </c>
+      <c r="J79" t="s">
+        <v>20</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>1</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79">
+        <v>0</v>
+      </c>
+      <c r="S79">
+        <v>0</v>
+      </c>
+      <c r="T79">
+        <v>1</v>
+      </c>
+      <c r="U79" t="str">
+        <f>TextData!B78</f>
         <v>テスト用</v>
       </c>
     </row>
@@ -6937,7 +7002,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="14.6363636363636" customWidth="1"/>
@@ -6948,10 +7013,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" t="s">
         <v>71</v>
-      </c>
-      <c r="C1" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -6959,7 +7024,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
@@ -6970,7 +7035,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
@@ -6981,10 +7046,10 @@
         <v>201</v>
       </c>
       <c r="B4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" t="s">
         <v>75</v>
-      </c>
-      <c r="C4" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -6992,10 +7057,10 @@
         <v>202</v>
       </c>
       <c r="B5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" t="s">
         <v>77</v>
-      </c>
-      <c r="C5" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7003,10 +7068,10 @@
         <v>203</v>
       </c>
       <c r="B6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C6" t="s">
         <v>79</v>
-      </c>
-      <c r="C6" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -7014,10 +7079,10 @@
         <v>204</v>
       </c>
       <c r="B7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" t="s">
         <v>81</v>
-      </c>
-      <c r="C7" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -7025,10 +7090,10 @@
         <v>205</v>
       </c>
       <c r="B8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" t="s">
         <v>83</v>
-      </c>
-      <c r="C8" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -7036,10 +7101,10 @@
         <v>1010</v>
       </c>
       <c r="B9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" t="s">
         <v>85</v>
-      </c>
-      <c r="C9" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -7047,10 +7112,10 @@
         <v>1011</v>
       </c>
       <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" t="s">
         <v>87</v>
-      </c>
-      <c r="C10" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7058,10 +7123,10 @@
         <v>1020</v>
       </c>
       <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
         <v>89</v>
-      </c>
-      <c r="C11" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -7069,10 +7134,10 @@
         <v>1030</v>
       </c>
       <c r="B12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" t="s">
         <v>91</v>
-      </c>
-      <c r="C12" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -7080,10 +7145,10 @@
         <v>1040</v>
       </c>
       <c r="B13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" t="s">
         <v>93</v>
-      </c>
-      <c r="C13" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -7091,10 +7156,10 @@
         <v>1041</v>
       </c>
       <c r="B14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" t="s">
         <v>95</v>
-      </c>
-      <c r="C14" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -7102,10 +7167,10 @@
         <v>1043</v>
       </c>
       <c r="B15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" t="s">
         <v>97</v>
-      </c>
-      <c r="C15" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -7113,10 +7178,10 @@
         <v>1044</v>
       </c>
       <c r="B16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" t="s">
         <v>93</v>
-      </c>
-      <c r="C16" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7124,10 +7189,10 @@
         <v>1050</v>
       </c>
       <c r="B17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" t="s">
         <v>99</v>
-      </c>
-      <c r="C17" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -7135,10 +7200,10 @@
         <v>1051</v>
       </c>
       <c r="B18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" t="s">
         <v>101</v>
-      </c>
-      <c r="C18" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -7146,647 +7211,658 @@
         <v>1052</v>
       </c>
       <c r="B19" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="B20" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="B24" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C24" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B25" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" t="s">
         <v>113</v>
-      </c>
-      <c r="C25" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B26" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C27" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B31" t="s">
+        <v>120</v>
+      </c>
+      <c r="C31" t="s">
         <v>121</v>
-      </c>
-      <c r="C31" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32">
-        <v>2010</v>
+        <v>1101</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="B34" t="s">
-        <v>125</v>
+        <v>35</v>
       </c>
       <c r="C34" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B35" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C35" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B36" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C36" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B37" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C37" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2040</v>
+        <v>2032</v>
       </c>
       <c r="B38" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="B41" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C41" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="B42" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C42" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="B43" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C43" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2120</v>
+        <v>2090</v>
       </c>
       <c r="B44" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C44" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="B45" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C45" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="B46" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C46" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2150</v>
+        <v>2140</v>
       </c>
       <c r="B47" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C47" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2180</v>
+        <v>2150</v>
       </c>
       <c r="B48" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C48" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2190</v>
+        <v>2180</v>
       </c>
       <c r="B49" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C49" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2210</v>
+        <v>2190</v>
       </c>
       <c r="B50" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C50" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2220</v>
+        <v>2210</v>
       </c>
       <c r="B51" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C51" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2230</v>
+        <v>2220</v>
       </c>
       <c r="B52" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C52" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2240</v>
+        <v>2230</v>
       </c>
       <c r="B53" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C53" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2250</v>
+        <v>2240</v>
       </c>
       <c r="B54" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C54" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2270</v>
+        <v>2250</v>
       </c>
       <c r="B55" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C55" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="B56" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C56" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="B57" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C57" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>2320</v>
+        <v>2290</v>
       </c>
       <c r="B58" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C58" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="B59" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C59" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="B60" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C60" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="B61" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C61" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>2350</v>
+        <v>2341</v>
       </c>
       <c r="B62" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C62" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>2360</v>
+        <v>2350</v>
       </c>
       <c r="B63" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C63" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>2370</v>
+        <v>2360</v>
       </c>
       <c r="B64" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C64" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>2380</v>
+        <v>2370</v>
       </c>
       <c r="B65" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C65" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>2390</v>
+        <v>2380</v>
       </c>
       <c r="B66" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C66" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>2400</v>
+        <v>2390</v>
       </c>
       <c r="B67" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C67" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="B68" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C68" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>2420</v>
+        <v>2410</v>
       </c>
       <c r="B69" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C69" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>2430</v>
+        <v>2420</v>
       </c>
       <c r="B70" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C70" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="B71" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C71" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>2450</v>
+        <v>2440</v>
       </c>
       <c r="B72" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C72" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="B73" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C73" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>2470</v>
+        <v>2460</v>
       </c>
       <c r="B74" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C74" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>3010</v>
+        <v>2470</v>
       </c>
       <c r="B75" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C75" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B76" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C76" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
+        <v>3020</v>
+      </c>
+      <c r="B77" t="s">
+        <v>208</v>
+      </c>
+      <c r="C77" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78">
         <v>9999</v>
       </c>
-      <c r="B77" t="s">
-        <v>211</v>
-      </c>
-      <c r="C77" t="s">
+      <c r="B78" t="s">
+        <v>210</v>
+      </c>
+      <c r="C78" t="s">
         <v>20</v>
       </c>
     </row>
@@ -7812,7 +7888,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7820,7 +7896,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7828,7 +7904,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7836,7 +7912,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -7844,7 +7920,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -7852,7 +7928,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -7860,7 +7936,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="220">
   <si>
     <t>Id</t>
   </si>
@@ -634,6 +634,12 @@
   </si>
   <si>
     <t>戦闘不能を回避し反撃ダメージ</t>
+  </si>
+  <si>
+    <t>ステータス交換</t>
+  </si>
+  <si>
+    <t>ステータス値を交換する</t>
   </si>
   <si>
     <t>チャージ</t>
@@ -691,8 +697,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -700,14 +722,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -723,13 +737,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -737,16 +744,30 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -759,8 +780,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -776,14 +820,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -791,45 +827,15 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -850,7 +856,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -862,43 +916,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -910,25 +928,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -940,49 +940,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1000,7 +964,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1012,19 +976,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1035,15 +1041,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1058,6 +1055,24 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1077,11 +1092,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1111,30 +1141,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1143,7 +1149,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1152,136 +1158,136 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -6852,7 +6858,7 @@
         <v>1</v>
       </c>
       <c r="U77" t="str">
-        <f>TextData!B76</f>
+        <f>TextData!B77</f>
         <v>チャージ</v>
       </c>
     </row>
@@ -6920,7 +6926,7 @@
         <v>1</v>
       </c>
       <c r="U78" t="str">
-        <f>TextData!B77</f>
+        <f>TextData!B78</f>
         <v>リンケージ</v>
       </c>
     </row>
@@ -6988,7 +6994,7 @@
         <v>1</v>
       </c>
       <c r="U79" t="str">
-        <f>TextData!B78</f>
+        <f>TextData!B79</f>
         <v>テスト用</v>
       </c>
     </row>
@@ -7002,7 +7008,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="14.6363636363636" customWidth="1"/>
@@ -7835,7 +7841,7 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>3010</v>
+        <v>2480</v>
       </c>
       <c r="B76" t="s">
         <v>206</v>
@@ -7846,7 +7852,7 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B77" t="s">
         <v>208</v>
@@ -7857,12 +7863,23 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>9999</v>
+        <v>3020</v>
       </c>
       <c r="B78" t="s">
         <v>210</v>
       </c>
       <c r="C78" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79">
+        <v>9999</v>
+      </c>
+      <c r="B79" t="s">
+        <v>212</v>
+      </c>
+      <c r="C79" t="s">
         <v>20</v>
       </c>
     </row>
@@ -7888,7 +7905,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7896,7 +7913,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7904,7 +7921,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7912,7 +7929,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -7920,7 +7937,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -7928,7 +7945,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -7936,7 +7953,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="222">
   <si>
     <t>Id</t>
   </si>
@@ -387,6 +387,12 @@
     <t>被ダメージを\dカットする</t>
   </si>
   <si>
+    <t>火傷耐性</t>
+  </si>
+  <si>
+    <t>火傷ダメージを\d%カットする</t>
+  </si>
+  <si>
     <t>行動後ダメージ</t>
   </si>
   <si>
@@ -636,10 +642,10 @@
     <t>戦闘不能を回避し反撃ダメージ</t>
   </si>
   <si>
-    <t>ステータス交換</t>
-  </si>
-  <si>
-    <t>ステータス値を交換する</t>
+    <t>付与無効化</t>
+  </si>
+  <si>
+    <t>対象の状態にならない</t>
   </si>
   <si>
     <t>チャージ</t>
@@ -698,7 +704,7 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -706,7 +712,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -720,17 +726,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -744,25 +756,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -782,14 +779,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -798,21 +796,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -835,9 +818,32 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -856,7 +862,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -868,7 +874,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -880,19 +898,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -904,13 +916,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -928,7 +940,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -940,43 +1006,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -988,7 +1018,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1000,37 +1036,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1062,17 +1068,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1092,17 +1104,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1110,8 +1116,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1149,7 +1155,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1158,13 +1164,13 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
@@ -1173,121 +1179,121 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1614,7 +1620,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U79"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="21.8181818181818" customWidth="1"/>
@@ -3806,20 +3812,20 @@
     </row>
     <row r="33" ht="12" customHeight="1" spans="1:21">
       <c r="A33">
-        <v>2010</v>
+        <v>1210</v>
       </c>
       <c r="B33">
-        <v>2010</v>
+        <v>1210</v>
       </c>
       <c r="C33" t="str">
         <f>INDEX(TextData!B:B,MATCH(B33,TextData!A:A))</f>
-        <v>毒</v>
+        <v>火傷耐性</v>
       </c>
       <c r="D33">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="F33" t="s">
         <v>32</v>
@@ -3835,10 +3841,10 @@
         <v>1</v>
       </c>
       <c r="J33" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33">
         <v>1</v>
@@ -3847,19 +3853,19 @@
         <v>0</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33">
         <v>0</v>
@@ -3869,18 +3875,19 @@
       </c>
       <c r="U33" t="str">
         <f>TextData!B33</f>
-        <v>毒</v>
+        <v>火傷耐性</v>
       </c>
     </row>
     <row r="34" ht="12" customHeight="1" spans="1:21">
       <c r="A34">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B34">
         <v>2010</v>
       </c>
-      <c r="C34" t="s">
-        <v>34</v>
+      <c r="C34" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B34,TextData!A:A))</f>
+        <v>毒</v>
       </c>
       <c r="D34">
         <v>26</v>
@@ -3935,25 +3942,25 @@
         <v>1</v>
       </c>
       <c r="U34" t="str">
-        <f>TextData!B33</f>
+        <f>TextData!B34</f>
         <v>毒</v>
       </c>
     </row>
     <row r="35" ht="12" customHeight="1" spans="1:21">
       <c r="A35">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B35">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E35">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="F35" t="s">
         <v>32</v>
@@ -4003,47 +4010,46 @@
       </c>
       <c r="U35" t="str">
         <f>TextData!B34</f>
-        <v>火傷</v>
+        <v>毒</v>
       </c>
     </row>
     <row r="36" ht="12" customHeight="1" spans="1:21">
       <c r="A36">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="B36">
-        <v>2020</v>
-      </c>
-      <c r="C36" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B36,TextData!A:A))</f>
-        <v>暗闇</v>
+        <v>2012</v>
+      </c>
+      <c r="C36" t="s">
+        <v>35</v>
       </c>
       <c r="D36">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="F36" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H36" t="str">
         <f>INDEX(Define!B:B,MATCH(G36,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I36">
         <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -4071,47 +4077,47 @@
       </c>
       <c r="U36" t="str">
         <f>TextData!B35</f>
-        <v>暗闇</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21">
+        <v>火傷</v>
+      </c>
+    </row>
+    <row r="37" ht="12" customHeight="1" spans="1:21">
       <c r="A37">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B37">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="C37" t="str">
         <f>INDEX(TextData!B:B,MATCH(B37,TextData!A:A))</f>
-        <v>カウンタ</v>
+        <v>暗闇</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E37">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="F37" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H37" t="str">
         <f>INDEX(Define!B:B,MATCH(G37,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K37">
         <v>0</v>
       </c>
       <c r="L37">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -4120,16 +4126,16 @@
         <v>0</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P37">
         <v>0</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -4139,19 +4145,19 @@
       </c>
       <c r="U37" t="str">
         <f>TextData!B36</f>
-        <v>カウンタ</v>
+        <v>暗闇</v>
       </c>
     </row>
     <row r="38" spans="1:21">
       <c r="A38">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B38">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C38" t="str">
         <f>INDEX(TextData!B:B,MATCH(B38,TextData!A:A))</f>
-        <v>CAダメージ</v>
+        <v>カウンタ</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -4170,10 +4176,10 @@
         <v>ターン数</v>
       </c>
       <c r="I38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -4207,19 +4213,19 @@
       </c>
       <c r="U38" t="str">
         <f>TextData!B37</f>
-        <v>CAダメージ</v>
+        <v>カウンタ</v>
       </c>
     </row>
     <row r="39" spans="1:21">
       <c r="A39">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B39">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="C39" t="str">
         <f>INDEX(TextData!B:B,MATCH(B39,TextData!A:A))</f>
-        <v>CAシェル</v>
+        <v>CAダメージ</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -4228,14 +4234,14 @@
         <v>66</v>
       </c>
       <c r="F39" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="str">
         <f>INDEX(Define!B:B,MATCH(G39,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I39">
         <v>1</v>
@@ -4275,35 +4281,35 @@
       </c>
       <c r="U39" t="str">
         <f>TextData!B38</f>
-        <v>CAシェル</v>
+        <v>CAダメージ</v>
       </c>
     </row>
     <row r="40" spans="1:21">
       <c r="A40">
-        <v>2040</v>
+        <v>2032</v>
       </c>
       <c r="B40">
-        <v>2040</v>
+        <v>2032</v>
       </c>
       <c r="C40" t="str">
         <f>INDEX(TextData!B:B,MATCH(B40,TextData!A:A))</f>
-        <v>リジェネ</v>
+        <v>CAシェル</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="F40" t="s">
         <v>39</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="str">
         <f>INDEX(Define!B:B,MATCH(G40,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I40">
         <v>1</v>
@@ -4343,41 +4349,41 @@
       </c>
       <c r="U40" t="str">
         <f>TextData!B39</f>
-        <v>リジェネ</v>
+        <v>CAシェル</v>
       </c>
     </row>
     <row r="41" spans="1:21">
       <c r="A41">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="B41">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C41" t="str">
         <f>INDEX(TextData!B:B,MATCH(B41,TextData!A:A))</f>
-        <v>攻撃無効</v>
+        <v>リジェネ</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>226</v>
+        <v>46</v>
       </c>
       <c r="F41" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H41" t="str">
         <f>INDEX(Define!B:B,MATCH(G41,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -4411,41 +4417,41 @@
       </c>
       <c r="U41" t="str">
         <f>TextData!B40</f>
-        <v>攻撃無効</v>
+        <v>リジェネ</v>
       </c>
     </row>
     <row r="42" spans="1:21">
       <c r="A42">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="B42">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="C42" t="str">
         <f>INDEX(TextData!B:B,MATCH(B42,TextData!A:A))</f>
-        <v>ドレイン</v>
+        <v>攻撃無効</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>167</v>
+        <v>226</v>
       </c>
       <c r="F42" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H42" t="str">
         <f>INDEX(Define!B:B,MATCH(G42,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -4479,28 +4485,28 @@
       </c>
       <c r="U42" t="str">
         <f>TextData!B41</f>
-        <v>ドレイン</v>
+        <v>攻撃無効</v>
       </c>
     </row>
     <row r="43" spans="1:21">
       <c r="A43">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="B43">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="C43" t="str">
         <f>INDEX(TextData!B:B,MATCH(B43,TextData!A:A))</f>
-        <v>状態異常CA</v>
+        <v>ドレイン</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>226</v>
+        <v>167</v>
       </c>
       <c r="F43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -4510,7 +4516,7 @@
         <v>ターン数</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="s">
         <v>20</v>
@@ -4547,35 +4553,35 @@
       </c>
       <c r="U43" t="str">
         <f>TextData!B42</f>
-        <v>状態異常CA</v>
+        <v>ドレイン</v>
       </c>
     </row>
     <row r="44" spans="1:21">
       <c r="A44">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="B44">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="C44" t="str">
         <f>INDEX(TextData!B:B,MATCH(B44,TextData!A:A))</f>
-        <v>反撃</v>
+        <v>状態異常CA</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>226</v>
       </c>
       <c r="F44" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H44" t="str">
         <f>INDEX(Define!B:B,MATCH(G44,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -4615,28 +4621,28 @@
       </c>
       <c r="U44" t="str">
         <f>TextData!B43</f>
-        <v>反撃</v>
+        <v>状態異常CA</v>
       </c>
     </row>
     <row r="45" spans="1:21">
       <c r="A45">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="B45">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="C45" t="str">
         <f>INDEX(TextData!B:B,MATCH(B45,TextData!A:A))</f>
-        <v>パッシブ封じ</v>
+        <v>反撃</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F45" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G45">
         <v>4</v>
@@ -4664,16 +4670,16 @@
         <v>0</v>
       </c>
       <c r="O45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P45">
         <v>0</v>
       </c>
       <c r="Q45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45">
         <v>0</v>
@@ -4683,28 +4689,28 @@
       </c>
       <c r="U45" t="str">
         <f>TextData!B44</f>
-        <v>パッシブ封じ</v>
+        <v>反撃</v>
       </c>
     </row>
     <row r="46" spans="1:21">
       <c r="A46">
-        <v>2120</v>
+        <v>2090</v>
       </c>
       <c r="B46">
-        <v>2120</v>
+        <v>2090</v>
       </c>
       <c r="C46" t="str">
         <f>INDEX(TextData!B:B,MATCH(B46,TextData!A:A))</f>
-        <v>デバフ強化</v>
+        <v>パッシブ封じ</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G46">
         <v>4</v>
@@ -4714,16 +4720,16 @@
         <v>効果発揮回数</v>
       </c>
       <c r="I46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="K46">
         <v>0</v>
       </c>
       <c r="L46">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M46">
         <v>0</v>
@@ -4732,13 +4738,13 @@
         <v>0</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P46">
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46">
         <v>1</v>
@@ -4751,47 +4757,47 @@
       </c>
       <c r="U46" t="str">
         <f>TextData!B45</f>
-        <v>デバフ強化</v>
+        <v>パッシブ封じ</v>
       </c>
     </row>
     <row r="47" spans="1:21">
       <c r="A47">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="B47">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="C47" t="str">
         <f>INDEX(TextData!B:B,MATCH(B47,TextData!A:A))</f>
-        <v>挑発</v>
+        <v>デバフ強化</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
+        <v>9</v>
+      </c>
+      <c r="F47" t="s">
+        <v>45</v>
+      </c>
+      <c r="G47">
         <v>4</v>
-      </c>
-      <c r="F47" t="s">
-        <v>47</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
       </c>
       <c r="H47" t="str">
         <f>INDEX(Define!B:B,MATCH(G47,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="K47">
         <v>0</v>
       </c>
       <c r="L47">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="M47">
         <v>0</v>
@@ -4819,41 +4825,41 @@
       </c>
       <c r="U47" t="str">
         <f>TextData!B46</f>
-        <v>挑発</v>
+        <v>デバフ強化</v>
       </c>
     </row>
     <row r="48" spans="1:21">
       <c r="A48">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="B48">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="C48" t="str">
         <f>INDEX(TextData!B:B,MATCH(B48,TextData!A:A))</f>
-        <v>凍結</v>
+        <v>挑発</v>
       </c>
       <c r="D48">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E48">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="F48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H48" t="str">
         <f>INDEX(Define!B:B,MATCH(G48,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -4868,13 +4874,13 @@
         <v>0</v>
       </c>
       <c r="O48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P48">
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48">
         <v>1</v>
@@ -4887,41 +4893,41 @@
       </c>
       <c r="U48" t="str">
         <f>TextData!B47</f>
-        <v>凍結</v>
+        <v>挑発</v>
       </c>
     </row>
     <row r="49" spans="1:21">
       <c r="A49">
-        <v>2150</v>
+        <v>2140</v>
       </c>
       <c r="B49">
-        <v>2150</v>
+        <v>2140</v>
       </c>
       <c r="C49" t="str">
         <f>INDEX(TextData!B:B,MATCH(B49,TextData!A:A))</f>
-        <v>スタン</v>
+        <v>凍結</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E49">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="F49" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H49" t="str">
         <f>INDEX(Define!B:B,MATCH(G49,Define!A:A))</f>
-        <v>APカウント</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -4955,41 +4961,41 @@
       </c>
       <c r="U49" t="str">
         <f>TextData!B48</f>
-        <v>スタン</v>
+        <v>凍結</v>
       </c>
     </row>
     <row r="50" spans="1:21">
       <c r="A50">
-        <v>2180</v>
+        <v>2150</v>
       </c>
       <c r="B50">
-        <v>2180</v>
+        <v>2150</v>
       </c>
       <c r="C50" t="str">
         <f>INDEX(TextData!B:B,MATCH(B50,TextData!A:A))</f>
-        <v>状態異常回避</v>
+        <v>スタン</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="F50" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G50">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H50" t="str">
         <f>INDEX(Define!B:B,MATCH(G50,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>APカウント</v>
       </c>
       <c r="I50">
         <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="K50">
         <v>0</v>
@@ -5004,16 +5010,16 @@
         <v>0</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P50">
         <v>0</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -5023,35 +5029,35 @@
       </c>
       <c r="U50" t="str">
         <f>TextData!B49</f>
-        <v>状態異常回避</v>
+        <v>スタン</v>
       </c>
     </row>
     <row r="51" spans="1:21">
       <c r="A51">
-        <v>2190</v>
+        <v>2180</v>
       </c>
       <c r="B51">
-        <v>2190</v>
+        <v>2180</v>
       </c>
       <c r="C51" t="str">
         <f>INDEX(TextData!B:B,MATCH(B51,TextData!A:A))</f>
-        <v>対象範囲延長</v>
+        <v>状態異常回避</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="F51" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H51" t="str">
         <f>INDEX(Define!B:B,MATCH(G51,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -5087,32 +5093,32 @@
         <v>0</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U51" t="str">
         <f>TextData!B50</f>
-        <v>対象範囲延長</v>
+        <v>状態異常回避</v>
       </c>
     </row>
     <row r="52" spans="1:21">
       <c r="A52">
-        <v>2210</v>
+        <v>2190</v>
       </c>
       <c r="B52">
-        <v>2210</v>
+        <v>2190</v>
       </c>
       <c r="C52" t="str">
         <f>INDEX(TextData!B:B,MATCH(B52,TextData!A:A))</f>
-        <v>アフターヒール</v>
+        <v>対象範囲延長</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F52" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -5122,7 +5128,7 @@
         <v>ターン数</v>
       </c>
       <c r="I52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J52" t="s">
         <v>20</v>
@@ -5155,32 +5161,32 @@
         <v>0</v>
       </c>
       <c r="T52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U52" t="str">
         <f>TextData!B51</f>
-        <v>アフターヒール</v>
+        <v>対象範囲延長</v>
       </c>
     </row>
     <row r="53" spans="1:21">
       <c r="A53">
-        <v>2220</v>
+        <v>2210</v>
       </c>
       <c r="B53">
-        <v>2220</v>
+        <v>2210</v>
       </c>
       <c r="C53" t="str">
         <f>INDEX(TextData!B:B,MATCH(B53,TextData!A:A))</f>
-        <v>即死付与</v>
+        <v>アフターヒール</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="F53" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -5190,7 +5196,7 @@
         <v>ターン数</v>
       </c>
       <c r="I53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" t="s">
         <v>20</v>
@@ -5217,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="R53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -5227,38 +5233,38 @@
       </c>
       <c r="U53" t="str">
         <f>TextData!B52</f>
-        <v>即死付与</v>
+        <v>アフターヒール</v>
       </c>
     </row>
     <row r="54" spans="1:21">
       <c r="A54">
-        <v>2230</v>
+        <v>2220</v>
       </c>
       <c r="B54">
-        <v>2230</v>
+        <v>2220</v>
       </c>
       <c r="C54" t="str">
         <f>INDEX(TextData!B:B,MATCH(B54,TextData!A:A))</f>
-        <v>同時回復</v>
+        <v>即死付与</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" t="str">
         <f>INDEX(Define!B:B,MATCH(G54,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="s">
         <v>20</v>
@@ -5285,7 +5291,7 @@
         <v>0</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54">
         <v>0</v>
@@ -5295,38 +5301,38 @@
       </c>
       <c r="U54" t="str">
         <f>TextData!B53</f>
-        <v>同時回復</v>
+        <v>即死付与</v>
       </c>
     </row>
     <row r="55" spans="1:21">
       <c r="A55">
-        <v>2240</v>
+        <v>2230</v>
       </c>
       <c r="B55">
-        <v>2240</v>
+        <v>2230</v>
       </c>
       <c r="C55" t="str">
         <f>INDEX(TextData!B:B,MATCH(B55,TextData!A:A))</f>
-        <v>必中</v>
+        <v>同時回復</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F55" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G55">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H55" t="str">
         <f>INDEX(Define!B:B,MATCH(G55,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>なし</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="s">
         <v>20</v>
@@ -5363,35 +5369,35 @@
       </c>
       <c r="U55" t="str">
         <f>TextData!B54</f>
-        <v>必中</v>
+        <v>同時回復</v>
       </c>
     </row>
     <row r="56" spans="1:21">
       <c r="A56">
-        <v>2250</v>
+        <v>2240</v>
       </c>
       <c r="B56">
-        <v>2250</v>
+        <v>2240</v>
       </c>
       <c r="C56" t="str">
         <f>INDEX(TextData!B:B,MATCH(B56,TextData!A:A))</f>
-        <v>アシストヒール</v>
+        <v>必中</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="F56" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H56" t="str">
         <f>INDEX(Define!B:B,MATCH(G56,Define!A:A))</f>
-        <v>なし</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -5431,28 +5437,28 @@
       </c>
       <c r="U56" t="str">
         <f>TextData!B55</f>
-        <v>アシストヒール</v>
+        <v>必中</v>
       </c>
     </row>
     <row r="57" spans="1:21">
       <c r="A57">
-        <v>2270</v>
+        <v>2250</v>
       </c>
       <c r="B57">
-        <v>2270</v>
+        <v>2250</v>
       </c>
       <c r="C57" t="str">
         <f>INDEX(TextData!B:B,MATCH(B57,TextData!A:A))</f>
-        <v>アンデッド</v>
+        <v>アシストヒール</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="F57" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5499,28 +5505,28 @@
       </c>
       <c r="U57" t="str">
         <f>TextData!B56</f>
-        <v>アンデッド</v>
+        <v>アシストヒール</v>
       </c>
     </row>
     <row r="58" spans="1:21">
       <c r="A58">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="B58">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="C58" t="str">
         <f>INDEX(TextData!B:B,MATCH(B58,TextData!A:A))</f>
-        <v>アクセル</v>
+        <v>アンデッド</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F58" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -5567,38 +5573,38 @@
       </c>
       <c r="U58" t="str">
         <f>TextData!B57</f>
-        <v>アクセル</v>
+        <v>アンデッド</v>
       </c>
     </row>
     <row r="59" spans="1:21">
       <c r="A59">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="B59">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="C59" t="str">
         <f>INDEX(TextData!B:B,MATCH(B59,TextData!A:A))</f>
-        <v>ダメージ威力アップ</v>
+        <v>アクセル</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
+        <v>25</v>
+      </c>
+      <c r="F59" t="s">
         <v>21</v>
       </c>
-      <c r="F59" t="s">
-        <v>56</v>
-      </c>
       <c r="G59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="str">
         <f>INDEX(Define!B:B,MATCH(G59,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" t="s">
         <v>20</v>
@@ -5610,7 +5616,7 @@
         <v>1</v>
       </c>
       <c r="M59">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N59">
         <v>0</v>
@@ -5619,7 +5625,7 @@
         <v>0</v>
       </c>
       <c r="P59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q59">
         <v>0</v>
@@ -5635,35 +5641,35 @@
       </c>
       <c r="U59" t="str">
         <f>TextData!B58</f>
-        <v>ダメージ威力アップ</v>
+        <v>アクセル</v>
       </c>
     </row>
     <row r="60" spans="1:21">
       <c r="A60">
-        <v>2320</v>
+        <v>2290</v>
       </c>
       <c r="B60">
-        <v>2320</v>
+        <v>2290</v>
       </c>
       <c r="C60" t="str">
         <f>INDEX(TextData!B:B,MATCH(B60,TextData!A:A))</f>
-        <v>バフ解除</v>
+        <v>ダメージ威力アップ</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>0</v>
-      </c>
-      <c r="F60">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="F60" t="s">
+        <v>56</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" t="str">
         <f>INDEX(Define!B:B,MATCH(G60,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I60">
         <v>1</v>
@@ -5678,7 +5684,7 @@
         <v>1</v>
       </c>
       <c r="M60">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N60">
         <v>0</v>
@@ -5687,7 +5693,7 @@
         <v>0</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -5703,35 +5709,35 @@
       </c>
       <c r="U60" t="str">
         <f>TextData!B59</f>
-        <v>バフ解除</v>
+        <v>ダメージ威力アップ</v>
       </c>
     </row>
     <row r="61" spans="1:21">
       <c r="A61">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="B61">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="C61" t="str">
         <f>INDEX(TextData!B:B,MATCH(B61,TextData!A:A))</f>
-        <v>貫通</v>
+        <v>バフ解除</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>56</v>
-      </c>
-      <c r="F61" t="s">
-        <v>57</v>
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>1</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="str">
         <f>INDEX(Define!B:B,MATCH(G61,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I61">
         <v>1</v>
@@ -5749,7 +5755,7 @@
         <v>0</v>
       </c>
       <c r="N61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -5771,28 +5777,28 @@
       </c>
       <c r="U61" t="str">
         <f>TextData!B60</f>
-        <v>貫通</v>
+        <v>バフ解除</v>
       </c>
     </row>
     <row r="62" spans="1:21">
       <c r="A62">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="B62">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="C62" t="str">
         <f>INDEX(TextData!B:B,MATCH(B62,TextData!A:A))</f>
-        <v>対象列化</v>
+        <v>貫通</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F62" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -5839,19 +5845,19 @@
       </c>
       <c r="U62" t="str">
         <f>TextData!B61</f>
-        <v>対象列化</v>
+        <v>貫通</v>
       </c>
     </row>
     <row r="63" spans="1:21">
       <c r="A63">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="B63">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="C63" t="str">
         <f>INDEX(TextData!B:B,MATCH(B63,TextData!A:A))</f>
-        <v>対象全体化</v>
+        <v>対象列化</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -5860,7 +5866,7 @@
         <v>66</v>
       </c>
       <c r="F63" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -5907,28 +5913,28 @@
       </c>
       <c r="U63" t="str">
         <f>TextData!B62</f>
-        <v>対象全体化</v>
+        <v>対象列化</v>
       </c>
     </row>
     <row r="64" spans="1:21">
       <c r="A64">
-        <v>2350</v>
+        <v>2341</v>
       </c>
       <c r="B64">
-        <v>2350</v>
+        <v>2341</v>
       </c>
       <c r="C64" t="str">
         <f>INDEX(TextData!B:B,MATCH(B64,TextData!A:A))</f>
-        <v>聖棺</v>
+        <v>対象全体化</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F64" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -5975,28 +5981,28 @@
       </c>
       <c r="U64" t="str">
         <f>TextData!B63</f>
-        <v>聖棺</v>
+        <v>対象全体化</v>
       </c>
     </row>
     <row r="65" spans="1:21">
       <c r="A65">
-        <v>2360</v>
+        <v>2350</v>
       </c>
       <c r="B65">
-        <v>2360</v>
+        <v>2350</v>
       </c>
       <c r="C65" t="str">
         <f>INDEX(TextData!B:B,MATCH(B65,TextData!A:A))</f>
-        <v>追加ダメージ</v>
+        <v>聖棺</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F65" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -6043,25 +6049,25 @@
       </c>
       <c r="U65" t="str">
         <f>TextData!B64</f>
-        <v>追加ダメージ</v>
+        <v>聖棺</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66">
-        <v>2370</v>
+        <v>2360</v>
       </c>
       <c r="B66">
-        <v>2370</v>
+        <v>2360</v>
       </c>
       <c r="C66" t="str">
         <f>INDEX(TextData!B:B,MATCH(B66,TextData!A:A))</f>
-        <v>追加効果</v>
+        <v>追加ダメージ</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F66" t="s">
         <v>61</v>
@@ -6111,28 +6117,28 @@
       </c>
       <c r="U66" t="str">
         <f>TextData!B65</f>
-        <v>追加効果</v>
+        <v>追加ダメージ</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67">
-        <v>2380</v>
+        <v>2370</v>
       </c>
       <c r="B67">
-        <v>2380</v>
+        <v>2370</v>
       </c>
       <c r="C67" t="str">
         <f>INDEX(TextData!B:B,MATCH(B67,TextData!A:A))</f>
-        <v>透明</v>
+        <v>追加効果</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F67" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -6179,28 +6185,28 @@
       </c>
       <c r="U67" t="str">
         <f>TextData!B66</f>
-        <v>透明</v>
+        <v>追加効果</v>
       </c>
     </row>
     <row r="68" spans="1:21">
       <c r="A68">
-        <v>2390</v>
+        <v>2380</v>
       </c>
       <c r="B68">
-        <v>2390</v>
+        <v>2380</v>
       </c>
       <c r="C68" t="str">
         <f>INDEX(TextData!B:B,MATCH(B68,TextData!A:A))</f>
-        <v>沈黙</v>
+        <v>透明</v>
       </c>
       <c r="D68">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E68">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F68" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -6225,19 +6231,19 @@
         <v>0</v>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P68">
         <v>0</v>
       </c>
       <c r="Q68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S68">
         <v>0</v>
@@ -6247,28 +6253,28 @@
       </c>
       <c r="U68" t="str">
         <f>TextData!B67</f>
-        <v>沈黙</v>
+        <v>透明</v>
       </c>
     </row>
     <row r="69" spans="1:21">
       <c r="A69">
-        <v>2400</v>
+        <v>2390</v>
       </c>
       <c r="B69">
-        <v>2400</v>
+        <v>2390</v>
       </c>
       <c r="C69" t="str">
         <f>INDEX(TextData!B:B,MATCH(B69,TextData!A:A))</f>
-        <v>不治</v>
+        <v>沈黙</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F69" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -6315,19 +6321,19 @@
       </c>
       <c r="U69" t="str">
         <f>TextData!B68</f>
-        <v>不治</v>
+        <v>沈黙</v>
       </c>
     </row>
     <row r="70" spans="1:21">
       <c r="A70">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="B70">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="C70" t="str">
         <f>INDEX(TextData!B:B,MATCH(B70,TextData!A:A))</f>
-        <v>シールド</v>
+        <v>不治</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -6336,7 +6342,7 @@
         <v>0</v>
       </c>
       <c r="F70" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -6361,19 +6367,19 @@
         <v>0</v>
       </c>
       <c r="N70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -6383,19 +6389,19 @@
       </c>
       <c r="U70" t="str">
         <f>TextData!B69</f>
-        <v>シールド</v>
+        <v>不治</v>
       </c>
     </row>
     <row r="71" spans="1:21">
       <c r="A71">
-        <v>2420</v>
+        <v>2410</v>
       </c>
       <c r="B71">
-        <v>2420</v>
+        <v>2410</v>
       </c>
       <c r="C71" t="str">
         <f>INDEX(TextData!B:B,MATCH(B71,TextData!A:A))</f>
-        <v>フォロー</v>
+        <v>シールド</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -6404,7 +6410,7 @@
         <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -6451,19 +6457,19 @@
       </c>
       <c r="U71" t="str">
         <f>TextData!B70</f>
-        <v>フォロー</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="72" spans="1:21">
       <c r="A72">
-        <v>2430</v>
+        <v>2420</v>
       </c>
       <c r="B72">
-        <v>2430</v>
+        <v>2420</v>
       </c>
       <c r="C72" t="str">
         <f>INDEX(TextData!B:B,MATCH(B72,TextData!A:A))</f>
-        <v>かばう</v>
+        <v>フォロー</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -6472,14 +6478,14 @@
         <v>0</v>
       </c>
       <c r="F72" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G72">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H72" t="str">
         <f>INDEX(Define!B:B,MATCH(G72,Define!A:A))</f>
-        <v>ターンの終了</v>
+        <v>ターン数</v>
       </c>
       <c r="I72">
         <v>1</v>
@@ -6512,26 +6518,26 @@
         <v>0</v>
       </c>
       <c r="S72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T72">
         <v>1</v>
       </c>
       <c r="U72" t="str">
         <f>TextData!B71</f>
-        <v>かばう</v>
+        <v>フォロー</v>
       </c>
     </row>
     <row r="73" spans="1:21">
       <c r="A73">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="B73">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="C73" t="str">
         <f>INDEX(TextData!B:B,MATCH(B73,TextData!A:A))</f>
-        <v>Ap消費半減</v>
+        <v>かばう</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -6540,14 +6546,14 @@
         <v>0</v>
       </c>
       <c r="F73" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H73" t="str">
         <f>INDEX(Define!B:B,MATCH(G73,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>ターンの終了</v>
       </c>
       <c r="I73">
         <v>1</v>
@@ -6577,29 +6583,29 @@
         <v>0</v>
       </c>
       <c r="R73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73">
         <v>1</v>
       </c>
       <c r="U73" t="str">
         <f>TextData!B72</f>
-        <v>Ap消費半減</v>
+        <v>かばう</v>
       </c>
     </row>
     <row r="74" spans="1:21">
       <c r="A74">
-        <v>2450</v>
+        <v>2440</v>
       </c>
       <c r="B74">
-        <v>2450</v>
+        <v>2440</v>
       </c>
       <c r="C74" t="str">
         <f>INDEX(TextData!B:B,MATCH(B74,TextData!A:A))</f>
-        <v>不死</v>
+        <v>Ap消費半減</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -6608,14 +6614,14 @@
         <v>0</v>
       </c>
       <c r="F74" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H74" t="str">
         <f>INDEX(Define!B:B,MATCH(G74,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I74">
         <v>1</v>
@@ -6655,19 +6661,19 @@
       </c>
       <c r="U74" t="str">
         <f>TextData!B73</f>
-        <v>不死</v>
+        <v>Ap消費半減</v>
       </c>
     </row>
     <row r="75" spans="1:21">
       <c r="A75">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="B75">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="C75" t="str">
         <f>INDEX(TextData!B:B,MATCH(B75,TextData!A:A))</f>
-        <v>Hp回復効果アップ</v>
+        <v>不死</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -6676,14 +6682,14 @@
         <v>0</v>
       </c>
       <c r="F75" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H75" t="str">
         <f>INDEX(Define!B:B,MATCH(G75,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I75">
         <v>1</v>
@@ -6713,7 +6719,7 @@
         <v>0</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S75">
         <v>0</v>
@@ -6723,19 +6729,19 @@
       </c>
       <c r="U75" t="str">
         <f>TextData!B74</f>
-        <v>Hp回復効果アップ</v>
+        <v>不死</v>
       </c>
     </row>
     <row r="76" spans="1:21">
       <c r="A76">
-        <v>2470</v>
+        <v>2460</v>
       </c>
       <c r="B76">
-        <v>2470</v>
+        <v>2460</v>
       </c>
       <c r="C76" t="str">
         <f>INDEX(TextData!B:B,MATCH(B76,TextData!A:A))</f>
-        <v>呪詛</v>
+        <v>Hp回復効果アップ</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -6744,14 +6750,14 @@
         <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H76" t="str">
         <f>INDEX(Define!B:B,MATCH(G76,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I76">
         <v>1</v>
@@ -6781,7 +6787,7 @@
         <v>0</v>
       </c>
       <c r="R76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -6791,19 +6797,19 @@
       </c>
       <c r="U76" t="str">
         <f>TextData!B75</f>
-        <v>呪詛</v>
+        <v>Hp回復効果アップ</v>
       </c>
     </row>
     <row r="77" spans="1:21">
       <c r="A77">
-        <v>3010</v>
+        <v>2470</v>
       </c>
       <c r="B77">
-        <v>3010</v>
+        <v>2470</v>
       </c>
       <c r="C77" t="str">
         <f>INDEX(TextData!B:B,MATCH(B77,TextData!A:A))</f>
-        <v>チャージ</v>
+        <v>呪詛</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -6812,14 +6818,14 @@
         <v>0</v>
       </c>
       <c r="F77" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H77" t="str">
         <f>INDEX(Define!B:B,MATCH(G77,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I77">
         <v>1</v>
@@ -6837,19 +6843,19 @@
         <v>0</v>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O77">
         <v>0</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q77">
         <v>0</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -6858,29 +6864,29 @@
         <v>1</v>
       </c>
       <c r="U77" t="str">
-        <f>TextData!B77</f>
-        <v>チャージ</v>
+        <f>TextData!B76</f>
+        <v>呪詛</v>
       </c>
     </row>
     <row r="78" spans="1:21">
       <c r="A78">
-        <v>3020</v>
+        <v>2480</v>
       </c>
       <c r="B78">
-        <v>3020</v>
+        <v>2480</v>
       </c>
       <c r="C78" t="str">
         <f>INDEX(TextData!B:B,MATCH(B78,TextData!A:A))</f>
-        <v>リンケージ</v>
+        <v>付与無効化</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="F78" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -6905,19 +6911,19 @@
         <v>0</v>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O78">
         <v>0</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q78">
         <v>0</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -6926,20 +6932,20 @@
         <v>1</v>
       </c>
       <c r="U78" t="str">
-        <f>TextData!B78</f>
-        <v>リンケージ</v>
+        <f>TextData!B77</f>
+        <v>付与無効化</v>
       </c>
     </row>
     <row r="79" spans="1:21">
       <c r="A79">
-        <v>9999</v>
+        <v>3010</v>
       </c>
       <c r="B79">
-        <v>9999</v>
+        <v>3010</v>
       </c>
       <c r="C79" t="str">
         <f>INDEX(TextData!B:B,MATCH(B79,TextData!A:A))</f>
-        <v>テスト用</v>
+        <v>チャージ</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -6994,7 +7000,143 @@
         <v>1</v>
       </c>
       <c r="U79" t="str">
+        <f>TextData!B78</f>
+        <v>チャージ</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21">
+      <c r="A80">
+        <v>3020</v>
+      </c>
+      <c r="B80">
+        <v>3020</v>
+      </c>
+      <c r="C80" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B80,TextData!A:A))</f>
+        <v>リンケージ</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80" t="s">
+        <v>61</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="H80" t="str">
+        <f>INDEX(Define!B:B,MATCH(G80,Define!A:A))</f>
+        <v>ターン数</v>
+      </c>
+      <c r="I80">
+        <v>1</v>
+      </c>
+      <c r="J80" t="s">
+        <v>20</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>1</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <v>0</v>
+      </c>
+      <c r="R80">
+        <v>0</v>
+      </c>
+      <c r="S80">
+        <v>0</v>
+      </c>
+      <c r="T80">
+        <v>1</v>
+      </c>
+      <c r="U80" t="str">
         <f>TextData!B79</f>
+        <v>リンケージ</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21">
+      <c r="A81">
+        <v>9999</v>
+      </c>
+      <c r="B81">
+        <v>9999</v>
+      </c>
+      <c r="C81" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B81,TextData!A:A))</f>
+        <v>テスト用</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81" t="s">
+        <v>61</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
+      </c>
+      <c r="H81" t="str">
+        <f>INDEX(Define!B:B,MATCH(G81,Define!A:A))</f>
+        <v>ターン数</v>
+      </c>
+      <c r="I81">
+        <v>1</v>
+      </c>
+      <c r="J81" t="s">
+        <v>20</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>1</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <v>0</v>
+      </c>
+      <c r="R81">
+        <v>0</v>
+      </c>
+      <c r="S81">
+        <v>0</v>
+      </c>
+      <c r="T81">
+        <v>1</v>
+      </c>
+      <c r="U81" t="str">
+        <f>TextData!B80</f>
         <v>テスト用</v>
       </c>
     </row>
@@ -7008,7 +7150,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
   <cols>
     <col min="2" max="2" width="14.6363636363636" customWidth="1"/>
@@ -7368,32 +7510,32 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33">
-        <v>2010</v>
+        <v>1210</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
+        <v>123</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="B35" t="s">
-        <v>124</v>
+        <v>35</v>
       </c>
       <c r="C35" t="s">
         <v>125</v>
@@ -7401,7 +7543,7 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B36" t="s">
         <v>126</v>
@@ -7412,7 +7554,7 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B37" t="s">
         <v>128</v>
@@ -7423,7 +7565,7 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B38" t="s">
         <v>130</v>
@@ -7434,7 +7576,7 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39">
-        <v>2040</v>
+        <v>2032</v>
       </c>
       <c r="B39" t="s">
         <v>132</v>
@@ -7445,7 +7587,7 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="B40" t="s">
         <v>134</v>
@@ -7456,7 +7598,7 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="B41" t="s">
         <v>136</v>
@@ -7467,7 +7609,7 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="B42" t="s">
         <v>138</v>
@@ -7478,7 +7620,7 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="B43" t="s">
         <v>140</v>
@@ -7489,7 +7631,7 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="B44" t="s">
         <v>142</v>
@@ -7500,7 +7642,7 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45">
-        <v>2120</v>
+        <v>2090</v>
       </c>
       <c r="B45" t="s">
         <v>144</v>
@@ -7511,7 +7653,7 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="B46" t="s">
         <v>146</v>
@@ -7522,7 +7664,7 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="B47" t="s">
         <v>148</v>
@@ -7533,7 +7675,7 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48">
-        <v>2150</v>
+        <v>2140</v>
       </c>
       <c r="B48" t="s">
         <v>150</v>
@@ -7544,7 +7686,7 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49">
-        <v>2180</v>
+        <v>2150</v>
       </c>
       <c r="B49" t="s">
         <v>152</v>
@@ -7555,7 +7697,7 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50">
-        <v>2190</v>
+        <v>2180</v>
       </c>
       <c r="B50" t="s">
         <v>154</v>
@@ -7566,7 +7708,7 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51">
-        <v>2210</v>
+        <v>2190</v>
       </c>
       <c r="B51" t="s">
         <v>156</v>
@@ -7577,7 +7719,7 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52">
-        <v>2220</v>
+        <v>2210</v>
       </c>
       <c r="B52" t="s">
         <v>158</v>
@@ -7588,7 +7730,7 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53">
-        <v>2230</v>
+        <v>2220</v>
       </c>
       <c r="B53" t="s">
         <v>160</v>
@@ -7599,7 +7741,7 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54">
-        <v>2240</v>
+        <v>2230</v>
       </c>
       <c r="B54" t="s">
         <v>162</v>
@@ -7610,7 +7752,7 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55">
-        <v>2250</v>
+        <v>2240</v>
       </c>
       <c r="B55" t="s">
         <v>164</v>
@@ -7621,7 +7763,7 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56">
-        <v>2270</v>
+        <v>2250</v>
       </c>
       <c r="B56" t="s">
         <v>166</v>
@@ -7632,7 +7774,7 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="B57" t="s">
         <v>168</v>
@@ -7643,7 +7785,7 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="B58" t="s">
         <v>170</v>
@@ -7654,7 +7796,7 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59">
-        <v>2320</v>
+        <v>2290</v>
       </c>
       <c r="B59" t="s">
         <v>172</v>
@@ -7665,7 +7807,7 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="B60" t="s">
         <v>174</v>
@@ -7676,7 +7818,7 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="B61" t="s">
         <v>176</v>
@@ -7687,7 +7829,7 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="B62" t="s">
         <v>178</v>
@@ -7698,7 +7840,7 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63">
-        <v>2350</v>
+        <v>2341</v>
       </c>
       <c r="B63" t="s">
         <v>180</v>
@@ -7709,7 +7851,7 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64">
-        <v>2360</v>
+        <v>2350</v>
       </c>
       <c r="B64" t="s">
         <v>182</v>
@@ -7720,7 +7862,7 @@
     </row>
     <row r="65" spans="1:3">
       <c r="A65">
-        <v>2370</v>
+        <v>2360</v>
       </c>
       <c r="B65" t="s">
         <v>184</v>
@@ -7731,7 +7873,7 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66">
-        <v>2380</v>
+        <v>2370</v>
       </c>
       <c r="B66" t="s">
         <v>186</v>
@@ -7742,7 +7884,7 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67">
-        <v>2390</v>
+        <v>2380</v>
       </c>
       <c r="B67" t="s">
         <v>188</v>
@@ -7753,7 +7895,7 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68">
-        <v>2400</v>
+        <v>2390</v>
       </c>
       <c r="B68" t="s">
         <v>190</v>
@@ -7764,7 +7906,7 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="B69" t="s">
         <v>192</v>
@@ -7775,7 +7917,7 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70">
-        <v>2420</v>
+        <v>2410</v>
       </c>
       <c r="B70" t="s">
         <v>194</v>
@@ -7786,7 +7928,7 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71">
-        <v>2430</v>
+        <v>2420</v>
       </c>
       <c r="B71" t="s">
         <v>196</v>
@@ -7797,7 +7939,7 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="B72" t="s">
         <v>198</v>
@@ -7808,7 +7950,7 @@
     </row>
     <row r="73" spans="1:3">
       <c r="A73">
-        <v>2450</v>
+        <v>2440</v>
       </c>
       <c r="B73" t="s">
         <v>200</v>
@@ -7819,7 +7961,7 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="B74" t="s">
         <v>202</v>
@@ -7830,7 +7972,7 @@
     </row>
     <row r="75" spans="1:3">
       <c r="A75">
-        <v>2470</v>
+        <v>2460</v>
       </c>
       <c r="B75" t="s">
         <v>204</v>
@@ -7841,7 +7983,7 @@
     </row>
     <row r="76" spans="1:3">
       <c r="A76">
-        <v>2480</v>
+        <v>2470</v>
       </c>
       <c r="B76" t="s">
         <v>206</v>
@@ -7852,7 +7994,7 @@
     </row>
     <row r="77" spans="1:3">
       <c r="A77">
-        <v>3010</v>
+        <v>2480</v>
       </c>
       <c r="B77" t="s">
         <v>208</v>
@@ -7863,7 +8005,7 @@
     </row>
     <row r="78" spans="1:3">
       <c r="A78">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B78" t="s">
         <v>210</v>
@@ -7874,12 +8016,23 @@
     </row>
     <row r="79" spans="1:3">
       <c r="A79">
-        <v>9999</v>
+        <v>3020</v>
       </c>
       <c r="B79" t="s">
         <v>212</v>
       </c>
       <c r="C79" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80">
+        <v>9999</v>
+      </c>
+      <c r="B80" t="s">
+        <v>214</v>
+      </c>
+      <c r="C80" t="s">
         <v>20</v>
       </c>
     </row>
@@ -7905,7 +8058,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7913,7 +8066,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7921,7 +8074,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7929,7 +8082,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -7937,7 +8090,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -7945,7 +8098,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -7953,7 +8106,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="States" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="224">
   <si>
     <t>Id</t>
   </si>
@@ -232,6 +232,12 @@
   </si>
   <si>
     <t>Help</t>
+  </si>
+  <si>
+    <t>EnglishText</t>
+  </si>
+  <si>
+    <t>EnglishHelp</t>
   </si>
   <si>
     <t>戦闘不能</t>
@@ -689,10 +695,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -703,11 +709,108 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -726,114 +829,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -846,6 +844,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -853,6 +859,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -868,7 +880,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -880,13 +910,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -898,13 +934,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -922,25 +958,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -958,61 +1006,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1030,13 +1030,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1068,23 +1074,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1113,11 +1104,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1133,16 +1139,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -1155,7 +1161,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1164,136 +1170,136 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -7150,13 +7156,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C80"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="2"/>
+  <dimension ref="A1:G80"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="14.6363636363636" customWidth="1"/>
+    <col min="3" max="3" width="36.7727272727273" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7166,360 +7173,558 @@
       <c r="C1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="F1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="F2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3">
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="F3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4">
         <v>201</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>77</v>
+      </c>
+      <c r="F4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5">
         <v>202</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>79</v>
+      </c>
+      <c r="F5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6">
         <v>203</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>81</v>
+      </c>
+      <c r="F6" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7">
         <v>204</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>83</v>
+      </c>
+      <c r="F7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>205</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>85</v>
+      </c>
+      <c r="F8" t="s">
+        <v>84</v>
+      </c>
+      <c r="G8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>1010</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>87</v>
+      </c>
+      <c r="F9" t="s">
+        <v>86</v>
+      </c>
+      <c r="G9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>1011</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>89</v>
+      </c>
+      <c r="F10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>1020</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>91</v>
+      </c>
+      <c r="F11" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>1030</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>93</v>
+      </c>
+      <c r="F12" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>1040</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>95</v>
+      </c>
+      <c r="F13" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14">
         <v>1041</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>97</v>
+      </c>
+      <c r="F14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15">
         <v>1043</v>
       </c>
       <c r="B15" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>99</v>
+      </c>
+      <c r="F15" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16">
         <v>1044</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>95</v>
+      </c>
+      <c r="F16" t="s">
+        <v>94</v>
+      </c>
+      <c r="G16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>1050</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>101</v>
+      </c>
+      <c r="F17" t="s">
+        <v>100</v>
+      </c>
+      <c r="G17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>1051</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>103</v>
+      </c>
+      <c r="F18" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
       <c r="A19">
         <v>1052</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>104</v>
+      </c>
+      <c r="F19" t="s">
+        <v>100</v>
+      </c>
+      <c r="G19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
       <c r="A20">
         <v>1053</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>105</v>
+      </c>
+      <c r="F20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G20" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
       <c r="A21">
         <v>1060</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>107</v>
+      </c>
+      <c r="F21" t="s">
+        <v>106</v>
+      </c>
+      <c r="G21" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22">
         <v>1070</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C22" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>109</v>
+      </c>
+      <c r="F22" t="s">
+        <v>108</v>
+      </c>
+      <c r="G22" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
       <c r="A23">
         <v>1071</v>
       </c>
       <c r="B23" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>111</v>
+      </c>
+      <c r="F23" t="s">
+        <v>110</v>
+      </c>
+      <c r="G23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
       <c r="A24">
         <v>1074</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>113</v>
+      </c>
+      <c r="F24" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25">
         <v>1080</v>
       </c>
       <c r="B25" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C25" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>115</v>
+      </c>
+      <c r="F25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G25" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26">
         <v>1081</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>115</v>
+      </c>
+      <c r="F26" t="s">
+        <v>114</v>
+      </c>
+      <c r="G26" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27">
         <v>1082</v>
       </c>
       <c r="B27" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>117</v>
+      </c>
+      <c r="F27" t="s">
+        <v>116</v>
+      </c>
+      <c r="G27" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28">
         <v>1090</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+        <v>119</v>
+      </c>
+      <c r="F28" t="s">
+        <v>118</v>
+      </c>
+      <c r="G28" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29">
         <v>1091</v>
       </c>
       <c r="B29" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+        <v>121</v>
+      </c>
+      <c r="F29" t="s">
+        <v>120</v>
+      </c>
+      <c r="G29" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30">
         <v>1092</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
+        <v>119</v>
+      </c>
+      <c r="F30" t="s">
+        <v>118</v>
+      </c>
+      <c r="G30" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31">
         <v>1100</v>
       </c>
       <c r="B31" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
+        <v>123</v>
+      </c>
+      <c r="F31" t="s">
+        <v>122</v>
+      </c>
+      <c r="G31" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32">
         <v>1101</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s">
+        <v>124</v>
+      </c>
+      <c r="F32" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="G32" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33">
         <v>1210</v>
       </c>
       <c r="B33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
+        <v>126</v>
+      </c>
+      <c r="F33" t="s">
+        <v>125</v>
+      </c>
+      <c r="G33" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34">
         <v>2010</v>
       </c>
@@ -7527,10 +7732,16 @@
         <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+        <v>127</v>
+      </c>
+      <c r="F34" t="s">
+        <v>34</v>
+      </c>
+      <c r="G34" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35">
         <v>2012</v>
       </c>
@@ -7538,501 +7749,777 @@
         <v>35</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
+        <v>127</v>
+      </c>
+      <c r="F35" t="s">
+        <v>35</v>
+      </c>
+      <c r="G35" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36">
         <v>2020</v>
       </c>
       <c r="B36" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
+        <v>129</v>
+      </c>
+      <c r="F36" t="s">
+        <v>128</v>
+      </c>
+      <c r="G36" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37">
         <v>2030</v>
       </c>
       <c r="B37" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
+        <v>131</v>
+      </c>
+      <c r="F37" t="s">
+        <v>130</v>
+      </c>
+      <c r="G37" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38">
         <v>2031</v>
       </c>
       <c r="B38" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C38" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
+        <v>133</v>
+      </c>
+      <c r="F38" t="s">
+        <v>132</v>
+      </c>
+      <c r="G38" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39">
         <v>2032</v>
       </c>
       <c r="B39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C39" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
+        <v>135</v>
+      </c>
+      <c r="F39" t="s">
+        <v>134</v>
+      </c>
+      <c r="G39" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40">
         <v>2040</v>
       </c>
       <c r="B40" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C40" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
+        <v>137</v>
+      </c>
+      <c r="F40" t="s">
+        <v>136</v>
+      </c>
+      <c r="G40" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41">
         <v>2050</v>
       </c>
       <c r="B41" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C41" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
+        <v>139</v>
+      </c>
+      <c r="F41" t="s">
+        <v>138</v>
+      </c>
+      <c r="G41" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42">
         <v>2060</v>
       </c>
       <c r="B42" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C42" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
+        <v>141</v>
+      </c>
+      <c r="F42" t="s">
+        <v>140</v>
+      </c>
+      <c r="G42" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43">
         <v>2070</v>
       </c>
       <c r="B43" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C43" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
+        <v>143</v>
+      </c>
+      <c r="F43" t="s">
+        <v>142</v>
+      </c>
+      <c r="G43" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44">
         <v>2080</v>
       </c>
       <c r="B44" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C44" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
+        <v>145</v>
+      </c>
+      <c r="F44" t="s">
+        <v>144</v>
+      </c>
+      <c r="G44" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45">
         <v>2090</v>
       </c>
       <c r="B45" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C45" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
+        <v>147</v>
+      </c>
+      <c r="F45" t="s">
+        <v>146</v>
+      </c>
+      <c r="G45" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46">
         <v>2120</v>
       </c>
       <c r="B46" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C46" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
+        <v>149</v>
+      </c>
+      <c r="F46" t="s">
+        <v>148</v>
+      </c>
+      <c r="G46" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47">
         <v>2130</v>
       </c>
       <c r="B47" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C47" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
+        <v>151</v>
+      </c>
+      <c r="F47" t="s">
+        <v>150</v>
+      </c>
+      <c r="G47" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48">
         <v>2140</v>
       </c>
       <c r="B48" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C48" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
+        <v>153</v>
+      </c>
+      <c r="F48" t="s">
+        <v>152</v>
+      </c>
+      <c r="G48" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
       <c r="A49">
         <v>2150</v>
       </c>
       <c r="B49" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C49" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
+        <v>155</v>
+      </c>
+      <c r="F49" t="s">
+        <v>154</v>
+      </c>
+      <c r="G49" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
       <c r="A50">
         <v>2180</v>
       </c>
       <c r="B50" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C50" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
+        <v>157</v>
+      </c>
+      <c r="F50" t="s">
+        <v>156</v>
+      </c>
+      <c r="G50" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
       <c r="A51">
         <v>2190</v>
       </c>
       <c r="B51" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C51" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
+        <v>159</v>
+      </c>
+      <c r="F51" t="s">
+        <v>158</v>
+      </c>
+      <c r="G51" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
       <c r="A52">
         <v>2210</v>
       </c>
       <c r="B52" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C52" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
+        <v>161</v>
+      </c>
+      <c r="F52" t="s">
+        <v>160</v>
+      </c>
+      <c r="G52" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
       <c r="A53">
         <v>2220</v>
       </c>
       <c r="B53" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C53" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
+        <v>163</v>
+      </c>
+      <c r="F53" t="s">
+        <v>162</v>
+      </c>
+      <c r="G53" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
       <c r="A54">
         <v>2230</v>
       </c>
       <c r="B54" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C54" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
+        <v>165</v>
+      </c>
+      <c r="F54" t="s">
+        <v>164</v>
+      </c>
+      <c r="G54" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
       <c r="A55">
         <v>2240</v>
       </c>
       <c r="B55" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C55" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
+        <v>167</v>
+      </c>
+      <c r="F55" t="s">
+        <v>166</v>
+      </c>
+      <c r="G55" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
       <c r="A56">
         <v>2250</v>
       </c>
       <c r="B56" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C56" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
+        <v>169</v>
+      </c>
+      <c r="F56" t="s">
+        <v>168</v>
+      </c>
+      <c r="G56" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
       <c r="A57">
         <v>2270</v>
       </c>
       <c r="B57" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C57" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
+        <v>171</v>
+      </c>
+      <c r="F57" t="s">
+        <v>170</v>
+      </c>
+      <c r="G57" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
       <c r="A58">
         <v>2280</v>
       </c>
       <c r="B58" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C58" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
+        <v>173</v>
+      </c>
+      <c r="F58" t="s">
+        <v>172</v>
+      </c>
+      <c r="G58" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
       <c r="A59">
         <v>2290</v>
       </c>
       <c r="B59" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C59" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
+        <v>175</v>
+      </c>
+      <c r="F59" t="s">
+        <v>174</v>
+      </c>
+      <c r="G59" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
       <c r="A60">
         <v>2320</v>
       </c>
       <c r="B60" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C60" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
+        <v>177</v>
+      </c>
+      <c r="F60" t="s">
+        <v>176</v>
+      </c>
+      <c r="G60" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
       <c r="A61">
         <v>2330</v>
       </c>
       <c r="B61" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C61" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
+        <v>179</v>
+      </c>
+      <c r="F61" t="s">
+        <v>178</v>
+      </c>
+      <c r="G61" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
       <c r="A62">
         <v>2340</v>
       </c>
       <c r="B62" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C62" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
+        <v>181</v>
+      </c>
+      <c r="F62" t="s">
+        <v>180</v>
+      </c>
+      <c r="G62" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
       <c r="A63">
         <v>2341</v>
       </c>
       <c r="B63" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C63" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
+        <v>183</v>
+      </c>
+      <c r="F63" t="s">
+        <v>182</v>
+      </c>
+      <c r="G63" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
       <c r="A64">
         <v>2350</v>
       </c>
       <c r="B64" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C64" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
+        <v>185</v>
+      </c>
+      <c r="F64" t="s">
+        <v>184</v>
+      </c>
+      <c r="G64" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
       <c r="A65">
         <v>2360</v>
       </c>
       <c r="B65" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C65" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
+        <v>187</v>
+      </c>
+      <c r="F65" t="s">
+        <v>186</v>
+      </c>
+      <c r="G65" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
       <c r="A66">
         <v>2370</v>
       </c>
       <c r="B66" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C66" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
+        <v>189</v>
+      </c>
+      <c r="F66" t="s">
+        <v>188</v>
+      </c>
+      <c r="G66" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
       <c r="A67">
         <v>2380</v>
       </c>
       <c r="B67" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C67" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
+        <v>191</v>
+      </c>
+      <c r="F67" t="s">
+        <v>190</v>
+      </c>
+      <c r="G67" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
       <c r="A68">
         <v>2390</v>
       </c>
       <c r="B68" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C68" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
+        <v>193</v>
+      </c>
+      <c r="F68" t="s">
+        <v>192</v>
+      </c>
+      <c r="G68" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
       <c r="A69">
         <v>2400</v>
       </c>
       <c r="B69" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C69" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
+        <v>195</v>
+      </c>
+      <c r="F69" t="s">
+        <v>194</v>
+      </c>
+      <c r="G69" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
       <c r="A70">
         <v>2410</v>
       </c>
       <c r="B70" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C70" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
+        <v>197</v>
+      </c>
+      <c r="F70" t="s">
+        <v>196</v>
+      </c>
+      <c r="G70" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
       <c r="A71">
         <v>2420</v>
       </c>
       <c r="B71" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C71" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
+        <v>199</v>
+      </c>
+      <c r="F71" t="s">
+        <v>198</v>
+      </c>
+      <c r="G71" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
       <c r="A72">
         <v>2430</v>
       </c>
       <c r="B72" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C72" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
+        <v>201</v>
+      </c>
+      <c r="F72" t="s">
+        <v>200</v>
+      </c>
+      <c r="G72" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
       <c r="A73">
         <v>2440</v>
       </c>
       <c r="B73" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C73" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
+        <v>203</v>
+      </c>
+      <c r="F73" t="s">
+        <v>202</v>
+      </c>
+      <c r="G73" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
       <c r="A74">
         <v>2450</v>
       </c>
       <c r="B74" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C74" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
+        <v>205</v>
+      </c>
+      <c r="F74" t="s">
+        <v>204</v>
+      </c>
+      <c r="G74" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
       <c r="A75">
         <v>2460</v>
       </c>
       <c r="B75" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C75" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
+        <v>207</v>
+      </c>
+      <c r="F75" t="s">
+        <v>206</v>
+      </c>
+      <c r="G75" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
       <c r="A76">
         <v>2470</v>
       </c>
       <c r="B76" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C76" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
+        <v>209</v>
+      </c>
+      <c r="F76" t="s">
+        <v>208</v>
+      </c>
+      <c r="G76" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
       <c r="A77">
         <v>2480</v>
       </c>
       <c r="B77" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C77" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
+        <v>211</v>
+      </c>
+      <c r="F77" t="s">
+        <v>210</v>
+      </c>
+      <c r="G77" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
       <c r="A78">
         <v>3010</v>
       </c>
       <c r="B78" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C78" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
+        <v>213</v>
+      </c>
+      <c r="F78" t="s">
+        <v>212</v>
+      </c>
+      <c r="G78" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
       <c r="A79">
         <v>3020</v>
       </c>
       <c r="B79" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C79" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
+        <v>215</v>
+      </c>
+      <c r="F79" t="s">
+        <v>214</v>
+      </c>
+      <c r="G79" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
       <c r="A80">
         <v>9999</v>
       </c>
       <c r="B80" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C80" t="s">
+        <v>20</v>
+      </c>
+      <c r="F80" t="s">
+        <v>216</v>
+      </c>
+      <c r="G80" t="s">
         <v>20</v>
       </c>
     </row>
@@ -8058,7 +8545,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -8066,7 +8553,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -8074,7 +8561,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -8082,7 +8569,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -8090,7 +8577,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -8098,7 +8585,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -8106,7 +8593,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="362">
   <si>
     <t>Id</t>
   </si>
@@ -243,181 +243,364 @@
     <t>戦闘不能</t>
   </si>
   <si>
+    <t>Defeated</t>
+  </si>
+  <si>
     <t>待機</t>
   </si>
   <si>
+    <t>Idle</t>
+  </si>
+  <si>
     <t>炎適正</t>
   </si>
   <si>
     <t>炎魔法の習得に必要な(Nu)コストをダウン</t>
   </si>
   <si>
+    <t>Fire Affinity</t>
+  </si>
+  <si>
+    <t>Reduce cost to learn Fire Magic by (Nu)</t>
+  </si>
+  <si>
     <t>雷適性</t>
   </si>
   <si>
     <t>雷魔法の習得に必要な(Nu)コストをダウン</t>
   </si>
   <si>
+    <t>Thunder Affinity</t>
+  </si>
+  <si>
+    <t>Reduce cost to learn Thunder Magic by (Nu)</t>
+  </si>
+  <si>
     <t>氷適性</t>
   </si>
   <si>
     <t>氷魔法の習得に必要な(Nu)コストをダウン</t>
   </si>
   <si>
+    <t>Ice Affinity</t>
+  </si>
+  <si>
+    <t>Reduce cost to learn Ice Magic by (Nu)</t>
+  </si>
+  <si>
     <t>光適性</t>
   </si>
   <si>
     <t>光魔法の習得に必要な(Nu)コストをダウン</t>
   </si>
   <si>
+    <t>Light Affinity</t>
+  </si>
+  <si>
+    <t>Reduce cost to learn Light Magic by (Nu)</t>
+  </si>
+  <si>
     <t>闇適性</t>
   </si>
   <si>
     <t>闇魔法の習得に必要な(Nu)コストをダウン</t>
   </si>
   <si>
+    <t>Dark Affinity</t>
+  </si>
+  <si>
+    <t>Reduce cost to learn Dark Magic by (Nu)</t>
+  </si>
+  <si>
     <t>覚醒</t>
   </si>
   <si>
-    <t>ATK,DEF,SPDが\dアップ</t>
+    <t>ATK,DEF,SPDが{0}アップ</t>
+  </si>
+  <si>
+    <t>Awaken</t>
+  </si>
+  <si>
+    <t>ATK, DEF, SPD +{0}</t>
   </si>
   <si>
     <t>全ステータスアップ</t>
   </si>
   <si>
-    <t>全てのステータスが\dアップ</t>
+    <t>全てのステータスが{0}アップ</t>
+  </si>
+  <si>
+    <t>All Stats Up</t>
+  </si>
+  <si>
+    <t>全てのステータスが{0}Up</t>
   </si>
   <si>
     <t>最大Hpアップ</t>
   </si>
   <si>
-    <t>MaxHp\dアップ</t>
+    <t>MaxHp{0}アップ</t>
+  </si>
+  <si>
+    <t>Max HP Up</t>
+  </si>
+  <si>
+    <t>MaxHp{0}Up</t>
   </si>
   <si>
     <t>最大Mpアップ</t>
   </si>
   <si>
-    <t>MaxMp\dアップ</t>
+    <t>MaxMp{0}アップ</t>
+  </si>
+  <si>
+    <t>Max MP Up</t>
+  </si>
+  <si>
+    <t>MaxMp{0}Up</t>
   </si>
   <si>
     <t>攻撃アップ</t>
   </si>
   <si>
-    <t>ATK\dアップ</t>
+    <t>ATK{0}アップ</t>
+  </si>
+  <si>
+    <t>Attack Up</t>
+  </si>
+  <si>
+    <t>ATK{0}Up</t>
   </si>
   <si>
     <t>攻撃ダウン</t>
   </si>
   <si>
-    <t>ATK\dダウン</t>
+    <t>ATK{0}ダウン</t>
+  </si>
+  <si>
+    <t>Attack Down</t>
+  </si>
+  <si>
+    <t>ATK{0}Down</t>
   </si>
   <si>
     <t>攻撃%ダウン</t>
   </si>
   <si>
-    <t>ATK\d%ダウン</t>
+    <t>ATK{0}%ダウン</t>
+  </si>
+  <si>
+    <t>Attack % Down</t>
+  </si>
+  <si>
+    <t>ATK{0}%Down</t>
   </si>
   <si>
     <t>防御アップ</t>
   </si>
   <si>
-    <t>DEF\dアップ</t>
+    <t>DEF{0}アップ</t>
+  </si>
+  <si>
+    <t>Defense Up</t>
+  </si>
+  <si>
+    <t>DEF{0}Up</t>
   </si>
   <si>
     <t>防御ダウン</t>
   </si>
   <si>
-    <t>DEF\dダウン</t>
-  </si>
-  <si>
-    <t>DEF\d%アップ</t>
-  </si>
-  <si>
-    <t>DEF\d%ダウン</t>
+    <t>DEF{0}ダウン</t>
+  </si>
+  <si>
+    <t>Defense Down</t>
+  </si>
+  <si>
+    <t>DEF{0}Down</t>
+  </si>
+  <si>
+    <t>DEF{0}%アップ</t>
+  </si>
+  <si>
+    <t>DEF{0}%Up</t>
+  </si>
+  <si>
+    <t>DEF{0}%ダウン</t>
+  </si>
+  <si>
+    <t>DEF{0}%Down</t>
   </si>
   <si>
     <t>速度アップ</t>
   </si>
   <si>
-    <t>SPD\dアップ</t>
+    <t>SPD{0}アップ</t>
+  </si>
+  <si>
+    <t>SPD{0}Up</t>
   </si>
   <si>
     <t>会心率アップ</t>
   </si>
   <si>
-    <t>会心率\d%アップ</t>
+    <t>会心率{0}%アップ</t>
+  </si>
+  <si>
+    <t>Critical Rate Up</t>
+  </si>
+  <si>
+    <t>Critical Rate{0}%Up</t>
   </si>
   <si>
     <t>会心率ダウン</t>
   </si>
   <si>
-    <t>会心率\d%ダウン</t>
+    <t>会心率{0}%ダウン</t>
+  </si>
+  <si>
+    <t>Critical Rate Down</t>
+  </si>
+  <si>
+    <t>Critical Rate{0}%Down</t>
   </si>
   <si>
     <t>会心ダメージアップ</t>
   </si>
   <si>
-    <t>会心ダメージ\d%アップ</t>
+    <t>会心ダメージ{0}%アップ</t>
+  </si>
+  <si>
+    <t>Critical Damage Up</t>
+  </si>
+  <si>
+    <t>Critical Damage{0}%Up</t>
   </si>
   <si>
     <t>命中アップ</t>
   </si>
   <si>
-    <t>命中率\d%アップ</t>
+    <t>命中率{0}%アップ</t>
+  </si>
+  <si>
+    <t>Accuracy Rate Up</t>
+  </si>
+  <si>
+    <t>Accuracy Rate{0}%Up</t>
   </si>
   <si>
     <t>命中ダウン</t>
   </si>
   <si>
-    <t>命中率\d%ダウン</t>
+    <t>命中率{0}%ダウン</t>
+  </si>
+  <si>
+    <t>Accuracy Rate Down</t>
+  </si>
+  <si>
+    <t>Accuracy Rate{0}%Down</t>
   </si>
   <si>
     <t>回避アップ</t>
   </si>
   <si>
-    <t>回避率\d%アップ</t>
+    <t>回避率{0}%アップ</t>
+  </si>
+  <si>
+    <t>Avoidance Rate Up</t>
+  </si>
+  <si>
+    <t>Avoidance Rate{0}%Up</t>
   </si>
   <si>
     <t>回避ダウン</t>
   </si>
   <si>
-    <t>回避率\d%ダウン</t>
+    <t>回避率{0}%ダウン</t>
+  </si>
+  <si>
+    <t>Avoidance Rate Down</t>
+  </si>
+  <si>
+    <t>Avoidance Rate{0}%Down</t>
   </si>
   <si>
     <t>ダメージカット</t>
   </si>
   <si>
-    <t>被ダメージを\d%カットする</t>
-  </si>
-  <si>
-    <t>被ダメージを\dカットする</t>
+    <t>被ダメージを{0}%カットする</t>
+  </si>
+  <si>
+    <t>Damage Cut</t>
+  </si>
+  <si>
+    <t>Reduce damage taken by {0}%</t>
+  </si>
+  <si>
+    <t>被ダメージを{0}カットする</t>
+  </si>
+  <si>
+    <t>Reduce damage taken by {0}</t>
   </si>
   <si>
     <t>火傷耐性</t>
   </si>
   <si>
-    <t>火傷ダメージを\d%カットする</t>
+    <t>火傷ダメージを{0}%カットする</t>
+  </si>
+  <si>
+    <t>Burn Resistance</t>
+  </si>
+  <si>
+    <t>Reduce burn damage taken by {0}%</t>
   </si>
   <si>
     <t>行動後ダメージ</t>
   </si>
   <si>
+    <t>Poison</t>
+  </si>
+  <si>
+    <t>Damage after action</t>
+  </si>
+  <si>
+    <t>Burn</t>
+  </si>
+  <si>
     <t>暗闇</t>
   </si>
   <si>
     <t>一度だけ魔法が相手に命中しなくなる</t>
   </si>
   <si>
+    <t>Darkness</t>
+  </si>
+  <si>
+    <t>Miss one spell attack against opponent</t>
+  </si>
+  <si>
     <t>カウンタ</t>
   </si>
   <si>
     <t>攻撃を受けると反撃ダメージ</t>
   </si>
   <si>
+    <t>Counter</t>
+  </si>
+  <si>
+    <t>Counter damage when attacked</t>
+  </si>
+  <si>
     <t>CAダメージ</t>
   </si>
   <si>
-    <t>CAの反撃ダメージ\dアップ</t>
+    <t>CAの反撃ダメージ{0}アップ</t>
+  </si>
+  <si>
+    <t>CA Damage</t>
+  </si>
+  <si>
+    <t>CA Counter Damage +{0}</t>
   </si>
   <si>
     <t>CAシェル</t>
@@ -426,10 +609,22 @@
     <t>CA成功時のダメージをダウン</t>
   </si>
   <si>
+    <t>CA Shell</t>
+  </si>
+  <si>
+    <t>Reduce CA success damage</t>
+  </si>
+  <si>
     <t>リジェネ</t>
   </si>
   <si>
-    <t>行動後Hp\d回復</t>
+    <t>行動後Hp{0}回復</t>
+  </si>
+  <si>
+    <t>Regene</t>
+  </si>
+  <si>
+    <t>Restore HP {0} after action</t>
   </si>
   <si>
     <t>攻撃無効</t>
@@ -438,10 +633,22 @@
     <t>攻撃が効かなくなる</t>
   </si>
   <si>
+    <t>Attack Ineffective</t>
+  </si>
+  <si>
+    <t>Attack becomes ineffective</t>
+  </si>
+  <si>
     <t>ドレイン</t>
   </si>
   <si>
-    <t>攻撃ダメージの\d%分Hp回復</t>
+    <t>攻撃ダメージの{0}%分Hp回復</t>
+  </si>
+  <si>
+    <t>Drain</t>
+  </si>
+  <si>
+    <t>Restore HP equal to {0}% of damage taken</t>
   </si>
   <si>
     <t>状態異常CA</t>
@@ -450,88 +657,172 @@
     <t>状態異常を反射しダメージを与える</t>
   </si>
   <si>
+    <t>Status Abnormal CA</t>
+  </si>
+  <si>
+    <t>Reflect status ailments and deal damage</t>
+  </si>
+  <si>
     <t>反撃</t>
   </si>
   <si>
     <t>攻撃された際に行動できる</t>
   </si>
   <si>
+    <t>Counterattack</t>
+  </si>
+  <si>
+    <t>Can act when attacked</t>
+  </si>
+  <si>
     <t>パッシブ封じ</t>
   </si>
   <si>
     <t>パッシブ魔法が発動しなくなる</t>
   </si>
   <si>
+    <t>Passive Block</t>
+  </si>
+  <si>
+    <t>Passive magic does not activate</t>
+  </si>
+  <si>
     <t>デバフ強化</t>
   </si>
   <si>
     <t>デバフ効果を増加する</t>
   </si>
   <si>
+    <t>Debuff Amplification</t>
+  </si>
+  <si>
+    <t>Increase debuff effects</t>
+  </si>
+  <si>
     <t>挑発</t>
   </si>
   <si>
     <t>攻撃の対象を自身に固定する</t>
   </si>
   <si>
+    <t>Taunt</t>
+  </si>
+  <si>
+    <t>Fix attack target to self</t>
+  </si>
+  <si>
     <t>凍結</t>
   </si>
   <si>
     <t>攻撃すると自身にダメージ</t>
   </si>
   <si>
+    <t>Deal damage to self on attack</t>
+  </si>
+  <si>
     <t>スタン</t>
   </si>
   <si>
     <t>一定時間行動できなくなる</t>
   </si>
   <si>
+    <t>Unable to act for a certain period of time</t>
+  </si>
+  <si>
     <t>状態異常回避</t>
   </si>
   <si>
     <t>状態異常を回避する</t>
   </si>
   <si>
+    <t>Status Avoidance</t>
+  </si>
+  <si>
+    <t>Avoid status ailments</t>
+  </si>
+  <si>
     <t>対象範囲延長</t>
   </si>
   <si>
     <t>範囲外の対象を選択できる</t>
   </si>
   <si>
+    <t>Extended Range</t>
+  </si>
+  <si>
+    <t>Can select targets outside of range</t>
+  </si>
+  <si>
     <t>アフターヒール</t>
   </si>
   <si>
     <t>行動後自身のHpを回復</t>
   </si>
   <si>
+    <t>After Heal</t>
+  </si>
+  <si>
+    <t>Restore own HP after action</t>
+  </si>
+  <si>
     <t>即死付与</t>
   </si>
   <si>
     <t>一定確率でダメージが対象のHpになる</t>
   </si>
   <si>
+    <t>Instant Death</t>
+  </si>
+  <si>
+    <t>Damage dealt has a certain chance to become target's HP</t>
+  </si>
+  <si>
     <t>同時回復</t>
   </si>
   <si>
     <t>Hpを回復すると自身のHpも回復する</t>
   </si>
   <si>
+    <t>Simultaneous Heal</t>
+  </si>
+  <si>
+    <t>Restoring HP heals own HP as well</t>
+  </si>
+  <si>
     <t>必中</t>
   </si>
   <si>
     <t>攻撃が必ずあたるようになる</t>
   </si>
   <si>
+    <t>Certain Hit</t>
+  </si>
+  <si>
+    <t>Attacks will always hit</t>
+  </si>
+  <si>
     <t>アシストヒール</t>
   </si>
   <si>
-    <t>攻撃成功時味方全員のHp\d回復</t>
+    <t>攻撃成功時味方全員のHp{0}回復</t>
+  </si>
+  <si>
+    <t>Assist Heal</t>
+  </si>
+  <si>
+    <t>Restore HP {0} to all allies on attack success</t>
   </si>
   <si>
     <t>アンデッド</t>
   </si>
   <si>
-    <t>1度だけ戦闘不能から復活し行動後Hpを\d回復</t>
+    <t>1度だけ戦闘不能から復活し行動後Hpを{0}回復</t>
+  </si>
+  <si>
+    <t>Undead</t>
+  </si>
+  <si>
+    <t>Revive from Defeated once and restore HP {0} after action</t>
   </si>
   <si>
     <t>アクセル</t>
@@ -540,10 +831,22 @@
     <t>行動後速度がアップしつづける</t>
   </si>
   <si>
+    <t>Accelerate</t>
+  </si>
+  <si>
+    <t>Increase speed after action continuously</t>
+  </si>
+  <si>
     <t>ダメージ威力アップ</t>
   </si>
   <si>
-    <t>攻撃魔法の威力が\d%アップ</t>
+    <t>攻撃魔法の威力が{0}%アップ</t>
+  </si>
+  <si>
+    <t>Damage Power Up</t>
+  </si>
+  <si>
+    <t>Attack magic power +{0}%</t>
   </si>
   <si>
     <t>バフ解除</t>
@@ -552,118 +855,229 @@
     <t>バフを解除する</t>
   </si>
   <si>
+    <t>Buff Removal</t>
+  </si>
+  <si>
+    <t>Remove buffs</t>
+  </si>
+  <si>
     <t>貫通</t>
   </si>
   <si>
     <t>攻撃時相手のDEFを無視する</t>
   </si>
   <si>
+    <t>Pierce</t>
+  </si>
+  <si>
+    <t>Ignore target's DEF when attacking</t>
+  </si>
+  <si>
     <t>対象列化</t>
   </si>
   <si>
     <t>単体の効果対象が列になる</t>
   </si>
   <si>
+    <t>Target Row</t>
+  </si>
+  <si>
+    <t>Single-target effect changes to row</t>
+  </si>
+  <si>
     <t>対象全体化</t>
   </si>
   <si>
     <t>効果対象が全体になる</t>
   </si>
   <si>
+    <t>Target All Rows</t>
+  </si>
+  <si>
+    <t>Effect targets all rows</t>
+  </si>
+  <si>
     <t>聖棺</t>
   </si>
   <si>
     <t>被ダメージアップ</t>
   </si>
   <si>
+    <t>Holy Coffin</t>
+  </si>
+  <si>
+    <t>Increase damage taken</t>
+  </si>
+  <si>
     <t>追加ダメージ</t>
   </si>
   <si>
     <t>消費Mpが0のMagicに追加ダメージ</t>
   </si>
   <si>
+    <t>Additional Damage</t>
+  </si>
+  <si>
+    <t>Additional damage to Magic with 0 MP cost</t>
+  </si>
+  <si>
     <t>追加効果</t>
   </si>
   <si>
     <t>消費Mpが0のMagicに追加効果</t>
   </si>
   <si>
+    <t>Additional Effect</t>
+  </si>
+  <si>
+    <t>Additional effect to Magic with 0 MP cost</t>
+  </si>
+  <si>
     <t>透明</t>
   </si>
   <si>
     <t>狙われなくなる</t>
   </si>
   <si>
+    <t>No longer targeted</t>
+  </si>
+  <si>
     <t>沈黙</t>
   </si>
   <si>
     <t>消費Mp0以外のMagic使用不可</t>
   </si>
   <si>
+    <t>Silence</t>
+  </si>
+  <si>
+    <t>Cannot use Magic with MP cost other than 0</t>
+  </si>
+  <si>
     <t>不治</t>
   </si>
   <si>
     <t>Hp回復しなくなる</t>
   </si>
   <si>
+    <t>Curse</t>
+  </si>
+  <si>
+    <t>Stop HP recovery</t>
+  </si>
+  <si>
     <t>シールド</t>
   </si>
   <si>
     <t>一定量までのダメージを無効にする</t>
   </si>
   <si>
+    <t>Nullify up to a certain amount of damage</t>
+  </si>
+  <si>
     <t>フォロー</t>
   </si>
   <si>
     <t>行動後自身以外の行動待機時間を短縮</t>
   </si>
   <si>
+    <t>Follow-Up</t>
+  </si>
+  <si>
+    <t>Reduce wait time after action for others</t>
+  </si>
+  <si>
     <t>かばう</t>
   </si>
   <si>
     <t>攻撃を代わりに受ける</t>
   </si>
   <si>
+    <t>Guard</t>
+  </si>
+  <si>
+    <t>Take attacks instead</t>
+  </si>
+  <si>
     <t>Ap消費半減</t>
   </si>
   <si>
     <t>Apの消費数が半分になる。端数は切り上げ</t>
   </si>
   <si>
+    <t>AP Halved</t>
+  </si>
+  <si>
+    <t>Half AP consumption. Round up fractions</t>
+  </si>
+  <si>
     <t>不死</t>
   </si>
   <si>
     <t>一度だけ戦闘不能を回避する</t>
   </si>
   <si>
+    <t>Undying</t>
+  </si>
+  <si>
+    <t>Avoid Defeated once</t>
+  </si>
+  <si>
     <t>Hp回復効果アップ</t>
   </si>
   <si>
     <t>Hp回復効果量アップ</t>
   </si>
   <si>
+    <t>HP Recovery Effect Up</t>
+  </si>
+  <si>
+    <t>Increase HP recovery effect</t>
+  </si>
+  <si>
     <t>呪詛</t>
   </si>
   <si>
     <t>戦闘不能を回避し反撃ダメージ</t>
   </si>
   <si>
+    <t>Avoid Defeated and deal counter damage</t>
+  </si>
+  <si>
     <t>付与無効化</t>
   </si>
   <si>
     <t>対象の状態にならない</t>
   </si>
   <si>
+    <t>Grant Immunity</t>
+  </si>
+  <si>
+    <t>Do not become a target of status effects</t>
+  </si>
+  <si>
     <t>チャージ</t>
   </si>
   <si>
     <t>次の行動でのフラグが立つ</t>
   </si>
   <si>
+    <t>Charge</t>
+  </si>
+  <si>
+    <t>Set flag for next action</t>
+  </si>
+  <si>
     <t>リンケージ</t>
   </si>
   <si>
     <t>行動後に後衛と交代する</t>
+  </si>
+  <si>
+    <t>Linkage</t>
+  </si>
+  <si>
+    <t>Swap positions with back row after action</t>
   </si>
   <si>
     <t>テスト用</t>
@@ -696,9 +1110,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -709,8 +1123,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -724,98 +1184,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -823,7 +1194,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -838,16 +1209,59 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -862,13 +1276,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -880,7 +1402,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -892,25 +1426,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -922,127 +1450,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1104,26 +1518,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1139,16 +1544,25 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -1161,145 +1575,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -7161,6 +7575,8 @@
   <cols>
     <col min="2" max="2" width="14.6363636363636" customWidth="1"/>
     <col min="3" max="3" width="36.7727272727273" customWidth="1"/>
+    <col min="6" max="6" width="18.9181818181818" customWidth="1"/>
+    <col min="7" max="7" width="34.8727272727273" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -7191,7 +7607,7 @@
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G2" t="s">
         <v>20</v>
@@ -7202,13 +7618,13 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G3" t="s">
         <v>20</v>
@@ -7219,16 +7635,16 @@
         <v>201</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -7236,16 +7652,16 @@
         <v>202</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="F5" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G5" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -7253,16 +7669,16 @@
         <v>203</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F6" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="G6" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -7270,16 +7686,16 @@
         <v>204</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F7" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G7" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -7287,16 +7703,16 @@
         <v>205</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F8" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="G8" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -7304,16 +7720,16 @@
         <v>1010</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="F9" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="G9" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -7321,16 +7737,16 @@
         <v>1011</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="F10" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="G10" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -7338,16 +7754,16 @@
         <v>1020</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="F11" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="G11" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -7355,16 +7771,16 @@
         <v>1030</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="F12" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="G12" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -7372,16 +7788,16 @@
         <v>1040</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="F13" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="G13" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -7389,16 +7805,16 @@
         <v>1041</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="F14" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="G14" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -7406,16 +7822,16 @@
         <v>1043</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="C15" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="F15" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="G15" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -7423,16 +7839,16 @@
         <v>1044</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="F16" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="G16" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -7440,16 +7856,16 @@
         <v>1050</v>
       </c>
       <c r="B17" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="F17" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="G17" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -7457,16 +7873,16 @@
         <v>1051</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="F18" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="G18" t="s">
-        <v>103</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -7474,16 +7890,16 @@
         <v>1052</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="C19" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="F19" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="G19" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -7491,16 +7907,16 @@
         <v>1053</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="C20" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="F20" t="s">
-        <v>102</v>
+        <v>132</v>
       </c>
       <c r="G20" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -7508,16 +7924,16 @@
         <v>1060</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="F21" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="G21" t="s">
-        <v>107</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -7525,16 +7941,16 @@
         <v>1070</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>141</v>
       </c>
       <c r="C22" t="s">
-        <v>109</v>
+        <v>142</v>
       </c>
       <c r="F22" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="G22" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -7542,16 +7958,16 @@
         <v>1071</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="F23" t="s">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="G23" t="s">
-        <v>111</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -7559,16 +7975,16 @@
         <v>1074</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="F24" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="G24" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -7576,16 +7992,16 @@
         <v>1080</v>
       </c>
       <c r="B25" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="F25" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="G25" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -7593,16 +8009,16 @@
         <v>1081</v>
       </c>
       <c r="B26" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="F26" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="G26" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -7610,16 +8026,16 @@
         <v>1082</v>
       </c>
       <c r="B27" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="F27" t="s">
-        <v>116</v>
+        <v>159</v>
       </c>
       <c r="G27" t="s">
-        <v>117</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -7627,16 +8043,16 @@
         <v>1090</v>
       </c>
       <c r="B28" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="F28" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="G28" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -7644,16 +8060,16 @@
         <v>1091</v>
       </c>
       <c r="B29" t="s">
-        <v>120</v>
+        <v>165</v>
       </c>
       <c r="C29" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="F29" t="s">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="G29" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -7661,16 +8077,16 @@
         <v>1092</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="F30" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
       <c r="G30" t="s">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -7678,16 +8094,16 @@
         <v>1100</v>
       </c>
       <c r="B31" t="s">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>170</v>
       </c>
       <c r="F31" t="s">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="G31" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -7695,16 +8111,16 @@
         <v>1101</v>
       </c>
       <c r="B32" t="s">
-        <v>122</v>
+        <v>169</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>173</v>
       </c>
       <c r="F32" t="s">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="G32" t="s">
-        <v>124</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -7712,16 +8128,16 @@
         <v>1210</v>
       </c>
       <c r="B33" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="C33" t="s">
-        <v>126</v>
+        <v>176</v>
       </c>
       <c r="F33" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="G33" t="s">
-        <v>126</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -7732,13 +8148,13 @@
         <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="F34" t="s">
-        <v>34</v>
+        <v>180</v>
       </c>
       <c r="G34" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -7749,13 +8165,13 @@
         <v>35</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>179</v>
       </c>
       <c r="F35" t="s">
-        <v>35</v>
+        <v>182</v>
       </c>
       <c r="G35" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -7763,16 +8179,16 @@
         <v>2020</v>
       </c>
       <c r="B36" t="s">
-        <v>128</v>
+        <v>183</v>
       </c>
       <c r="C36" t="s">
-        <v>129</v>
+        <v>184</v>
       </c>
       <c r="F36" t="s">
-        <v>128</v>
+        <v>185</v>
       </c>
       <c r="G36" t="s">
-        <v>129</v>
+        <v>186</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -7780,16 +8196,16 @@
         <v>2030</v>
       </c>
       <c r="B37" t="s">
-        <v>130</v>
+        <v>187</v>
       </c>
       <c r="C37" t="s">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="F37" t="s">
-        <v>130</v>
+        <v>189</v>
       </c>
       <c r="G37" t="s">
-        <v>131</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -7797,16 +8213,16 @@
         <v>2031</v>
       </c>
       <c r="B38" t="s">
-        <v>132</v>
+        <v>191</v>
       </c>
       <c r="C38" t="s">
-        <v>133</v>
+        <v>192</v>
       </c>
       <c r="F38" t="s">
-        <v>132</v>
+        <v>193</v>
       </c>
       <c r="G38" t="s">
-        <v>133</v>
+        <v>194</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -7814,16 +8230,16 @@
         <v>2032</v>
       </c>
       <c r="B39" t="s">
-        <v>134</v>
+        <v>195</v>
       </c>
       <c r="C39" t="s">
-        <v>135</v>
+        <v>196</v>
       </c>
       <c r="F39" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="G39" t="s">
-        <v>135</v>
+        <v>198</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -7831,16 +8247,16 @@
         <v>2040</v>
       </c>
       <c r="B40" t="s">
-        <v>136</v>
+        <v>199</v>
       </c>
       <c r="C40" t="s">
-        <v>137</v>
+        <v>200</v>
       </c>
       <c r="F40" t="s">
-        <v>136</v>
+        <v>201</v>
       </c>
       <c r="G40" t="s">
-        <v>137</v>
+        <v>202</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -7848,16 +8264,16 @@
         <v>2050</v>
       </c>
       <c r="B41" t="s">
-        <v>138</v>
+        <v>203</v>
       </c>
       <c r="C41" t="s">
-        <v>139</v>
+        <v>204</v>
       </c>
       <c r="F41" t="s">
-        <v>138</v>
+        <v>205</v>
       </c>
       <c r="G41" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -7865,16 +8281,16 @@
         <v>2060</v>
       </c>
       <c r="B42" t="s">
-        <v>140</v>
+        <v>207</v>
       </c>
       <c r="C42" t="s">
-        <v>141</v>
+        <v>208</v>
       </c>
       <c r="F42" t="s">
-        <v>140</v>
+        <v>209</v>
       </c>
       <c r="G42" t="s">
-        <v>141</v>
+        <v>210</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -7882,16 +8298,16 @@
         <v>2070</v>
       </c>
       <c r="B43" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
       <c r="C43" t="s">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="F43" t="s">
-        <v>142</v>
+        <v>213</v>
       </c>
       <c r="G43" t="s">
-        <v>143</v>
+        <v>214</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -7899,16 +8315,16 @@
         <v>2080</v>
       </c>
       <c r="B44" t="s">
-        <v>144</v>
+        <v>215</v>
       </c>
       <c r="C44" t="s">
-        <v>145</v>
+        <v>216</v>
       </c>
       <c r="F44" t="s">
-        <v>144</v>
+        <v>217</v>
       </c>
       <c r="G44" t="s">
-        <v>145</v>
+        <v>218</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -7916,16 +8332,16 @@
         <v>2090</v>
       </c>
       <c r="B45" t="s">
-        <v>146</v>
+        <v>219</v>
       </c>
       <c r="C45" t="s">
-        <v>147</v>
+        <v>220</v>
       </c>
       <c r="F45" t="s">
-        <v>146</v>
+        <v>221</v>
       </c>
       <c r="G45" t="s">
-        <v>147</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -7933,16 +8349,16 @@
         <v>2120</v>
       </c>
       <c r="B46" t="s">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="C46" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
       <c r="F46" t="s">
-        <v>148</v>
+        <v>225</v>
       </c>
       <c r="G46" t="s">
-        <v>149</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -7950,16 +8366,16 @@
         <v>2130</v>
       </c>
       <c r="B47" t="s">
-        <v>150</v>
+        <v>227</v>
       </c>
       <c r="C47" t="s">
-        <v>151</v>
+        <v>228</v>
       </c>
       <c r="F47" t="s">
-        <v>150</v>
+        <v>229</v>
       </c>
       <c r="G47" t="s">
-        <v>151</v>
+        <v>230</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -7967,16 +8383,16 @@
         <v>2140</v>
       </c>
       <c r="B48" t="s">
-        <v>152</v>
+        <v>231</v>
       </c>
       <c r="C48" t="s">
-        <v>153</v>
+        <v>232</v>
       </c>
       <c r="F48" t="s">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="G48" t="s">
-        <v>153</v>
+        <v>233</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -7984,16 +8400,16 @@
         <v>2150</v>
       </c>
       <c r="B49" t="s">
-        <v>154</v>
+        <v>234</v>
       </c>
       <c r="C49" t="s">
-        <v>155</v>
+        <v>235</v>
       </c>
       <c r="F49" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="G49" t="s">
-        <v>155</v>
+        <v>236</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -8001,16 +8417,16 @@
         <v>2180</v>
       </c>
       <c r="B50" t="s">
-        <v>156</v>
+        <v>237</v>
       </c>
       <c r="C50" t="s">
-        <v>157</v>
+        <v>238</v>
       </c>
       <c r="F50" t="s">
-        <v>156</v>
+        <v>239</v>
       </c>
       <c r="G50" t="s">
-        <v>157</v>
+        <v>240</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -8018,16 +8434,16 @@
         <v>2190</v>
       </c>
       <c r="B51" t="s">
-        <v>158</v>
+        <v>241</v>
       </c>
       <c r="C51" t="s">
-        <v>159</v>
+        <v>242</v>
       </c>
       <c r="F51" t="s">
-        <v>158</v>
+        <v>243</v>
       </c>
       <c r="G51" t="s">
-        <v>159</v>
+        <v>244</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -8035,16 +8451,16 @@
         <v>2210</v>
       </c>
       <c r="B52" t="s">
-        <v>160</v>
+        <v>245</v>
       </c>
       <c r="C52" t="s">
-        <v>161</v>
+        <v>246</v>
       </c>
       <c r="F52" t="s">
-        <v>160</v>
+        <v>247</v>
       </c>
       <c r="G52" t="s">
-        <v>161</v>
+        <v>248</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -8052,16 +8468,16 @@
         <v>2220</v>
       </c>
       <c r="B53" t="s">
-        <v>162</v>
+        <v>249</v>
       </c>
       <c r="C53" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="F53" t="s">
-        <v>162</v>
+        <v>251</v>
       </c>
       <c r="G53" t="s">
-        <v>163</v>
+        <v>252</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -8069,16 +8485,16 @@
         <v>2230</v>
       </c>
       <c r="B54" t="s">
-        <v>164</v>
+        <v>253</v>
       </c>
       <c r="C54" t="s">
-        <v>165</v>
+        <v>254</v>
       </c>
       <c r="F54" t="s">
-        <v>164</v>
+        <v>255</v>
       </c>
       <c r="G54" t="s">
-        <v>165</v>
+        <v>256</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -8086,16 +8502,16 @@
         <v>2240</v>
       </c>
       <c r="B55" t="s">
-        <v>166</v>
+        <v>257</v>
       </c>
       <c r="C55" t="s">
-        <v>167</v>
+        <v>258</v>
       </c>
       <c r="F55" t="s">
-        <v>166</v>
+        <v>259</v>
       </c>
       <c r="G55" t="s">
-        <v>167</v>
+        <v>260</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -8103,16 +8519,16 @@
         <v>2250</v>
       </c>
       <c r="B56" t="s">
-        <v>168</v>
+        <v>261</v>
       </c>
       <c r="C56" t="s">
-        <v>169</v>
+        <v>262</v>
       </c>
       <c r="F56" t="s">
-        <v>168</v>
+        <v>263</v>
       </c>
       <c r="G56" t="s">
-        <v>169</v>
+        <v>264</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -8120,16 +8536,16 @@
         <v>2270</v>
       </c>
       <c r="B57" t="s">
-        <v>170</v>
+        <v>265</v>
       </c>
       <c r="C57" t="s">
-        <v>171</v>
+        <v>266</v>
       </c>
       <c r="F57" t="s">
-        <v>170</v>
+        <v>267</v>
       </c>
       <c r="G57" t="s">
-        <v>171</v>
+        <v>268</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -8137,16 +8553,16 @@
         <v>2280</v>
       </c>
       <c r="B58" t="s">
-        <v>172</v>
+        <v>269</v>
       </c>
       <c r="C58" t="s">
-        <v>173</v>
+        <v>270</v>
       </c>
       <c r="F58" t="s">
-        <v>172</v>
+        <v>271</v>
       </c>
       <c r="G58" t="s">
-        <v>173</v>
+        <v>272</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -8154,16 +8570,16 @@
         <v>2290</v>
       </c>
       <c r="B59" t="s">
-        <v>174</v>
+        <v>273</v>
       </c>
       <c r="C59" t="s">
-        <v>175</v>
+        <v>274</v>
       </c>
       <c r="F59" t="s">
-        <v>174</v>
+        <v>275</v>
       </c>
       <c r="G59" t="s">
-        <v>175</v>
+        <v>276</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -8171,16 +8587,16 @@
         <v>2320</v>
       </c>
       <c r="B60" t="s">
-        <v>176</v>
+        <v>277</v>
       </c>
       <c r="C60" t="s">
-        <v>177</v>
+        <v>278</v>
       </c>
       <c r="F60" t="s">
-        <v>176</v>
+        <v>279</v>
       </c>
       <c r="G60" t="s">
-        <v>177</v>
+        <v>280</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -8188,16 +8604,16 @@
         <v>2330</v>
       </c>
       <c r="B61" t="s">
-        <v>178</v>
+        <v>281</v>
       </c>
       <c r="C61" t="s">
-        <v>179</v>
+        <v>282</v>
       </c>
       <c r="F61" t="s">
-        <v>178</v>
+        <v>283</v>
       </c>
       <c r="G61" t="s">
-        <v>179</v>
+        <v>284</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -8205,16 +8621,16 @@
         <v>2340</v>
       </c>
       <c r="B62" t="s">
-        <v>180</v>
+        <v>285</v>
       </c>
       <c r="C62" t="s">
-        <v>181</v>
+        <v>286</v>
       </c>
       <c r="F62" t="s">
-        <v>180</v>
+        <v>287</v>
       </c>
       <c r="G62" t="s">
-        <v>181</v>
+        <v>288</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -8222,16 +8638,16 @@
         <v>2341</v>
       </c>
       <c r="B63" t="s">
-        <v>182</v>
+        <v>289</v>
       </c>
       <c r="C63" t="s">
-        <v>183</v>
+        <v>290</v>
       </c>
       <c r="F63" t="s">
-        <v>182</v>
+        <v>291</v>
       </c>
       <c r="G63" t="s">
-        <v>183</v>
+        <v>292</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -8239,16 +8655,16 @@
         <v>2350</v>
       </c>
       <c r="B64" t="s">
-        <v>184</v>
+        <v>293</v>
       </c>
       <c r="C64" t="s">
-        <v>185</v>
+        <v>294</v>
       </c>
       <c r="F64" t="s">
-        <v>184</v>
+        <v>295</v>
       </c>
       <c r="G64" t="s">
-        <v>185</v>
+        <v>296</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -8256,16 +8672,16 @@
         <v>2360</v>
       </c>
       <c r="B65" t="s">
-        <v>186</v>
+        <v>297</v>
       </c>
       <c r="C65" t="s">
-        <v>187</v>
+        <v>298</v>
       </c>
       <c r="F65" t="s">
-        <v>186</v>
+        <v>299</v>
       </c>
       <c r="G65" t="s">
-        <v>187</v>
+        <v>300</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -8273,16 +8689,16 @@
         <v>2370</v>
       </c>
       <c r="B66" t="s">
-        <v>188</v>
+        <v>301</v>
       </c>
       <c r="C66" t="s">
-        <v>189</v>
+        <v>302</v>
       </c>
       <c r="F66" t="s">
-        <v>188</v>
+        <v>303</v>
       </c>
       <c r="G66" t="s">
-        <v>189</v>
+        <v>304</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -8290,16 +8706,16 @@
         <v>2380</v>
       </c>
       <c r="B67" t="s">
-        <v>190</v>
+        <v>305</v>
       </c>
       <c r="C67" t="s">
-        <v>191</v>
+        <v>306</v>
       </c>
       <c r="F67" t="s">
-        <v>190</v>
+        <v>62</v>
       </c>
       <c r="G67" t="s">
-        <v>191</v>
+        <v>307</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -8307,16 +8723,16 @@
         <v>2390</v>
       </c>
       <c r="B68" t="s">
-        <v>192</v>
+        <v>308</v>
       </c>
       <c r="C68" t="s">
-        <v>193</v>
+        <v>309</v>
       </c>
       <c r="F68" t="s">
-        <v>192</v>
+        <v>310</v>
       </c>
       <c r="G68" t="s">
-        <v>193</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -8324,16 +8740,16 @@
         <v>2400</v>
       </c>
       <c r="B69" t="s">
-        <v>194</v>
+        <v>312</v>
       </c>
       <c r="C69" t="s">
-        <v>195</v>
+        <v>313</v>
       </c>
       <c r="F69" t="s">
-        <v>194</v>
+        <v>314</v>
       </c>
       <c r="G69" t="s">
-        <v>195</v>
+        <v>315</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -8341,16 +8757,16 @@
         <v>2410</v>
       </c>
       <c r="B70" t="s">
-        <v>196</v>
+        <v>316</v>
       </c>
       <c r="C70" t="s">
-        <v>197</v>
+        <v>317</v>
       </c>
       <c r="F70" t="s">
-        <v>196</v>
+        <v>27</v>
       </c>
       <c r="G70" t="s">
-        <v>197</v>
+        <v>318</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -8358,16 +8774,16 @@
         <v>2420</v>
       </c>
       <c r="B71" t="s">
-        <v>198</v>
+        <v>319</v>
       </c>
       <c r="C71" t="s">
-        <v>199</v>
+        <v>320</v>
       </c>
       <c r="F71" t="s">
-        <v>198</v>
+        <v>321</v>
       </c>
       <c r="G71" t="s">
-        <v>199</v>
+        <v>322</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -8375,16 +8791,16 @@
         <v>2430</v>
       </c>
       <c r="B72" t="s">
-        <v>200</v>
+        <v>323</v>
       </c>
       <c r="C72" t="s">
-        <v>201</v>
+        <v>324</v>
       </c>
       <c r="F72" t="s">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="G72" t="s">
-        <v>201</v>
+        <v>326</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -8392,16 +8808,16 @@
         <v>2440</v>
       </c>
       <c r="B73" t="s">
-        <v>202</v>
+        <v>327</v>
       </c>
       <c r="C73" t="s">
-        <v>203</v>
+        <v>328</v>
       </c>
       <c r="F73" t="s">
-        <v>202</v>
+        <v>329</v>
       </c>
       <c r="G73" t="s">
-        <v>203</v>
+        <v>330</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -8409,16 +8825,16 @@
         <v>2450</v>
       </c>
       <c r="B74" t="s">
-        <v>204</v>
+        <v>331</v>
       </c>
       <c r="C74" t="s">
-        <v>205</v>
+        <v>332</v>
       </c>
       <c r="F74" t="s">
-        <v>204</v>
+        <v>333</v>
       </c>
       <c r="G74" t="s">
-        <v>205</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -8426,16 +8842,16 @@
         <v>2460</v>
       </c>
       <c r="B75" t="s">
-        <v>206</v>
+        <v>335</v>
       </c>
       <c r="C75" t="s">
-        <v>207</v>
+        <v>336</v>
       </c>
       <c r="F75" t="s">
-        <v>206</v>
+        <v>337</v>
       </c>
       <c r="G75" t="s">
-        <v>207</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -8443,16 +8859,16 @@
         <v>2470</v>
       </c>
       <c r="B76" t="s">
-        <v>208</v>
+        <v>339</v>
       </c>
       <c r="C76" t="s">
-        <v>209</v>
+        <v>340</v>
       </c>
       <c r="F76" t="s">
-        <v>208</v>
+        <v>314</v>
       </c>
       <c r="G76" t="s">
-        <v>209</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -8460,16 +8876,16 @@
         <v>2480</v>
       </c>
       <c r="B77" t="s">
-        <v>210</v>
+        <v>342</v>
       </c>
       <c r="C77" t="s">
-        <v>211</v>
+        <v>343</v>
       </c>
       <c r="F77" t="s">
-        <v>210</v>
+        <v>344</v>
       </c>
       <c r="G77" t="s">
-        <v>211</v>
+        <v>345</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -8477,16 +8893,16 @@
         <v>3010</v>
       </c>
       <c r="B78" t="s">
-        <v>212</v>
+        <v>346</v>
       </c>
       <c r="C78" t="s">
-        <v>213</v>
+        <v>347</v>
       </c>
       <c r="F78" t="s">
-        <v>212</v>
+        <v>348</v>
       </c>
       <c r="G78" t="s">
-        <v>213</v>
+        <v>349</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -8494,16 +8910,16 @@
         <v>3020</v>
       </c>
       <c r="B79" t="s">
-        <v>214</v>
+        <v>350</v>
       </c>
       <c r="C79" t="s">
-        <v>215</v>
+        <v>351</v>
       </c>
       <c r="F79" t="s">
-        <v>214</v>
+        <v>352</v>
       </c>
       <c r="G79" t="s">
-        <v>215</v>
+        <v>353</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -8511,13 +8927,13 @@
         <v>9999</v>
       </c>
       <c r="B80" t="s">
-        <v>216</v>
+        <v>354</v>
       </c>
       <c r="C80" t="s">
         <v>20</v>
       </c>
       <c r="F80" t="s">
-        <v>216</v>
+        <v>354</v>
       </c>
       <c r="G80" t="s">
         <v>20</v>
@@ -8545,7 +8961,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>217</v>
+        <v>355</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -8553,7 +8969,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>218</v>
+        <v>356</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -8561,7 +8977,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>219</v>
+        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -8569,7 +8985,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>220</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -8577,7 +8993,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>221</v>
+        <v>359</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -8585,7 +9001,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>222</v>
+        <v>360</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -8593,7 +9009,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>223</v>
+        <v>361</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8120" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="States" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="364">
   <si>
     <t>Id</t>
   </si>
@@ -228,6 +228,9 @@
     <t>CursedStar</t>
   </si>
   <si>
+    <t>かばう無視</t>
+  </si>
+  <si>
     <t>Text</t>
   </si>
   <si>
@@ -1054,6 +1057,9 @@
   </si>
   <si>
     <t>Do not become a target of status effects</t>
+  </si>
+  <si>
+    <t>攻撃時敵のかばう効果を無視する</t>
   </si>
   <si>
     <t>チャージ</t>
@@ -1110,45 +1116,14 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1162,15 +1137,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1184,23 +1153,20 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1208,9 +1174,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1232,14 +1197,54 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1253,15 +1258,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1282,25 +1288,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1318,13 +1324,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1336,7 +1336,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1348,67 +1432,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1420,43 +1462,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1485,15 +1491,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1513,7 +1510,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1535,20 +1541,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1567,6 +1562,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1575,16 +1581,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1599,121 +1605,121 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2040,7 +2046,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U81"/>
+  <dimension ref="A1:U82"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="21.8181818181818" customWidth="1"/>
@@ -5350,7 +5356,7 @@
         <v>49</v>
       </c>
       <c r="K49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49">
         <v>1</v>
@@ -7358,23 +7364,23 @@
     </row>
     <row r="79" spans="1:21">
       <c r="A79">
-        <v>3010</v>
+        <v>2490</v>
       </c>
       <c r="B79">
-        <v>3010</v>
+        <v>2490</v>
       </c>
       <c r="C79" t="str">
         <f>INDEX(TextData!B:B,MATCH(B79,TextData!A:A))</f>
-        <v>チャージ</v>
+        <v>かばう無視</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="F79" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G79">
         <v>1</v>
@@ -7399,13 +7405,13 @@
         <v>0</v>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O79">
         <v>0</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -7419,21 +7425,20 @@
       <c r="T79">
         <v>1</v>
       </c>
-      <c r="U79" t="str">
-        <f>TextData!B78</f>
-        <v>チャージ</v>
+      <c r="U79" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="80" spans="1:21">
       <c r="A80">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B80">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="C80" t="str">
         <f>INDEX(TextData!B:B,MATCH(B80,TextData!A:A))</f>
-        <v>リンケージ</v>
+        <v>チャージ</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -7489,19 +7494,19 @@
       </c>
       <c r="U80" t="str">
         <f>TextData!B79</f>
-        <v>リンケージ</v>
+        <v>チャージ</v>
       </c>
     </row>
     <row r="81" spans="1:21">
       <c r="A81">
-        <v>9999</v>
+        <v>3020</v>
       </c>
       <c r="B81">
-        <v>9999</v>
+        <v>3020</v>
       </c>
       <c r="C81" t="str">
         <f>INDEX(TextData!B:B,MATCH(B81,TextData!A:A))</f>
-        <v>テスト用</v>
+        <v>リンケージ</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -7557,6 +7562,74 @@
       </c>
       <c r="U81" t="str">
         <f>TextData!B80</f>
+        <v>リンケージ</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21">
+      <c r="A82">
+        <v>9999</v>
+      </c>
+      <c r="B82">
+        <v>9999</v>
+      </c>
+      <c r="C82" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B82,TextData!A:A))</f>
+        <v>テスト用</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82" t="s">
+        <v>61</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+      <c r="H82" t="str">
+        <f>INDEX(Define!B:B,MATCH(G82,Define!A:A))</f>
+        <v>ターン数</v>
+      </c>
+      <c r="I82">
+        <v>1</v>
+      </c>
+      <c r="J82" t="s">
+        <v>20</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>1</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <v>0</v>
+      </c>
+      <c r="R82">
+        <v>0</v>
+      </c>
+      <c r="S82">
+        <v>0</v>
+      </c>
+      <c r="T82">
+        <v>1</v>
+      </c>
+      <c r="U82" t="str">
+        <f>TextData!B81</f>
         <v>テスト用</v>
       </c>
     </row>
@@ -7570,7 +7643,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="14.6363636363636" customWidth="1"/>
@@ -7584,16 +7657,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -7601,13 +7674,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="F2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G2" t="s">
         <v>20</v>
@@ -7618,13 +7691,13 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s">
         <v>20</v>
@@ -7635,16 +7708,16 @@
         <v>201</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -7652,16 +7725,16 @@
         <v>202</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -7669,16 +7742,16 @@
         <v>203</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -7686,16 +7759,16 @@
         <v>204</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -7703,16 +7776,16 @@
         <v>205</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -7720,16 +7793,16 @@
         <v>1010</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -7737,16 +7810,16 @@
         <v>1011</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F10" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -7754,16 +7827,16 @@
         <v>1020</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F11" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -7771,16 +7844,16 @@
         <v>1030</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -7788,16 +7861,16 @@
         <v>1040</v>
       </c>
       <c r="B13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -7805,16 +7878,16 @@
         <v>1041</v>
       </c>
       <c r="B14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -7822,16 +7895,16 @@
         <v>1043</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -7839,16 +7912,16 @@
         <v>1044</v>
       </c>
       <c r="B16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F16" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -7856,16 +7929,16 @@
         <v>1050</v>
       </c>
       <c r="B17" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -7873,16 +7946,16 @@
         <v>1051</v>
       </c>
       <c r="B18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -7890,16 +7963,16 @@
         <v>1052</v>
       </c>
       <c r="B19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C19" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G19" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -7907,16 +7980,16 @@
         <v>1053</v>
       </c>
       <c r="B20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C20" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -7924,16 +7997,16 @@
         <v>1060</v>
       </c>
       <c r="B21" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F21" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -7941,16 +8014,16 @@
         <v>1070</v>
       </c>
       <c r="B22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C22" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F22" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G22" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -7958,16 +8031,16 @@
         <v>1071</v>
       </c>
       <c r="B23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C23" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F23" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -7975,16 +8048,16 @@
         <v>1074</v>
       </c>
       <c r="B24" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G24" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -7992,16 +8065,16 @@
         <v>1080</v>
       </c>
       <c r="B25" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C25" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F25" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G25" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -8009,16 +8082,16 @@
         <v>1081</v>
       </c>
       <c r="B26" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C26" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G26" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -8026,16 +8099,16 @@
         <v>1082</v>
       </c>
       <c r="B27" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G27" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -8043,16 +8116,16 @@
         <v>1090</v>
       </c>
       <c r="B28" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C28" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F28" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G28" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -8060,16 +8133,16 @@
         <v>1091</v>
       </c>
       <c r="B29" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C29" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F29" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G29" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -8077,16 +8150,16 @@
         <v>1092</v>
       </c>
       <c r="B30" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C30" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F30" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G30" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -8094,16 +8167,16 @@
         <v>1100</v>
       </c>
       <c r="B31" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C31" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F31" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G31" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -8111,16 +8184,16 @@
         <v>1101</v>
       </c>
       <c r="B32" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C32" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F32" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G32" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -8128,16 +8201,16 @@
         <v>1210</v>
       </c>
       <c r="B33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -8148,13 +8221,13 @@
         <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F34" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G34" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -8165,13 +8238,13 @@
         <v>35</v>
       </c>
       <c r="C35" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F35" t="s">
+        <v>183</v>
+      </c>
+      <c r="G35" t="s">
         <v>182</v>
-      </c>
-      <c r="G35" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -8179,16 +8252,16 @@
         <v>2020</v>
       </c>
       <c r="B36" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C36" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G36" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -8196,16 +8269,16 @@
         <v>2030</v>
       </c>
       <c r="B37" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F37" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G37" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -8213,16 +8286,16 @@
         <v>2031</v>
       </c>
       <c r="B38" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C38" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F38" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G38" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -8230,16 +8303,16 @@
         <v>2032</v>
       </c>
       <c r="B39" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C39" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F39" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G39" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -8247,16 +8320,16 @@
         <v>2040</v>
       </c>
       <c r="B40" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C40" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F40" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G40" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -8264,16 +8337,16 @@
         <v>2050</v>
       </c>
       <c r="B41" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C41" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F41" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G41" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -8281,16 +8354,16 @@
         <v>2060</v>
       </c>
       <c r="B42" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C42" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F42" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G42" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -8298,16 +8371,16 @@
         <v>2070</v>
       </c>
       <c r="B43" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C43" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F43" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G43" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -8315,16 +8388,16 @@
         <v>2080</v>
       </c>
       <c r="B44" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C44" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F44" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G44" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -8332,16 +8405,16 @@
         <v>2090</v>
       </c>
       <c r="B45" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C45" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F45" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G45" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -8349,16 +8422,16 @@
         <v>2120</v>
       </c>
       <c r="B46" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C46" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F46" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G46" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -8366,16 +8439,16 @@
         <v>2130</v>
       </c>
       <c r="B47" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C47" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F47" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G47" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -8383,16 +8456,16 @@
         <v>2140</v>
       </c>
       <c r="B48" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C48" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F48" t="s">
         <v>48</v>
       </c>
       <c r="G48" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -8400,16 +8473,16 @@
         <v>2150</v>
       </c>
       <c r="B49" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C49" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F49" t="s">
         <v>50</v>
       </c>
       <c r="G49" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -8417,16 +8490,16 @@
         <v>2180</v>
       </c>
       <c r="B50" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C50" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F50" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G50" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -8434,16 +8507,16 @@
         <v>2190</v>
       </c>
       <c r="B51" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C51" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F51" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G51" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -8451,16 +8524,16 @@
         <v>2210</v>
       </c>
       <c r="B52" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C52" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F52" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G52" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -8468,16 +8541,16 @@
         <v>2220</v>
       </c>
       <c r="B53" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C53" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F53" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G53" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -8485,16 +8558,16 @@
         <v>2230</v>
       </c>
       <c r="B54" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C54" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F54" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G54" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -8502,16 +8575,16 @@
         <v>2240</v>
       </c>
       <c r="B55" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C55" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F55" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G55" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -8519,16 +8592,16 @@
         <v>2250</v>
       </c>
       <c r="B56" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C56" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F56" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G56" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -8536,16 +8609,16 @@
         <v>2270</v>
       </c>
       <c r="B57" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C57" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F57" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G57" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -8553,16 +8626,16 @@
         <v>2280</v>
       </c>
       <c r="B58" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C58" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F58" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G58" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -8570,16 +8643,16 @@
         <v>2290</v>
       </c>
       <c r="B59" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C59" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F59" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G59" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -8587,16 +8660,16 @@
         <v>2320</v>
       </c>
       <c r="B60" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C60" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F60" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G60" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -8604,16 +8677,16 @@
         <v>2330</v>
       </c>
       <c r="B61" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C61" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F61" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G61" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -8621,16 +8694,16 @@
         <v>2340</v>
       </c>
       <c r="B62" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C62" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F62" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G62" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -8638,16 +8711,16 @@
         <v>2341</v>
       </c>
       <c r="B63" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C63" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F63" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="G63" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -8655,16 +8728,16 @@
         <v>2350</v>
       </c>
       <c r="B64" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C64" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F64" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G64" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -8672,16 +8745,16 @@
         <v>2360</v>
       </c>
       <c r="B65" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C65" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F65" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G65" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -8689,16 +8762,16 @@
         <v>2370</v>
       </c>
       <c r="B66" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C66" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F66" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="G66" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -8706,16 +8779,16 @@
         <v>2380</v>
       </c>
       <c r="B67" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C67" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F67" t="s">
         <v>62</v>
       </c>
       <c r="G67" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -8723,16 +8796,16 @@
         <v>2390</v>
       </c>
       <c r="B68" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C68" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F68" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G68" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -8740,16 +8813,16 @@
         <v>2400</v>
       </c>
       <c r="B69" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C69" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F69" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G69" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -8757,16 +8830,16 @@
         <v>2410</v>
       </c>
       <c r="B70" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C70" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F70" t="s">
         <v>27</v>
       </c>
       <c r="G70" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -8774,16 +8847,16 @@
         <v>2420</v>
       </c>
       <c r="B71" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C71" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F71" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G71" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -8791,16 +8864,16 @@
         <v>2430</v>
       </c>
       <c r="B72" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C72" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F72" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G72" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -8808,16 +8881,16 @@
         <v>2440</v>
       </c>
       <c r="B73" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C73" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F73" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="G73" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -8825,16 +8898,16 @@
         <v>2450</v>
       </c>
       <c r="B74" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C74" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F74" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="G74" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -8842,16 +8915,16 @@
         <v>2460</v>
       </c>
       <c r="B75" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C75" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G75" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -8859,16 +8932,16 @@
         <v>2470</v>
       </c>
       <c r="B76" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C76" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F76" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G76" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -8876,66 +8949,83 @@
         <v>2480</v>
       </c>
       <c r="B77" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C77" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F77" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="G77" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78">
-        <v>3010</v>
+        <v>2490</v>
       </c>
       <c r="B78" t="s">
-        <v>346</v>
+        <v>70</v>
       </c>
       <c r="C78" t="s">
         <v>347</v>
       </c>
       <c r="F78" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="G78" t="s">
-        <v>349</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B79" t="s">
+        <v>348</v>
+      </c>
+      <c r="C79" t="s">
+        <v>349</v>
+      </c>
+      <c r="F79" t="s">
         <v>350</v>
       </c>
-      <c r="C79" t="s">
+      <c r="G79" t="s">
         <v>351</v>
-      </c>
-      <c r="F79" t="s">
-        <v>352</v>
-      </c>
-      <c r="G79" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80">
-        <v>9999</v>
+        <v>3020</v>
       </c>
       <c r="B80" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C80" t="s">
-        <v>20</v>
+        <v>353</v>
       </c>
       <c r="F80" t="s">
         <v>354</v>
       </c>
       <c r="G80" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81">
+        <v>9999</v>
+      </c>
+      <c r="B81" t="s">
+        <v>356</v>
+      </c>
+      <c r="C81" t="s">
+        <v>20</v>
+      </c>
+      <c r="F81" t="s">
+        <v>356</v>
+      </c>
+      <c r="G81" t="s">
         <v>20</v>
       </c>
     </row>
@@ -8961,7 +9051,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -8969,7 +9059,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -8977,7 +9067,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -8985,7 +9075,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -8993,7 +9083,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -9001,7 +9091,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9009,7 +9099,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -1115,10 +1115,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -1126,44 +1126,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1181,8 +1143,99 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1196,8 +1249,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1211,63 +1265,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1282,13 +1282,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1300,97 +1354,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1408,25 +1372,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1438,31 +1432,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1473,6 +1473,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1487,6 +1496,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1509,17 +1542,19 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1538,41 +1573,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1581,145 +1581,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8120" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="States" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="366">
   <si>
     <t>Id</t>
   </si>
@@ -556,6 +556,12 @@
   </si>
   <si>
     <t>Reduce burn damage taken by {0}%</t>
+  </si>
+  <si>
+    <t>凍結耐性</t>
+  </si>
+  <si>
+    <t>凍結ダメージを{0}%カットする</t>
   </si>
   <si>
     <t>行動後ダメージ</t>
@@ -1115,10 +1121,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -1129,6 +1135,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1136,18 +1190,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1167,16 +1229,37 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1189,85 +1272,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1282,7 +1288,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1300,19 +1330,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1324,31 +1366,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1360,37 +1432,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1408,61 +1456,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1476,11 +1482,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1496,6 +1508,50 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1523,56 +1579,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1581,7 +1587,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1590,136 +1596,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2046,7 +2052,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U82"/>
+  <dimension ref="A1:U83"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="21.8181818181818" customWidth="1"/>
@@ -4306,20 +4312,20 @@
     </row>
     <row r="34" ht="12" customHeight="1" spans="1:21">
       <c r="A34">
-        <v>2010</v>
+        <v>1220</v>
       </c>
       <c r="B34">
-        <v>2010</v>
+        <v>1220</v>
       </c>
       <c r="C34" t="str">
         <f>INDEX(TextData!B:B,MATCH(B34,TextData!A:A))</f>
-        <v>毒</v>
+        <v>凍結耐性</v>
       </c>
       <c r="D34">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="F34" t="s">
         <v>32</v>
@@ -4335,10 +4341,10 @@
         <v>1</v>
       </c>
       <c r="J34" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34">
         <v>1</v>
@@ -4347,19 +4353,19 @@
         <v>0</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34">
         <v>0</v>
@@ -4369,18 +4375,19 @@
       </c>
       <c r="U34" t="str">
         <f>TextData!B34</f>
-        <v>毒</v>
+        <v>凍結耐性</v>
       </c>
     </row>
     <row r="35" ht="12" customHeight="1" spans="1:21">
       <c r="A35">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B35">
         <v>2010</v>
       </c>
-      <c r="C35" t="s">
-        <v>34</v>
+      <c r="C35" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B35,TextData!A:A))</f>
+        <v>毒</v>
       </c>
       <c r="D35">
         <v>26</v>
@@ -4435,25 +4442,25 @@
         <v>1</v>
       </c>
       <c r="U35" t="str">
-        <f>TextData!B34</f>
+        <f>TextData!B35</f>
         <v>毒</v>
       </c>
     </row>
     <row r="36" ht="12" customHeight="1" spans="1:21">
       <c r="A36">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B36">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E36">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="F36" t="s">
         <v>32</v>
@@ -4503,47 +4510,46 @@
       </c>
       <c r="U36" t="str">
         <f>TextData!B35</f>
-        <v>火傷</v>
+        <v>毒</v>
       </c>
     </row>
     <row r="37" ht="12" customHeight="1" spans="1:21">
       <c r="A37">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="B37">
-        <v>2020</v>
-      </c>
-      <c r="C37" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B37,TextData!A:A))</f>
-        <v>暗闇</v>
+        <v>2012</v>
+      </c>
+      <c r="C37" t="s">
+        <v>35</v>
       </c>
       <c r="D37">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="F37" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H37" t="str">
         <f>INDEX(Define!B:B,MATCH(G37,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I37">
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -4571,47 +4577,47 @@
       </c>
       <c r="U37" t="str">
         <f>TextData!B36</f>
-        <v>暗闇</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21">
+        <v>火傷</v>
+      </c>
+    </row>
+    <row r="38" ht="12" customHeight="1" spans="1:21">
       <c r="A38">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B38">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="C38" t="str">
         <f>INDEX(TextData!B:B,MATCH(B38,TextData!A:A))</f>
-        <v>カウンタ</v>
+        <v>暗闇</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E38">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="F38" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H38" t="str">
         <f>INDEX(Define!B:B,MATCH(G38,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K38">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="M38">
         <v>0</v>
@@ -4620,16 +4626,16 @@
         <v>0</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P38">
         <v>0</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -4639,19 +4645,19 @@
       </c>
       <c r="U38" t="str">
         <f>TextData!B37</f>
-        <v>カウンタ</v>
+        <v>暗闇</v>
       </c>
     </row>
     <row r="39" spans="1:21">
       <c r="A39">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B39">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C39" t="str">
         <f>INDEX(TextData!B:B,MATCH(B39,TextData!A:A))</f>
-        <v>CAダメージ</v>
+        <v>カウンタ</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -4670,10 +4676,10 @@
         <v>ターン数</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -4707,19 +4713,19 @@
       </c>
       <c r="U39" t="str">
         <f>TextData!B38</f>
-        <v>CAダメージ</v>
+        <v>カウンタ</v>
       </c>
     </row>
     <row r="40" spans="1:21">
       <c r="A40">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B40">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="C40" t="str">
         <f>INDEX(TextData!B:B,MATCH(B40,TextData!A:A))</f>
-        <v>CAシェル</v>
+        <v>CAダメージ</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -4728,14 +4734,14 @@
         <v>66</v>
       </c>
       <c r="F40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="str">
         <f>INDEX(Define!B:B,MATCH(G40,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I40">
         <v>1</v>
@@ -4775,35 +4781,35 @@
       </c>
       <c r="U40" t="str">
         <f>TextData!B39</f>
-        <v>CAシェル</v>
+        <v>CAダメージ</v>
       </c>
     </row>
     <row r="41" spans="1:21">
       <c r="A41">
-        <v>2040</v>
+        <v>2032</v>
       </c>
       <c r="B41">
-        <v>2040</v>
+        <v>2032</v>
       </c>
       <c r="C41" t="str">
         <f>INDEX(TextData!B:B,MATCH(B41,TextData!A:A))</f>
-        <v>リジェネ</v>
+        <v>CAシェル</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="F41" t="s">
         <v>39</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="str">
         <f>INDEX(Define!B:B,MATCH(G41,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I41">
         <v>1</v>
@@ -4843,41 +4849,41 @@
       </c>
       <c r="U41" t="str">
         <f>TextData!B40</f>
-        <v>リジェネ</v>
+        <v>CAシェル</v>
       </c>
     </row>
     <row r="42" spans="1:21">
       <c r="A42">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="B42">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C42" t="str">
         <f>INDEX(TextData!B:B,MATCH(B42,TextData!A:A))</f>
-        <v>攻撃無効</v>
+        <v>リジェネ</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>226</v>
+        <v>46</v>
       </c>
       <c r="F42" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H42" t="str">
         <f>INDEX(Define!B:B,MATCH(G42,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -4911,41 +4917,41 @@
       </c>
       <c r="U42" t="str">
         <f>TextData!B41</f>
-        <v>攻撃無効</v>
+        <v>リジェネ</v>
       </c>
     </row>
     <row r="43" spans="1:21">
       <c r="A43">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="B43">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="C43" t="str">
         <f>INDEX(TextData!B:B,MATCH(B43,TextData!A:A))</f>
-        <v>ドレイン</v>
+        <v>攻撃無効</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>167</v>
+        <v>226</v>
       </c>
       <c r="F43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H43" t="str">
         <f>INDEX(Define!B:B,MATCH(G43,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -4979,28 +4985,28 @@
       </c>
       <c r="U43" t="str">
         <f>TextData!B42</f>
-        <v>ドレイン</v>
+        <v>攻撃無効</v>
       </c>
     </row>
     <row r="44" spans="1:21">
       <c r="A44">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="B44">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="C44" t="str">
         <f>INDEX(TextData!B:B,MATCH(B44,TextData!A:A))</f>
-        <v>状態異常CA</v>
+        <v>ドレイン</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>226</v>
+        <v>167</v>
       </c>
       <c r="F44" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -5010,7 +5016,7 @@
         <v>ターン数</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="s">
         <v>20</v>
@@ -5047,35 +5053,35 @@
       </c>
       <c r="U44" t="str">
         <f>TextData!B43</f>
-        <v>状態異常CA</v>
+        <v>ドレイン</v>
       </c>
     </row>
     <row r="45" spans="1:21">
       <c r="A45">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="B45">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="C45" t="str">
         <f>INDEX(TextData!B:B,MATCH(B45,TextData!A:A))</f>
-        <v>反撃</v>
+        <v>状態異常CA</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>4</v>
+        <v>226</v>
       </c>
       <c r="F45" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H45" t="str">
         <f>INDEX(Define!B:B,MATCH(G45,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -5115,28 +5121,28 @@
       </c>
       <c r="U45" t="str">
         <f>TextData!B44</f>
-        <v>反撃</v>
+        <v>状態異常CA</v>
       </c>
     </row>
     <row r="46" spans="1:21">
       <c r="A46">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="B46">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="C46" t="str">
         <f>INDEX(TextData!B:B,MATCH(B46,TextData!A:A))</f>
-        <v>パッシブ封じ</v>
+        <v>反撃</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F46" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G46">
         <v>4</v>
@@ -5164,16 +5170,16 @@
         <v>0</v>
       </c>
       <c r="O46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P46">
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46">
         <v>0</v>
@@ -5183,28 +5189,28 @@
       </c>
       <c r="U46" t="str">
         <f>TextData!B45</f>
-        <v>パッシブ封じ</v>
+        <v>反撃</v>
       </c>
     </row>
     <row r="47" spans="1:21">
       <c r="A47">
-        <v>2120</v>
+        <v>2090</v>
       </c>
       <c r="B47">
-        <v>2120</v>
+        <v>2090</v>
       </c>
       <c r="C47" t="str">
         <f>INDEX(TextData!B:B,MATCH(B47,TextData!A:A))</f>
-        <v>デバフ強化</v>
+        <v>パッシブ封じ</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G47">
         <v>4</v>
@@ -5214,16 +5220,16 @@
         <v>効果発揮回数</v>
       </c>
       <c r="I47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="K47">
         <v>0</v>
       </c>
       <c r="L47">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M47">
         <v>0</v>
@@ -5232,13 +5238,13 @@
         <v>0</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P47">
         <v>0</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47">
         <v>1</v>
@@ -5251,47 +5257,47 @@
       </c>
       <c r="U47" t="str">
         <f>TextData!B46</f>
-        <v>デバフ強化</v>
+        <v>パッシブ封じ</v>
       </c>
     </row>
     <row r="48" spans="1:21">
       <c r="A48">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="B48">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="C48" t="str">
         <f>INDEX(TextData!B:B,MATCH(B48,TextData!A:A))</f>
-        <v>挑発</v>
+        <v>デバフ強化</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
+        <v>9</v>
+      </c>
+      <c r="F48" t="s">
+        <v>45</v>
+      </c>
+      <c r="G48">
         <v>4</v>
-      </c>
-      <c r="F48" t="s">
-        <v>47</v>
-      </c>
-      <c r="G48">
-        <v>1</v>
       </c>
       <c r="H48" t="str">
         <f>INDEX(Define!B:B,MATCH(G48,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="K48">
         <v>0</v>
       </c>
       <c r="L48">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="M48">
         <v>0</v>
@@ -5319,44 +5325,44 @@
       </c>
       <c r="U48" t="str">
         <f>TextData!B47</f>
-        <v>挑発</v>
+        <v>デバフ強化</v>
       </c>
     </row>
     <row r="49" spans="1:21">
       <c r="A49">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="B49">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="C49" t="str">
         <f>INDEX(TextData!B:B,MATCH(B49,TextData!A:A))</f>
-        <v>凍結</v>
+        <v>挑発</v>
       </c>
       <c r="D49">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="F49" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H49" t="str">
         <f>INDEX(Define!B:B,MATCH(G49,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="K49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49">
         <v>1</v>
@@ -5368,13 +5374,13 @@
         <v>0</v>
       </c>
       <c r="O49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P49">
         <v>0</v>
       </c>
       <c r="Q49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49">
         <v>1</v>
@@ -5387,44 +5393,44 @@
       </c>
       <c r="U49" t="str">
         <f>TextData!B48</f>
-        <v>凍結</v>
+        <v>挑発</v>
       </c>
     </row>
     <row r="50" spans="1:21">
       <c r="A50">
-        <v>2150</v>
+        <v>2140</v>
       </c>
       <c r="B50">
-        <v>2150</v>
+        <v>2140</v>
       </c>
       <c r="C50" t="str">
         <f>INDEX(TextData!B:B,MATCH(B50,TextData!A:A))</f>
-        <v>スタン</v>
+        <v>凍結</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E50">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="F50" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H50" t="str">
         <f>INDEX(Define!B:B,MATCH(G50,Define!A:A))</f>
-        <v>APカウント</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50">
         <v>1</v>
@@ -5455,41 +5461,41 @@
       </c>
       <c r="U50" t="str">
         <f>TextData!B49</f>
-        <v>スタン</v>
+        <v>凍結</v>
       </c>
     </row>
     <row r="51" spans="1:21">
       <c r="A51">
-        <v>2180</v>
+        <v>2150</v>
       </c>
       <c r="B51">
-        <v>2180</v>
+        <v>2150</v>
       </c>
       <c r="C51" t="str">
         <f>INDEX(TextData!B:B,MATCH(B51,TextData!A:A))</f>
-        <v>状態異常回避</v>
+        <v>スタン</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="F51" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G51">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H51" t="str">
         <f>INDEX(Define!B:B,MATCH(G51,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>APカウント</v>
       </c>
       <c r="I51">
         <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="K51">
         <v>0</v>
@@ -5504,16 +5510,16 @@
         <v>0</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P51">
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -5523,35 +5529,35 @@
       </c>
       <c r="U51" t="str">
         <f>TextData!B50</f>
-        <v>状態異常回避</v>
+        <v>スタン</v>
       </c>
     </row>
     <row r="52" spans="1:21">
       <c r="A52">
-        <v>2190</v>
+        <v>2180</v>
       </c>
       <c r="B52">
-        <v>2190</v>
+        <v>2180</v>
       </c>
       <c r="C52" t="str">
         <f>INDEX(TextData!B:B,MATCH(B52,TextData!A:A))</f>
-        <v>対象範囲延長</v>
+        <v>状態異常回避</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="F52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H52" t="str">
         <f>INDEX(Define!B:B,MATCH(G52,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -5587,32 +5593,32 @@
         <v>0</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U52" t="str">
         <f>TextData!B51</f>
-        <v>対象範囲延長</v>
+        <v>状態異常回避</v>
       </c>
     </row>
     <row r="53" spans="1:21">
       <c r="A53">
-        <v>2210</v>
+        <v>2190</v>
       </c>
       <c r="B53">
-        <v>2210</v>
+        <v>2190</v>
       </c>
       <c r="C53" t="str">
         <f>INDEX(TextData!B:B,MATCH(B53,TextData!A:A))</f>
-        <v>アフターヒール</v>
+        <v>対象範囲延長</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F53" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -5622,7 +5628,7 @@
         <v>ターン数</v>
       </c>
       <c r="I53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J53" t="s">
         <v>20</v>
@@ -5655,32 +5661,32 @@
         <v>0</v>
       </c>
       <c r="T53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U53" t="str">
         <f>TextData!B52</f>
-        <v>アフターヒール</v>
+        <v>対象範囲延長</v>
       </c>
     </row>
     <row r="54" spans="1:21">
       <c r="A54">
-        <v>2220</v>
+        <v>2210</v>
       </c>
       <c r="B54">
-        <v>2220</v>
+        <v>2210</v>
       </c>
       <c r="C54" t="str">
         <f>INDEX(TextData!B:B,MATCH(B54,TextData!A:A))</f>
-        <v>即死付与</v>
+        <v>アフターヒール</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="F54" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -5690,7 +5696,7 @@
         <v>ターン数</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="s">
         <v>20</v>
@@ -5717,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="R54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54">
         <v>0</v>
@@ -5727,38 +5733,38 @@
       </c>
       <c r="U54" t="str">
         <f>TextData!B53</f>
-        <v>即死付与</v>
+        <v>アフターヒール</v>
       </c>
     </row>
     <row r="55" spans="1:21">
       <c r="A55">
-        <v>2230</v>
+        <v>2220</v>
       </c>
       <c r="B55">
-        <v>2230</v>
+        <v>2220</v>
       </c>
       <c r="C55" t="str">
         <f>INDEX(TextData!B:B,MATCH(B55,TextData!A:A))</f>
-        <v>同時回復</v>
+        <v>即死付与</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55" t="str">
         <f>INDEX(Define!B:B,MATCH(G55,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="s">
         <v>20</v>
@@ -5785,7 +5791,7 @@
         <v>0</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55">
         <v>0</v>
@@ -5795,38 +5801,38 @@
       </c>
       <c r="U55" t="str">
         <f>TextData!B54</f>
-        <v>同時回復</v>
+        <v>即死付与</v>
       </c>
     </row>
     <row r="56" spans="1:21">
       <c r="A56">
-        <v>2240</v>
+        <v>2230</v>
       </c>
       <c r="B56">
-        <v>2240</v>
+        <v>2230</v>
       </c>
       <c r="C56" t="str">
         <f>INDEX(TextData!B:B,MATCH(B56,TextData!A:A))</f>
-        <v>必中</v>
+        <v>同時回復</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F56" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G56">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H56" t="str">
         <f>INDEX(Define!B:B,MATCH(G56,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>なし</v>
       </c>
       <c r="I56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="s">
         <v>20</v>
@@ -5863,35 +5869,35 @@
       </c>
       <c r="U56" t="str">
         <f>TextData!B55</f>
-        <v>必中</v>
+        <v>同時回復</v>
       </c>
     </row>
     <row r="57" spans="1:21">
       <c r="A57">
-        <v>2250</v>
+        <v>2240</v>
       </c>
       <c r="B57">
-        <v>2250</v>
+        <v>2240</v>
       </c>
       <c r="C57" t="str">
         <f>INDEX(TextData!B:B,MATCH(B57,TextData!A:A))</f>
-        <v>アシストヒール</v>
+        <v>必中</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="F57" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H57" t="str">
         <f>INDEX(Define!B:B,MATCH(G57,Define!A:A))</f>
-        <v>なし</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -5931,28 +5937,28 @@
       </c>
       <c r="U57" t="str">
         <f>TextData!B56</f>
-        <v>アシストヒール</v>
+        <v>必中</v>
       </c>
     </row>
     <row r="58" spans="1:21">
       <c r="A58">
-        <v>2270</v>
+        <v>2250</v>
       </c>
       <c r="B58">
-        <v>2270</v>
+        <v>2250</v>
       </c>
       <c r="C58" t="str">
         <f>INDEX(TextData!B:B,MATCH(B58,TextData!A:A))</f>
-        <v>アンデッド</v>
+        <v>アシストヒール</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="F58" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -5999,28 +6005,28 @@
       </c>
       <c r="U58" t="str">
         <f>TextData!B57</f>
-        <v>アンデッド</v>
+        <v>アシストヒール</v>
       </c>
     </row>
     <row r="59" spans="1:21">
       <c r="A59">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="B59">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="C59" t="str">
         <f>INDEX(TextData!B:B,MATCH(B59,TextData!A:A))</f>
-        <v>アクセル</v>
+        <v>アンデッド</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F59" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6067,38 +6073,38 @@
       </c>
       <c r="U59" t="str">
         <f>TextData!B58</f>
-        <v>アクセル</v>
+        <v>アンデッド</v>
       </c>
     </row>
     <row r="60" spans="1:21">
       <c r="A60">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="B60">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="C60" t="str">
         <f>INDEX(TextData!B:B,MATCH(B60,TextData!A:A))</f>
-        <v>ダメージ威力アップ</v>
+        <v>アクセル</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
+        <v>25</v>
+      </c>
+      <c r="F60" t="s">
         <v>21</v>
       </c>
-      <c r="F60" t="s">
-        <v>56</v>
-      </c>
       <c r="G60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" t="str">
         <f>INDEX(Define!B:B,MATCH(G60,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="s">
         <v>20</v>
@@ -6110,7 +6116,7 @@
         <v>1</v>
       </c>
       <c r="M60">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N60">
         <v>0</v>
@@ -6119,7 +6125,7 @@
         <v>0</v>
       </c>
       <c r="P60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -6135,35 +6141,35 @@
       </c>
       <c r="U60" t="str">
         <f>TextData!B59</f>
-        <v>ダメージ威力アップ</v>
+        <v>アクセル</v>
       </c>
     </row>
     <row r="61" spans="1:21">
       <c r="A61">
-        <v>2320</v>
+        <v>2290</v>
       </c>
       <c r="B61">
-        <v>2320</v>
+        <v>2290</v>
       </c>
       <c r="C61" t="str">
         <f>INDEX(TextData!B:B,MATCH(B61,TextData!A:A))</f>
-        <v>バフ解除</v>
+        <v>ダメージ威力アップ</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>0</v>
-      </c>
-      <c r="F61">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="F61" t="s">
+        <v>56</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="str">
         <f>INDEX(Define!B:B,MATCH(G61,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I61">
         <v>1</v>
@@ -6178,7 +6184,7 @@
         <v>1</v>
       </c>
       <c r="M61">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N61">
         <v>0</v>
@@ -6187,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -6203,35 +6209,35 @@
       </c>
       <c r="U61" t="str">
         <f>TextData!B60</f>
-        <v>バフ解除</v>
+        <v>ダメージ威力アップ</v>
       </c>
     </row>
     <row r="62" spans="1:21">
       <c r="A62">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="B62">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="C62" t="str">
         <f>INDEX(TextData!B:B,MATCH(B62,TextData!A:A))</f>
-        <v>貫通</v>
+        <v>バフ解除</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>56</v>
-      </c>
-      <c r="F62" t="s">
-        <v>57</v>
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" t="str">
         <f>INDEX(Define!B:B,MATCH(G62,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I62">
         <v>1</v>
@@ -6249,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="N62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O62">
         <v>0</v>
@@ -6271,28 +6277,28 @@
       </c>
       <c r="U62" t="str">
         <f>TextData!B61</f>
-        <v>貫通</v>
+        <v>バフ解除</v>
       </c>
     </row>
     <row r="63" spans="1:21">
       <c r="A63">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="B63">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="C63" t="str">
         <f>INDEX(TextData!B:B,MATCH(B63,TextData!A:A))</f>
-        <v>対象列化</v>
+        <v>貫通</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F63" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -6339,19 +6345,19 @@
       </c>
       <c r="U63" t="str">
         <f>TextData!B62</f>
-        <v>対象列化</v>
+        <v>貫通</v>
       </c>
     </row>
     <row r="64" spans="1:21">
       <c r="A64">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="B64">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="C64" t="str">
         <f>INDEX(TextData!B:B,MATCH(B64,TextData!A:A))</f>
-        <v>対象全体化</v>
+        <v>対象列化</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -6360,7 +6366,7 @@
         <v>66</v>
       </c>
       <c r="F64" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -6407,28 +6413,28 @@
       </c>
       <c r="U64" t="str">
         <f>TextData!B63</f>
-        <v>対象全体化</v>
+        <v>対象列化</v>
       </c>
     </row>
     <row r="65" spans="1:21">
       <c r="A65">
-        <v>2350</v>
+        <v>2341</v>
       </c>
       <c r="B65">
-        <v>2350</v>
+        <v>2341</v>
       </c>
       <c r="C65" t="str">
         <f>INDEX(TextData!B:B,MATCH(B65,TextData!A:A))</f>
-        <v>聖棺</v>
+        <v>対象全体化</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F65" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -6475,28 +6481,28 @@
       </c>
       <c r="U65" t="str">
         <f>TextData!B64</f>
-        <v>聖棺</v>
+        <v>対象全体化</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66">
-        <v>2360</v>
+        <v>2350</v>
       </c>
       <c r="B66">
-        <v>2360</v>
+        <v>2350</v>
       </c>
       <c r="C66" t="str">
         <f>INDEX(TextData!B:B,MATCH(B66,TextData!A:A))</f>
-        <v>追加ダメージ</v>
+        <v>聖棺</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F66" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -6543,25 +6549,25 @@
       </c>
       <c r="U66" t="str">
         <f>TextData!B65</f>
-        <v>追加ダメージ</v>
+        <v>聖棺</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67">
-        <v>2370</v>
+        <v>2360</v>
       </c>
       <c r="B67">
-        <v>2370</v>
+        <v>2360</v>
       </c>
       <c r="C67" t="str">
         <f>INDEX(TextData!B:B,MATCH(B67,TextData!A:A))</f>
-        <v>追加効果</v>
+        <v>追加ダメージ</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F67" t="s">
         <v>61</v>
@@ -6611,28 +6617,28 @@
       </c>
       <c r="U67" t="str">
         <f>TextData!B66</f>
-        <v>追加効果</v>
+        <v>追加ダメージ</v>
       </c>
     </row>
     <row r="68" spans="1:21">
       <c r="A68">
-        <v>2380</v>
+        <v>2370</v>
       </c>
       <c r="B68">
-        <v>2380</v>
+        <v>2370</v>
       </c>
       <c r="C68" t="str">
         <f>INDEX(TextData!B:B,MATCH(B68,TextData!A:A))</f>
-        <v>透明</v>
+        <v>追加効果</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F68" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -6679,28 +6685,28 @@
       </c>
       <c r="U68" t="str">
         <f>TextData!B67</f>
-        <v>透明</v>
+        <v>追加効果</v>
       </c>
     </row>
     <row r="69" spans="1:21">
       <c r="A69">
-        <v>2390</v>
+        <v>2380</v>
       </c>
       <c r="B69">
-        <v>2390</v>
+        <v>2380</v>
       </c>
       <c r="C69" t="str">
         <f>INDEX(TextData!B:B,MATCH(B69,TextData!A:A))</f>
-        <v>沈黙</v>
+        <v>透明</v>
       </c>
       <c r="D69">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E69">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F69" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -6725,19 +6731,19 @@
         <v>0</v>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P69">
         <v>0</v>
       </c>
       <c r="Q69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S69">
         <v>0</v>
@@ -6747,28 +6753,28 @@
       </c>
       <c r="U69" t="str">
         <f>TextData!B68</f>
-        <v>沈黙</v>
+        <v>透明</v>
       </c>
     </row>
     <row r="70" spans="1:21">
       <c r="A70">
-        <v>2400</v>
+        <v>2390</v>
       </c>
       <c r="B70">
-        <v>2400</v>
+        <v>2390</v>
       </c>
       <c r="C70" t="str">
         <f>INDEX(TextData!B:B,MATCH(B70,TextData!A:A))</f>
-        <v>不治</v>
+        <v>沈黙</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F70" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -6815,19 +6821,19 @@
       </c>
       <c r="U70" t="str">
         <f>TextData!B69</f>
-        <v>不治</v>
+        <v>沈黙</v>
       </c>
     </row>
     <row r="71" spans="1:21">
       <c r="A71">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="B71">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="C71" t="str">
         <f>INDEX(TextData!B:B,MATCH(B71,TextData!A:A))</f>
-        <v>シールド</v>
+        <v>不治</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -6836,7 +6842,7 @@
         <v>0</v>
       </c>
       <c r="F71" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -6861,19 +6867,19 @@
         <v>0</v>
       </c>
       <c r="N71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -6883,19 +6889,19 @@
       </c>
       <c r="U71" t="str">
         <f>TextData!B70</f>
-        <v>シールド</v>
+        <v>不治</v>
       </c>
     </row>
     <row r="72" spans="1:21">
       <c r="A72">
-        <v>2420</v>
+        <v>2410</v>
       </c>
       <c r="B72">
-        <v>2420</v>
+        <v>2410</v>
       </c>
       <c r="C72" t="str">
         <f>INDEX(TextData!B:B,MATCH(B72,TextData!A:A))</f>
-        <v>フォロー</v>
+        <v>シールド</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -6904,7 +6910,7 @@
         <v>0</v>
       </c>
       <c r="F72" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -6951,19 +6957,19 @@
       </c>
       <c r="U72" t="str">
         <f>TextData!B71</f>
-        <v>フォロー</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="73" spans="1:21">
       <c r="A73">
-        <v>2430</v>
+        <v>2420</v>
       </c>
       <c r="B73">
-        <v>2430</v>
+        <v>2420</v>
       </c>
       <c r="C73" t="str">
         <f>INDEX(TextData!B:B,MATCH(B73,TextData!A:A))</f>
-        <v>かばう</v>
+        <v>フォロー</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -6972,14 +6978,14 @@
         <v>0</v>
       </c>
       <c r="F73" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G73">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H73" t="str">
         <f>INDEX(Define!B:B,MATCH(G73,Define!A:A))</f>
-        <v>ターンの終了</v>
+        <v>ターン数</v>
       </c>
       <c r="I73">
         <v>1</v>
@@ -7012,26 +7018,26 @@
         <v>0</v>
       </c>
       <c r="S73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T73">
         <v>1</v>
       </c>
       <c r="U73" t="str">
         <f>TextData!B72</f>
-        <v>かばう</v>
+        <v>フォロー</v>
       </c>
     </row>
     <row r="74" spans="1:21">
       <c r="A74">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="B74">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="C74" t="str">
         <f>INDEX(TextData!B:B,MATCH(B74,TextData!A:A))</f>
-        <v>Ap消費半減</v>
+        <v>かばう</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -7040,14 +7046,14 @@
         <v>0</v>
       </c>
       <c r="F74" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="G74">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H74" t="str">
         <f>INDEX(Define!B:B,MATCH(G74,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>ターンの終了</v>
       </c>
       <c r="I74">
         <v>1</v>
@@ -7077,29 +7083,29 @@
         <v>0</v>
       </c>
       <c r="R74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74">
         <v>1</v>
       </c>
       <c r="U74" t="str">
         <f>TextData!B73</f>
-        <v>Ap消費半減</v>
+        <v>かばう</v>
       </c>
     </row>
     <row r="75" spans="1:21">
       <c r="A75">
-        <v>2450</v>
+        <v>2440</v>
       </c>
       <c r="B75">
-        <v>2450</v>
+        <v>2440</v>
       </c>
       <c r="C75" t="str">
         <f>INDEX(TextData!B:B,MATCH(B75,TextData!A:A))</f>
-        <v>不死</v>
+        <v>Ap消費半減</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -7108,14 +7114,14 @@
         <v>0</v>
       </c>
       <c r="F75" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H75" t="str">
         <f>INDEX(Define!B:B,MATCH(G75,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I75">
         <v>1</v>
@@ -7155,19 +7161,19 @@
       </c>
       <c r="U75" t="str">
         <f>TextData!B74</f>
-        <v>不死</v>
+        <v>Ap消費半減</v>
       </c>
     </row>
     <row r="76" spans="1:21">
       <c r="A76">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="B76">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="C76" t="str">
         <f>INDEX(TextData!B:B,MATCH(B76,TextData!A:A))</f>
-        <v>Hp回復効果アップ</v>
+        <v>不死</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -7176,14 +7182,14 @@
         <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G76">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H76" t="str">
         <f>INDEX(Define!B:B,MATCH(G76,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I76">
         <v>1</v>
@@ -7213,7 +7219,7 @@
         <v>0</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S76">
         <v>0</v>
@@ -7223,19 +7229,19 @@
       </c>
       <c r="U76" t="str">
         <f>TextData!B75</f>
-        <v>Hp回復効果アップ</v>
+        <v>不死</v>
       </c>
     </row>
     <row r="77" spans="1:21">
       <c r="A77">
-        <v>2470</v>
+        <v>2460</v>
       </c>
       <c r="B77">
-        <v>2470</v>
+        <v>2460</v>
       </c>
       <c r="C77" t="str">
         <f>INDEX(TextData!B:B,MATCH(B77,TextData!A:A))</f>
-        <v>呪詛</v>
+        <v>Hp回復効果アップ</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -7244,14 +7250,14 @@
         <v>0</v>
       </c>
       <c r="F77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H77" t="str">
         <f>INDEX(Define!B:B,MATCH(G77,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I77">
         <v>1</v>
@@ -7281,7 +7287,7 @@
         <v>0</v>
       </c>
       <c r="R77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -7291,35 +7297,35 @@
       </c>
       <c r="U77" t="str">
         <f>TextData!B76</f>
-        <v>呪詛</v>
+        <v>Hp回復効果アップ</v>
       </c>
     </row>
     <row r="78" spans="1:21">
       <c r="A78">
-        <v>2480</v>
+        <v>2470</v>
       </c>
       <c r="B78">
-        <v>2480</v>
+        <v>2470</v>
       </c>
       <c r="C78" t="str">
         <f>INDEX(TextData!B:B,MATCH(B78,TextData!A:A))</f>
-        <v>付与無効化</v>
+        <v>呪詛</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="F78" t="s">
         <v>69</v>
       </c>
       <c r="G78">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H78" t="str">
         <f>INDEX(Define!B:B,MATCH(G78,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I78">
         <v>1</v>
@@ -7359,19 +7365,19 @@
       </c>
       <c r="U78" t="str">
         <f>TextData!B77</f>
-        <v>付与無効化</v>
+        <v>呪詛</v>
       </c>
     </row>
     <row r="79" spans="1:21">
       <c r="A79">
-        <v>2490</v>
+        <v>2480</v>
       </c>
       <c r="B79">
-        <v>2490</v>
+        <v>2480</v>
       </c>
       <c r="C79" t="str">
         <f>INDEX(TextData!B:B,MATCH(B79,TextData!A:A))</f>
-        <v>かばう無視</v>
+        <v>付与無効化</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -7417,7 +7423,7 @@
         <v>0</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -7425,29 +7431,30 @@
       <c r="T79">
         <v>1</v>
       </c>
-      <c r="U79" t="s">
-        <v>70</v>
+      <c r="U79" t="str">
+        <f>TextData!B78</f>
+        <v>付与無効化</v>
       </c>
     </row>
     <row r="80" spans="1:21">
       <c r="A80">
-        <v>3010</v>
+        <v>2490</v>
       </c>
       <c r="B80">
-        <v>3010</v>
+        <v>2490</v>
       </c>
       <c r="C80" t="str">
         <f>INDEX(TextData!B:B,MATCH(B80,TextData!A:A))</f>
-        <v>チャージ</v>
+        <v>かばう無視</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="F80" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -7472,13 +7479,13 @@
         <v>0</v>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O80">
         <v>0</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -7492,21 +7499,20 @@
       <c r="T80">
         <v>1</v>
       </c>
-      <c r="U80" t="str">
-        <f>TextData!B79</f>
-        <v>チャージ</v>
+      <c r="U80" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="81" spans="1:21">
       <c r="A81">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B81">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="C81" t="str">
         <f>INDEX(TextData!B:B,MATCH(B81,TextData!A:A))</f>
-        <v>リンケージ</v>
+        <v>チャージ</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -7562,19 +7568,19 @@
       </c>
       <c r="U81" t="str">
         <f>TextData!B80</f>
-        <v>リンケージ</v>
+        <v>チャージ</v>
       </c>
     </row>
     <row r="82" spans="1:21">
       <c r="A82">
-        <v>9999</v>
+        <v>3020</v>
       </c>
       <c r="B82">
-        <v>9999</v>
+        <v>3020</v>
       </c>
       <c r="C82" t="str">
         <f>INDEX(TextData!B:B,MATCH(B82,TextData!A:A))</f>
-        <v>テスト用</v>
+        <v>リンケージ</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -7630,6 +7636,74 @@
       </c>
       <c r="U82" t="str">
         <f>TextData!B81</f>
+        <v>リンケージ</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21">
+      <c r="A83">
+        <v>9999</v>
+      </c>
+      <c r="B83">
+        <v>9999</v>
+      </c>
+      <c r="C83" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B83,TextData!A:A))</f>
+        <v>テスト用</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83" t="s">
+        <v>61</v>
+      </c>
+      <c r="G83">
+        <v>1</v>
+      </c>
+      <c r="H83" t="str">
+        <f>INDEX(Define!B:B,MATCH(G83,Define!A:A))</f>
+        <v>ターン数</v>
+      </c>
+      <c r="I83">
+        <v>1</v>
+      </c>
+      <c r="J83" t="s">
+        <v>20</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>1</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <v>0</v>
+      </c>
+      <c r="R83">
+        <v>0</v>
+      </c>
+      <c r="S83">
+        <v>0</v>
+      </c>
+      <c r="T83">
+        <v>1</v>
+      </c>
+      <c r="U83" t="str">
+        <f>TextData!B82</f>
         <v>テスト用</v>
       </c>
     </row>
@@ -7643,7 +7717,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="14.6363636363636" customWidth="1"/>
@@ -8215,817 +8289,834 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>2010</v>
+        <v>1220</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>180</v>
       </c>
       <c r="C34" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F34" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G34" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C35" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F35" t="s">
         <v>183</v>
       </c>
       <c r="G35" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="B36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" t="s">
+        <v>182</v>
+      </c>
+      <c r="F36" t="s">
+        <v>185</v>
+      </c>
+      <c r="G36" t="s">
         <v>184</v>
-      </c>
-      <c r="C36" t="s">
-        <v>185</v>
-      </c>
-      <c r="F36" t="s">
-        <v>186</v>
-      </c>
-      <c r="G36" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B37" t="s">
+        <v>186</v>
+      </c>
+      <c r="C37" t="s">
+        <v>187</v>
+      </c>
+      <c r="F37" t="s">
         <v>188</v>
       </c>
-      <c r="C37" t="s">
+      <c r="G37" t="s">
         <v>189</v>
-      </c>
-      <c r="F37" t="s">
-        <v>190</v>
-      </c>
-      <c r="G37" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B38" t="s">
+        <v>190</v>
+      </c>
+      <c r="C38" t="s">
+        <v>191</v>
+      </c>
+      <c r="F38" t="s">
         <v>192</v>
       </c>
-      <c r="C38" t="s">
+      <c r="G38" t="s">
         <v>193</v>
-      </c>
-      <c r="F38" t="s">
-        <v>194</v>
-      </c>
-      <c r="G38" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B39" t="s">
+        <v>194</v>
+      </c>
+      <c r="C39" t="s">
+        <v>195</v>
+      </c>
+      <c r="F39" t="s">
         <v>196</v>
       </c>
-      <c r="C39" t="s">
+      <c r="G39" t="s">
         <v>197</v>
-      </c>
-      <c r="F39" t="s">
-        <v>198</v>
-      </c>
-      <c r="G39" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>2040</v>
+        <v>2032</v>
       </c>
       <c r="B40" t="s">
+        <v>198</v>
+      </c>
+      <c r="C40" t="s">
+        <v>199</v>
+      </c>
+      <c r="F40" t="s">
         <v>200</v>
       </c>
-      <c r="C40" t="s">
+      <c r="G40" t="s">
         <v>201</v>
-      </c>
-      <c r="F40" t="s">
-        <v>202</v>
-      </c>
-      <c r="G40" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="B41" t="s">
+        <v>202</v>
+      </c>
+      <c r="C41" t="s">
+        <v>203</v>
+      </c>
+      <c r="F41" t="s">
         <v>204</v>
       </c>
-      <c r="C41" t="s">
+      <c r="G41" t="s">
         <v>205</v>
-      </c>
-      <c r="F41" t="s">
-        <v>206</v>
-      </c>
-      <c r="G41" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="B42" t="s">
+        <v>206</v>
+      </c>
+      <c r="C42" t="s">
+        <v>207</v>
+      </c>
+      <c r="F42" t="s">
         <v>208</v>
       </c>
-      <c r="C42" t="s">
+      <c r="G42" t="s">
         <v>209</v>
-      </c>
-      <c r="F42" t="s">
-        <v>210</v>
-      </c>
-      <c r="G42" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="B43" t="s">
+        <v>210</v>
+      </c>
+      <c r="C43" t="s">
+        <v>211</v>
+      </c>
+      <c r="F43" t="s">
         <v>212</v>
       </c>
-      <c r="C43" t="s">
+      <c r="G43" t="s">
         <v>213</v>
-      </c>
-      <c r="F43" t="s">
-        <v>214</v>
-      </c>
-      <c r="G43" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="B44" t="s">
+        <v>214</v>
+      </c>
+      <c r="C44" t="s">
+        <v>215</v>
+      </c>
+      <c r="F44" t="s">
         <v>216</v>
       </c>
-      <c r="C44" t="s">
+      <c r="G44" t="s">
         <v>217</v>
-      </c>
-      <c r="F44" t="s">
-        <v>218</v>
-      </c>
-      <c r="G44" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="B45" t="s">
+        <v>218</v>
+      </c>
+      <c r="C45" t="s">
+        <v>219</v>
+      </c>
+      <c r="F45" t="s">
         <v>220</v>
       </c>
-      <c r="C45" t="s">
+      <c r="G45" t="s">
         <v>221</v>
-      </c>
-      <c r="F45" t="s">
-        <v>222</v>
-      </c>
-      <c r="G45" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>2120</v>
+        <v>2090</v>
       </c>
       <c r="B46" t="s">
+        <v>222</v>
+      </c>
+      <c r="C46" t="s">
+        <v>223</v>
+      </c>
+      <c r="F46" t="s">
         <v>224</v>
       </c>
-      <c r="C46" t="s">
+      <c r="G46" t="s">
         <v>225</v>
-      </c>
-      <c r="F46" t="s">
-        <v>226</v>
-      </c>
-      <c r="G46" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="B47" t="s">
+        <v>226</v>
+      </c>
+      <c r="C47" t="s">
+        <v>227</v>
+      </c>
+      <c r="F47" t="s">
         <v>228</v>
       </c>
-      <c r="C47" t="s">
+      <c r="G47" t="s">
         <v>229</v>
-      </c>
-      <c r="F47" t="s">
-        <v>230</v>
-      </c>
-      <c r="G47" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="B48" t="s">
+        <v>230</v>
+      </c>
+      <c r="C48" t="s">
+        <v>231</v>
+      </c>
+      <c r="F48" t="s">
         <v>232</v>
       </c>
-      <c r="C48" t="s">
+      <c r="G48" t="s">
         <v>233</v>
-      </c>
-      <c r="F48" t="s">
-        <v>48</v>
-      </c>
-      <c r="G48" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>2150</v>
+        <v>2140</v>
       </c>
       <c r="B49" t="s">
+        <v>234</v>
+      </c>
+      <c r="C49" t="s">
         <v>235</v>
       </c>
-      <c r="C49" t="s">
+      <c r="F49" t="s">
+        <v>48</v>
+      </c>
+      <c r="G49" t="s">
         <v>236</v>
-      </c>
-      <c r="F49" t="s">
-        <v>50</v>
-      </c>
-      <c r="G49" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>2180</v>
+        <v>2150</v>
       </c>
       <c r="B50" t="s">
+        <v>237</v>
+      </c>
+      <c r="C50" t="s">
         <v>238</v>
       </c>
-      <c r="C50" t="s">
+      <c r="F50" t="s">
+        <v>50</v>
+      </c>
+      <c r="G50" t="s">
         <v>239</v>
-      </c>
-      <c r="F50" t="s">
-        <v>240</v>
-      </c>
-      <c r="G50" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>2190</v>
+        <v>2180</v>
       </c>
       <c r="B51" t="s">
+        <v>240</v>
+      </c>
+      <c r="C51" t="s">
+        <v>241</v>
+      </c>
+      <c r="F51" t="s">
         <v>242</v>
       </c>
-      <c r="C51" t="s">
+      <c r="G51" t="s">
         <v>243</v>
-      </c>
-      <c r="F51" t="s">
-        <v>244</v>
-      </c>
-      <c r="G51" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>2210</v>
+        <v>2190</v>
       </c>
       <c r="B52" t="s">
+        <v>244</v>
+      </c>
+      <c r="C52" t="s">
+        <v>245</v>
+      </c>
+      <c r="F52" t="s">
         <v>246</v>
       </c>
-      <c r="C52" t="s">
+      <c r="G52" t="s">
         <v>247</v>
-      </c>
-      <c r="F52" t="s">
-        <v>248</v>
-      </c>
-      <c r="G52" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>2220</v>
+        <v>2210</v>
       </c>
       <c r="B53" t="s">
+        <v>248</v>
+      </c>
+      <c r="C53" t="s">
+        <v>249</v>
+      </c>
+      <c r="F53" t="s">
         <v>250</v>
       </c>
-      <c r="C53" t="s">
+      <c r="G53" t="s">
         <v>251</v>
-      </c>
-      <c r="F53" t="s">
-        <v>252</v>
-      </c>
-      <c r="G53" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>2230</v>
+        <v>2220</v>
       </c>
       <c r="B54" t="s">
+        <v>252</v>
+      </c>
+      <c r="C54" t="s">
+        <v>253</v>
+      </c>
+      <c r="F54" t="s">
         <v>254</v>
       </c>
-      <c r="C54" t="s">
+      <c r="G54" t="s">
         <v>255</v>
-      </c>
-      <c r="F54" t="s">
-        <v>256</v>
-      </c>
-      <c r="G54" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>2240</v>
+        <v>2230</v>
       </c>
       <c r="B55" t="s">
+        <v>256</v>
+      </c>
+      <c r="C55" t="s">
+        <v>257</v>
+      </c>
+      <c r="F55" t="s">
         <v>258</v>
       </c>
-      <c r="C55" t="s">
+      <c r="G55" t="s">
         <v>259</v>
-      </c>
-      <c r="F55" t="s">
-        <v>260</v>
-      </c>
-      <c r="G55" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>2250</v>
+        <v>2240</v>
       </c>
       <c r="B56" t="s">
+        <v>260</v>
+      </c>
+      <c r="C56" t="s">
+        <v>261</v>
+      </c>
+      <c r="F56" t="s">
         <v>262</v>
       </c>
-      <c r="C56" t="s">
+      <c r="G56" t="s">
         <v>263</v>
-      </c>
-      <c r="F56" t="s">
-        <v>264</v>
-      </c>
-      <c r="G56" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>2270</v>
+        <v>2250</v>
       </c>
       <c r="B57" t="s">
+        <v>264</v>
+      </c>
+      <c r="C57" t="s">
+        <v>265</v>
+      </c>
+      <c r="F57" t="s">
         <v>266</v>
       </c>
-      <c r="C57" t="s">
+      <c r="G57" t="s">
         <v>267</v>
-      </c>
-      <c r="F57" t="s">
-        <v>268</v>
-      </c>
-      <c r="G57" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="B58" t="s">
+        <v>268</v>
+      </c>
+      <c r="C58" t="s">
+        <v>269</v>
+      </c>
+      <c r="F58" t="s">
         <v>270</v>
       </c>
-      <c r="C58" t="s">
+      <c r="G58" t="s">
         <v>271</v>
-      </c>
-      <c r="F58" t="s">
-        <v>272</v>
-      </c>
-      <c r="G58" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="B59" t="s">
+        <v>272</v>
+      </c>
+      <c r="C59" t="s">
+        <v>273</v>
+      </c>
+      <c r="F59" t="s">
         <v>274</v>
       </c>
-      <c r="C59" t="s">
+      <c r="G59" t="s">
         <v>275</v>
-      </c>
-      <c r="F59" t="s">
-        <v>276</v>
-      </c>
-      <c r="G59" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>2320</v>
+        <v>2290</v>
       </c>
       <c r="B60" t="s">
+        <v>276</v>
+      </c>
+      <c r="C60" t="s">
+        <v>277</v>
+      </c>
+      <c r="F60" t="s">
         <v>278</v>
       </c>
-      <c r="C60" t="s">
+      <c r="G60" t="s">
         <v>279</v>
-      </c>
-      <c r="F60" t="s">
-        <v>280</v>
-      </c>
-      <c r="G60" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="B61" t="s">
+        <v>280</v>
+      </c>
+      <c r="C61" t="s">
+        <v>281</v>
+      </c>
+      <c r="F61" t="s">
         <v>282</v>
       </c>
-      <c r="C61" t="s">
+      <c r="G61" t="s">
         <v>283</v>
-      </c>
-      <c r="F61" t="s">
-        <v>284</v>
-      </c>
-      <c r="G61" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="B62" t="s">
+        <v>284</v>
+      </c>
+      <c r="C62" t="s">
+        <v>285</v>
+      </c>
+      <c r="F62" t="s">
         <v>286</v>
       </c>
-      <c r="C62" t="s">
+      <c r="G62" t="s">
         <v>287</v>
-      </c>
-      <c r="F62" t="s">
-        <v>288</v>
-      </c>
-      <c r="G62" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="B63" t="s">
+        <v>288</v>
+      </c>
+      <c r="C63" t="s">
+        <v>289</v>
+      </c>
+      <c r="F63" t="s">
         <v>290</v>
       </c>
-      <c r="C63" t="s">
+      <c r="G63" t="s">
         <v>291</v>
-      </c>
-      <c r="F63" t="s">
-        <v>292</v>
-      </c>
-      <c r="G63" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64">
-        <v>2350</v>
+        <v>2341</v>
       </c>
       <c r="B64" t="s">
+        <v>292</v>
+      </c>
+      <c r="C64" t="s">
+        <v>293</v>
+      </c>
+      <c r="F64" t="s">
         <v>294</v>
       </c>
-      <c r="C64" t="s">
+      <c r="G64" t="s">
         <v>295</v>
-      </c>
-      <c r="F64" t="s">
-        <v>296</v>
-      </c>
-      <c r="G64" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65">
-        <v>2360</v>
+        <v>2350</v>
       </c>
       <c r="B65" t="s">
+        <v>296</v>
+      </c>
+      <c r="C65" t="s">
+        <v>297</v>
+      </c>
+      <c r="F65" t="s">
         <v>298</v>
       </c>
-      <c r="C65" t="s">
+      <c r="G65" t="s">
         <v>299</v>
-      </c>
-      <c r="F65" t="s">
-        <v>300</v>
-      </c>
-      <c r="G65" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66">
-        <v>2370</v>
+        <v>2360</v>
       </c>
       <c r="B66" t="s">
+        <v>300</v>
+      </c>
+      <c r="C66" t="s">
+        <v>301</v>
+      </c>
+      <c r="F66" t="s">
         <v>302</v>
       </c>
-      <c r="C66" t="s">
+      <c r="G66" t="s">
         <v>303</v>
-      </c>
-      <c r="F66" t="s">
-        <v>304</v>
-      </c>
-      <c r="G66" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67">
-        <v>2380</v>
+        <v>2370</v>
       </c>
       <c r="B67" t="s">
+        <v>304</v>
+      </c>
+      <c r="C67" t="s">
+        <v>305</v>
+      </c>
+      <c r="F67" t="s">
         <v>306</v>
       </c>
-      <c r="C67" t="s">
+      <c r="G67" t="s">
         <v>307</v>
-      </c>
-      <c r="F67" t="s">
-        <v>62</v>
-      </c>
-      <c r="G67" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68">
-        <v>2390</v>
+        <v>2380</v>
       </c>
       <c r="B68" t="s">
+        <v>308</v>
+      </c>
+      <c r="C68" t="s">
         <v>309</v>
       </c>
-      <c r="C68" t="s">
+      <c r="F68" t="s">
+        <v>62</v>
+      </c>
+      <c r="G68" t="s">
         <v>310</v>
-      </c>
-      <c r="F68" t="s">
-        <v>311</v>
-      </c>
-      <c r="G68" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69">
-        <v>2400</v>
+        <v>2390</v>
       </c>
       <c r="B69" t="s">
+        <v>311</v>
+      </c>
+      <c r="C69" t="s">
+        <v>312</v>
+      </c>
+      <c r="F69" t="s">
         <v>313</v>
       </c>
-      <c r="C69" t="s">
+      <c r="G69" t="s">
         <v>314</v>
-      </c>
-      <c r="F69" t="s">
-        <v>315</v>
-      </c>
-      <c r="G69" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="B70" t="s">
+        <v>315</v>
+      </c>
+      <c r="C70" t="s">
+        <v>316</v>
+      </c>
+      <c r="F70" t="s">
         <v>317</v>
       </c>
-      <c r="C70" t="s">
+      <c r="G70" t="s">
         <v>318</v>
-      </c>
-      <c r="F70" t="s">
-        <v>27</v>
-      </c>
-      <c r="G70" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71">
-        <v>2420</v>
+        <v>2410</v>
       </c>
       <c r="B71" t="s">
+        <v>319</v>
+      </c>
+      <c r="C71" t="s">
         <v>320</v>
       </c>
-      <c r="C71" t="s">
+      <c r="F71" t="s">
+        <v>27</v>
+      </c>
+      <c r="G71" t="s">
         <v>321</v>
-      </c>
-      <c r="F71" t="s">
-        <v>322</v>
-      </c>
-      <c r="G71" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72">
-        <v>2430</v>
+        <v>2420</v>
       </c>
       <c r="B72" t="s">
+        <v>322</v>
+      </c>
+      <c r="C72" t="s">
+        <v>323</v>
+      </c>
+      <c r="F72" t="s">
         <v>324</v>
       </c>
-      <c r="C72" t="s">
+      <c r="G72" t="s">
         <v>325</v>
-      </c>
-      <c r="F72" t="s">
-        <v>326</v>
-      </c>
-      <c r="G72" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="B73" t="s">
+        <v>326</v>
+      </c>
+      <c r="C73" t="s">
+        <v>327</v>
+      </c>
+      <c r="F73" t="s">
         <v>328</v>
       </c>
-      <c r="C73" t="s">
+      <c r="G73" t="s">
         <v>329</v>
-      </c>
-      <c r="F73" t="s">
-        <v>330</v>
-      </c>
-      <c r="G73" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74">
-        <v>2450</v>
+        <v>2440</v>
       </c>
       <c r="B74" t="s">
+        <v>330</v>
+      </c>
+      <c r="C74" t="s">
+        <v>331</v>
+      </c>
+      <c r="F74" t="s">
         <v>332</v>
       </c>
-      <c r="C74" t="s">
+      <c r="G74" t="s">
         <v>333</v>
-      </c>
-      <c r="F74" t="s">
-        <v>334</v>
-      </c>
-      <c r="G74" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="B75" t="s">
+        <v>334</v>
+      </c>
+      <c r="C75" t="s">
+        <v>335</v>
+      </c>
+      <c r="F75" t="s">
         <v>336</v>
       </c>
-      <c r="C75" t="s">
+      <c r="G75" t="s">
         <v>337</v>
-      </c>
-      <c r="F75" t="s">
-        <v>338</v>
-      </c>
-      <c r="G75" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76">
-        <v>2470</v>
+        <v>2460</v>
       </c>
       <c r="B76" t="s">
+        <v>338</v>
+      </c>
+      <c r="C76" t="s">
+        <v>339</v>
+      </c>
+      <c r="F76" t="s">
         <v>340</v>
       </c>
-      <c r="C76" t="s">
+      <c r="G76" t="s">
         <v>341</v>
-      </c>
-      <c r="F76" t="s">
-        <v>315</v>
-      </c>
-      <c r="G76" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77">
-        <v>2480</v>
+        <v>2470</v>
       </c>
       <c r="B77" t="s">
+        <v>342</v>
+      </c>
+      <c r="C77" t="s">
         <v>343</v>
       </c>
-      <c r="C77" t="s">
+      <c r="F77" t="s">
+        <v>317</v>
+      </c>
+      <c r="G77" t="s">
         <v>344</v>
-      </c>
-      <c r="F77" t="s">
-        <v>345</v>
-      </c>
-      <c r="G77" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78">
-        <v>2490</v>
+        <v>2480</v>
       </c>
       <c r="B78" t="s">
-        <v>70</v>
+        <v>345</v>
       </c>
       <c r="C78" t="s">
+        <v>346</v>
+      </c>
+      <c r="F78" t="s">
         <v>347</v>
       </c>
-      <c r="F78" t="s">
-        <v>345</v>
-      </c>
       <c r="G78" t="s">
-        <v>20</v>
+        <v>348</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79">
-        <v>3010</v>
+        <v>2490</v>
       </c>
       <c r="B79" t="s">
-        <v>348</v>
+        <v>70</v>
       </c>
       <c r="C79" t="s">
         <v>349</v>
       </c>
       <c r="F79" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="G79" t="s">
-        <v>351</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B80" t="s">
+        <v>350</v>
+      </c>
+      <c r="C80" t="s">
+        <v>351</v>
+      </c>
+      <c r="F80" t="s">
         <v>352</v>
       </c>
-      <c r="C80" t="s">
+      <c r="G80" t="s">
         <v>353</v>
-      </c>
-      <c r="F80" t="s">
-        <v>354</v>
-      </c>
-      <c r="G80" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81">
-        <v>9999</v>
+        <v>3020</v>
       </c>
       <c r="B81" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C81" t="s">
-        <v>20</v>
+        <v>355</v>
       </c>
       <c r="F81" t="s">
         <v>356</v>
       </c>
       <c r="G81" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82">
+        <v>9999</v>
+      </c>
+      <c r="B82" t="s">
+        <v>358</v>
+      </c>
+      <c r="C82" t="s">
+        <v>20</v>
+      </c>
+      <c r="F82" t="s">
+        <v>358</v>
+      </c>
+      <c r="G82" t="s">
         <v>20</v>
       </c>
     </row>
@@ -9051,7 +9142,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9059,7 +9150,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9067,7 +9158,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9075,7 +9166,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -9083,7 +9174,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -9091,7 +9182,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9099,7 +9190,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="369">
   <si>
     <t>Id</t>
   </si>
@@ -385,6 +385,15 @@
   </si>
   <si>
     <t>ATK{0}Down</t>
+  </si>
+  <si>
+    <t>攻撃%アップ</t>
+  </si>
+  <si>
+    <t>ATK{0}%アップ</t>
+  </si>
+  <si>
+    <t>ATK{0}%Up</t>
   </si>
   <si>
     <t>攻撃%ダウン</t>
@@ -1121,10 +1130,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -1135,9 +1144,75 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1153,9 +1228,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1167,14 +1250,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1182,9 +1265,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1205,79 +1287,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -1288,19 +1297,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1312,25 +1315,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1348,7 +1333,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1360,7 +1411,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1372,25 +1441,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1402,37 +1459,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1444,31 +1477,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1483,21 +1492,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -1508,50 +1502,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1575,7 +1525,66 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1587,145 +1596,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2052,7 +2061,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U83"/>
+  <dimension ref="A1:U84"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="21.8181818181818" customWidth="1"/>
@@ -3020,20 +3029,20 @@
     </row>
     <row r="15" spans="1:21">
       <c r="A15">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B15">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C15" t="str">
         <f>INDEX(TextData!B:B,MATCH(B15,TextData!A:A))</f>
-        <v>攻撃ダウン</v>
+        <v>攻撃%アップ</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F15" t="s">
         <v>26</v>
@@ -3061,16 +3070,16 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -3083,19 +3092,19 @@
       </c>
       <c r="U15" t="str">
         <f>TextData!B15</f>
-        <v>攻撃%ダウン</v>
+        <v>攻撃%アップ</v>
       </c>
     </row>
     <row r="16" spans="1:21">
       <c r="A16">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B16">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C16" t="str">
         <f>INDEX(TextData!B:B,MATCH(B16,TextData!A:A))</f>
-        <v>攻撃アップ</v>
+        <v>攻撃%ダウン</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -3126,19 +3135,19 @@
         <v>1</v>
       </c>
       <c r="M16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -3151,28 +3160,28 @@
       </c>
       <c r="U16" t="str">
         <f>TextData!B16</f>
-        <v>攻撃アップ</v>
+        <v>攻撃%ダウン</v>
       </c>
     </row>
     <row r="17" spans="1:21">
       <c r="A17">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="B17">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="C17" t="str">
         <f>INDEX(TextData!B:B,MATCH(B17,TextData!A:A))</f>
-        <v>防御アップ</v>
+        <v>攻撃アップ</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -3194,7 +3203,7 @@
         <v>1</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -3219,25 +3228,25 @@
       </c>
       <c r="U17" t="str">
         <f>TextData!B17</f>
-        <v>防御アップ</v>
+        <v>攻撃アップ</v>
       </c>
     </row>
     <row r="18" spans="1:21">
       <c r="A18">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B18">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="C18" t="str">
         <f>INDEX(TextData!B:B,MATCH(B18,TextData!A:A))</f>
-        <v>防御ダウン</v>
+        <v>防御アップ</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F18" t="s">
         <v>27</v>
@@ -3265,16 +3274,16 @@
         <v>0</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -3287,25 +3296,25 @@
       </c>
       <c r="U18" t="str">
         <f>TextData!B18</f>
-        <v>防御ダウン</v>
+        <v>防御アップ</v>
       </c>
     </row>
     <row r="19" spans="1:21">
       <c r="A19">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B19">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="C19" t="str">
         <f>INDEX(TextData!B:B,MATCH(B19,TextData!A:A))</f>
-        <v>防御アップ</v>
+        <v>防御ダウン</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F19" t="s">
         <v>27</v>
@@ -3333,16 +3342,16 @@
         <v>0</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -3355,25 +3364,25 @@
       </c>
       <c r="U19" t="str">
         <f>TextData!B19</f>
-        <v>防御アップ</v>
+        <v>防御ダウン</v>
       </c>
     </row>
     <row r="20" spans="1:21">
       <c r="A20">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B20">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="C20" t="str">
         <f>INDEX(TextData!B:B,MATCH(B20,TextData!A:A))</f>
-        <v>防御ダウン</v>
+        <v>防御アップ</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s">
         <v>27</v>
@@ -3401,16 +3410,16 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -3423,28 +3432,28 @@
       </c>
       <c r="U20" t="str">
         <f>TextData!B20</f>
-        <v>防御ダウン</v>
+        <v>防御アップ</v>
       </c>
     </row>
     <row r="21" spans="1:21">
       <c r="A21">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="B21">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="C21" t="str">
         <f>INDEX(TextData!B:B,MATCH(B21,TextData!A:A))</f>
-        <v>速度アップ</v>
+        <v>防御ダウン</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F21" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G21">
         <v>1</v>
@@ -3469,16 +3478,16 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -3491,28 +3500,28 @@
       </c>
       <c r="U21" t="str">
         <f>TextData!B21</f>
-        <v>速度アップ</v>
+        <v>防御ダウン</v>
       </c>
     </row>
     <row r="22" spans="1:21">
       <c r="A22">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="B22">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="C22" t="str">
         <f>INDEX(TextData!B:B,MATCH(B22,TextData!A:A))</f>
-        <v>会心率アップ</v>
+        <v>速度アップ</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F22" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -3559,19 +3568,19 @@
       </c>
       <c r="U22" t="str">
         <f>TextData!B22</f>
-        <v>会心率アップ</v>
+        <v>速度アップ</v>
       </c>
     </row>
     <row r="23" spans="1:21">
       <c r="A23">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B23">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="C23" t="str">
         <f>INDEX(TextData!B:B,MATCH(B23,TextData!A:A))</f>
-        <v>会心率ダウン</v>
+        <v>会心率アップ</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -3605,16 +3614,16 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -3627,19 +3636,19 @@
       </c>
       <c r="U23" t="str">
         <f>TextData!B23</f>
-        <v>会心率ダウン</v>
+        <v>会心率アップ</v>
       </c>
     </row>
     <row r="24" spans="1:21">
       <c r="A24">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="B24">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="C24" t="str">
         <f>INDEX(TextData!B:B,MATCH(B24,TextData!A:A))</f>
-        <v>会心ダメージアップ</v>
+        <v>会心率ダウン</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -3673,16 +3682,16 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -3695,19 +3704,19 @@
       </c>
       <c r="U24" t="str">
         <f>TextData!B24</f>
-        <v>会心ダメージアップ</v>
+        <v>会心率ダウン</v>
       </c>
     </row>
     <row r="25" spans="1:21">
       <c r="A25">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="B25">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="C25" t="str">
         <f>INDEX(TextData!B:B,MATCH(B25,TextData!A:A))</f>
-        <v>命中アップ</v>
+        <v>会心ダメージアップ</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -3716,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -3763,15 +3772,15 @@
       </c>
       <c r="U25" t="str">
         <f>TextData!B25</f>
-        <v>命中アップ</v>
+        <v>会心ダメージアップ</v>
       </c>
     </row>
     <row r="26" spans="1:21">
       <c r="A26">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B26">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C26" t="str">
         <f>INDEX(TextData!B:B,MATCH(B26,TextData!A:A))</f>
@@ -3806,7 +3815,7 @@
         <v>1</v>
       </c>
       <c r="M26">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N26">
         <v>1</v>
@@ -3830,20 +3839,20 @@
         <v>1</v>
       </c>
       <c r="U26" t="str">
-        <f>TextData!B28</f>
-        <v>回避アップ</v>
+        <f>TextData!B26</f>
+        <v>命中アップ</v>
       </c>
     </row>
     <row r="27" spans="1:21">
       <c r="A27">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B27">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C27" t="str">
         <f>INDEX(TextData!B:B,MATCH(B27,TextData!A:A))</f>
-        <v>命中ダウン</v>
+        <v>命中アップ</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -3874,19 +3883,19 @@
         <v>1</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -3899,19 +3908,19 @@
       </c>
       <c r="U27" t="str">
         <f>TextData!B29</f>
-        <v>回避ダウン</v>
+        <v>回避アップ</v>
       </c>
     </row>
     <row r="28" spans="1:21">
       <c r="A28">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="B28">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="C28" t="str">
         <f>INDEX(TextData!B:B,MATCH(B28,TextData!A:A))</f>
-        <v>回避アップ</v>
+        <v>命中ダウン</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -3920,7 +3929,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -3945,16 +3954,16 @@
         <v>0</v>
       </c>
       <c r="N28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -3966,20 +3975,20 @@
         <v>1</v>
       </c>
       <c r="U28" t="str">
-        <f>TextData!B28</f>
-        <v>回避アップ</v>
+        <f>TextData!B30</f>
+        <v>回避ダウン</v>
       </c>
     </row>
     <row r="29" spans="1:21">
       <c r="A29">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B29">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="C29" t="str">
         <f>INDEX(TextData!B:B,MATCH(B29,TextData!A:A))</f>
-        <v>回避ダウン</v>
+        <v>回避アップ</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -4019,10 +4028,10 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -4035,19 +4044,19 @@
       </c>
       <c r="U29" t="str">
         <f>TextData!B29</f>
-        <v>回避ダウン</v>
+        <v>回避アップ</v>
       </c>
     </row>
     <row r="30" spans="1:21">
       <c r="A30">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B30">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="C30" t="str">
         <f>INDEX(TextData!B:B,MATCH(B30,TextData!A:A))</f>
-        <v>回避アップ</v>
+        <v>回避ダウン</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -4078,7 +4087,7 @@
         <v>1</v>
       </c>
       <c r="M30">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N30">
         <v>1</v>
@@ -4087,10 +4096,10 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -4103,35 +4112,35 @@
       </c>
       <c r="U30" t="str">
         <f>TextData!B30</f>
-        <v>回避アップ</v>
+        <v>回避ダウン</v>
       </c>
     </row>
     <row r="31" spans="1:21">
       <c r="A31">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="B31">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="C31" t="str">
         <f>INDEX(TextData!B:B,MATCH(B31,TextData!A:A))</f>
-        <v>ダメージカット</v>
+        <v>回避アップ</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H31" t="str">
         <f>INDEX(Define!B:B,MATCH(G31,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I31">
         <v>1</v>
@@ -4146,7 +4155,7 @@
         <v>1</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N31">
         <v>1</v>
@@ -4171,15 +4180,15 @@
       </c>
       <c r="U31" t="str">
         <f>TextData!B31</f>
-        <v>ダメージカット</v>
+        <v>回避アップ</v>
       </c>
     </row>
     <row r="32" spans="1:21">
       <c r="A32">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B32">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C32" t="str">
         <f>INDEX(TextData!B:B,MATCH(B32,TextData!A:A))</f>
@@ -4242,32 +4251,32 @@
         <v>ダメージカット</v>
       </c>
     </row>
-    <row r="33" ht="12" customHeight="1" spans="1:21">
+    <row r="33" spans="1:21">
       <c r="A33">
-        <v>1210</v>
+        <v>1101</v>
       </c>
       <c r="B33">
-        <v>1210</v>
+        <v>1101</v>
       </c>
       <c r="C33" t="str">
         <f>INDEX(TextData!B:B,MATCH(B33,TextData!A:A))</f>
-        <v>火傷耐性</v>
+        <v>ダメージカット</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="F33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H33" t="str">
         <f>INDEX(Define!B:B,MATCH(G33,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I33">
         <v>1</v>
@@ -4307,25 +4316,25 @@
       </c>
       <c r="U33" t="str">
         <f>TextData!B33</f>
-        <v>火傷耐性</v>
+        <v>ダメージカット</v>
       </c>
     </row>
     <row r="34" ht="12" customHeight="1" spans="1:21">
       <c r="A34">
-        <v>1220</v>
+        <v>1210</v>
       </c>
       <c r="B34">
-        <v>1220</v>
+        <v>1210</v>
       </c>
       <c r="C34" t="str">
         <f>INDEX(TextData!B:B,MATCH(B34,TextData!A:A))</f>
-        <v>凍結耐性</v>
+        <v>火傷耐性</v>
       </c>
       <c r="D34">
         <v>2</v>
       </c>
       <c r="E34">
-        <v>96</v>
+        <v>43</v>
       </c>
       <c r="F34" t="s">
         <v>32</v>
@@ -4375,25 +4384,25 @@
       </c>
       <c r="U34" t="str">
         <f>TextData!B34</f>
-        <v>凍結耐性</v>
+        <v>火傷耐性</v>
       </c>
     </row>
     <row r="35" ht="12" customHeight="1" spans="1:21">
       <c r="A35">
-        <v>2010</v>
+        <v>1220</v>
       </c>
       <c r="B35">
-        <v>2010</v>
+        <v>1220</v>
       </c>
       <c r="C35" t="str">
         <f>INDEX(TextData!B:B,MATCH(B35,TextData!A:A))</f>
-        <v>毒</v>
+        <v>凍結耐性</v>
       </c>
       <c r="D35">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="F35" t="s">
         <v>32</v>
@@ -4409,10 +4418,10 @@
         <v>1</v>
       </c>
       <c r="J35" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35">
         <v>1</v>
@@ -4421,19 +4430,19 @@
         <v>0</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35">
         <v>0</v>
@@ -4443,18 +4452,19 @@
       </c>
       <c r="U35" t="str">
         <f>TextData!B35</f>
-        <v>毒</v>
+        <v>凍結耐性</v>
       </c>
     </row>
     <row r="36" ht="12" customHeight="1" spans="1:21">
       <c r="A36">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B36">
         <v>2010</v>
       </c>
-      <c r="C36" t="s">
-        <v>34</v>
+      <c r="C36" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B36,TextData!A:A))</f>
+        <v>毒</v>
       </c>
       <c r="D36">
         <v>26</v>
@@ -4509,25 +4519,25 @@
         <v>1</v>
       </c>
       <c r="U36" t="str">
-        <f>TextData!B35</f>
+        <f>TextData!B36</f>
         <v>毒</v>
       </c>
     </row>
     <row r="37" ht="12" customHeight="1" spans="1:21">
       <c r="A37">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B37">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="E37">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="F37" t="s">
         <v>32</v>
@@ -4577,47 +4587,46 @@
       </c>
       <c r="U37" t="str">
         <f>TextData!B36</f>
-        <v>火傷</v>
+        <v>毒</v>
       </c>
     </row>
     <row r="38" ht="12" customHeight="1" spans="1:21">
       <c r="A38">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="B38">
-        <v>2020</v>
-      </c>
-      <c r="C38" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B38,TextData!A:A))</f>
-        <v>暗闇</v>
+        <v>2012</v>
+      </c>
+      <c r="C38" t="s">
+        <v>35</v>
       </c>
       <c r="D38">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="F38" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H38" t="str">
         <f>INDEX(Define!B:B,MATCH(G38,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I38">
         <v>1</v>
       </c>
       <c r="J38" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="M38">
         <v>0</v>
@@ -4645,47 +4654,47 @@
       </c>
       <c r="U38" t="str">
         <f>TextData!B37</f>
-        <v>暗闇</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21">
+        <v>火傷</v>
+      </c>
+    </row>
+    <row r="39" ht="12" customHeight="1" spans="1:21">
       <c r="A39">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B39">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="C39" t="str">
         <f>INDEX(TextData!B:B,MATCH(B39,TextData!A:A))</f>
-        <v>カウンタ</v>
+        <v>暗闇</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E39">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="F39" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H39" t="str">
         <f>INDEX(Define!B:B,MATCH(G39,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K39">
         <v>0</v>
       </c>
       <c r="L39">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="M39">
         <v>0</v>
@@ -4694,16 +4703,16 @@
         <v>0</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P39">
         <v>0</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -4713,19 +4722,19 @@
       </c>
       <c r="U39" t="str">
         <f>TextData!B38</f>
-        <v>カウンタ</v>
+        <v>暗闇</v>
       </c>
     </row>
     <row r="40" spans="1:21">
       <c r="A40">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B40">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="C40" t="str">
         <f>INDEX(TextData!B:B,MATCH(B40,TextData!A:A))</f>
-        <v>CAダメージ</v>
+        <v>カウンタ</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -4744,10 +4753,10 @@
         <v>ターン数</v>
       </c>
       <c r="I40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J40" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -4781,19 +4790,19 @@
       </c>
       <c r="U40" t="str">
         <f>TextData!B39</f>
-        <v>CAダメージ</v>
+        <v>カウンタ</v>
       </c>
     </row>
     <row r="41" spans="1:21">
       <c r="A41">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B41">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="C41" t="str">
         <f>INDEX(TextData!B:B,MATCH(B41,TextData!A:A))</f>
-        <v>CAシェル</v>
+        <v>CAダメージ</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -4802,14 +4811,14 @@
         <v>66</v>
       </c>
       <c r="F41" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="str">
         <f>INDEX(Define!B:B,MATCH(G41,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I41">
         <v>1</v>
@@ -4849,35 +4858,35 @@
       </c>
       <c r="U41" t="str">
         <f>TextData!B40</f>
-        <v>CAシェル</v>
+        <v>CAダメージ</v>
       </c>
     </row>
     <row r="42" spans="1:21">
       <c r="A42">
-        <v>2040</v>
+        <v>2032</v>
       </c>
       <c r="B42">
-        <v>2040</v>
+        <v>2032</v>
       </c>
       <c r="C42" t="str">
         <f>INDEX(TextData!B:B,MATCH(B42,TextData!A:A))</f>
-        <v>リジェネ</v>
+        <v>CAシェル</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="F42" t="s">
         <v>39</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="str">
         <f>INDEX(Define!B:B,MATCH(G42,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I42">
         <v>1</v>
@@ -4917,41 +4926,41 @@
       </c>
       <c r="U42" t="str">
         <f>TextData!B41</f>
-        <v>リジェネ</v>
+        <v>CAシェル</v>
       </c>
     </row>
     <row r="43" spans="1:21">
       <c r="A43">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="B43">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C43" t="str">
         <f>INDEX(TextData!B:B,MATCH(B43,TextData!A:A))</f>
-        <v>攻撃無効</v>
+        <v>リジェネ</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>226</v>
+        <v>46</v>
       </c>
       <c r="F43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H43" t="str">
         <f>INDEX(Define!B:B,MATCH(G43,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="K43">
         <v>0</v>
@@ -4985,41 +4994,41 @@
       </c>
       <c r="U43" t="str">
         <f>TextData!B42</f>
-        <v>攻撃無効</v>
+        <v>リジェネ</v>
       </c>
     </row>
     <row r="44" spans="1:21">
       <c r="A44">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="B44">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="C44" t="str">
         <f>INDEX(TextData!B:B,MATCH(B44,TextData!A:A))</f>
-        <v>ドレイン</v>
+        <v>攻撃無効</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>167</v>
+        <v>226</v>
       </c>
       <c r="F44" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H44" t="str">
         <f>INDEX(Define!B:B,MATCH(G44,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="K44">
         <v>0</v>
@@ -5053,28 +5062,28 @@
       </c>
       <c r="U44" t="str">
         <f>TextData!B43</f>
-        <v>ドレイン</v>
+        <v>攻撃無効</v>
       </c>
     </row>
     <row r="45" spans="1:21">
       <c r="A45">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="B45">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="C45" t="str">
         <f>INDEX(TextData!B:B,MATCH(B45,TextData!A:A))</f>
-        <v>状態異常CA</v>
+        <v>ドレイン</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>226</v>
+        <v>167</v>
       </c>
       <c r="F45" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -5084,7 +5093,7 @@
         <v>ターン数</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="s">
         <v>20</v>
@@ -5121,35 +5130,35 @@
       </c>
       <c r="U45" t="str">
         <f>TextData!B44</f>
-        <v>状態異常CA</v>
+        <v>ドレイン</v>
       </c>
     </row>
     <row r="46" spans="1:21">
       <c r="A46">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="B46">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="C46" t="str">
         <f>INDEX(TextData!B:B,MATCH(B46,TextData!A:A))</f>
-        <v>反撃</v>
+        <v>状態異常CA</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>4</v>
+        <v>226</v>
       </c>
       <c r="F46" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H46" t="str">
         <f>INDEX(Define!B:B,MATCH(G46,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -5189,28 +5198,28 @@
       </c>
       <c r="U46" t="str">
         <f>TextData!B45</f>
-        <v>反撃</v>
+        <v>状態異常CA</v>
       </c>
     </row>
     <row r="47" spans="1:21">
       <c r="A47">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="B47">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="C47" t="str">
         <f>INDEX(TextData!B:B,MATCH(B47,TextData!A:A))</f>
-        <v>パッシブ封じ</v>
+        <v>反撃</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F47" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G47">
         <v>4</v>
@@ -5238,16 +5247,16 @@
         <v>0</v>
       </c>
       <c r="O47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P47">
         <v>0</v>
       </c>
       <c r="Q47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47">
         <v>0</v>
@@ -5257,28 +5266,28 @@
       </c>
       <c r="U47" t="str">
         <f>TextData!B46</f>
-        <v>パッシブ封じ</v>
+        <v>反撃</v>
       </c>
     </row>
     <row r="48" spans="1:21">
       <c r="A48">
-        <v>2120</v>
+        <v>2090</v>
       </c>
       <c r="B48">
-        <v>2120</v>
+        <v>2090</v>
       </c>
       <c r="C48" t="str">
         <f>INDEX(TextData!B:B,MATCH(B48,TextData!A:A))</f>
-        <v>デバフ強化</v>
+        <v>パッシブ封じ</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G48">
         <v>4</v>
@@ -5288,16 +5297,16 @@
         <v>効果発揮回数</v>
       </c>
       <c r="I48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="K48">
         <v>0</v>
       </c>
       <c r="L48">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M48">
         <v>0</v>
@@ -5306,13 +5315,13 @@
         <v>0</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P48">
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48">
         <v>1</v>
@@ -5325,47 +5334,47 @@
       </c>
       <c r="U48" t="str">
         <f>TextData!B47</f>
-        <v>デバフ強化</v>
+        <v>パッシブ封じ</v>
       </c>
     </row>
     <row r="49" spans="1:21">
       <c r="A49">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="B49">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="C49" t="str">
         <f>INDEX(TextData!B:B,MATCH(B49,TextData!A:A))</f>
-        <v>挑発</v>
+        <v>デバフ強化</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
+        <v>9</v>
+      </c>
+      <c r="F49" t="s">
+        <v>45</v>
+      </c>
+      <c r="G49">
         <v>4</v>
-      </c>
-      <c r="F49" t="s">
-        <v>47</v>
-      </c>
-      <c r="G49">
-        <v>1</v>
       </c>
       <c r="H49" t="str">
         <f>INDEX(Define!B:B,MATCH(G49,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="M49">
         <v>0</v>
@@ -5393,44 +5402,44 @@
       </c>
       <c r="U49" t="str">
         <f>TextData!B48</f>
-        <v>挑発</v>
+        <v>デバフ強化</v>
       </c>
     </row>
     <row r="50" spans="1:21">
       <c r="A50">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="B50">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="C50" t="str">
         <f>INDEX(TextData!B:B,MATCH(B50,TextData!A:A))</f>
-        <v>凍結</v>
+        <v>挑発</v>
       </c>
       <c r="D50">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E50">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="F50" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H50" t="str">
         <f>INDEX(Define!B:B,MATCH(G50,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="K50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50">
         <v>1</v>
@@ -5442,13 +5451,13 @@
         <v>0</v>
       </c>
       <c r="O50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P50">
         <v>0</v>
       </c>
       <c r="Q50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R50">
         <v>1</v>
@@ -5461,44 +5470,44 @@
       </c>
       <c r="U50" t="str">
         <f>TextData!B49</f>
-        <v>凍結</v>
+        <v>挑発</v>
       </c>
     </row>
     <row r="51" spans="1:21">
       <c r="A51">
-        <v>2150</v>
+        <v>2140</v>
       </c>
       <c r="B51">
-        <v>2150</v>
+        <v>2140</v>
       </c>
       <c r="C51" t="str">
         <f>INDEX(TextData!B:B,MATCH(B51,TextData!A:A))</f>
-        <v>スタン</v>
+        <v>凍結</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E51">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="F51" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G51">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H51" t="str">
         <f>INDEX(Define!B:B,MATCH(G51,Define!A:A))</f>
-        <v>APカウント</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J51" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="K51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51">
         <v>1</v>
@@ -5529,41 +5538,41 @@
       </c>
       <c r="U51" t="str">
         <f>TextData!B50</f>
-        <v>スタン</v>
+        <v>凍結</v>
       </c>
     </row>
     <row r="52" spans="1:21">
       <c r="A52">
-        <v>2180</v>
+        <v>2150</v>
       </c>
       <c r="B52">
-        <v>2180</v>
+        <v>2150</v>
       </c>
       <c r="C52" t="str">
         <f>INDEX(TextData!B:B,MATCH(B52,TextData!A:A))</f>
-        <v>状態異常回避</v>
+        <v>スタン</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>99</v>
+        <v>5</v>
       </c>
       <c r="F52" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H52" t="str">
         <f>INDEX(Define!B:B,MATCH(G52,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>APカウント</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
       <c r="J52" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -5578,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P52">
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -5597,35 +5606,35 @@
       </c>
       <c r="U52" t="str">
         <f>TextData!B51</f>
-        <v>状態異常回避</v>
+        <v>スタン</v>
       </c>
     </row>
     <row r="53" spans="1:21">
       <c r="A53">
-        <v>2190</v>
+        <v>2180</v>
       </c>
       <c r="B53">
-        <v>2190</v>
+        <v>2180</v>
       </c>
       <c r="C53" t="str">
         <f>INDEX(TextData!B:B,MATCH(B53,TextData!A:A))</f>
-        <v>対象範囲延長</v>
+        <v>状態異常回避</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="F53" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H53" t="str">
         <f>INDEX(Define!B:B,MATCH(G53,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -5661,32 +5670,32 @@
         <v>0</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U53" t="str">
         <f>TextData!B52</f>
-        <v>対象範囲延長</v>
+        <v>状態異常回避</v>
       </c>
     </row>
     <row r="54" spans="1:21">
       <c r="A54">
-        <v>2210</v>
+        <v>2190</v>
       </c>
       <c r="B54">
-        <v>2210</v>
+        <v>2190</v>
       </c>
       <c r="C54" t="str">
         <f>INDEX(TextData!B:B,MATCH(B54,TextData!A:A))</f>
-        <v>アフターヒール</v>
+        <v>対象範囲延長</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="F54" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -5696,7 +5705,7 @@
         <v>ターン数</v>
       </c>
       <c r="I54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J54" t="s">
         <v>20</v>
@@ -5729,32 +5738,32 @@
         <v>0</v>
       </c>
       <c r="T54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U54" t="str">
         <f>TextData!B53</f>
-        <v>アフターヒール</v>
+        <v>対象範囲延長</v>
       </c>
     </row>
     <row r="55" spans="1:21">
       <c r="A55">
-        <v>2220</v>
+        <v>2210</v>
       </c>
       <c r="B55">
-        <v>2220</v>
+        <v>2210</v>
       </c>
       <c r="C55" t="str">
         <f>INDEX(TextData!B:B,MATCH(B55,TextData!A:A))</f>
-        <v>即死付与</v>
+        <v>アフターヒール</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>63</v>
       </c>
       <c r="F55" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -5764,7 +5773,7 @@
         <v>ターン数</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="s">
         <v>20</v>
@@ -5791,7 +5800,7 @@
         <v>0</v>
       </c>
       <c r="R55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55">
         <v>0</v>
@@ -5801,38 +5810,38 @@
       </c>
       <c r="U55" t="str">
         <f>TextData!B54</f>
-        <v>即死付与</v>
+        <v>アフターヒール</v>
       </c>
     </row>
     <row r="56" spans="1:21">
       <c r="A56">
-        <v>2230</v>
+        <v>2220</v>
       </c>
       <c r="B56">
-        <v>2230</v>
+        <v>2220</v>
       </c>
       <c r="C56" t="str">
         <f>INDEX(TextData!B:B,MATCH(B56,TextData!A:A))</f>
-        <v>同時回復</v>
+        <v>即死付与</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
       <c r="E56">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="str">
         <f>INDEX(Define!B:B,MATCH(G56,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="s">
         <v>20</v>
@@ -5859,7 +5868,7 @@
         <v>0</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56">
         <v>0</v>
@@ -5869,38 +5878,38 @@
       </c>
       <c r="U56" t="str">
         <f>TextData!B55</f>
-        <v>同時回復</v>
+        <v>即死付与</v>
       </c>
     </row>
     <row r="57" spans="1:21">
       <c r="A57">
-        <v>2240</v>
+        <v>2230</v>
       </c>
       <c r="B57">
-        <v>2240</v>
+        <v>2230</v>
       </c>
       <c r="C57" t="str">
         <f>INDEX(TextData!B:B,MATCH(B57,TextData!A:A))</f>
-        <v>必中</v>
+        <v>同時回復</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="F57" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="G57">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H57" t="str">
         <f>INDEX(Define!B:B,MATCH(G57,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>なし</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="s">
         <v>20</v>
@@ -5937,35 +5946,35 @@
       </c>
       <c r="U57" t="str">
         <f>TextData!B56</f>
-        <v>必中</v>
+        <v>同時回復</v>
       </c>
     </row>
     <row r="58" spans="1:21">
       <c r="A58">
-        <v>2250</v>
+        <v>2240</v>
       </c>
       <c r="B58">
-        <v>2250</v>
+        <v>2240</v>
       </c>
       <c r="C58" t="str">
         <f>INDEX(TextData!B:B,MATCH(B58,TextData!A:A))</f>
-        <v>アシストヒール</v>
+        <v>必中</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="F58" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H58" t="str">
         <f>INDEX(Define!B:B,MATCH(G58,Define!A:A))</f>
-        <v>なし</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -6005,28 +6014,28 @@
       </c>
       <c r="U58" t="str">
         <f>TextData!B57</f>
-        <v>アシストヒール</v>
+        <v>必中</v>
       </c>
     </row>
     <row r="59" spans="1:21">
       <c r="A59">
-        <v>2270</v>
+        <v>2250</v>
       </c>
       <c r="B59">
-        <v>2270</v>
+        <v>2250</v>
       </c>
       <c r="C59" t="str">
         <f>INDEX(TextData!B:B,MATCH(B59,TextData!A:A))</f>
-        <v>アンデッド</v>
+        <v>アシストヒール</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="F59" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6073,28 +6082,28 @@
       </c>
       <c r="U59" t="str">
         <f>TextData!B58</f>
-        <v>アンデッド</v>
+        <v>アシストヒール</v>
       </c>
     </row>
     <row r="60" spans="1:21">
       <c r="A60">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="B60">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="C60" t="str">
         <f>INDEX(TextData!B:B,MATCH(B60,TextData!A:A))</f>
-        <v>アクセル</v>
+        <v>アンデッド</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F60" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6141,38 +6150,38 @@
       </c>
       <c r="U60" t="str">
         <f>TextData!B59</f>
-        <v>アクセル</v>
+        <v>アンデッド</v>
       </c>
     </row>
     <row r="61" spans="1:21">
       <c r="A61">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="B61">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="C61" t="str">
         <f>INDEX(TextData!B:B,MATCH(B61,TextData!A:A))</f>
-        <v>ダメージ威力アップ</v>
+        <v>アクセル</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
+        <v>25</v>
+      </c>
+      <c r="F61" t="s">
         <v>21</v>
       </c>
-      <c r="F61" t="s">
-        <v>56</v>
-      </c>
       <c r="G61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H61" t="str">
         <f>INDEX(Define!B:B,MATCH(G61,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J61" t="s">
         <v>20</v>
@@ -6184,7 +6193,7 @@
         <v>1</v>
       </c>
       <c r="M61">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N61">
         <v>0</v>
@@ -6193,7 +6202,7 @@
         <v>0</v>
       </c>
       <c r="P61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q61">
         <v>0</v>
@@ -6209,35 +6218,35 @@
       </c>
       <c r="U61" t="str">
         <f>TextData!B60</f>
-        <v>ダメージ威力アップ</v>
+        <v>アクセル</v>
       </c>
     </row>
     <row r="62" spans="1:21">
       <c r="A62">
-        <v>2320</v>
+        <v>2290</v>
       </c>
       <c r="B62">
-        <v>2320</v>
+        <v>2290</v>
       </c>
       <c r="C62" t="str">
         <f>INDEX(TextData!B:B,MATCH(B62,TextData!A:A))</f>
-        <v>バフ解除</v>
+        <v>ダメージ威力アップ</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>0</v>
-      </c>
-      <c r="F62">
-        <v>1</v>
+        <v>21</v>
+      </c>
+      <c r="F62" t="s">
+        <v>56</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="str">
         <f>INDEX(Define!B:B,MATCH(G62,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I62">
         <v>1</v>
@@ -6252,7 +6261,7 @@
         <v>1</v>
       </c>
       <c r="M62">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N62">
         <v>0</v>
@@ -6261,7 +6270,7 @@
         <v>0</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -6277,35 +6286,35 @@
       </c>
       <c r="U62" t="str">
         <f>TextData!B61</f>
-        <v>バフ解除</v>
+        <v>ダメージ威力アップ</v>
       </c>
     </row>
     <row r="63" spans="1:21">
       <c r="A63">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="B63">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="C63" t="str">
         <f>INDEX(TextData!B:B,MATCH(B63,TextData!A:A))</f>
-        <v>貫通</v>
+        <v>バフ解除</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>56</v>
-      </c>
-      <c r="F63" t="s">
-        <v>57</v>
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63" t="str">
         <f>INDEX(Define!B:B,MATCH(G63,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I63">
         <v>1</v>
@@ -6323,7 +6332,7 @@
         <v>0</v>
       </c>
       <c r="N63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -6345,28 +6354,28 @@
       </c>
       <c r="U63" t="str">
         <f>TextData!B62</f>
-        <v>貫通</v>
+        <v>バフ解除</v>
       </c>
     </row>
     <row r="64" spans="1:21">
       <c r="A64">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="B64">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="C64" t="str">
         <f>INDEX(TextData!B:B,MATCH(B64,TextData!A:A))</f>
-        <v>対象列化</v>
+        <v>貫通</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F64" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -6413,19 +6422,19 @@
       </c>
       <c r="U64" t="str">
         <f>TextData!B63</f>
-        <v>対象列化</v>
+        <v>貫通</v>
       </c>
     </row>
     <row r="65" spans="1:21">
       <c r="A65">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="B65">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="C65" t="str">
         <f>INDEX(TextData!B:B,MATCH(B65,TextData!A:A))</f>
-        <v>対象全体化</v>
+        <v>対象列化</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -6434,7 +6443,7 @@
         <v>66</v>
       </c>
       <c r="F65" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -6481,28 +6490,28 @@
       </c>
       <c r="U65" t="str">
         <f>TextData!B64</f>
-        <v>対象全体化</v>
+        <v>対象列化</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66">
-        <v>2350</v>
+        <v>2341</v>
       </c>
       <c r="B66">
-        <v>2350</v>
+        <v>2341</v>
       </c>
       <c r="C66" t="str">
         <f>INDEX(TextData!B:B,MATCH(B66,TextData!A:A))</f>
-        <v>聖棺</v>
+        <v>対象全体化</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F66" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -6549,28 +6558,28 @@
       </c>
       <c r="U66" t="str">
         <f>TextData!B65</f>
-        <v>聖棺</v>
+        <v>対象全体化</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67">
-        <v>2360</v>
+        <v>2350</v>
       </c>
       <c r="B67">
-        <v>2360</v>
+        <v>2350</v>
       </c>
       <c r="C67" t="str">
         <f>INDEX(TextData!B:B,MATCH(B67,TextData!A:A))</f>
-        <v>追加ダメージ</v>
+        <v>聖棺</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F67" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -6617,25 +6626,25 @@
       </c>
       <c r="U67" t="str">
         <f>TextData!B66</f>
-        <v>追加ダメージ</v>
+        <v>聖棺</v>
       </c>
     </row>
     <row r="68" spans="1:21">
       <c r="A68">
-        <v>2370</v>
+        <v>2360</v>
       </c>
       <c r="B68">
-        <v>2370</v>
+        <v>2360</v>
       </c>
       <c r="C68" t="str">
         <f>INDEX(TextData!B:B,MATCH(B68,TextData!A:A))</f>
-        <v>追加効果</v>
+        <v>追加ダメージ</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="F68" t="s">
         <v>61</v>
@@ -6685,28 +6694,28 @@
       </c>
       <c r="U68" t="str">
         <f>TextData!B67</f>
-        <v>追加効果</v>
+        <v>追加ダメージ</v>
       </c>
     </row>
     <row r="69" spans="1:21">
       <c r="A69">
-        <v>2380</v>
+        <v>2370</v>
       </c>
       <c r="B69">
-        <v>2380</v>
+        <v>2370</v>
       </c>
       <c r="C69" t="str">
         <f>INDEX(TextData!B:B,MATCH(B69,TextData!A:A))</f>
-        <v>透明</v>
+        <v>追加効果</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F69" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -6753,28 +6762,28 @@
       </c>
       <c r="U69" t="str">
         <f>TextData!B68</f>
-        <v>透明</v>
+        <v>追加効果</v>
       </c>
     </row>
     <row r="70" spans="1:21">
       <c r="A70">
-        <v>2390</v>
+        <v>2380</v>
       </c>
       <c r="B70">
-        <v>2390</v>
+        <v>2380</v>
       </c>
       <c r="C70" t="str">
         <f>INDEX(TextData!B:B,MATCH(B70,TextData!A:A))</f>
-        <v>沈黙</v>
+        <v>透明</v>
       </c>
       <c r="D70">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E70">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F70" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -6799,19 +6808,19 @@
         <v>0</v>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P70">
         <v>0</v>
       </c>
       <c r="Q70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S70">
         <v>0</v>
@@ -6821,28 +6830,28 @@
       </c>
       <c r="U70" t="str">
         <f>TextData!B69</f>
-        <v>沈黙</v>
+        <v>透明</v>
       </c>
     </row>
     <row r="71" spans="1:21">
       <c r="A71">
-        <v>2400</v>
+        <v>2390</v>
       </c>
       <c r="B71">
-        <v>2400</v>
+        <v>2390</v>
       </c>
       <c r="C71" t="str">
         <f>INDEX(TextData!B:B,MATCH(B71,TextData!A:A))</f>
-        <v>不治</v>
+        <v>沈黙</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F71" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -6889,19 +6898,19 @@
       </c>
       <c r="U71" t="str">
         <f>TextData!B70</f>
-        <v>不治</v>
+        <v>沈黙</v>
       </c>
     </row>
     <row r="72" spans="1:21">
       <c r="A72">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="B72">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="C72" t="str">
         <f>INDEX(TextData!B:B,MATCH(B72,TextData!A:A))</f>
-        <v>シールド</v>
+        <v>不治</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -6910,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="F72" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -6935,19 +6944,19 @@
         <v>0</v>
       </c>
       <c r="N72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -6957,19 +6966,19 @@
       </c>
       <c r="U72" t="str">
         <f>TextData!B71</f>
-        <v>シールド</v>
+        <v>不治</v>
       </c>
     </row>
     <row r="73" spans="1:21">
       <c r="A73">
-        <v>2420</v>
+        <v>2410</v>
       </c>
       <c r="B73">
-        <v>2420</v>
+        <v>2410</v>
       </c>
       <c r="C73" t="str">
         <f>INDEX(TextData!B:B,MATCH(B73,TextData!A:A))</f>
-        <v>フォロー</v>
+        <v>シールド</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -6978,7 +6987,7 @@
         <v>0</v>
       </c>
       <c r="F73" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -7025,19 +7034,19 @@
       </c>
       <c r="U73" t="str">
         <f>TextData!B72</f>
-        <v>フォロー</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="74" spans="1:21">
       <c r="A74">
-        <v>2430</v>
+        <v>2420</v>
       </c>
       <c r="B74">
-        <v>2430</v>
+        <v>2420</v>
       </c>
       <c r="C74" t="str">
         <f>INDEX(TextData!B:B,MATCH(B74,TextData!A:A))</f>
-        <v>かばう</v>
+        <v>フォロー</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -7046,14 +7055,14 @@
         <v>0</v>
       </c>
       <c r="F74" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G74">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H74" t="str">
         <f>INDEX(Define!B:B,MATCH(G74,Define!A:A))</f>
-        <v>ターンの終了</v>
+        <v>ターン数</v>
       </c>
       <c r="I74">
         <v>1</v>
@@ -7086,26 +7095,26 @@
         <v>0</v>
       </c>
       <c r="S74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T74">
         <v>1</v>
       </c>
       <c r="U74" t="str">
         <f>TextData!B73</f>
-        <v>かばう</v>
+        <v>フォロー</v>
       </c>
     </row>
     <row r="75" spans="1:21">
       <c r="A75">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="B75">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="C75" t="str">
         <f>INDEX(TextData!B:B,MATCH(B75,TextData!A:A))</f>
-        <v>Ap消費半減</v>
+        <v>かばう</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -7114,14 +7123,14 @@
         <v>0</v>
       </c>
       <c r="F75" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H75" t="str">
         <f>INDEX(Define!B:B,MATCH(G75,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>ターンの終了</v>
       </c>
       <c r="I75">
         <v>1</v>
@@ -7151,29 +7160,29 @@
         <v>0</v>
       </c>
       <c r="R75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T75">
         <v>1</v>
       </c>
       <c r="U75" t="str">
         <f>TextData!B74</f>
-        <v>Ap消費半減</v>
+        <v>かばう</v>
       </c>
     </row>
     <row r="76" spans="1:21">
       <c r="A76">
-        <v>2450</v>
+        <v>2440</v>
       </c>
       <c r="B76">
-        <v>2450</v>
+        <v>2440</v>
       </c>
       <c r="C76" t="str">
         <f>INDEX(TextData!B:B,MATCH(B76,TextData!A:A))</f>
-        <v>不死</v>
+        <v>Ap消費半減</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -7182,14 +7191,14 @@
         <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="G76">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H76" t="str">
         <f>INDEX(Define!B:B,MATCH(G76,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I76">
         <v>1</v>
@@ -7229,19 +7238,19 @@
       </c>
       <c r="U76" t="str">
         <f>TextData!B75</f>
-        <v>不死</v>
+        <v>Ap消費半減</v>
       </c>
     </row>
     <row r="77" spans="1:21">
       <c r="A77">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="B77">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="C77" t="str">
         <f>INDEX(TextData!B:B,MATCH(B77,TextData!A:A))</f>
-        <v>Hp回復効果アップ</v>
+        <v>不死</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -7250,14 +7259,14 @@
         <v>0</v>
       </c>
       <c r="F77" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H77" t="str">
         <f>INDEX(Define!B:B,MATCH(G77,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I77">
         <v>1</v>
@@ -7287,7 +7296,7 @@
         <v>0</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S77">
         <v>0</v>
@@ -7297,19 +7306,19 @@
       </c>
       <c r="U77" t="str">
         <f>TextData!B76</f>
-        <v>Hp回復効果アップ</v>
+        <v>不死</v>
       </c>
     </row>
     <row r="78" spans="1:21">
       <c r="A78">
-        <v>2470</v>
+        <v>2460</v>
       </c>
       <c r="B78">
-        <v>2470</v>
+        <v>2460</v>
       </c>
       <c r="C78" t="str">
         <f>INDEX(TextData!B:B,MATCH(B78,TextData!A:A))</f>
-        <v>呪詛</v>
+        <v>Hp回復効果アップ</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -7318,14 +7327,14 @@
         <v>0</v>
       </c>
       <c r="F78" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G78">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H78" t="str">
         <f>INDEX(Define!B:B,MATCH(G78,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I78">
         <v>1</v>
@@ -7355,7 +7364,7 @@
         <v>0</v>
       </c>
       <c r="R78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S78">
         <v>0</v>
@@ -7365,35 +7374,35 @@
       </c>
       <c r="U78" t="str">
         <f>TextData!B77</f>
-        <v>呪詛</v>
+        <v>Hp回復効果アップ</v>
       </c>
     </row>
     <row r="79" spans="1:21">
       <c r="A79">
-        <v>2480</v>
+        <v>2470</v>
       </c>
       <c r="B79">
-        <v>2480</v>
+        <v>2470</v>
       </c>
       <c r="C79" t="str">
         <f>INDEX(TextData!B:B,MATCH(B79,TextData!A:A))</f>
-        <v>付与無効化</v>
+        <v>呪詛</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
       <c r="E79">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="F79" t="s">
         <v>69</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H79" t="str">
         <f>INDEX(Define!B:B,MATCH(G79,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I79">
         <v>1</v>
@@ -7433,19 +7442,19 @@
       </c>
       <c r="U79" t="str">
         <f>TextData!B78</f>
-        <v>付与無効化</v>
+        <v>呪詛</v>
       </c>
     </row>
     <row r="80" spans="1:21">
       <c r="A80">
-        <v>2490</v>
+        <v>2480</v>
       </c>
       <c r="B80">
-        <v>2490</v>
+        <v>2480</v>
       </c>
       <c r="C80" t="str">
         <f>INDEX(TextData!B:B,MATCH(B80,TextData!A:A))</f>
-        <v>かばう無視</v>
+        <v>付与無効化</v>
       </c>
       <c r="D80">
         <v>0</v>
@@ -7491,7 +7500,7 @@
         <v>0</v>
       </c>
       <c r="R80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S80">
         <v>0</v>
@@ -7499,29 +7508,30 @@
       <c r="T80">
         <v>1</v>
       </c>
-      <c r="U80" t="s">
-        <v>70</v>
+      <c r="U80" t="str">
+        <f>TextData!B79</f>
+        <v>付与無効化</v>
       </c>
     </row>
     <row r="81" spans="1:21">
       <c r="A81">
-        <v>3010</v>
+        <v>2490</v>
       </c>
       <c r="B81">
-        <v>3010</v>
+        <v>2490</v>
       </c>
       <c r="C81" t="str">
         <f>INDEX(TextData!B:B,MATCH(B81,TextData!A:A))</f>
-        <v>チャージ</v>
+        <v>かばう無視</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="F81" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -7546,13 +7556,13 @@
         <v>0</v>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O81">
         <v>0</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -7566,21 +7576,20 @@
       <c r="T81">
         <v>1</v>
       </c>
-      <c r="U81" t="str">
-        <f>TextData!B80</f>
-        <v>チャージ</v>
+      <c r="U81" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="82" spans="1:21">
       <c r="A82">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B82">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="C82" t="str">
         <f>INDEX(TextData!B:B,MATCH(B82,TextData!A:A))</f>
-        <v>リンケージ</v>
+        <v>チャージ</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -7636,19 +7645,19 @@
       </c>
       <c r="U82" t="str">
         <f>TextData!B81</f>
-        <v>リンケージ</v>
+        <v>チャージ</v>
       </c>
     </row>
     <row r="83" spans="1:21">
       <c r="A83">
-        <v>9999</v>
+        <v>3020</v>
       </c>
       <c r="B83">
-        <v>9999</v>
+        <v>3020</v>
       </c>
       <c r="C83" t="str">
         <f>INDEX(TextData!B:B,MATCH(B83,TextData!A:A))</f>
-        <v>テスト用</v>
+        <v>リンケージ</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -7704,6 +7713,74 @@
       </c>
       <c r="U83" t="str">
         <f>TextData!B82</f>
+        <v>リンケージ</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21">
+      <c r="A84">
+        <v>9999</v>
+      </c>
+      <c r="B84">
+        <v>9999</v>
+      </c>
+      <c r="C84" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B84,TextData!A:A))</f>
+        <v>テスト用</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84" t="s">
+        <v>61</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
+      <c r="H84" t="str">
+        <f>INDEX(Define!B:B,MATCH(G84,Define!A:A))</f>
+        <v>ターン数</v>
+      </c>
+      <c r="I84">
+        <v>1</v>
+      </c>
+      <c r="J84" t="s">
+        <v>20</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>1</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <v>0</v>
+      </c>
+      <c r="R84">
+        <v>0</v>
+      </c>
+      <c r="S84">
+        <v>0</v>
+      </c>
+      <c r="T84">
+        <v>1</v>
+      </c>
+      <c r="U84" t="str">
+        <f>TextData!B83</f>
         <v>テスト用</v>
       </c>
     </row>
@@ -7717,7 +7794,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="14.6363636363636" customWidth="1"/>
@@ -7966,7 +8043,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B15" t="s">
         <v>123</v>
@@ -7975,109 +8052,109 @@
         <v>124</v>
       </c>
       <c r="F15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G15" t="s">
         <v>125</v>
-      </c>
-      <c r="G15" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="F16" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="G16" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>1050</v>
+        <v>1044</v>
       </c>
       <c r="B17" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="F17" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="G17" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" t="s">
         <v>131</v>
       </c>
-      <c r="C18" t="s">
+      <c r="F18" t="s">
         <v>132</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>133</v>
-      </c>
-      <c r="G18" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B19" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C19" t="s">
         <v>135</v>
       </c>
       <c r="F19" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="B20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C20" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F20" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G20" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="B21" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C21" t="s">
         <v>140</v>
       </c>
       <c r="F21" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="G21" t="s">
         <v>141</v>
@@ -8085,7 +8162,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="B22" t="s">
         <v>142</v>
@@ -8094,466 +8171,466 @@
         <v>143</v>
       </c>
       <c r="F22" t="s">
+        <v>136</v>
+      </c>
+      <c r="G22" t="s">
         <v>144</v>
-      </c>
-      <c r="G22" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B23" t="s">
+        <v>145</v>
+      </c>
+      <c r="C23" t="s">
         <v>146</v>
       </c>
-      <c r="C23" t="s">
+      <c r="F23" t="s">
         <v>147</v>
       </c>
-      <c r="F23" t="s">
+      <c r="G23" t="s">
         <v>148</v>
-      </c>
-      <c r="G23" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="B24" t="s">
+        <v>149</v>
+      </c>
+      <c r="C24" t="s">
         <v>150</v>
       </c>
-      <c r="C24" t="s">
+      <c r="F24" t="s">
         <v>151</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>152</v>
-      </c>
-      <c r="G24" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="B25" t="s">
+        <v>153</v>
+      </c>
+      <c r="C25" t="s">
         <v>154</v>
       </c>
-      <c r="C25" t="s">
+      <c r="F25" t="s">
         <v>155</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>156</v>
-      </c>
-      <c r="G25" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B26" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C26" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F26" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G26" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B27" t="s">
+        <v>157</v>
+      </c>
+      <c r="C27" t="s">
         <v>158</v>
       </c>
-      <c r="C27" t="s">
+      <c r="F27" t="s">
         <v>159</v>
       </c>
-      <c r="F27" t="s">
+      <c r="G27" t="s">
         <v>160</v>
-      </c>
-      <c r="G27" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>1090</v>
+        <v>1082</v>
       </c>
       <c r="B28" t="s">
+        <v>161</v>
+      </c>
+      <c r="C28" t="s">
         <v>162</v>
       </c>
-      <c r="C28" t="s">
+      <c r="F28" t="s">
         <v>163</v>
       </c>
-      <c r="F28" t="s">
+      <c r="G28" t="s">
         <v>164</v>
-      </c>
-      <c r="G28" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B29" t="s">
+        <v>165</v>
+      </c>
+      <c r="C29" t="s">
         <v>166</v>
       </c>
-      <c r="C29" t="s">
+      <c r="F29" t="s">
         <v>167</v>
       </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
         <v>168</v>
-      </c>
-      <c r="G29" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B30" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C30" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="F30" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="G30" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="B31" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C31" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F31" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G31" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B32" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C32" t="s">
         <v>174</v>
       </c>
       <c r="F32" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="G32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>1210</v>
+        <v>1101</v>
       </c>
       <c r="B33" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C33" t="s">
         <v>177</v>
       </c>
       <c r="F33" t="s">
+        <v>175</v>
+      </c>
+      <c r="G33" t="s">
         <v>178</v>
-      </c>
-      <c r="G33" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>1220</v>
+        <v>1210</v>
       </c>
       <c r="B34" t="s">
+        <v>179</v>
+      </c>
+      <c r="C34" t="s">
         <v>180</v>
       </c>
-      <c r="C34" t="s">
+      <c r="F34" t="s">
         <v>181</v>
       </c>
-      <c r="F34" t="s">
-        <v>178</v>
-      </c>
       <c r="G34" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>2010</v>
+        <v>1220</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>183</v>
       </c>
       <c r="C35" t="s">
+        <v>184</v>
+      </c>
+      <c r="F35" t="s">
+        <v>181</v>
+      </c>
+      <c r="G35" t="s">
         <v>182</v>
-      </c>
-      <c r="F35" t="s">
-        <v>183</v>
-      </c>
-      <c r="G35" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C36" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G36" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="B37" t="s">
-        <v>186</v>
+        <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F37" t="s">
         <v>188</v>
       </c>
       <c r="G37" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>2030</v>
+        <v>2020</v>
       </c>
       <c r="B38" t="s">
+        <v>189</v>
+      </c>
+      <c r="C38" t="s">
         <v>190</v>
       </c>
-      <c r="C38" t="s">
+      <c r="F38" t="s">
         <v>191</v>
       </c>
-      <c r="F38" t="s">
+      <c r="G38" t="s">
         <v>192</v>
-      </c>
-      <c r="G38" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B39" t="s">
+        <v>193</v>
+      </c>
+      <c r="C39" t="s">
         <v>194</v>
       </c>
-      <c r="C39" t="s">
+      <c r="F39" t="s">
         <v>195</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>196</v>
-      </c>
-      <c r="G39" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B40" t="s">
+        <v>197</v>
+      </c>
+      <c r="C40" t="s">
         <v>198</v>
       </c>
-      <c r="C40" t="s">
+      <c r="F40" t="s">
         <v>199</v>
       </c>
-      <c r="F40" t="s">
+      <c r="G40" t="s">
         <v>200</v>
-      </c>
-      <c r="G40" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>2040</v>
+        <v>2032</v>
       </c>
       <c r="B41" t="s">
+        <v>201</v>
+      </c>
+      <c r="C41" t="s">
         <v>202</v>
       </c>
-      <c r="C41" t="s">
+      <c r="F41" t="s">
         <v>203</v>
       </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>204</v>
-      </c>
-      <c r="G41" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="B42" t="s">
+        <v>205</v>
+      </c>
+      <c r="C42" t="s">
         <v>206</v>
       </c>
-      <c r="C42" t="s">
+      <c r="F42" t="s">
         <v>207</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>208</v>
-      </c>
-      <c r="G42" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>2060</v>
+        <v>2050</v>
       </c>
       <c r="B43" t="s">
+        <v>209</v>
+      </c>
+      <c r="C43" t="s">
         <v>210</v>
       </c>
-      <c r="C43" t="s">
+      <c r="F43" t="s">
         <v>211</v>
       </c>
-      <c r="F43" t="s">
+      <c r="G43" t="s">
         <v>212</v>
-      </c>
-      <c r="G43" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>2070</v>
+        <v>2060</v>
       </c>
       <c r="B44" t="s">
+        <v>213</v>
+      </c>
+      <c r="C44" t="s">
         <v>214</v>
       </c>
-      <c r="C44" t="s">
+      <c r="F44" t="s">
         <v>215</v>
       </c>
-      <c r="F44" t="s">
+      <c r="G44" t="s">
         <v>216</v>
-      </c>
-      <c r="G44" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>2080</v>
+        <v>2070</v>
       </c>
       <c r="B45" t="s">
+        <v>217</v>
+      </c>
+      <c r="C45" t="s">
         <v>218</v>
       </c>
-      <c r="C45" t="s">
+      <c r="F45" t="s">
         <v>219</v>
       </c>
-      <c r="F45" t="s">
+      <c r="G45" t="s">
         <v>220</v>
-      </c>
-      <c r="G45" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>2090</v>
+        <v>2080</v>
       </c>
       <c r="B46" t="s">
+        <v>221</v>
+      </c>
+      <c r="C46" t="s">
         <v>222</v>
       </c>
-      <c r="C46" t="s">
+      <c r="F46" t="s">
         <v>223</v>
       </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>224</v>
-      </c>
-      <c r="G46" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>2120</v>
+        <v>2090</v>
       </c>
       <c r="B47" t="s">
+        <v>225</v>
+      </c>
+      <c r="C47" t="s">
         <v>226</v>
       </c>
-      <c r="C47" t="s">
+      <c r="F47" t="s">
         <v>227</v>
       </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
         <v>228</v>
-      </c>
-      <c r="G47" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>2130</v>
+        <v>2120</v>
       </c>
       <c r="B48" t="s">
+        <v>229</v>
+      </c>
+      <c r="C48" t="s">
         <v>230</v>
       </c>
-      <c r="C48" t="s">
+      <c r="F48" t="s">
         <v>231</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" t="s">
         <v>232</v>
-      </c>
-      <c r="G48" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>2140</v>
+        <v>2130</v>
       </c>
       <c r="B49" t="s">
+        <v>233</v>
+      </c>
+      <c r="C49" t="s">
         <v>234</v>
       </c>
-      <c r="C49" t="s">
+      <c r="F49" t="s">
         <v>235</v>
-      </c>
-      <c r="F49" t="s">
-        <v>48</v>
       </c>
       <c r="G49" t="s">
         <v>236</v>
@@ -8561,7 +8638,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>2150</v>
+        <v>2140</v>
       </c>
       <c r="B50" t="s">
         <v>237</v>
@@ -8570,7 +8647,7 @@
         <v>238</v>
       </c>
       <c r="F50" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G50" t="s">
         <v>239</v>
@@ -8578,7 +8655,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>2180</v>
+        <v>2150</v>
       </c>
       <c r="B51" t="s">
         <v>240</v>
@@ -8587,296 +8664,296 @@
         <v>241</v>
       </c>
       <c r="F51" t="s">
+        <v>50</v>
+      </c>
+      <c r="G51" t="s">
         <v>242</v>
-      </c>
-      <c r="G51" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>2190</v>
+        <v>2180</v>
       </c>
       <c r="B52" t="s">
+        <v>243</v>
+      </c>
+      <c r="C52" t="s">
         <v>244</v>
       </c>
-      <c r="C52" t="s">
+      <c r="F52" t="s">
         <v>245</v>
       </c>
-      <c r="F52" t="s">
+      <c r="G52" t="s">
         <v>246</v>
-      </c>
-      <c r="G52" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>2210</v>
+        <v>2190</v>
       </c>
       <c r="B53" t="s">
+        <v>247</v>
+      </c>
+      <c r="C53" t="s">
         <v>248</v>
       </c>
-      <c r="C53" t="s">
+      <c r="F53" t="s">
         <v>249</v>
       </c>
-      <c r="F53" t="s">
+      <c r="G53" t="s">
         <v>250</v>
-      </c>
-      <c r="G53" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>2220</v>
+        <v>2210</v>
       </c>
       <c r="B54" t="s">
+        <v>251</v>
+      </c>
+      <c r="C54" t="s">
         <v>252</v>
       </c>
-      <c r="C54" t="s">
+      <c r="F54" t="s">
         <v>253</v>
       </c>
-      <c r="F54" t="s">
+      <c r="G54" t="s">
         <v>254</v>
-      </c>
-      <c r="G54" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>2230</v>
+        <v>2220</v>
       </c>
       <c r="B55" t="s">
+        <v>255</v>
+      </c>
+      <c r="C55" t="s">
         <v>256</v>
       </c>
-      <c r="C55" t="s">
+      <c r="F55" t="s">
         <v>257</v>
       </c>
-      <c r="F55" t="s">
+      <c r="G55" t="s">
         <v>258</v>
-      </c>
-      <c r="G55" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>2240</v>
+        <v>2230</v>
       </c>
       <c r="B56" t="s">
+        <v>259</v>
+      </c>
+      <c r="C56" t="s">
         <v>260</v>
       </c>
-      <c r="C56" t="s">
+      <c r="F56" t="s">
         <v>261</v>
       </c>
-      <c r="F56" t="s">
+      <c r="G56" t="s">
         <v>262</v>
-      </c>
-      <c r="G56" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>2250</v>
+        <v>2240</v>
       </c>
       <c r="B57" t="s">
+        <v>263</v>
+      </c>
+      <c r="C57" t="s">
         <v>264</v>
       </c>
-      <c r="C57" t="s">
+      <c r="F57" t="s">
         <v>265</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>266</v>
-      </c>
-      <c r="G57" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>2270</v>
+        <v>2250</v>
       </c>
       <c r="B58" t="s">
+        <v>267</v>
+      </c>
+      <c r="C58" t="s">
         <v>268</v>
       </c>
-      <c r="C58" t="s">
+      <c r="F58" t="s">
         <v>269</v>
       </c>
-      <c r="F58" t="s">
+      <c r="G58" t="s">
         <v>270</v>
-      </c>
-      <c r="G58" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>2280</v>
+        <v>2270</v>
       </c>
       <c r="B59" t="s">
+        <v>271</v>
+      </c>
+      <c r="C59" t="s">
         <v>272</v>
       </c>
-      <c r="C59" t="s">
+      <c r="F59" t="s">
         <v>273</v>
       </c>
-      <c r="F59" t="s">
+      <c r="G59" t="s">
         <v>274</v>
-      </c>
-      <c r="G59" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>2290</v>
+        <v>2280</v>
       </c>
       <c r="B60" t="s">
+        <v>275</v>
+      </c>
+      <c r="C60" t="s">
         <v>276</v>
       </c>
-      <c r="C60" t="s">
+      <c r="F60" t="s">
         <v>277</v>
       </c>
-      <c r="F60" t="s">
+      <c r="G60" t="s">
         <v>278</v>
-      </c>
-      <c r="G60" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61">
-        <v>2320</v>
+        <v>2290</v>
       </c>
       <c r="B61" t="s">
+        <v>279</v>
+      </c>
+      <c r="C61" t="s">
         <v>280</v>
       </c>
-      <c r="C61" t="s">
+      <c r="F61" t="s">
         <v>281</v>
       </c>
-      <c r="F61" t="s">
+      <c r="G61" t="s">
         <v>282</v>
-      </c>
-      <c r="G61" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62">
-        <v>2330</v>
+        <v>2320</v>
       </c>
       <c r="B62" t="s">
+        <v>283</v>
+      </c>
+      <c r="C62" t="s">
         <v>284</v>
       </c>
-      <c r="C62" t="s">
+      <c r="F62" t="s">
         <v>285</v>
       </c>
-      <c r="F62" t="s">
+      <c r="G62" t="s">
         <v>286</v>
-      </c>
-      <c r="G62" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63">
-        <v>2340</v>
+        <v>2330</v>
       </c>
       <c r="B63" t="s">
+        <v>287</v>
+      </c>
+      <c r="C63" t="s">
         <v>288</v>
       </c>
-      <c r="C63" t="s">
+      <c r="F63" t="s">
         <v>289</v>
       </c>
-      <c r="F63" t="s">
+      <c r="G63" t="s">
         <v>290</v>
-      </c>
-      <c r="G63" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="B64" t="s">
+        <v>291</v>
+      </c>
+      <c r="C64" t="s">
         <v>292</v>
       </c>
-      <c r="C64" t="s">
+      <c r="F64" t="s">
         <v>293</v>
       </c>
-      <c r="F64" t="s">
+      <c r="G64" t="s">
         <v>294</v>
-      </c>
-      <c r="G64" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65">
-        <v>2350</v>
+        <v>2341</v>
       </c>
       <c r="B65" t="s">
+        <v>295</v>
+      </c>
+      <c r="C65" t="s">
         <v>296</v>
       </c>
-      <c r="C65" t="s">
+      <c r="F65" t="s">
         <v>297</v>
       </c>
-      <c r="F65" t="s">
+      <c r="G65" t="s">
         <v>298</v>
-      </c>
-      <c r="G65" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66">
-        <v>2360</v>
+        <v>2350</v>
       </c>
       <c r="B66" t="s">
+        <v>299</v>
+      </c>
+      <c r="C66" t="s">
         <v>300</v>
       </c>
-      <c r="C66" t="s">
+      <c r="F66" t="s">
         <v>301</v>
       </c>
-      <c r="F66" t="s">
+      <c r="G66" t="s">
         <v>302</v>
-      </c>
-      <c r="G66" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67">
-        <v>2370</v>
+        <v>2360</v>
       </c>
       <c r="B67" t="s">
+        <v>303</v>
+      </c>
+      <c r="C67" t="s">
         <v>304</v>
       </c>
-      <c r="C67" t="s">
+      <c r="F67" t="s">
         <v>305</v>
       </c>
-      <c r="F67" t="s">
+      <c r="G67" t="s">
         <v>306</v>
-      </c>
-      <c r="G67" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68">
-        <v>2380</v>
+        <v>2370</v>
       </c>
       <c r="B68" t="s">
+        <v>307</v>
+      </c>
+      <c r="C68" t="s">
         <v>308</v>
       </c>
-      <c r="C68" t="s">
+      <c r="F68" t="s">
         <v>309</v>
-      </c>
-      <c r="F68" t="s">
-        <v>62</v>
       </c>
       <c r="G68" t="s">
         <v>310</v>
@@ -8884,7 +8961,7 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69">
-        <v>2390</v>
+        <v>2380</v>
       </c>
       <c r="B69" t="s">
         <v>311</v>
@@ -8893,41 +8970,41 @@
         <v>312</v>
       </c>
       <c r="F69" t="s">
+        <v>62</v>
+      </c>
+      <c r="G69" t="s">
         <v>313</v>
-      </c>
-      <c r="G69" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70">
-        <v>2400</v>
+        <v>2390</v>
       </c>
       <c r="B70" t="s">
+        <v>314</v>
+      </c>
+      <c r="C70" t="s">
         <v>315</v>
       </c>
-      <c r="C70" t="s">
+      <c r="F70" t="s">
         <v>316</v>
       </c>
-      <c r="F70" t="s">
+      <c r="G70" t="s">
         <v>317</v>
-      </c>
-      <c r="G70" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71">
-        <v>2410</v>
+        <v>2400</v>
       </c>
       <c r="B71" t="s">
+        <v>318</v>
+      </c>
+      <c r="C71" t="s">
         <v>319</v>
       </c>
-      <c r="C71" t="s">
+      <c r="F71" t="s">
         <v>320</v>
-      </c>
-      <c r="F71" t="s">
-        <v>27</v>
       </c>
       <c r="G71" t="s">
         <v>321</v>
@@ -8935,7 +9012,7 @@
     </row>
     <row r="72" spans="1:7">
       <c r="A72">
-        <v>2420</v>
+        <v>2410</v>
       </c>
       <c r="B72" t="s">
         <v>322</v>
@@ -8944,92 +9021,92 @@
         <v>323</v>
       </c>
       <c r="F72" t="s">
+        <v>27</v>
+      </c>
+      <c r="G72" t="s">
         <v>324</v>
-      </c>
-      <c r="G72" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73">
-        <v>2430</v>
+        <v>2420</v>
       </c>
       <c r="B73" t="s">
+        <v>325</v>
+      </c>
+      <c r="C73" t="s">
         <v>326</v>
       </c>
-      <c r="C73" t="s">
+      <c r="F73" t="s">
         <v>327</v>
       </c>
-      <c r="F73" t="s">
+      <c r="G73" t="s">
         <v>328</v>
-      </c>
-      <c r="G73" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74">
-        <v>2440</v>
+        <v>2430</v>
       </c>
       <c r="B74" t="s">
+        <v>329</v>
+      </c>
+      <c r="C74" t="s">
         <v>330</v>
       </c>
-      <c r="C74" t="s">
+      <c r="F74" t="s">
         <v>331</v>
       </c>
-      <c r="F74" t="s">
+      <c r="G74" t="s">
         <v>332</v>
-      </c>
-      <c r="G74" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75">
-        <v>2450</v>
+        <v>2440</v>
       </c>
       <c r="B75" t="s">
+        <v>333</v>
+      </c>
+      <c r="C75" t="s">
         <v>334</v>
       </c>
-      <c r="C75" t="s">
+      <c r="F75" t="s">
         <v>335</v>
       </c>
-      <c r="F75" t="s">
+      <c r="G75" t="s">
         <v>336</v>
-      </c>
-      <c r="G75" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76">
-        <v>2460</v>
+        <v>2450</v>
       </c>
       <c r="B76" t="s">
+        <v>337</v>
+      </c>
+      <c r="C76" t="s">
         <v>338</v>
       </c>
-      <c r="C76" t="s">
+      <c r="F76" t="s">
         <v>339</v>
       </c>
-      <c r="F76" t="s">
+      <c r="G76" t="s">
         <v>340</v>
-      </c>
-      <c r="G76" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77">
-        <v>2470</v>
+        <v>2460</v>
       </c>
       <c r="B77" t="s">
+        <v>341</v>
+      </c>
+      <c r="C77" t="s">
         <v>342</v>
       </c>
-      <c r="C77" t="s">
+      <c r="F77" t="s">
         <v>343</v>
-      </c>
-      <c r="F77" t="s">
-        <v>317</v>
       </c>
       <c r="G77" t="s">
         <v>344</v>
@@ -9037,7 +9114,7 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78">
-        <v>2480</v>
+        <v>2470</v>
       </c>
       <c r="B78" t="s">
         <v>345</v>
@@ -9046,77 +9123,94 @@
         <v>346</v>
       </c>
       <c r="F78" t="s">
+        <v>320</v>
+      </c>
+      <c r="G78" t="s">
         <v>347</v>
-      </c>
-      <c r="G78" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79">
-        <v>2490</v>
+        <v>2480</v>
       </c>
       <c r="B79" t="s">
-        <v>70</v>
+        <v>348</v>
       </c>
       <c r="C79" t="s">
         <v>349</v>
       </c>
       <c r="F79" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G79" t="s">
-        <v>20</v>
+        <v>351</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80">
-        <v>3010</v>
+        <v>2490</v>
       </c>
       <c r="B80" t="s">
+        <v>70</v>
+      </c>
+      <c r="C80" t="s">
+        <v>352</v>
+      </c>
+      <c r="F80" t="s">
         <v>350</v>
       </c>
-      <c r="C80" t="s">
-        <v>351</v>
-      </c>
-      <c r="F80" t="s">
-        <v>352</v>
-      </c>
       <c r="G80" t="s">
-        <v>353</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="B81" t="s">
+        <v>353</v>
+      </c>
+      <c r="C81" t="s">
         <v>354</v>
       </c>
-      <c r="C81" t="s">
+      <c r="F81" t="s">
         <v>355</v>
       </c>
-      <c r="F81" t="s">
+      <c r="G81" t="s">
         <v>356</v>
-      </c>
-      <c r="G81" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82">
+        <v>3020</v>
+      </c>
+      <c r="B82" t="s">
+        <v>357</v>
+      </c>
+      <c r="C82" t="s">
+        <v>358</v>
+      </c>
+      <c r="F82" t="s">
+        <v>359</v>
+      </c>
+      <c r="G82" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83">
         <v>9999</v>
       </c>
-      <c r="B82" t="s">
-        <v>358</v>
-      </c>
-      <c r="C82" t="s">
+      <c r="B83" t="s">
+        <v>361</v>
+      </c>
+      <c r="C83" t="s">
         <v>20</v>
       </c>
-      <c r="F82" t="s">
-        <v>358</v>
-      </c>
-      <c r="G82" t="s">
+      <c r="F83" t="s">
+        <v>361</v>
+      </c>
+      <c r="G83" t="s">
         <v>20</v>
       </c>
     </row>
@@ -9142,7 +9236,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9150,7 +9244,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9158,7 +9252,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9166,7 +9260,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -9174,7 +9268,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -9182,7 +9276,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9190,7 +9284,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/States.xlsx
+++ b/Assets/Data/States.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="States" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="391">
   <si>
     <t>Id</t>
   </si>
@@ -573,6 +573,66 @@
     <t>凍結ダメージを{0}%カットする</t>
   </si>
   <si>
+    <t>炎耐性</t>
+  </si>
+  <si>
+    <t>炎属性ダメージを{0}%カットする</t>
+  </si>
+  <si>
+    <t>Fire Resistance</t>
+  </si>
+  <si>
+    <t>Reduce fire damage taken by {0}%</t>
+  </si>
+  <si>
+    <t>雷耐性</t>
+  </si>
+  <si>
+    <t>雷属性ダメージを{0}%カットする</t>
+  </si>
+  <si>
+    <t>Thunder Resistance</t>
+  </si>
+  <si>
+    <t>Reduce thunder damage taken by {0}%</t>
+  </si>
+  <si>
+    <t>氷耐性</t>
+  </si>
+  <si>
+    <t>氷属性ダメージを{0}%カットする</t>
+  </si>
+  <si>
+    <t>Ice Resistance</t>
+  </si>
+  <si>
+    <t>Reduce ice damage taken by {0}%</t>
+  </si>
+  <si>
+    <t>光耐性</t>
+  </si>
+  <si>
+    <t>光属性ダメージを{0}%カットする</t>
+  </si>
+  <si>
+    <t>Shine Resistance</t>
+  </si>
+  <si>
+    <t>Reduce shine damage taken by {0}%</t>
+  </si>
+  <si>
+    <t>闇耐性</t>
+  </si>
+  <si>
+    <t>闇属性ダメージを{0}%カットする</t>
+  </si>
+  <si>
+    <t>Dark Resistance</t>
+  </si>
+  <si>
+    <t>Reduce dark damage taken by {0}%</t>
+  </si>
+  <si>
     <t>行動後ダメージ</t>
   </si>
   <si>
@@ -1075,6 +1135,12 @@
   </si>
   <si>
     <t>攻撃時敵のかばう効果を無視する</t>
+  </si>
+  <si>
+    <t>ダメージカット無効</t>
+  </si>
+  <si>
+    <t>ダメージアップ効果を無視する</t>
   </si>
   <si>
     <t>チャージ</t>
@@ -1130,10 +1196,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -1145,12 +1211,105 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1166,24 +1325,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1196,93 +1339,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1297,19 +1363,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1321,43 +1453,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1375,31 +1507,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1411,61 +1525,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1477,7 +1537,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1488,6 +1554,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1506,17 +1581,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1525,7 +1594,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1545,21 +1629,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -1571,20 +1640,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1596,7 +1662,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1605,16 +1671,16 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1623,118 +1689,118 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2061,7 +2127,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U84"/>
+  <dimension ref="A1:U90"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="3" max="3" width="21.8181818181818" customWidth="1"/>
@@ -4457,20 +4523,20 @@
     </row>
     <row r="36" ht="12" customHeight="1" spans="1:21">
       <c r="A36">
-        <v>2010</v>
+        <v>1310</v>
       </c>
       <c r="B36">
-        <v>2010</v>
+        <v>1310</v>
       </c>
       <c r="C36" t="str">
         <f>INDEX(TextData!B:B,MATCH(B36,TextData!A:A))</f>
-        <v>毒</v>
+        <v>炎耐性</v>
       </c>
       <c r="D36">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="F36" t="s">
         <v>32</v>
@@ -4486,10 +4552,10 @@
         <v>1</v>
       </c>
       <c r="J36" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36">
         <v>1</v>
@@ -4498,19 +4564,19 @@
         <v>0</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <v>0</v>
@@ -4520,24 +4586,25 @@
       </c>
       <c r="U36" t="str">
         <f>TextData!B36</f>
-        <v>毒</v>
+        <v>炎耐性</v>
       </c>
     </row>
     <row r="37" ht="12" customHeight="1" spans="1:21">
       <c r="A37">
-        <v>2011</v>
+        <v>1320</v>
       </c>
       <c r="B37">
-        <v>2010</v>
-      </c>
-      <c r="C37" t="s">
-        <v>34</v>
+        <v>1320</v>
+      </c>
+      <c r="C37" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B37,TextData!A:A))</f>
+        <v>雷耐性</v>
       </c>
       <c r="D37">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="F37" t="s">
         <v>32</v>
@@ -4553,10 +4620,10 @@
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37">
         <v>1</v>
@@ -4565,19 +4632,19 @@
         <v>0</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <v>0</v>
@@ -4586,25 +4653,26 @@
         <v>1</v>
       </c>
       <c r="U37" t="str">
-        <f>TextData!B36</f>
-        <v>毒</v>
+        <f>TextData!B37</f>
+        <v>雷耐性</v>
       </c>
     </row>
     <row r="38" ht="12" customHeight="1" spans="1:21">
       <c r="A38">
-        <v>2012</v>
+        <v>1330</v>
       </c>
       <c r="B38">
-        <v>2012</v>
-      </c>
-      <c r="C38" t="s">
-        <v>35</v>
+        <v>1330</v>
+      </c>
+      <c r="C38" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B38,TextData!A:A))</f>
+        <v>氷耐性</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E38">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F38" t="s">
         <v>32</v>
@@ -4620,10 +4688,10 @@
         <v>1</v>
       </c>
       <c r="J38" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="K38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38">
         <v>1</v>
@@ -4632,19 +4700,19 @@
         <v>0</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <v>0</v>
@@ -4653,66 +4721,66 @@
         <v>1</v>
       </c>
       <c r="U38" t="str">
-        <f>TextData!B37</f>
-        <v>火傷</v>
+        <f>TextData!B38</f>
+        <v>氷耐性</v>
       </c>
     </row>
     <row r="39" ht="12" customHeight="1" spans="1:21">
       <c r="A39">
-        <v>2020</v>
+        <v>1340</v>
       </c>
       <c r="B39">
-        <v>2020</v>
+        <v>1340</v>
       </c>
       <c r="C39" t="str">
         <f>INDEX(TextData!B:B,MATCH(B39,TextData!A:A))</f>
-        <v>暗闇</v>
+        <v>光耐性</v>
       </c>
       <c r="D39">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="F39" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H39" t="str">
         <f>INDEX(Define!B:B,MATCH(G39,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I39">
         <v>1</v>
       </c>
       <c r="J39" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="K39">
         <v>0</v>
       </c>
       <c r="L39">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="M39">
         <v>0</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39">
         <v>0</v>
@@ -4721,29 +4789,29 @@
         <v>1</v>
       </c>
       <c r="U39" t="str">
-        <f>TextData!B38</f>
-        <v>暗闇</v>
-      </c>
-    </row>
-    <row r="40" spans="1:21">
+        <f>TextData!B39</f>
+        <v>光耐性</v>
+      </c>
+    </row>
+    <row r="40" ht="12" customHeight="1" spans="1:21">
       <c r="A40">
-        <v>2030</v>
+        <v>1350</v>
       </c>
       <c r="B40">
-        <v>2030</v>
+        <v>1350</v>
       </c>
       <c r="C40" t="str">
         <f>INDEX(TextData!B:B,MATCH(B40,TextData!A:A))</f>
-        <v>カウンタ</v>
+        <v>闇耐性</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E40">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="F40" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G40">
         <v>1</v>
@@ -4753,10 +4821,10 @@
         <v>ターン数</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -4768,13 +4836,13 @@
         <v>0</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -4789,29 +4857,29 @@
         <v>1</v>
       </c>
       <c r="U40" t="str">
-        <f>TextData!B39</f>
-        <v>カウンタ</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21">
+        <f>TextData!B40</f>
+        <v>闇耐性</v>
+      </c>
+    </row>
+    <row r="41" ht="12" customHeight="1" spans="1:21">
       <c r="A41">
-        <v>2031</v>
+        <v>2010</v>
       </c>
       <c r="B41">
-        <v>2031</v>
+        <v>2010</v>
       </c>
       <c r="C41" t="str">
         <f>INDEX(TextData!B:B,MATCH(B41,TextData!A:A))</f>
-        <v>CAダメージ</v>
+        <v>毒</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E41">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="G41">
         <v>1</v>
@@ -4824,10 +4892,10 @@
         <v>1</v>
       </c>
       <c r="J41" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41">
         <v>1</v>
@@ -4839,16 +4907,16 @@
         <v>0</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P41">
         <v>0</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -4857,45 +4925,44 @@
         <v>1</v>
       </c>
       <c r="U41" t="str">
-        <f>TextData!B40</f>
-        <v>CAダメージ</v>
-      </c>
-    </row>
-    <row r="42" spans="1:21">
+        <f>TextData!B41</f>
+        <v>毒</v>
+      </c>
+    </row>
+    <row r="42" ht="12" customHeight="1" spans="1:21">
       <c r="A42">
-        <v>2032</v>
+        <v>2011</v>
       </c>
       <c r="B42">
-        <v>2032</v>
-      </c>
-      <c r="C42" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B42,TextData!A:A))</f>
-        <v>CAシェル</v>
+        <v>2010</v>
+      </c>
+      <c r="C42" t="s">
+        <v>34</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="E42">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="str">
         <f>INDEX(Define!B:B,MATCH(G42,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I42">
         <v>1</v>
       </c>
       <c r="J42" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42">
         <v>1</v>
@@ -4907,16 +4974,16 @@
         <v>0</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P42">
         <v>0</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42">
         <v>0</v>
@@ -4926,28 +4993,27 @@
       </c>
       <c r="U42" t="str">
         <f>TextData!B41</f>
-        <v>CAシェル</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21">
+        <v>毒</v>
+      </c>
+    </row>
+    <row r="43" ht="12" customHeight="1" spans="1:21">
       <c r="A43">
-        <v>2040</v>
+        <v>2012</v>
       </c>
       <c r="B43">
-        <v>2040</v>
-      </c>
-      <c r="C43" t="str">
-        <f>INDEX(TextData!B:B,MATCH(B43,TextData!A:A))</f>
-        <v>リジェネ</v>
+        <v>2012</v>
+      </c>
+      <c r="C43" t="s">
+        <v>35</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E43">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F43" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="G43">
         <v>1</v>
@@ -4960,10 +5026,10 @@
         <v>1</v>
       </c>
       <c r="J43" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43">
         <v>1</v>
@@ -4975,16 +5041,16 @@
         <v>0</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P43">
         <v>0</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S43">
         <v>0</v>
@@ -4994,28 +5060,28 @@
       </c>
       <c r="U43" t="str">
         <f>TextData!B42</f>
-        <v>リジェネ</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21">
+        <v>火傷</v>
+      </c>
+    </row>
+    <row r="44" ht="12" customHeight="1" spans="1:21">
       <c r="A44">
-        <v>2050</v>
+        <v>2020</v>
       </c>
       <c r="B44">
-        <v>2050</v>
+        <v>2020</v>
       </c>
       <c r="C44" t="str">
         <f>INDEX(TextData!B:B,MATCH(B44,TextData!A:A))</f>
-        <v>攻撃無効</v>
+        <v>暗闇</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="E44">
-        <v>226</v>
+        <v>2</v>
       </c>
       <c r="F44" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="G44">
         <v>4</v>
@@ -5025,16 +5091,16 @@
         <v>効果発揮回数</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K44">
         <v>0</v>
       </c>
       <c r="L44">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="M44">
         <v>0</v>
@@ -5043,16 +5109,16 @@
         <v>0</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P44">
         <v>0</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44">
         <v>0</v>
@@ -5062,28 +5128,28 @@
       </c>
       <c r="U44" t="str">
         <f>TextData!B43</f>
-        <v>攻撃無効</v>
+        <v>暗闇</v>
       </c>
     </row>
     <row r="45" spans="1:21">
       <c r="A45">
-        <v>2060</v>
+        <v>2030</v>
       </c>
       <c r="B45">
-        <v>2060</v>
+        <v>2030</v>
       </c>
       <c r="C45" t="str">
         <f>INDEX(TextData!B:B,MATCH(B45,TextData!A:A))</f>
-        <v>ドレイン</v>
+        <v>カウンタ</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="F45" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G45">
         <v>1</v>
@@ -5093,10 +5159,10 @@
         <v>ターン数</v>
       </c>
       <c r="I45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K45">
         <v>0</v>
@@ -5130,28 +5196,28 @@
       </c>
       <c r="U45" t="str">
         <f>TextData!B44</f>
-        <v>ドレイン</v>
+        <v>カウンタ</v>
       </c>
     </row>
     <row r="46" spans="1:21">
       <c r="A46">
-        <v>2070</v>
+        <v>2031</v>
       </c>
       <c r="B46">
-        <v>2070</v>
+        <v>2031</v>
       </c>
       <c r="C46" t="str">
         <f>INDEX(TextData!B:B,MATCH(B46,TextData!A:A))</f>
-        <v>状態異常CA</v>
+        <v>CAダメージ</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>226</v>
+        <v>66</v>
       </c>
       <c r="F46" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G46">
         <v>1</v>
@@ -5161,7 +5227,7 @@
         <v>ターン数</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="s">
         <v>20</v>
@@ -5198,38 +5264,38 @@
       </c>
       <c r="U46" t="str">
         <f>TextData!B45</f>
-        <v>状態異常CA</v>
+        <v>CAダメージ</v>
       </c>
     </row>
     <row r="47" spans="1:21">
       <c r="A47">
-        <v>2080</v>
+        <v>2032</v>
       </c>
       <c r="B47">
-        <v>2080</v>
+        <v>2032</v>
       </c>
       <c r="C47" t="str">
         <f>INDEX(TextData!B:B,MATCH(B47,TextData!A:A))</f>
-        <v>反撃</v>
+        <v>CAシェル</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="F47" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H47" t="str">
         <f>INDEX(Define!B:B,MATCH(G47,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>なし</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="s">
         <v>20</v>
@@ -5266,38 +5332,38 @@
       </c>
       <c r="U47" t="str">
         <f>TextData!B46</f>
-        <v>反撃</v>
+        <v>CAシェル</v>
       </c>
     </row>
     <row r="48" spans="1:21">
       <c r="A48">
-        <v>2090</v>
+        <v>2040</v>
       </c>
       <c r="B48">
-        <v>2090</v>
+        <v>2040</v>
       </c>
       <c r="C48" t="str">
         <f>INDEX(TextData!B:B,MATCH(B48,TextData!A:A))</f>
-        <v>パッシブ封じ</v>
+        <v>リジェネ</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="F48" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H48" t="str">
         <f>INDEX(Define!B:B,MATCH(G48,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J48" t="s">
         <v>20</v>
@@ -5315,16 +5381,16 @@
         <v>0</v>
       </c>
       <c r="O48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P48">
         <v>0</v>
       </c>
       <c r="Q48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48">
         <v>0</v>
@@ -5334,28 +5400,28 @@
       </c>
       <c r="U48" t="str">
         <f>TextData!B47</f>
-        <v>パッシブ封じ</v>
+        <v>リジェネ</v>
       </c>
     </row>
     <row r="49" spans="1:21">
       <c r="A49">
-        <v>2120</v>
+        <v>2050</v>
       </c>
       <c r="B49">
-        <v>2120</v>
+        <v>2050</v>
       </c>
       <c r="C49" t="str">
         <f>INDEX(TextData!B:B,MATCH(B49,TextData!A:A))</f>
-        <v>デバフ強化</v>
+        <v>攻撃無効</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>9</v>
+        <v>226</v>
       </c>
       <c r="F49" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G49">
         <v>4</v>
@@ -5365,16 +5431,16 @@
         <v>効果発揮回数</v>
       </c>
       <c r="I49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J49" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="K49">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="M49">
         <v>0</v>
@@ -5392,7 +5458,7 @@
         <v>0</v>
       </c>
       <c r="R49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49">
         <v>0</v>
@@ -5402,28 +5468,28 @@
       </c>
       <c r="U49" t="str">
         <f>TextData!B48</f>
-        <v>デバフ強化</v>
+        <v>攻撃無効</v>
       </c>
     </row>
     <row r="50" spans="1:21">
       <c r="A50">
-        <v>2130</v>
+        <v>2060</v>
       </c>
       <c r="B50">
-        <v>2130</v>
+        <v>2060</v>
       </c>
       <c r="C50" t="str">
         <f>INDEX(TextData!B:B,MATCH(B50,TextData!A:A))</f>
-        <v>挑発</v>
+        <v>ドレイン</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="F50" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -5433,7 +5499,7 @@
         <v>ターン数</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="s">
         <v>20</v>
@@ -5460,7 +5526,7 @@
         <v>0</v>
       </c>
       <c r="R50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50">
         <v>0</v>
@@ -5470,44 +5536,44 @@
       </c>
       <c r="U50" t="str">
         <f>TextData!B49</f>
-        <v>挑発</v>
+        <v>ドレイン</v>
       </c>
     </row>
     <row r="51" spans="1:21">
       <c r="A51">
-        <v>2140</v>
+        <v>2070</v>
       </c>
       <c r="B51">
-        <v>2140</v>
+        <v>2070</v>
       </c>
       <c r="C51" t="str">
         <f>INDEX(TextData!B:B,MATCH(B51,TextData!A:A))</f>
-        <v>凍結</v>
+        <v>状態異常CA</v>
       </c>
       <c r="D51">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E51">
-        <v>44</v>
+        <v>226</v>
       </c>
       <c r="F51" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H51" t="str">
         <f>INDEX(Define!B:B,MATCH(G51,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J51" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="K51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51">
         <v>1</v>
@@ -5519,16 +5585,16 @@
         <v>0</v>
       </c>
       <c r="O51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P51">
         <v>0</v>
       </c>
       <c r="Q51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51">
         <v>0</v>
@@ -5538,41 +5604,41 @@
       </c>
       <c r="U51" t="str">
         <f>TextData!B50</f>
-        <v>凍結</v>
+        <v>状態異常CA</v>
       </c>
     </row>
     <row r="52" spans="1:21">
       <c r="A52">
-        <v>2150</v>
+        <v>2080</v>
       </c>
       <c r="B52">
-        <v>2150</v>
+        <v>2080</v>
       </c>
       <c r="C52" t="str">
         <f>INDEX(TextData!B:B,MATCH(B52,TextData!A:A))</f>
-        <v>スタン</v>
+        <v>反撃</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F52" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H52" t="str">
         <f>INDEX(Define!B:B,MATCH(G52,Define!A:A))</f>
-        <v>APカウント</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I52">
         <v>0</v>
       </c>
       <c r="J52" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -5587,16 +5653,16 @@
         <v>0</v>
       </c>
       <c r="O52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P52">
         <v>0</v>
       </c>
       <c r="Q52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52">
         <v>0</v>
@@ -5606,28 +5672,28 @@
       </c>
       <c r="U52" t="str">
         <f>TextData!B51</f>
-        <v>スタン</v>
+        <v>反撃</v>
       </c>
     </row>
     <row r="53" spans="1:21">
       <c r="A53">
-        <v>2180</v>
+        <v>2090</v>
       </c>
       <c r="B53">
-        <v>2180</v>
+        <v>2090</v>
       </c>
       <c r="C53" t="str">
         <f>INDEX(TextData!B:B,MATCH(B53,TextData!A:A))</f>
-        <v>状態異常回避</v>
+        <v>パッシブ封じ</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="F53" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G53">
         <v>4</v>
@@ -5655,16 +5721,16 @@
         <v>0</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P53">
         <v>0</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S53">
         <v>0</v>
@@ -5674,47 +5740,47 @@
       </c>
       <c r="U53" t="str">
         <f>TextData!B52</f>
-        <v>状態異常回避</v>
+        <v>パッシブ封じ</v>
       </c>
     </row>
     <row r="54" spans="1:21">
       <c r="A54">
-        <v>2190</v>
+        <v>2120</v>
       </c>
       <c r="B54">
-        <v>2190</v>
+        <v>2120</v>
       </c>
       <c r="C54" t="str">
         <f>INDEX(TextData!B:B,MATCH(B54,TextData!A:A))</f>
-        <v>対象範囲延長</v>
+        <v>デバフ強化</v>
       </c>
       <c r="D54">
         <v>0</v>
       </c>
       <c r="E54">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="F54" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H54" t="str">
         <f>INDEX(Define!B:B,MATCH(G54,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="K54">
         <v>0</v>
       </c>
       <c r="L54">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="M54">
         <v>0</v>
@@ -5732,38 +5798,38 @@
         <v>0</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54">
         <v>0</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U54" t="str">
         <f>TextData!B53</f>
-        <v>対象範囲延長</v>
+        <v>デバフ強化</v>
       </c>
     </row>
     <row r="55" spans="1:21">
       <c r="A55">
-        <v>2210</v>
+        <v>2130</v>
       </c>
       <c r="B55">
-        <v>2210</v>
+        <v>2130</v>
       </c>
       <c r="C55" t="str">
         <f>INDEX(TextData!B:B,MATCH(B55,TextData!A:A))</f>
-        <v>アフターヒール</v>
+        <v>挑発</v>
       </c>
       <c r="D55">
         <v>0</v>
       </c>
       <c r="E55">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="F55" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -5773,7 +5839,7 @@
         <v>ターン数</v>
       </c>
       <c r="I55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="s">
         <v>20</v>
@@ -5800,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55">
         <v>0</v>
@@ -5810,44 +5876,44 @@
       </c>
       <c r="U55" t="str">
         <f>TextData!B54</f>
-        <v>アフターヒール</v>
+        <v>挑発</v>
       </c>
     </row>
     <row r="56" spans="1:21">
       <c r="A56">
-        <v>2220</v>
+        <v>2140</v>
       </c>
       <c r="B56">
-        <v>2220</v>
+        <v>2140</v>
       </c>
       <c r="C56" t="str">
         <f>INDEX(TextData!B:B,MATCH(B56,TextData!A:A))</f>
-        <v>即死付与</v>
+        <v>凍結</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E56">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="F56" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H56" t="str">
         <f>INDEX(Define!B:B,MATCH(G56,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="K56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56">
         <v>1</v>
@@ -5859,13 +5925,13 @@
         <v>0</v>
       </c>
       <c r="O56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P56">
         <v>0</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56">
         <v>1</v>
@@ -5878,41 +5944,41 @@
       </c>
       <c r="U56" t="str">
         <f>TextData!B55</f>
-        <v>即死付与</v>
+        <v>凍結</v>
       </c>
     </row>
     <row r="57" spans="1:21">
       <c r="A57">
-        <v>2230</v>
+        <v>2150</v>
       </c>
       <c r="B57">
-        <v>2230</v>
+        <v>2150</v>
       </c>
       <c r="C57" t="str">
         <f>INDEX(TextData!B:B,MATCH(B57,TextData!A:A))</f>
-        <v>同時回復</v>
+        <v>スタン</v>
       </c>
       <c r="D57">
         <v>0</v>
       </c>
       <c r="E57">
-        <v>46</v>
+        <v>5</v>
       </c>
       <c r="F57" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H57" t="str">
         <f>INDEX(Define!B:B,MATCH(G57,Define!A:A))</f>
-        <v>なし</v>
+        <v>APカウント</v>
       </c>
       <c r="I57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="K57">
         <v>0</v>
@@ -5927,16 +5993,16 @@
         <v>0</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P57">
         <v>0</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S57">
         <v>0</v>
@@ -5946,28 +6012,28 @@
       </c>
       <c r="U57" t="str">
         <f>TextData!B56</f>
-        <v>同時回復</v>
+        <v>スタン</v>
       </c>
     </row>
     <row r="58" spans="1:21">
       <c r="A58">
-        <v>2240</v>
+        <v>2180</v>
       </c>
       <c r="B58">
-        <v>2240</v>
+        <v>2180</v>
       </c>
       <c r="C58" t="str">
         <f>INDEX(TextData!B:B,MATCH(B58,TextData!A:A))</f>
-        <v>必中</v>
+        <v>状態異常回避</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
       <c r="E58">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="F58" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="G58">
         <v>4</v>
@@ -6014,35 +6080,35 @@
       </c>
       <c r="U58" t="str">
         <f>TextData!B57</f>
-        <v>必中</v>
+        <v>状態異常回避</v>
       </c>
     </row>
     <row r="59" spans="1:21">
       <c r="A59">
-        <v>2250</v>
+        <v>2190</v>
       </c>
       <c r="B59">
-        <v>2250</v>
+        <v>2190</v>
       </c>
       <c r="C59" t="str">
         <f>INDEX(TextData!B:B,MATCH(B59,TextData!A:A))</f>
-        <v>アシストヒール</v>
+        <v>対象範囲延長</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
       <c r="E59">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="F59" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="str">
         <f>INDEX(Define!B:B,MATCH(G59,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -6078,42 +6144,42 @@
         <v>0</v>
       </c>
       <c r="T59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U59" t="str">
         <f>TextData!B58</f>
-        <v>アシストヒール</v>
+        <v>対象範囲延長</v>
       </c>
     </row>
     <row r="60" spans="1:21">
       <c r="A60">
-        <v>2270</v>
+        <v>2210</v>
       </c>
       <c r="B60">
-        <v>2270</v>
+        <v>2210</v>
       </c>
       <c r="C60" t="str">
         <f>INDEX(TextData!B:B,MATCH(B60,TextData!A:A))</f>
-        <v>アンデッド</v>
+        <v>アフターヒール</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="F60" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" t="str">
         <f>INDEX(Define!B:B,MATCH(G60,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="s">
         <v>20</v>
@@ -6150,35 +6216,35 @@
       </c>
       <c r="U60" t="str">
         <f>TextData!B59</f>
-        <v>アンデッド</v>
+        <v>アフターヒール</v>
       </c>
     </row>
     <row r="61" spans="1:21">
       <c r="A61">
-        <v>2280</v>
+        <v>2220</v>
       </c>
       <c r="B61">
-        <v>2280</v>
+        <v>2220</v>
       </c>
       <c r="C61" t="str">
         <f>INDEX(TextData!B:B,MATCH(B61,TextData!A:A))</f>
-        <v>アクセル</v>
+        <v>即死付与</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
       <c r="E61">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F61" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="str">
         <f>INDEX(Define!B:B,MATCH(G61,Define!A:A))</f>
-        <v>なし</v>
+        <v>ターン数</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -6208,7 +6274,7 @@
         <v>0</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S61">
         <v>0</v>
@@ -6218,35 +6284,35 @@
       </c>
       <c r="U61" t="str">
         <f>TextData!B60</f>
-        <v>アクセル</v>
+        <v>即死付与</v>
       </c>
     </row>
     <row r="62" spans="1:21">
       <c r="A62">
-        <v>2290</v>
+        <v>2230</v>
       </c>
       <c r="B62">
-        <v>2290</v>
+        <v>2230</v>
       </c>
       <c r="C62" t="str">
         <f>INDEX(TextData!B:B,MATCH(B62,TextData!A:A))</f>
-        <v>ダメージ威力アップ</v>
+        <v>同時回復</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
       <c r="E62">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="F62" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" t="str">
         <f>INDEX(Define!B:B,MATCH(G62,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I62">
         <v>1</v>
@@ -6261,7 +6327,7 @@
         <v>1</v>
       </c>
       <c r="M62">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N62">
         <v>0</v>
@@ -6270,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="P62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q62">
         <v>0</v>
@@ -6286,38 +6352,38 @@
       </c>
       <c r="U62" t="str">
         <f>TextData!B61</f>
-        <v>ダメージ威力アップ</v>
+        <v>同時回復</v>
       </c>
     </row>
     <row r="63" spans="1:21">
       <c r="A63">
-        <v>2320</v>
+        <v>2240</v>
       </c>
       <c r="B63">
-        <v>2320</v>
+        <v>2240</v>
       </c>
       <c r="C63" t="str">
         <f>INDEX(TextData!B:B,MATCH(B63,TextData!A:A))</f>
-        <v>バフ解除</v>
+        <v>必中</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
       <c r="E63">
-        <v>0</v>
-      </c>
-      <c r="F63">
-        <v>1</v>
+        <v>62</v>
+      </c>
+      <c r="F63" t="s">
+        <v>29</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H63" t="str">
         <f>INDEX(Define!B:B,MATCH(G63,Define!A:A))</f>
-        <v>なし</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="s">
         <v>20</v>
@@ -6354,38 +6420,38 @@
       </c>
       <c r="U63" t="str">
         <f>TextData!B62</f>
-        <v>バフ解除</v>
+        <v>必中</v>
       </c>
     </row>
     <row r="64" spans="1:21">
       <c r="A64">
-        <v>2330</v>
+        <v>2250</v>
       </c>
       <c r="B64">
-        <v>2330</v>
+        <v>2250</v>
       </c>
       <c r="C64" t="str">
         <f>INDEX(TextData!B:B,MATCH(B64,TextData!A:A))</f>
-        <v>貫通</v>
+        <v>アシストヒール</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
       <c r="E64">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="F64" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" t="str">
         <f>INDEX(Define!B:B,MATCH(G64,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="s">
         <v>20</v>
@@ -6400,7 +6466,7 @@
         <v>0</v>
       </c>
       <c r="N64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -6422,38 +6488,38 @@
       </c>
       <c r="U64" t="str">
         <f>TextData!B63</f>
-        <v>貫通</v>
+        <v>アシストヒール</v>
       </c>
     </row>
     <row r="65" spans="1:21">
       <c r="A65">
-        <v>2340</v>
+        <v>2270</v>
       </c>
       <c r="B65">
-        <v>2340</v>
+        <v>2270</v>
       </c>
       <c r="C65" t="str">
         <f>INDEX(TextData!B:B,MATCH(B65,TextData!A:A))</f>
-        <v>対象列化</v>
+        <v>アンデッド</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
       <c r="E65">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="F65" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H65" t="str">
         <f>INDEX(Define!B:B,MATCH(G65,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="s">
         <v>20</v>
@@ -6468,7 +6534,7 @@
         <v>0</v>
       </c>
       <c r="N65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -6490,38 +6556,38 @@
       </c>
       <c r="U65" t="str">
         <f>TextData!B64</f>
-        <v>対象列化</v>
+        <v>アンデッド</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66">
-        <v>2341</v>
+        <v>2280</v>
       </c>
       <c r="B66">
-        <v>2341</v>
+        <v>2280</v>
       </c>
       <c r="C66" t="str">
         <f>INDEX(TextData!B:B,MATCH(B66,TextData!A:A))</f>
-        <v>対象全体化</v>
+        <v>アクセル</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
       <c r="E66">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="F66" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="G66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H66" t="str">
         <f>INDEX(Define!B:B,MATCH(G66,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J66" t="s">
         <v>20</v>
@@ -6536,7 +6602,7 @@
         <v>0</v>
       </c>
       <c r="N66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -6558,28 +6624,28 @@
       </c>
       <c r="U66" t="str">
         <f>TextData!B65</f>
-        <v>対象全体化</v>
+        <v>アクセル</v>
       </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67">
-        <v>2350</v>
+        <v>2290</v>
       </c>
       <c r="B67">
-        <v>2350</v>
+        <v>2290</v>
       </c>
       <c r="C67" t="str">
         <f>INDEX(TextData!B:B,MATCH(B67,TextData!A:A))</f>
-        <v>聖棺</v>
+        <v>ダメージ威力アップ</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F67" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G67">
         <v>1</v>
@@ -6601,16 +6667,16 @@
         <v>1</v>
       </c>
       <c r="M67">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67">
         <v>0</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -6626,35 +6692,35 @@
       </c>
       <c r="U67" t="str">
         <f>TextData!B66</f>
-        <v>聖棺</v>
+        <v>ダメージ威力アップ</v>
       </c>
     </row>
     <row r="68" spans="1:21">
       <c r="A68">
-        <v>2360</v>
+        <v>2320</v>
       </c>
       <c r="B68">
-        <v>2360</v>
+        <v>2320</v>
       </c>
       <c r="C68" t="str">
         <f>INDEX(TextData!B:B,MATCH(B68,TextData!A:A))</f>
-        <v>追加ダメージ</v>
+        <v>バフ解除</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
       <c r="E68">
-        <v>13</v>
-      </c>
-      <c r="F68" t="s">
-        <v>61</v>
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="str">
         <f>INDEX(Define!B:B,MATCH(G68,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>なし</v>
       </c>
       <c r="I68">
         <v>1</v>
@@ -6672,7 +6738,7 @@
         <v>0</v>
       </c>
       <c r="N68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68">
         <v>0</v>
@@ -6694,19 +6760,19 @@
       </c>
       <c r="U68" t="str">
         <f>TextData!B67</f>
-        <v>追加ダメージ</v>
+        <v>バフ解除</v>
       </c>
     </row>
     <row r="69" spans="1:21">
       <c r="A69">
-        <v>2370</v>
+        <v>2330</v>
       </c>
       <c r="B69">
-        <v>2370</v>
+        <v>2330</v>
       </c>
       <c r="C69" t="str">
         <f>INDEX(TextData!B:B,MATCH(B69,TextData!A:A))</f>
-        <v>追加効果</v>
+        <v>貫通</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -6715,7 +6781,7 @@
         <v>56</v>
       </c>
       <c r="F69" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -6762,28 +6828,28 @@
       </c>
       <c r="U69" t="str">
         <f>TextData!B68</f>
-        <v>追加効果</v>
+        <v>貫通</v>
       </c>
     </row>
     <row r="70" spans="1:21">
       <c r="A70">
-        <v>2380</v>
+        <v>2340</v>
       </c>
       <c r="B70">
-        <v>2380</v>
+        <v>2340</v>
       </c>
       <c r="C70" t="str">
         <f>INDEX(TextData!B:B,MATCH(B70,TextData!A:A))</f>
-        <v>透明</v>
+        <v>対象列化</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F70" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -6830,28 +6896,28 @@
       </c>
       <c r="U70" t="str">
         <f>TextData!B69</f>
-        <v>透明</v>
+        <v>対象列化</v>
       </c>
     </row>
     <row r="71" spans="1:21">
       <c r="A71">
-        <v>2390</v>
+        <v>2341</v>
       </c>
       <c r="B71">
-        <v>2390</v>
+        <v>2341</v>
       </c>
       <c r="C71" t="str">
         <f>INDEX(TextData!B:B,MATCH(B71,TextData!A:A))</f>
-        <v>沈黙</v>
+        <v>対象全体化</v>
       </c>
       <c r="D71">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E71">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="F71" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G71">
         <v>1</v>
@@ -6876,19 +6942,19 @@
         <v>0</v>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P71">
         <v>0</v>
       </c>
       <c r="Q71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S71">
         <v>0</v>
@@ -6898,19 +6964,19 @@
       </c>
       <c r="U71" t="str">
         <f>TextData!B70</f>
-        <v>沈黙</v>
+        <v>対象全体化</v>
       </c>
     </row>
     <row r="72" spans="1:21">
       <c r="A72">
-        <v>2400</v>
+        <v>2350</v>
       </c>
       <c r="B72">
-        <v>2400</v>
+        <v>2350</v>
       </c>
       <c r="C72" t="str">
         <f>INDEX(TextData!B:B,MATCH(B72,TextData!A:A))</f>
-        <v>不治</v>
+        <v>聖棺</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -6919,7 +6985,7 @@
         <v>0</v>
       </c>
       <c r="F72" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G72">
         <v>1</v>
@@ -6944,19 +7010,19 @@
         <v>0</v>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P72">
         <v>0</v>
       </c>
       <c r="Q72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S72">
         <v>0</v>
@@ -6966,28 +7032,28 @@
       </c>
       <c r="U72" t="str">
         <f>TextData!B71</f>
-        <v>不治</v>
+        <v>聖棺</v>
       </c>
     </row>
     <row r="73" spans="1:21">
       <c r="A73">
-        <v>2410</v>
+        <v>2360</v>
       </c>
       <c r="B73">
-        <v>2410</v>
+        <v>2360</v>
       </c>
       <c r="C73" t="str">
         <f>INDEX(TextData!B:B,MATCH(B73,TextData!A:A))</f>
-        <v>シールド</v>
+        <v>追加ダメージ</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F73" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G73">
         <v>1</v>
@@ -7018,7 +7084,7 @@
         <v>0</v>
       </c>
       <c r="P73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -7034,28 +7100,28 @@
       </c>
       <c r="U73" t="str">
         <f>TextData!B72</f>
-        <v>シールド</v>
+        <v>追加ダメージ</v>
       </c>
     </row>
     <row r="74" spans="1:21">
       <c r="A74">
-        <v>2420</v>
+        <v>2370</v>
       </c>
       <c r="B74">
-        <v>2420</v>
+        <v>2370</v>
       </c>
       <c r="C74" t="str">
         <f>INDEX(TextData!B:B,MATCH(B74,TextData!A:A))</f>
-        <v>フォロー</v>
+        <v>追加効果</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F74" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G74">
         <v>1</v>
@@ -7086,7 +7152,7 @@
         <v>0</v>
       </c>
       <c r="P74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -7102,19 +7168,19 @@
       </c>
       <c r="U74" t="str">
         <f>TextData!B73</f>
-        <v>フォロー</v>
+        <v>追加効果</v>
       </c>
     </row>
     <row r="75" spans="1:21">
       <c r="A75">
-        <v>2430</v>
+        <v>2380</v>
       </c>
       <c r="B75">
-        <v>2430</v>
+        <v>2380</v>
       </c>
       <c r="C75" t="str">
         <f>INDEX(TextData!B:B,MATCH(B75,TextData!A:A))</f>
-        <v>かばう</v>
+        <v>透明</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -7123,14 +7189,14 @@
         <v>0</v>
       </c>
       <c r="F75" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G75">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H75" t="str">
         <f>INDEX(Define!B:B,MATCH(G75,Define!A:A))</f>
-        <v>ターンの終了</v>
+        <v>ターン数</v>
       </c>
       <c r="I75">
         <v>1</v>
@@ -7154,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="P75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -7163,35 +7229,35 @@
         <v>0</v>
       </c>
       <c r="S75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T75">
         <v>1</v>
       </c>
       <c r="U75" t="str">
         <f>TextData!B74</f>
-        <v>かばう</v>
+        <v>透明</v>
       </c>
     </row>
     <row r="76" spans="1:21">
       <c r="A76">
-        <v>2440</v>
+        <v>2390</v>
       </c>
       <c r="B76">
-        <v>2440</v>
+        <v>2390</v>
       </c>
       <c r="C76" t="str">
         <f>INDEX(TextData!B:B,MATCH(B76,TextData!A:A))</f>
-        <v>Ap消費半減</v>
+        <v>沈黙</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F76" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="G76">
         <v>1</v>
@@ -7216,16 +7282,16 @@
         <v>0</v>
       </c>
       <c r="N76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R76">
         <v>1</v>
@@ -7238,19 +7304,19 @@
       </c>
       <c r="U76" t="str">
         <f>TextData!B75</f>
-        <v>Ap消費半減</v>
+        <v>沈黙</v>
       </c>
     </row>
     <row r="77" spans="1:21">
       <c r="A77">
-        <v>2450</v>
+        <v>2400</v>
       </c>
       <c r="B77">
-        <v>2450</v>
+        <v>2400</v>
       </c>
       <c r="C77" t="str">
         <f>INDEX(TextData!B:B,MATCH(B77,TextData!A:A))</f>
-        <v>不死</v>
+        <v>不治</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -7259,14 +7325,14 @@
         <v>0</v>
       </c>
       <c r="F77" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G77">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H77" t="str">
         <f>INDEX(Define!B:B,MATCH(G77,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I77">
         <v>1</v>
@@ -7284,16 +7350,16 @@
         <v>0</v>
       </c>
       <c r="N77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77">
         <v>1</v>
@@ -7306,19 +7372,19 @@
       </c>
       <c r="U77" t="str">
         <f>TextData!B76</f>
-        <v>不死</v>
+        <v>不治</v>
       </c>
     </row>
     <row r="78" spans="1:21">
       <c r="A78">
-        <v>2460</v>
+        <v>2410</v>
       </c>
       <c r="B78">
-        <v>2460</v>
+        <v>2410</v>
       </c>
       <c r="C78" t="str">
         <f>INDEX(TextData!B:B,MATCH(B78,TextData!A:A))</f>
-        <v>Hp回復効果アップ</v>
+        <v>シールド</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -7327,7 +7393,7 @@
         <v>0</v>
       </c>
       <c r="F78" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G78">
         <v>1</v>
@@ -7374,19 +7440,19 @@
       </c>
       <c r="U78" t="str">
         <f>TextData!B77</f>
-        <v>Hp回復効果アップ</v>
+        <v>シールド</v>
       </c>
     </row>
     <row r="79" spans="1:21">
       <c r="A79">
-        <v>2470</v>
+        <v>2420</v>
       </c>
       <c r="B79">
-        <v>2470</v>
+        <v>2420</v>
       </c>
       <c r="C79" t="str">
         <f>INDEX(TextData!B:B,MATCH(B79,TextData!A:A))</f>
-        <v>呪詛</v>
+        <v>フォロー</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -7395,14 +7461,14 @@
         <v>0</v>
       </c>
       <c r="F79" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G79">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H79" t="str">
         <f>INDEX(Define!B:B,MATCH(G79,Define!A:A))</f>
-        <v>効果発揮回数</v>
+        <v>ターン数</v>
       </c>
       <c r="I79">
         <v>1</v>
@@ -7432,7 +7498,7 @@
         <v>0</v>
       </c>
       <c r="R79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S79">
         <v>0</v>
@@ -7442,35 +7508,35 @@
       </c>
       <c r="U79" t="str">
         <f>TextData!B78</f>
-        <v>呪詛</v>
+        <v>フォロー</v>
       </c>
     </row>
     <row r="80" spans="1:21">
       <c r="A80">
-        <v>2480</v>
+        <v>2430</v>
       </c>
       <c r="B80">
-        <v>2480</v>
+        <v>2430</v>
       </c>
       <c r="C80" t="str">
         <f>INDEX(TextData!B:B,MATCH(B80,TextData!A:A))</f>
-        <v>付与無効化</v>
+        <v>かばう</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
       <c r="E80">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="F80" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G80">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H80" t="str">
         <f>INDEX(Define!B:B,MATCH(G80,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>ターンの終了</v>
       </c>
       <c r="I80">
         <v>1</v>
@@ -7500,38 +7566,38 @@
         <v>0</v>
       </c>
       <c r="R80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T80">
         <v>1</v>
       </c>
       <c r="U80" t="str">
         <f>TextData!B79</f>
-        <v>付与無効化</v>
+        <v>かばう</v>
       </c>
     </row>
     <row r="81" spans="1:21">
       <c r="A81">
-        <v>2490</v>
+        <v>2440</v>
       </c>
       <c r="B81">
-        <v>2490</v>
+        <v>2440</v>
       </c>
       <c r="C81" t="str">
         <f>INDEX(TextData!B:B,MATCH(B81,TextData!A:A))</f>
-        <v>かばう無視</v>
+        <v>Ap消費半減</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
       <c r="E81">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="F81" t="s">
-        <v>69</v>
+        <v>21</v>
       </c>
       <c r="G81">
         <v>1</v>
@@ -7568,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S81">
         <v>0</v>
@@ -7576,20 +7642,21 @@
       <c r="T81">
         <v>1</v>
       </c>
-      <c r="U81" t="s">
-        <v>70</v>
+      <c r="U81" t="str">
+        <f>TextData!B80</f>
+        <v>Ap消費半減</v>
       </c>
     </row>
     <row r="82" spans="1:21">
       <c r="A82">
-        <v>3010</v>
+        <v>2450</v>
       </c>
       <c r="B82">
-        <v>3010</v>
+        <v>2450</v>
       </c>
       <c r="C82" t="str">
         <f>INDEX(TextData!B:B,MATCH(B82,TextData!A:A))</f>
-        <v>チャージ</v>
+        <v>不死</v>
       </c>
       <c r="D82">
         <v>0</v>
@@ -7598,14 +7665,14 @@
         <v>0</v>
       </c>
       <c r="F82" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G82">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H82" t="str">
         <f>INDEX(Define!B:B,MATCH(G82,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I82">
         <v>1</v>
@@ -7623,19 +7690,19 @@
         <v>0</v>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O82">
         <v>0</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q82">
         <v>0</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S82">
         <v>0</v>
@@ -7645,19 +7712,19 @@
       </c>
       <c r="U82" t="str">
         <f>TextData!B81</f>
-        <v>チャージ</v>
+        <v>不死</v>
       </c>
     </row>
     <row r="83" spans="1:21">
       <c r="A83">
-        <v>3020</v>
+        <v>2460</v>
       </c>
       <c r="B83">
-        <v>3020</v>
+        <v>2460</v>
       </c>
       <c r="C83" t="str">
         <f>INDEX(TextData!B:B,MATCH(B83,TextData!A:A))</f>
-        <v>リンケージ</v>
+        <v>Hp回復効果アップ</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -7666,7 +7733,7 @@
         <v>0</v>
       </c>
       <c r="F83" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G83">
         <v>1</v>
@@ -7691,13 +7758,13 @@
         <v>0</v>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O83">
         <v>0</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -7713,19 +7780,19 @@
       </c>
       <c r="U83" t="str">
         <f>TextData!B82</f>
-        <v>リンケージ</v>
+        <v>Hp回復効果アップ</v>
       </c>
     </row>
     <row r="84" spans="1:21">
       <c r="A84">
-        <v>9999</v>
+        <v>2470</v>
       </c>
       <c r="B84">
-        <v>9999</v>
+        <v>2470</v>
       </c>
       <c r="C84" t="str">
         <f>INDEX(TextData!B:B,MATCH(B84,TextData!A:A))</f>
-        <v>テスト用</v>
+        <v>呪詛</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -7734,14 +7801,14 @@
         <v>0</v>
       </c>
       <c r="F84" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H84" t="str">
         <f>INDEX(Define!B:B,MATCH(G84,Define!A:A))</f>
-        <v>ターン数</v>
+        <v>効果発揮回数</v>
       </c>
       <c r="I84">
         <v>1</v>
@@ -7759,19 +7826,19 @@
         <v>0</v>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O84">
         <v>0</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q84">
         <v>0</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -7781,6 +7848,413 @@
       </c>
       <c r="U84" t="str">
         <f>TextData!B83</f>
+        <v>呪詛</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21">
+      <c r="A85">
+        <v>2480</v>
+      </c>
+      <c r="B85">
+        <v>2480</v>
+      </c>
+      <c r="C85" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B85,TextData!A:A))</f>
+        <v>付与無効化</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>99</v>
+      </c>
+      <c r="F85" t="s">
+        <v>69</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+      <c r="H85" t="str">
+        <f>INDEX(Define!B:B,MATCH(G85,Define!A:A))</f>
+        <v>ターン数</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+      <c r="J85" t="s">
+        <v>20</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>1</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>1</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>1</v>
+      </c>
+      <c r="Q85">
+        <v>0</v>
+      </c>
+      <c r="R85">
+        <v>1</v>
+      </c>
+      <c r="S85">
+        <v>0</v>
+      </c>
+      <c r="T85">
+        <v>1</v>
+      </c>
+      <c r="U85" t="str">
+        <f>TextData!B84</f>
+        <v>付与無効化</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21">
+      <c r="A86">
+        <v>2490</v>
+      </c>
+      <c r="B86">
+        <v>2490</v>
+      </c>
+      <c r="C86" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B86,TextData!A:A))</f>
+        <v>かばう無視</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>99</v>
+      </c>
+      <c r="F86" t="s">
+        <v>69</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+      <c r="H86" t="str">
+        <f>INDEX(Define!B:B,MATCH(G86,Define!A:A))</f>
+        <v>ターン数</v>
+      </c>
+      <c r="I86">
+        <v>1</v>
+      </c>
+      <c r="J86" t="s">
+        <v>20</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>1</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>1</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>1</v>
+      </c>
+      <c r="Q86">
+        <v>0</v>
+      </c>
+      <c r="R86">
+        <v>0</v>
+      </c>
+      <c r="S86">
+        <v>0</v>
+      </c>
+      <c r="T86">
+        <v>1</v>
+      </c>
+      <c r="U86" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21">
+      <c r="A87">
+        <v>2500</v>
+      </c>
+      <c r="B87">
+        <v>2500</v>
+      </c>
+      <c r="C87" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B87,TextData!A:A))</f>
+        <v>ダメージカット無効</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+      <c r="E87">
+        <v>56</v>
+      </c>
+      <c r="F87" t="s">
+        <v>57</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+      <c r="H87" t="str">
+        <f>INDEX(Define!B:B,MATCH(G87,Define!A:A))</f>
+        <v>ターン数</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="J87" t="s">
+        <v>20</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>1</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>1</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <v>0</v>
+      </c>
+      <c r="R87">
+        <v>0</v>
+      </c>
+      <c r="S87">
+        <v>0</v>
+      </c>
+      <c r="T87">
+        <v>1</v>
+      </c>
+      <c r="U87" t="str">
+        <f>TextData!B86</f>
+        <v>ダメージカット無効</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21">
+      <c r="A88">
+        <v>3010</v>
+      </c>
+      <c r="B88">
+        <v>3010</v>
+      </c>
+      <c r="C88" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B88,TextData!A:A))</f>
+        <v>チャージ</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88" t="s">
+        <v>61</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88" t="str">
+        <f>INDEX(Define!B:B,MATCH(G88,Define!A:A))</f>
+        <v>ターン数</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+      <c r="J88" t="s">
+        <v>20</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>1</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <v>0</v>
+      </c>
+      <c r="R88">
+        <v>0</v>
+      </c>
+      <c r="S88">
+        <v>0</v>
+      </c>
+      <c r="T88">
+        <v>1</v>
+      </c>
+      <c r="U88" t="str">
+        <f>TextData!B87</f>
+        <v>チャージ</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21">
+      <c r="A89">
+        <v>3020</v>
+      </c>
+      <c r="B89">
+        <v>3020</v>
+      </c>
+      <c r="C89" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B89,TextData!A:A))</f>
+        <v>リンケージ</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89" t="s">
+        <v>61</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89" t="str">
+        <f>INDEX(Define!B:B,MATCH(G89,Define!A:A))</f>
+        <v>ターン数</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="J89" t="s">
+        <v>20</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>1</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <v>0</v>
+      </c>
+      <c r="R89">
+        <v>0</v>
+      </c>
+      <c r="S89">
+        <v>0</v>
+      </c>
+      <c r="T89">
+        <v>1</v>
+      </c>
+      <c r="U89" t="str">
+        <f>TextData!B88</f>
+        <v>リンケージ</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21">
+      <c r="A90">
+        <v>9999</v>
+      </c>
+      <c r="B90">
+        <v>9999</v>
+      </c>
+      <c r="C90" t="str">
+        <f>INDEX(TextData!B:B,MATCH(B90,TextData!A:A))</f>
+        <v>テスト用</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90" t="s">
+        <v>61</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+      <c r="H90" t="str">
+        <f>INDEX(Define!B:B,MATCH(G90,Define!A:A))</f>
+        <v>ターン数</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90" t="s">
+        <v>20</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>1</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <v>0</v>
+      </c>
+      <c r="R90">
+        <v>0</v>
+      </c>
+      <c r="S90">
+        <v>0</v>
+      </c>
+      <c r="T90">
+        <v>1</v>
+      </c>
+      <c r="U90" t="str">
+        <f>TextData!B89</f>
         <v>テスト用</v>
       </c>
     </row>
@@ -7794,7 +8268,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="14.6363636363636" customWidth="1"/>
@@ -8400,126 +8874,126 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>2010</v>
+        <v>1310</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
       <c r="C36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F36" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G36" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>2012</v>
+        <v>1320</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="C37" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F37" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="G37" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>2020</v>
+        <v>1330</v>
       </c>
       <c r="B38" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C38" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="F38" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="G38" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>2030</v>
+        <v>1340</v>
       </c>
       <c r="B39" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C39" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="F39" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G39" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>2031</v>
+        <v>1350</v>
       </c>
       <c r="B40" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C40" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="F40" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="G40" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>2032</v>
+        <v>2010</v>
       </c>
       <c r="B41" t="s">
-        <v>201</v>
+        <v>34</v>
       </c>
       <c r="C41" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F41" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G41" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>2040</v>
+        <v>2012</v>
       </c>
       <c r="B42" t="s">
+        <v>35</v>
+      </c>
+      <c r="C42" t="s">
         <v>205</v>
       </c>
-      <c r="C42" t="s">
-        <v>206</v>
-      </c>
       <c r="F42" t="s">
+        <v>208</v>
+      </c>
+      <c r="G42" t="s">
         <v>207</v>
-      </c>
-      <c r="G42" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>2050</v>
+        <v>2020</v>
       </c>
       <c r="B43" t="s">
         <v>209</v>
@@ -8536,7 +9010,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>2060</v>
+        <v>2030</v>
       </c>
       <c r="B44" t="s">
         <v>213</v>
@@ -8553,7 +9027,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>2070</v>
+        <v>2031</v>
       </c>
       <c r="B45" t="s">
         <v>217</v>
@@ -8570,7 +9044,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>2080</v>
+        <v>2032</v>
       </c>
       <c r="B46" t="s">
         <v>221</v>
@@ -8587,7 +9061,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>2090</v>
+        <v>2040</v>
       </c>
       <c r="B47" t="s">
         <v>225</v>
@@ -8604,7 +9078,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>2120</v>
+        <v>2050</v>
       </c>
       <c r="B48" t="s">
         <v>229</v>
@@ -8621,7 +9095,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>2130</v>
+        <v>2060</v>
       </c>
       <c r="B49" t="s">
         <v>233</v>
@@ -8638,7 +9112,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>2140</v>
+        <v>2070</v>
       </c>
       <c r="B50" t="s">
         <v>237</v>
@@ -8647,109 +9121,109 @@
         <v>238</v>
       </c>
       <c r="F50" t="s">
-        <v>48</v>
+        <v>239</v>
       </c>
       <c r="G50" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>2150</v>
+        <v>2080</v>
       </c>
       <c r="B51" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C51" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F51" t="s">
-        <v>50</v>
+        <v>243</v>
       </c>
       <c r="G51" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>2180</v>
+        <v>2090</v>
       </c>
       <c r="B52" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C52" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F52" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G52" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>2190</v>
+        <v>2120</v>
       </c>
       <c r="B53" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C53" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F53" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G53" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>2210</v>
+        <v>2130</v>
       </c>
       <c r="B54" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C54" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F54" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G54" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>2220</v>
+        <v>2140</v>
       </c>
       <c r="B55" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C55" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F55" t="s">
-        <v>257</v>
+        <v>48</v>
       </c>
       <c r="G55" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>2230</v>
+        <v>2150</v>
       </c>
       <c r="B56" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C56" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F56" t="s">
-        <v>261</v>
+        <v>50</v>
       </c>
       <c r="G56" t="s">
         <v>262</v>
@@ -8757,7 +9231,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>2240</v>
+        <v>2180</v>
       </c>
       <c r="B57" t="s">
         <v>263</v>
@@ -8774,7 +9248,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>2250</v>
+        <v>2190</v>
       </c>
       <c r="B58" t="s">
         <v>267</v>
@@ -8791,7 +9265,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>2270</v>
+        <v>2210</v>
       </c>
       <c r="B59" t="s">
         <v>271</v>
@@ -8808,7 +9282,7 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>2280</v>
+        <v>2220</v>
       </c>
       <c r="B60" t="s">
         <v>275</v>
@@ -8825,7 +9299,7 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61">
-        <v>2290</v>
+        <v>2230</v>
       </c>
       <c r="B61" t="s">
         <v>279</v>
@@ -8842,7 +9316,7 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62">
-        <v>2320</v>
+        <v>2240</v>
       </c>
       <c r="B62" t="s">
         <v>283</v>
@@ -8859,7 +9333,7 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63">
-        <v>2330</v>
+        <v>2250</v>
       </c>
       <c r="B63" t="s">
         <v>287</v>
@@ -8876,7 +9350,7 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64">
-        <v>2340</v>
+        <v>2270</v>
       </c>
       <c r="B64" t="s">
         <v>291</v>
@@ -8893,7 +9367,7 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65">
-        <v>2341</v>
+        <v>2280</v>
       </c>
       <c r="B65" t="s">
         <v>295</v>
@@ -8910,7 +9384,7 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66">
-        <v>2350</v>
+        <v>2290</v>
       </c>
       <c r="B66" t="s">
         <v>299</v>
@@ -8927,7 +9401,7 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67">
-        <v>2360</v>
+        <v>2320</v>
       </c>
       <c r="B67" t="s">
         <v>303</v>
@@ -8944,7 +9418,7 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68">
-        <v>2370</v>
+        <v>2330</v>
       </c>
       <c r="B68" t="s">
         <v>307</v>
@@ -8961,7 +9435,7 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69">
-        <v>2380</v>
+        <v>2340</v>
       </c>
       <c r="B69" t="s">
         <v>311</v>
@@ -8970,143 +9444,143 @@
         <v>312</v>
       </c>
       <c r="F69" t="s">
-        <v>62</v>
+        <v>313</v>
       </c>
       <c r="G69" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70">
-        <v>2390</v>
+        <v>2341</v>
       </c>
       <c r="B70" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C70" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F70" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G70" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="71" spans="1:7">
       <c r="A71">
-        <v>2400</v>
+        <v>2350</v>
       </c>
       <c r="B71" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C71" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F71" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G71" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72">
-        <v>2410</v>
+        <v>2360</v>
       </c>
       <c r="B72" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C72" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F72" t="s">
-        <v>27</v>
+        <v>325</v>
       </c>
       <c r="G72" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73">
-        <v>2420</v>
+        <v>2370</v>
       </c>
       <c r="B73" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C73" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F73" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G73" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74">
-        <v>2430</v>
+        <v>2380</v>
       </c>
       <c r="B74" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C74" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F74" t="s">
-        <v>331</v>
+        <v>62</v>
       </c>
       <c r="G74" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75">
-        <v>2440</v>
+        <v>2390</v>
       </c>
       <c r="B75" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C75" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F75" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G75" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76">
-        <v>2450</v>
+        <v>2400</v>
       </c>
       <c r="B76" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F76" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="G76" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77">
-        <v>2460</v>
+        <v>2410</v>
       </c>
       <c r="B77" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C77" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F77" t="s">
-        <v>343</v>
+        <v>27</v>
       </c>
       <c r="G77" t="s">
         <v>344</v>
@@ -9114,7 +9588,7 @@
     </row>
     <row r="78" spans="1:7">
       <c r="A78">
-        <v>2470</v>
+        <v>2420</v>
       </c>
       <c r="B78" t="s">
         <v>345</v>
@@ -9123,94 +9597,196 @@
         <v>346</v>
       </c>
       <c r="F78" t="s">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="G78" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79">
-        <v>2480</v>
+        <v>2430</v>
       </c>
       <c r="B79" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C79" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F79" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="G79" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80">
-        <v>2490</v>
+        <v>2440</v>
       </c>
       <c r="B80" t="s">
-        <v>70</v>
+        <v>353</v>
       </c>
       <c r="C80" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F80" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G80" t="s">
-        <v>20</v>
+        <v>356</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81">
-        <v>3010</v>
+        <v>2450</v>
       </c>
       <c r="B81" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C81" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F81" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="G81" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82">
-        <v>3020</v>
+        <v>2460</v>
       </c>
       <c r="B82" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C82" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F82" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="G82" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83">
+        <v>2470</v>
+      </c>
+      <c r="B83" t="s">
+        <v>365</v>
+      </c>
+      <c r="C83" t="s">
+        <v>366</v>
+      </c>
+      <c r="F83" t="s">
+        <v>340</v>
+      </c>
+      <c r="G83" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84">
+        <v>2480</v>
+      </c>
+      <c r="B84" t="s">
+        <v>368</v>
+      </c>
+      <c r="C84" t="s">
+        <v>369</v>
+      </c>
+      <c r="F84" t="s">
+        <v>370</v>
+      </c>
+      <c r="G84" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85">
+        <v>2490</v>
+      </c>
+      <c r="B85" t="s">
+        <v>70</v>
+      </c>
+      <c r="C85" t="s">
+        <v>372</v>
+      </c>
+      <c r="F85" t="s">
+        <v>370</v>
+      </c>
+      <c r="G85" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86">
+        <v>2500</v>
+      </c>
+      <c r="B86" t="s">
+        <v>373</v>
+      </c>
+      <c r="C86" t="s">
+        <v>374</v>
+      </c>
+      <c r="F86" t="s">
+        <v>309</v>
+      </c>
+      <c r="G86" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87">
+        <v>3010</v>
+      </c>
+      <c r="B87" t="s">
+        <v>375</v>
+      </c>
+      <c r="C87" t="s">
+        <v>376</v>
+      </c>
+      <c r="F87" t="s">
+        <v>377</v>
+      </c>
+      <c r="G87" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88">
+        <v>3020</v>
+      </c>
+      <c r="B88" t="s">
+        <v>379</v>
+      </c>
+      <c r="C88" t="s">
+        <v>380</v>
+      </c>
+      <c r="F88" t="s">
+        <v>381</v>
+      </c>
+      <c r="G88" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89">
         <v>9999</v>
       </c>
-      <c r="B83" t="s">
-        <v>361</v>
-      </c>
-      <c r="C83" t="s">
+      <c r="B89" t="s">
+        <v>383</v>
+      </c>
+      <c r="C89" t="s">
         <v>20</v>
       </c>
-      <c r="F83" t="s">
-        <v>361</v>
-      </c>
-      <c r="G83" t="s">
+      <c r="F89" t="s">
+        <v>383</v>
+      </c>
+      <c r="G89" t="s">
         <v>20</v>
       </c>
     </row>
@@ -9236,7 +9812,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -9244,7 +9820,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -9252,7 +9828,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -9260,7 +9836,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -9268,7 +9844,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>366</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -9276,7 +9852,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -9284,7 +9860,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
